--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -721,9 +721,6 @@
     <t>2021-03-17</t>
   </si>
   <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
     <t>2021-07-06</t>
   </si>
   <si>
@@ -737,6 +734,9 @@
   </si>
   <si>
     <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
   </si>
   <si>
     <t>2021-05-10</t>
@@ -1273,7 +1273,7 @@
     <t>2021-04-30</t>
   </si>
   <si>
-    <t>2021-07-22</t>
+    <t>2021-07-23</t>
   </si>
   <si>
     <t>2021-05-17</t>
@@ -79752,10 +79752,10 @@
         <v>1</v>
       </c>
       <c r="B1556" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C1556">
-        <v>3.050897428883052</v>
+        <v>2.986632807697001</v>
       </c>
       <c r="D1556" t="s">
         <v>418</v>
@@ -79767,22 +79767,22 @@
         <v>-1</v>
       </c>
       <c r="G1556">
-        <v>0.00812910257111695</v>
+        <v>0.008093367192302999</v>
       </c>
       <c r="H1556">
         <v>0.007652117912221571</v>
       </c>
       <c r="I1556">
-        <v>0.263015341104623</v>
+        <v>0.1987507199185727</v>
       </c>
       <c r="J1556">
         <v>0.7132310593025135</v>
       </c>
       <c r="K1556">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="L1556">
-        <v>5.59</v>
+        <v>5.54</v>
       </c>
       <c r="M1556">
         <v>3.41</v>
@@ -79852,7 +79852,7 @@
         <v>3</v>
       </c>
       <c r="B1558" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C1558">
         <v>2.640528299638931</v>
@@ -79861,7 +79861,7 @@
         <v>419</v>
       </c>
       <c r="E1558">
-        <v>2.773248337348258</v>
+        <v>2.731777579720359</v>
       </c>
       <c r="F1558">
         <v>1</v>
@@ -79870,10 +79870,10 @@
         <v>0.007219471700361068</v>
       </c>
       <c r="H1558">
-        <v>0.007166751662651741</v>
+        <v>0.007068222420279641</v>
       </c>
       <c r="I1558">
-        <v>0.1327200377093267</v>
+        <v>0.09124928008142819</v>
       </c>
       <c r="J1558">
         <v>0.7132310593025135</v>
@@ -79885,10 +79885,10 @@
         <v>4.93</v>
       </c>
       <c r="M1558">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="N1558">
-        <v>4.97</v>
+        <v>4.9</v>
       </c>
       <c r="O1558">
         <v>1</v>
@@ -79902,7 +79902,7 @@
         <v>4</v>
       </c>
       <c r="B1559" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1559">
         <v>2.603248337348258</v>
@@ -79911,7 +79911,7 @@
         <v>419</v>
       </c>
       <c r="E1559">
-        <v>2.773248337348258</v>
+        <v>2.731777579720359</v>
       </c>
       <c r="F1559">
         <v>1</v>
@@ -79920,10 +79920,10 @@
         <v>0.006996751662651741</v>
       </c>
       <c r="H1559">
-        <v>0.007166751662651741</v>
+        <v>0.007068222420279641</v>
       </c>
       <c r="I1559">
-        <v>0.1699999999999999</v>
+        <v>0.1285292423721014</v>
       </c>
       <c r="J1559">
         <v>0.7132310593025135</v>
@@ -79935,10 +79935,10 @@
         <v>4.8</v>
       </c>
       <c r="M1559">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="N1559">
-        <v>4.97</v>
+        <v>4.9</v>
       </c>
       <c r="O1559">
         <v>1</v>
@@ -79952,7 +79952,7 @@
         <v>5</v>
       </c>
       <c r="B1560" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C1560">
         <v>2.561851405569183</v>
@@ -79961,7 +79961,7 @@
         <v>419</v>
       </c>
       <c r="E1560">
-        <v>2.773248337348258</v>
+        <v>2.731777579720359</v>
       </c>
       <c r="F1560">
         <v>1</v>
@@ -79970,10 +79970,10 @@
         <v>0.006998148594430817</v>
       </c>
       <c r="H1560">
-        <v>0.007166751662651741</v>
+        <v>0.007068222420279641</v>
       </c>
       <c r="I1560">
-        <v>0.2113969317790745</v>
+        <v>0.1699261741511759</v>
       </c>
       <c r="J1560">
         <v>0.7132310593025135</v>
@@ -79985,10 +79985,10 @@
         <v>4.78</v>
       </c>
       <c r="M1560">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="N1560">
-        <v>4.97</v>
+        <v>4.9</v>
       </c>
       <c r="O1560">
         <v>1</v>
@@ -80002,7 +80002,7 @@
         <v>0</v>
       </c>
       <c r="B1561" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C1561">
         <v>2.140622595222724</v>
@@ -80052,7 +80052,7 @@
         <v>1</v>
       </c>
       <c r="B1562" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C1562">
         <v>2.49970236281472</v>
@@ -80102,7 +80102,7 @@
         <v>2</v>
       </c>
       <c r="B1563" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C1563">
         <v>2.515171233053583</v>
@@ -80302,7 +80302,7 @@
         <v>6</v>
       </c>
       <c r="B1567" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C1567">
         <v>2.157471814073596</v>
@@ -80352,7 +80352,7 @@
         <v>7</v>
       </c>
       <c r="B1568" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1568">
         <v>2.139754887023886</v>
@@ -80361,7 +80361,7 @@
         <v>419</v>
       </c>
       <c r="E1568">
-        <v>2.309754887023886</v>
+        <v>2.274303524854746</v>
       </c>
       <c r="F1568">
         <v>1</v>
@@ -80370,10 +80370,10 @@
         <v>0.007460245112976114</v>
       </c>
       <c r="H1568">
-        <v>0.007630245112976114</v>
+        <v>0.007525696475145255</v>
       </c>
       <c r="I1568">
-        <v>0.1699999999999999</v>
+        <v>0.1345486378308594</v>
       </c>
       <c r="J1568">
         <v>0.8637159457714654</v>
@@ -80385,10 +80385,10 @@
         <v>4.8</v>
       </c>
       <c r="M1568">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="N1568">
-        <v>4.97</v>
+        <v>4.9</v>
       </c>
       <c r="O1568">
         <v>1</v>
@@ -80402,7 +80402,7 @@
         <v>8</v>
       </c>
       <c r="B1569" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C1569">
         <v>2.093843408650743</v>
@@ -80411,7 +80411,7 @@
         <v>419</v>
       </c>
       <c r="E1569">
-        <v>2.309754887023886</v>
+        <v>2.274303524854746</v>
       </c>
       <c r="F1569">
         <v>1</v>
@@ -80420,10 +80420,10 @@
         <v>0.007466156591349258</v>
       </c>
       <c r="H1569">
-        <v>0.007630245112976114</v>
+        <v>0.007525696475145255</v>
       </c>
       <c r="I1569">
-        <v>0.2159114783731431</v>
+        <v>0.1804601162040025</v>
       </c>
       <c r="J1569">
         <v>0.8637159457714654</v>
@@ -80435,10 +80435,10 @@
         <v>4.78</v>
       </c>
       <c r="M1569">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="N1569">
-        <v>4.97</v>
+        <v>4.9</v>
       </c>
       <c r="O1569">
         <v>1</v>
@@ -80452,7 +80452,7 @@
         <v>0</v>
       </c>
       <c r="B1570" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C1570">
         <v>1.99772260130418</v>
@@ -80502,7 +80502,7 @@
         <v>1</v>
       </c>
       <c r="B1571" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C1571">
         <v>2.351245146910454</v>
@@ -80552,7 +80552,7 @@
         <v>2</v>
       </c>
       <c r="B1572" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C1572">
         <v>2.373859016845244</v>
@@ -80752,7 +80752,7 @@
         <v>6</v>
       </c>
       <c r="B1576" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C1576">
         <v>2.03005265282956</v>
@@ -80802,7 +80802,7 @@
         <v>7</v>
       </c>
       <c r="B1577" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1577">
         <v>2.01749600333802</v>
@@ -80852,7 +80852,7 @@
         <v>8</v>
       </c>
       <c r="B1578" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C1578">
         <v>1.970393691682222</v>
@@ -80902,7 +80902,7 @@
         <v>0</v>
       </c>
       <c r="B1579" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C1579">
         <v>1.893712084063664</v>
@@ -80952,7 +80952,7 @@
         <v>1</v>
       </c>
       <c r="B1580" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C1580">
         <v>2.243189776221695</v>
@@ -81002,7 +81002,7 @@
         <v>2</v>
       </c>
       <c r="B1581" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C1581">
         <v>2.271004172018512</v>
@@ -81252,7 +81252,7 @@
         <v>7</v>
       </c>
       <c r="B1586" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C1586">
         <v>1.937309941623433</v>
@@ -81302,7 +81302,7 @@
         <v>8</v>
       </c>
       <c r="B1587" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1587">
         <v>1.92850922747669</v>
@@ -81352,7 +81352,7 @@
         <v>9</v>
       </c>
       <c r="B1588" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C1588">
         <v>1.880540161510555</v>
@@ -81402,7 +81402,7 @@
         <v>0</v>
       </c>
       <c r="B1589" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C1589">
         <v>1.792368417943001</v>
@@ -81502,7 +81502,7 @@
         <v>2</v>
       </c>
       <c r="B1591" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C1591">
         <v>2.137904967529674</v>
@@ -81552,7 +81552,7 @@
         <v>3</v>
       </c>
       <c r="B1592" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C1592">
         <v>2.170786546632523</v>
@@ -81902,7 +81902,7 @@
         <v>10</v>
       </c>
       <c r="B1599" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C1599">
         <v>1.846945172665842</v>
@@ -81952,7 +81952,7 @@
         <v>11</v>
       </c>
       <c r="B1600" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1600">
         <v>1.841804090906789</v>
@@ -82002,7 +82002,7 @@
         <v>12</v>
       </c>
       <c r="B1601" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C1601">
         <v>1.792990494389648</v>
@@ -82052,7 +82052,7 @@
         <v>0</v>
       </c>
       <c r="B1602" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C1602">
         <v>1.676370302057997</v>
@@ -82152,7 +82152,7 @@
         <v>2</v>
       </c>
       <c r="B1604" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C1604">
         <v>2.017395813804697</v>
@@ -82202,7 +82202,7 @@
         <v>3</v>
       </c>
       <c r="B1605" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C1605">
         <v>2.056077298701796</v>
@@ -82452,10 +82452,10 @@
         <v>8</v>
       </c>
       <c r="B1610" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C1610">
-        <v>1.744758783598896</v>
+        <v>1.765637793667497</v>
       </c>
       <c r="D1610" t="s">
         <v>421</v>
@@ -82467,22 +82467,22 @@
         <v>1</v>
       </c>
       <c r="G1610">
-        <v>0.008455241216401102</v>
+        <v>0.008714362206332503</v>
       </c>
       <c r="H1610">
         <v>0.008027585243250703</v>
       </c>
       <c r="I1610">
-        <v>0.2076559731504011</v>
+        <v>0.1867769630818006</v>
       </c>
       <c r="J1610">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1610">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="L1610">
-        <v>5.1</v>
+        <v>5.24</v>
       </c>
       <c r="M1610">
         <v>3.06</v>
@@ -82502,10 +82502,10 @@
         <v>9</v>
       </c>
       <c r="B1611" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C1611">
-        <v>1.755125037794147</v>
+        <v>1.744758783598896</v>
       </c>
       <c r="D1611" t="s">
         <v>421</v>
@@ -82517,22 +82517,22 @@
         <v>1</v>
       </c>
       <c r="G1611">
-        <v>0.008564874962205853</v>
+        <v>0.008455241216401102</v>
       </c>
       <c r="H1611">
         <v>0.008027585243250703</v>
       </c>
       <c r="I1611">
-        <v>0.1972897189551506</v>
+        <v>0.2076559731504011</v>
       </c>
       <c r="J1611">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1611">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="L1611">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="M1611">
         <v>3.06</v>
@@ -82552,10 +82552,10 @@
         <v>10</v>
       </c>
       <c r="B1612" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C1612">
-        <v>1.743513519335047</v>
+        <v>1.755125037794147</v>
       </c>
       <c r="D1612" t="s">
         <v>421</v>
@@ -82567,22 +82567,22 @@
         <v>1</v>
       </c>
       <c r="G1612">
-        <v>0.008116486480664953</v>
+        <v>0.008564874962205853</v>
       </c>
       <c r="H1612">
         <v>0.008027585243250703</v>
       </c>
       <c r="I1612">
-        <v>0.2089012374142509</v>
+        <v>0.1972897189551506</v>
       </c>
       <c r="J1612">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1612">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="L1612">
-        <v>4.93</v>
+        <v>5.16</v>
       </c>
       <c r="M1612">
         <v>3.06</v>
@@ -82602,43 +82602,43 @@
         <v>11</v>
       </c>
       <c r="B1613" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C1613">
-        <v>1.692781010944548</v>
+        <v>1.743513519335047</v>
       </c>
       <c r="D1613" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E1613">
-        <v>1.912634509266448</v>
+        <v>1.952414756749298</v>
       </c>
       <c r="F1613">
         <v>1</v>
       </c>
       <c r="G1613">
-        <v>0.007867218989055453</v>
+        <v>0.008116486480664953</v>
       </c>
       <c r="H1613">
-        <v>0.008047365490733554</v>
+        <v>0.008027585243250703</v>
       </c>
       <c r="I1613">
-        <v>0.2198534983219003</v>
+        <v>0.2089012374142509</v>
       </c>
       <c r="J1613">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1613">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="L1613">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="M1613">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="N1613">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="O1613">
         <v>1</v>
@@ -82649,213 +82649,213 @@
     </row>
     <row r="1614" spans="1:16">
       <c r="A1614" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B1614" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C1614">
-        <v>1.605356319289299</v>
+        <v>1.692781010944548</v>
       </c>
       <c r="D1614" t="s">
-        <v>231</v>
+        <v>422</v>
       </c>
       <c r="E1614">
-        <v>1.823785857909699</v>
+        <v>1.912634509266448</v>
       </c>
       <c r="F1614">
         <v>1</v>
       </c>
       <c r="G1614">
-        <v>0.009134643680710703</v>
+        <v>0.007867218989055453</v>
       </c>
       <c r="H1614">
-        <v>0.009456214142090301</v>
+        <v>0.008047365490733554</v>
       </c>
       <c r="I1614">
-        <v>0.2184295386204007</v>
+        <v>0.2198534983219003</v>
       </c>
       <c r="J1614">
-        <v>1.031409227591973</v>
+        <v>0.9926749160950009</v>
       </c>
       <c r="K1614">
-        <v>3.65</v>
+        <v>3.11</v>
       </c>
       <c r="L1614">
-        <v>5.37</v>
+        <v>4.78</v>
       </c>
       <c r="M1614">
-        <v>3.7</v>
+        <v>3.09</v>
       </c>
       <c r="N1614">
-        <v>5.64</v>
+        <v>4.98</v>
       </c>
       <c r="O1614">
         <v>1</v>
       </c>
       <c r="P1614" t="s">
-        <v>239</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1615" spans="1:16">
       <c r="A1615" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1615" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C1615">
-        <v>1.872529488806021</v>
+        <v>1.605356319289299</v>
       </c>
       <c r="D1615" t="s">
-        <v>423</v>
+        <v>231</v>
       </c>
       <c r="E1615">
-        <v>1.744099950185619</v>
+        <v>1.823785857909699</v>
       </c>
       <c r="F1615">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1615">
-        <v>0.00958747051119398</v>
+        <v>0.009134643680710703</v>
       </c>
       <c r="H1615">
-        <v>0.00935590004981438</v>
+        <v>0.009456214142090301</v>
       </c>
       <c r="I1615">
-        <v>0.1284295386204017</v>
+        <v>0.2184295386204007</v>
       </c>
       <c r="J1615">
         <v>1.031409227591973</v>
       </c>
       <c r="K1615">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="L1615">
-        <v>5.73</v>
+        <v>5.37</v>
       </c>
       <c r="M1615">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="N1615">
-        <v>5.55</v>
+        <v>5.64</v>
       </c>
       <c r="O1615">
         <v>1</v>
       </c>
       <c r="P1615" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1616" spans="1:16">
       <c r="A1616" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1616" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C1616">
-        <v>1.918183149772576</v>
+        <v>1.872529488806021</v>
       </c>
       <c r="D1616" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E1616">
-        <v>1.702894533911371</v>
+        <v>1.744099950185619</v>
       </c>
       <c r="F1616">
         <v>-1</v>
       </c>
       <c r="G1616">
-        <v>0.009261816850227424</v>
+        <v>0.00958747051119398</v>
       </c>
       <c r="H1616">
-        <v>0.00873710546608863</v>
+        <v>0.00935590004981438</v>
       </c>
       <c r="I1616">
-        <v>0.2152886158612044</v>
+        <v>0.1284295386204017</v>
       </c>
       <c r="J1616">
         <v>1.031409227591973</v>
       </c>
       <c r="K1616">
-        <v>3.56</v>
+        <v>3.74</v>
       </c>
       <c r="L1616">
-        <v>5.59</v>
+        <v>5.73</v>
       </c>
       <c r="M1616">
-        <v>3.41</v>
+        <v>3.69</v>
       </c>
       <c r="N1616">
-        <v>5.22</v>
+        <v>5.55</v>
       </c>
       <c r="O1616">
         <v>1</v>
       </c>
       <c r="P1616" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1617" spans="1:16">
       <c r="A1617" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1617" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C1617">
-        <v>1.572580441635452</v>
+        <v>1.918183149772576</v>
       </c>
       <c r="D1617" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E1617">
-        <v>1.811324072531773</v>
+        <v>1.702894533911371</v>
       </c>
       <c r="F1617">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1617">
-        <v>0.008627419558364548</v>
+        <v>0.009261816850227424</v>
       </c>
       <c r="H1617">
-        <v>0.008948675927468227</v>
+        <v>0.00873710546608863</v>
       </c>
       <c r="I1617">
-        <v>0.2387436308963213</v>
+        <v>0.2152886158612044</v>
       </c>
       <c r="J1617">
         <v>1.031409227591973</v>
       </c>
       <c r="K1617">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="L1617">
-        <v>5.1</v>
+        <v>5.59</v>
       </c>
       <c r="M1617">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="N1617">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="O1617">
         <v>1</v>
       </c>
       <c r="P1617" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1618" spans="1:16">
       <c r="A1618" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1618" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C1618">
-        <v>1.622894533911371</v>
+        <v>1.572580441635452</v>
       </c>
       <c r="D1618" t="s">
         <v>420</v>
@@ -82867,22 +82867,22 @@
         <v>1</v>
       </c>
       <c r="G1618">
-        <v>0.00865710546608863</v>
+        <v>0.008627419558364548</v>
       </c>
       <c r="H1618">
         <v>0.008948675927468227</v>
       </c>
       <c r="I1618">
-        <v>0.1884295386204018</v>
+        <v>0.2387436308963213</v>
       </c>
       <c r="J1618">
         <v>1.031409227591973</v>
       </c>
       <c r="K1618">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="L1618">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="M1618">
         <v>3.46</v>
@@ -82894,118 +82894,118 @@
         <v>1</v>
       </c>
       <c r="P1618" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1619" spans="1:16">
       <c r="A1619" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1619" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C1619">
-        <v>1.897869057496656</v>
+        <v>1.622894533911371</v>
       </c>
       <c r="D1619" t="s">
-        <v>249</v>
+        <v>420</v>
       </c>
       <c r="E1619">
-        <v>1.658183149772576</v>
+        <v>1.811324072531773</v>
       </c>
       <c r="F1619">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1619">
-        <v>0.009262130942503345</v>
+        <v>0.00865710546608863</v>
       </c>
       <c r="H1619">
-        <v>0.009001816850227424</v>
+        <v>0.008948675927468227</v>
       </c>
       <c r="I1619">
-        <v>0.2396859077240805</v>
+        <v>0.1884295386204018</v>
       </c>
       <c r="J1619">
         <v>1.031409227591973</v>
       </c>
       <c r="K1619">
-        <v>3.57</v>
+        <v>3.41</v>
       </c>
       <c r="L1619">
-        <v>5.58</v>
+        <v>5.14</v>
       </c>
       <c r="M1619">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="N1619">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="O1619">
         <v>1</v>
       </c>
       <c r="P1619" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1620" spans="1:16">
       <c r="A1620" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1620" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C1620">
-        <v>1.580381795704013</v>
+        <v>1.897869057496656</v>
       </c>
       <c r="D1620" t="s">
-        <v>421</v>
+        <v>249</v>
       </c>
       <c r="E1620">
-        <v>1.833887763568562</v>
+        <v>1.658183149772576</v>
       </c>
       <c r="F1620">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1620">
-        <v>0.008779618204295986</v>
+        <v>0.009262130942503345</v>
       </c>
       <c r="H1620">
-        <v>0.008146112236431439</v>
+        <v>0.009001816850227424</v>
       </c>
       <c r="I1620">
-        <v>0.253505967864549</v>
+        <v>0.2396859077240805</v>
       </c>
       <c r="J1620">
         <v>1.031409227591973</v>
       </c>
       <c r="K1620">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="L1620">
-        <v>5.18</v>
+        <v>5.58</v>
       </c>
       <c r="M1620">
-        <v>3.06</v>
+        <v>3.56</v>
       </c>
       <c r="N1620">
-        <v>4.99</v>
+        <v>5.33</v>
       </c>
       <c r="O1620">
         <v>1</v>
       </c>
       <c r="P1620" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1621" spans="1:16">
       <c r="A1621" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1621" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C1621">
-        <v>1.630067703428094</v>
+        <v>1.580381795704013</v>
       </c>
       <c r="D1621" t="s">
         <v>421</v>
@@ -83017,22 +83017,22 @@
         <v>1</v>
       </c>
       <c r="G1621">
-        <v>0.008849932296571906</v>
+        <v>0.008779618204295986</v>
       </c>
       <c r="H1621">
         <v>0.008146112236431439</v>
       </c>
       <c r="I1621">
-        <v>0.2038200601404681</v>
+        <v>0.253505967864549</v>
       </c>
       <c r="J1621">
         <v>1.031409227591973</v>
       </c>
       <c r="K1621">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="L1621">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="M1621">
         <v>3.06</v>
@@ -83044,18 +83044,18 @@
         <v>1</v>
       </c>
       <c r="P1621" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1622" spans="1:16">
       <c r="A1622" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1622" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C1622">
-        <v>1.613836810739131</v>
+        <v>1.630067703428094</v>
       </c>
       <c r="D1622" t="s">
         <v>421</v>
@@ -83067,22 +83067,22 @@
         <v>1</v>
       </c>
       <c r="G1622">
-        <v>0.00858616318926087</v>
+        <v>0.008849932296571906</v>
       </c>
       <c r="H1622">
         <v>0.008146112236431439</v>
       </c>
       <c r="I1622">
-        <v>0.2200509528294314</v>
+        <v>0.2038200601404681</v>
       </c>
       <c r="J1622">
         <v>1.031409227591973</v>
       </c>
       <c r="K1622">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="L1622">
-        <v>5.1</v>
+        <v>5.24</v>
       </c>
       <c r="M1622">
         <v>3.06</v>
@@ -83094,18 +83094,18 @@
         <v>1</v>
       </c>
       <c r="P1622" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1623" spans="1:16">
       <c r="A1623" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1623" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C1623">
-        <v>1.622266349359532</v>
+        <v>1.613836810739131</v>
       </c>
       <c r="D1623" t="s">
         <v>421</v>
@@ -83117,22 +83117,22 @@
         <v>1</v>
       </c>
       <c r="G1623">
-        <v>0.008697733650640469</v>
+        <v>0.00858616318926087</v>
       </c>
       <c r="H1623">
         <v>0.008146112236431439</v>
       </c>
       <c r="I1623">
-        <v>0.2116214142090302</v>
+        <v>0.2200509528294314</v>
       </c>
       <c r="J1623">
         <v>1.031409227591973</v>
       </c>
       <c r="K1623">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="L1623">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="M1623">
         <v>3.06</v>
@@ -83144,18 +83144,18 @@
         <v>1</v>
       </c>
       <c r="P1623" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1624" spans="1:16">
       <c r="A1624" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1624" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C1624">
-        <v>1.619176379429766</v>
+        <v>1.622266349359532</v>
       </c>
       <c r="D1624" t="s">
         <v>421</v>
@@ -83167,22 +83167,22 @@
         <v>1</v>
       </c>
       <c r="G1624">
-        <v>0.008240823620570232</v>
+        <v>0.008697733650640469</v>
       </c>
       <c r="H1624">
         <v>0.008146112236431439</v>
       </c>
       <c r="I1624">
-        <v>0.2147113841387962</v>
+        <v>0.2116214142090302</v>
       </c>
       <c r="J1624">
         <v>1.031409227591973</v>
       </c>
       <c r="K1624">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="L1624">
-        <v>4.93</v>
+        <v>5.16</v>
       </c>
       <c r="M1624">
         <v>3.06</v>
@@ -83194,118 +83194,118 @@
         <v>1</v>
       </c>
       <c r="P1624" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1625" spans="1:16">
       <c r="A1625" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1625" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C1625">
-        <v>1.572317302188964</v>
+        <v>1.619176379429766</v>
       </c>
       <c r="D1625" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E1625">
-        <v>1.759804563981606</v>
+        <v>1.833887763568562</v>
       </c>
       <c r="F1625">
         <v>1</v>
       </c>
       <c r="G1625">
-        <v>0.007987682697811038</v>
+        <v>0.008240823620570232</v>
       </c>
       <c r="H1625">
-        <v>0.008340195436018395</v>
+        <v>0.008146112236431439</v>
       </c>
       <c r="I1625">
-        <v>0.1874872617926417</v>
+        <v>0.2147113841387962</v>
       </c>
       <c r="J1625">
         <v>1.031409227591973</v>
       </c>
       <c r="K1625">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="L1625">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="M1625">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="N1625">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="O1625">
         <v>1</v>
       </c>
       <c r="P1625" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1626" spans="1:16">
       <c r="A1626" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B1626" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C1626">
-        <v>1.561057407303271</v>
+        <v>1.572317302188964</v>
       </c>
       <c r="D1626" t="s">
-        <v>231</v>
+        <v>424</v>
       </c>
       <c r="E1626">
-        <v>1.733292087439065</v>
+        <v>1.759804563981606</v>
       </c>
       <c r="F1626">
         <v>1</v>
       </c>
       <c r="G1626">
-        <v>0.00945894259269673</v>
+        <v>0.007987682697811038</v>
       </c>
       <c r="H1626">
-        <v>0.009546707912560935</v>
+        <v>0.008340195436018395</v>
       </c>
       <c r="I1626">
-        <v>0.1722346801357939</v>
+        <v>0.1874872617926417</v>
       </c>
       <c r="J1626">
-        <v>1.055867003394847</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1626">
-        <v>3.74</v>
+        <v>3.11</v>
       </c>
       <c r="L1626">
-        <v>5.51</v>
+        <v>4.78</v>
       </c>
       <c r="M1626">
-        <v>3.7</v>
+        <v>3.19</v>
       </c>
       <c r="N1626">
-        <v>5.64</v>
+        <v>5.05</v>
       </c>
       <c r="O1626">
         <v>1</v>
       </c>
       <c r="P1626" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="1627" spans="1:16">
       <c r="A1627" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1627" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C1627">
-        <v>1.516085437608808</v>
+        <v>1.561057407303271</v>
       </c>
       <c r="D1627" t="s">
         <v>231</v>
@@ -83317,22 +83317,22 @@
         <v>1</v>
       </c>
       <c r="G1627">
-        <v>0.009223914562391192</v>
+        <v>0.00945894259269673</v>
       </c>
       <c r="H1627">
         <v>0.009546707912560935</v>
       </c>
       <c r="I1627">
-        <v>0.2172066498302567</v>
+        <v>0.1722346801357939</v>
       </c>
       <c r="J1627">
         <v>1.055867003394847</v>
       </c>
       <c r="K1627">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="L1627">
-        <v>5.37</v>
+        <v>5.51</v>
       </c>
       <c r="M1627">
         <v>3.7</v>
@@ -83349,46 +83349,46 @@
     </row>
     <row r="1628" spans="1:16">
       <c r="A1628" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1628" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C1628">
-        <v>1.831113467914344</v>
+        <v>1.516085437608808</v>
       </c>
       <c r="D1628" t="s">
-        <v>418</v>
+        <v>231</v>
       </c>
       <c r="E1628">
-        <v>1.619493518423571</v>
+        <v>1.733292087439065</v>
       </c>
       <c r="F1628">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1628">
-        <v>0.009348886532085656</v>
+        <v>0.009223914562391192</v>
       </c>
       <c r="H1628">
-        <v>0.008820506481576429</v>
+        <v>0.009546707912560935</v>
       </c>
       <c r="I1628">
-        <v>0.2116199494907733</v>
+        <v>0.2172066498302567</v>
       </c>
       <c r="J1628">
         <v>1.055867003394847</v>
       </c>
       <c r="K1628">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="L1628">
-        <v>5.59</v>
+        <v>5.37</v>
       </c>
       <c r="M1628">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="N1628">
-        <v>5.22</v>
+        <v>5.64</v>
       </c>
       <c r="O1628">
         <v>1</v>
@@ -83399,46 +83399,46 @@
     </row>
     <row r="1629" spans="1:16">
       <c r="A1629" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1629" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C1629">
-        <v>1.488934848389623</v>
+        <v>1.831113467914344</v>
       </c>
       <c r="D1629" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E1629">
-        <v>1.726700168253829</v>
+        <v>1.619493518423571</v>
       </c>
       <c r="F1629">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1629">
-        <v>0.008711065151610378</v>
+        <v>0.009348886532085656</v>
       </c>
       <c r="H1629">
-        <v>0.00903329983174617</v>
+        <v>0.008820506481576429</v>
       </c>
       <c r="I1629">
-        <v>0.2377653198642062</v>
+        <v>0.2116199494907733</v>
       </c>
       <c r="J1629">
         <v>1.055867003394847</v>
       </c>
       <c r="K1629">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="L1629">
-        <v>5.1</v>
+        <v>5.59</v>
       </c>
       <c r="M1629">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="N1629">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="O1629">
         <v>1</v>
@@ -83449,13 +83449,13 @@
     </row>
     <row r="1630" spans="1:16">
       <c r="A1630" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1630" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C1630">
-        <v>1.539493518423571</v>
+        <v>1.488934848389623</v>
       </c>
       <c r="D1630" t="s">
         <v>420</v>
@@ -83467,22 +83467,22 @@
         <v>1</v>
       </c>
       <c r="G1630">
-        <v>0.008740506481576428</v>
+        <v>0.008711065151610378</v>
       </c>
       <c r="H1630">
         <v>0.00903329983174617</v>
       </c>
       <c r="I1630">
-        <v>0.1872066498302583</v>
+        <v>0.2377653198642062</v>
       </c>
       <c r="J1630">
         <v>1.055867003394847</v>
       </c>
       <c r="K1630">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="L1630">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="M1630">
         <v>3.46</v>
@@ -83499,46 +83499,46 @@
     </row>
     <row r="1631" spans="1:16">
       <c r="A1631" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1631" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C1631">
-        <v>1.810554797880396</v>
+        <v>1.539493518423571</v>
       </c>
       <c r="D1631" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E1631">
-        <v>1.673348148050138</v>
+        <v>1.726700168253829</v>
       </c>
       <c r="F1631">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1631">
-        <v>0.009349445202119604</v>
+        <v>0.008740506481576428</v>
       </c>
       <c r="H1631">
-        <v>0.009106651851949862</v>
+        <v>0.00903329983174617</v>
       </c>
       <c r="I1631">
-        <v>0.137206649830258</v>
+        <v>0.1872066498302583</v>
       </c>
       <c r="J1631">
         <v>1.055867003394847</v>
       </c>
       <c r="K1631">
-        <v>3.57</v>
+        <v>3.41</v>
       </c>
       <c r="L1631">
-        <v>5.58</v>
+        <v>5.14</v>
       </c>
       <c r="M1631">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="N1631">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="O1631">
         <v>1</v>
@@ -83549,46 +83549,46 @@
     </row>
     <row r="1632" spans="1:16">
       <c r="A1632" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1632" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C1632">
-        <v>1.495024158151983</v>
+        <v>1.810554797880396</v>
       </c>
       <c r="D1632" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E1632">
-        <v>1.759046969611768</v>
+        <v>1.673348148050138</v>
       </c>
       <c r="F1632">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1632">
-        <v>0.008864975841848017</v>
+        <v>0.009349445202119604</v>
       </c>
       <c r="H1632">
-        <v>0.008220953030388231</v>
+        <v>0.009106651851949862</v>
       </c>
       <c r="I1632">
-        <v>0.2640228114597849</v>
+        <v>0.137206649830258</v>
       </c>
       <c r="J1632">
         <v>1.055867003394847</v>
       </c>
       <c r="K1632">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="L1632">
-        <v>5.18</v>
+        <v>5.58</v>
       </c>
       <c r="M1632">
-        <v>3.06</v>
+        <v>3.52</v>
       </c>
       <c r="N1632">
-        <v>4.99</v>
+        <v>5.39</v>
       </c>
       <c r="O1632">
         <v>1</v>
@@ -83599,13 +83599,13 @@
     </row>
     <row r="1633" spans="1:16">
       <c r="A1633" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1633" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C1633">
-        <v>1.544465488118035</v>
+        <v>1.495024158151983</v>
       </c>
       <c r="D1633" t="s">
         <v>421</v>
@@ -83617,22 +83617,22 @@
         <v>1</v>
       </c>
       <c r="G1633">
-        <v>0.008935534511881966</v>
+        <v>0.008864975841848017</v>
       </c>
       <c r="H1633">
         <v>0.008220953030388231</v>
       </c>
       <c r="I1633">
-        <v>0.2145814814937328</v>
+        <v>0.2640228114597849</v>
       </c>
       <c r="J1633">
         <v>1.055867003394847</v>
       </c>
       <c r="K1633">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="L1633">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="M1633">
         <v>3.06</v>
@@ -83649,13 +83649,13 @@
     </row>
     <row r="1634" spans="1:16">
       <c r="A1634" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1634" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C1634">
-        <v>1.538376178355674</v>
+        <v>1.544465488118035</v>
       </c>
       <c r="D1634" t="s">
         <v>421</v>
@@ -83667,22 +83667,22 @@
         <v>1</v>
       </c>
       <c r="G1634">
-        <v>0.008781623821644326</v>
+        <v>0.008935534511881966</v>
       </c>
       <c r="H1634">
         <v>0.008220953030388231</v>
       </c>
       <c r="I1634">
-        <v>0.2206707912560937</v>
+        <v>0.2145814814937328</v>
       </c>
       <c r="J1634">
         <v>1.055867003394847</v>
       </c>
       <c r="K1634">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="L1634">
-        <v>5.16</v>
+        <v>5.24</v>
       </c>
       <c r="M1634">
         <v>3.06</v>
@@ -83699,13 +83699,13 @@
     </row>
     <row r="1635" spans="1:16">
       <c r="A1635" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1635" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C1635">
-        <v>1.54066691910254</v>
+        <v>1.538376178355674</v>
       </c>
       <c r="D1635" t="s">
         <v>421</v>
@@ -83717,22 +83717,22 @@
         <v>1</v>
       </c>
       <c r="G1635">
-        <v>0.008319333080897461</v>
+        <v>0.008781623821644326</v>
       </c>
       <c r="H1635">
         <v>0.008220953030388231</v>
       </c>
       <c r="I1635">
-        <v>0.2183800505092277</v>
+        <v>0.2206707912560937</v>
       </c>
       <c r="J1635">
         <v>1.055867003394847</v>
       </c>
       <c r="K1635">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="L1635">
-        <v>4.93</v>
+        <v>5.16</v>
       </c>
       <c r="M1635">
         <v>3.06</v>
@@ -83749,46 +83749,46 @@
     </row>
     <row r="1636" spans="1:16">
       <c r="A1636" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1636" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C1636">
-        <v>1.496253619442026</v>
+        <v>1.54066691910254</v>
       </c>
       <c r="D1636" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E1636">
-        <v>1.681784259170438</v>
+        <v>1.759046969611768</v>
       </c>
       <c r="F1636">
         <v>1</v>
       </c>
       <c r="G1636">
-        <v>0.008063746380557974</v>
+        <v>0.008319333080897461</v>
       </c>
       <c r="H1636">
-        <v>0.008418215740829562</v>
+        <v>0.008220953030388231</v>
       </c>
       <c r="I1636">
-        <v>0.185530639728412</v>
+        <v>0.2183800505092277</v>
       </c>
       <c r="J1636">
         <v>1.055867003394847</v>
       </c>
       <c r="K1636">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="L1636">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="M1636">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="N1636">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="O1636">
         <v>1</v>
@@ -83799,96 +83799,96 @@
     </row>
     <row r="1637" spans="1:16">
       <c r="A1637" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1637" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C1637">
-        <v>1.244990997067842</v>
+        <v>1.496253619442026</v>
       </c>
       <c r="D1637" t="s">
-        <v>231</v>
+        <v>424</v>
       </c>
       <c r="E1637">
-        <v>1.458484024424935</v>
+        <v>1.681784259170438</v>
       </c>
       <c r="F1637">
         <v>1</v>
       </c>
       <c r="G1637">
-        <v>0.009495009002932157</v>
+        <v>0.008063746380557974</v>
       </c>
       <c r="H1637">
-        <v>0.009821515975575065</v>
+        <v>0.008418215740829562</v>
       </c>
       <c r="I1637">
-        <v>0.2134930273570932</v>
+        <v>0.185530639728412</v>
       </c>
       <c r="J1637">
-        <v>1.130139452858125</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1637">
-        <v>3.65</v>
+        <v>3.11</v>
       </c>
       <c r="L1637">
-        <v>5.37</v>
+        <v>4.78</v>
       </c>
       <c r="M1637">
-        <v>3.7</v>
+        <v>3.19</v>
       </c>
       <c r="N1637">
-        <v>5.64</v>
+        <v>5.05</v>
       </c>
       <c r="O1637">
         <v>1</v>
       </c>
       <c r="P1637" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1638" spans="1:16">
       <c r="A1638" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1638" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C1638">
-        <v>1.566703547825073</v>
+        <v>1.244990997067842</v>
       </c>
       <c r="D1638" t="s">
-        <v>426</v>
+        <v>231</v>
       </c>
       <c r="E1638">
-        <v>1.415813309525142</v>
+        <v>1.458484024424935</v>
       </c>
       <c r="F1638">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1638">
-        <v>0.009613296452174926</v>
+        <v>0.009495009002932157</v>
       </c>
       <c r="H1638">
-        <v>0.009304186690474857</v>
+        <v>0.009821515975575065</v>
       </c>
       <c r="I1638">
-        <v>0.1508902382999304</v>
+        <v>0.2134930273570932</v>
       </c>
       <c r="J1638">
         <v>1.130139452858125</v>
       </c>
       <c r="K1638">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="L1638">
-        <v>5.59</v>
+        <v>5.37</v>
       </c>
       <c r="M1638">
-        <v>3.49</v>
+        <v>3.7</v>
       </c>
       <c r="N1638">
-        <v>5.36</v>
+        <v>5.64</v>
       </c>
       <c r="O1638">
         <v>1</v>
@@ -83899,46 +83899,46 @@
     </row>
     <row r="1639" spans="1:16">
       <c r="A1639" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1639" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C1639">
-        <v>1.234923071225211</v>
+        <v>1.566703547825073</v>
       </c>
       <c r="D1639" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E1639">
-        <v>1.469717493110886</v>
+        <v>1.415813309525142</v>
       </c>
       <c r="F1639">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1639">
-        <v>0.008965076928774789</v>
+        <v>0.009613296452174926</v>
       </c>
       <c r="H1639">
-        <v>0.009290282506889113</v>
+        <v>0.009304186690474857</v>
       </c>
       <c r="I1639">
-        <v>0.2347944218856752</v>
+        <v>0.1508902382999304</v>
       </c>
       <c r="J1639">
         <v>1.130139452858125</v>
       </c>
       <c r="K1639">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="L1639">
-        <v>5.1</v>
+        <v>5.59</v>
       </c>
       <c r="M1639">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="N1639">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="O1639">
         <v>1</v>
@@ -83949,13 +83949,13 @@
     </row>
     <row r="1640" spans="1:16">
       <c r="A1640" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1640" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C1640">
-        <v>1.286224465753792</v>
+        <v>1.234923071225211</v>
       </c>
       <c r="D1640" t="s">
         <v>420</v>
@@ -83967,22 +83967,22 @@
         <v>1</v>
       </c>
       <c r="G1640">
-        <v>0.008993775534246207</v>
+        <v>0.008965076928774789</v>
       </c>
       <c r="H1640">
         <v>0.009290282506889113</v>
       </c>
       <c r="I1640">
-        <v>0.1834930273570943</v>
+        <v>0.2347944218856752</v>
       </c>
       <c r="J1640">
         <v>1.130139452858125</v>
       </c>
       <c r="K1640">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="L1640">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="M1640">
         <v>3.46</v>
@@ -83999,46 +83999,46 @@
     </row>
     <row r="1641" spans="1:16">
       <c r="A1641" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1641" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C1641">
-        <v>1.545402153296492</v>
+        <v>1.286224465753792</v>
       </c>
       <c r="D1641" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E1641">
-        <v>1.411909125939398</v>
+        <v>1.469717493110886</v>
       </c>
       <c r="F1641">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1641">
-        <v>0.009614597846703507</v>
+        <v>0.008993775534246207</v>
       </c>
       <c r="H1641">
-        <v>0.009368090874060602</v>
+        <v>0.009290282506889113</v>
       </c>
       <c r="I1641">
-        <v>0.133493027357094</v>
+        <v>0.1834930273570943</v>
       </c>
       <c r="J1641">
         <v>1.130139452858125</v>
       </c>
       <c r="K1641">
-        <v>3.57</v>
+        <v>3.41</v>
       </c>
       <c r="L1641">
-        <v>5.58</v>
+        <v>5.14</v>
       </c>
       <c r="M1641">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="N1641">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="O1641">
         <v>1</v>
@@ -84049,46 +84049,46 @@
     </row>
     <row r="1642" spans="1:16">
       <c r="A1642" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1642" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="C1642">
-        <v>1.306703547825073</v>
+        <v>1.545402153296492</v>
       </c>
       <c r="D1642" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E1642">
-        <v>1.531773274254136</v>
+        <v>1.411909125939398</v>
       </c>
       <c r="F1642">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1642">
-        <v>0.009353296452174927</v>
+        <v>0.009614597846703507</v>
       </c>
       <c r="H1642">
-        <v>0.008448226725745866</v>
+        <v>0.009368090874060602</v>
       </c>
       <c r="I1642">
-        <v>0.2250697264290631</v>
+        <v>0.133493027357094</v>
       </c>
       <c r="J1642">
         <v>1.130139452858125</v>
       </c>
       <c r="K1642">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="L1642">
-        <v>5.33</v>
+        <v>5.58</v>
       </c>
       <c r="M1642">
-        <v>3.06</v>
+        <v>3.52</v>
       </c>
       <c r="N1642">
-        <v>4.99</v>
+        <v>5.39</v>
       </c>
       <c r="O1642">
         <v>1</v>
@@ -84099,13 +84099,13 @@
     </row>
     <row r="1643" spans="1:16">
       <c r="A1643" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1643" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C1643">
-        <v>1.235813309525142</v>
+        <v>1.306703547825073</v>
       </c>
       <c r="D1643" t="s">
         <v>421</v>
@@ -84117,22 +84117,22 @@
         <v>1</v>
       </c>
       <c r="G1643">
-        <v>0.009124186690474857</v>
+        <v>0.009353296452174927</v>
       </c>
       <c r="H1643">
         <v>0.008448226725745866</v>
       </c>
       <c r="I1643">
-        <v>0.2959599647289943</v>
+        <v>0.2250697264290631</v>
       </c>
       <c r="J1643">
         <v>1.130139452858125</v>
       </c>
       <c r="K1643">
-        <v>3.49</v>
+        <v>3.56</v>
       </c>
       <c r="L1643">
-        <v>5.18</v>
+        <v>5.33</v>
       </c>
       <c r="M1643">
         <v>3.06</v>
@@ -84149,13 +84149,13 @@
     </row>
     <row r="1644" spans="1:16">
       <c r="A1644" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1644" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C1644">
-        <v>1.284511914996561</v>
+        <v>1.235813309525142</v>
       </c>
       <c r="D1644" t="s">
         <v>421</v>
@@ -84167,22 +84167,22 @@
         <v>1</v>
       </c>
       <c r="G1644">
-        <v>0.00919548808500344</v>
+        <v>0.009124186690474857</v>
       </c>
       <c r="H1644">
         <v>0.008448226725745866</v>
       </c>
       <c r="I1644">
-        <v>0.2472613592575748</v>
+        <v>0.2959599647289943</v>
       </c>
       <c r="J1644">
         <v>1.130139452858125</v>
       </c>
       <c r="K1644">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="L1644">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="M1644">
         <v>3.06</v>
@@ -84199,13 +84199,13 @@
     </row>
     <row r="1645" spans="1:16">
       <c r="A1645" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1645" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C1645">
-        <v>1.28362167669663</v>
+        <v>1.284511914996561</v>
       </c>
       <c r="D1645" t="s">
         <v>421</v>
@@ -84217,22 +84217,22 @@
         <v>1</v>
       </c>
       <c r="G1645">
-        <v>0.009036378323303371</v>
+        <v>0.00919548808500344</v>
       </c>
       <c r="H1645">
         <v>0.008448226725745866</v>
       </c>
       <c r="I1645">
-        <v>0.2481515975575066</v>
+        <v>0.2472613592575748</v>
       </c>
       <c r="J1645">
         <v>1.130139452858125</v>
       </c>
       <c r="K1645">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="L1645">
-        <v>5.16</v>
+        <v>5.24</v>
       </c>
       <c r="M1645">
         <v>3.06</v>
@@ -84249,13 +84249,13 @@
     </row>
     <row r="1646" spans="1:16">
       <c r="A1646" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1646" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C1646">
-        <v>1.302252356325417</v>
+        <v>1.28362167669663</v>
       </c>
       <c r="D1646" t="s">
         <v>421</v>
@@ -84267,22 +84267,22 @@
         <v>1</v>
       </c>
       <c r="G1646">
-        <v>0.008557747643674583</v>
+        <v>0.009036378323303371</v>
       </c>
       <c r="H1646">
         <v>0.008448226725745866</v>
       </c>
       <c r="I1646">
-        <v>0.2295209179287192</v>
+        <v>0.2481515975575066</v>
       </c>
       <c r="J1646">
         <v>1.130139452858125</v>
       </c>
       <c r="K1646">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="L1646">
-        <v>4.93</v>
+        <v>5.16</v>
       </c>
       <c r="M1646">
         <v>3.06</v>
@@ -84299,46 +84299,46 @@
     </row>
     <row r="1647" spans="1:16">
       <c r="A1647" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1647" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C1647">
-        <v>1.26526630161123</v>
+        <v>1.302252356325417</v>
       </c>
       <c r="D1647" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E1647">
-        <v>1.422252356325417</v>
+        <v>1.531773274254136</v>
       </c>
       <c r="F1647">
         <v>1</v>
       </c>
       <c r="G1647">
-        <v>0.008294733698388771</v>
+        <v>0.008557747643674583</v>
       </c>
       <c r="H1647">
-        <v>0.008677747643674582</v>
+        <v>0.008448226725745866</v>
       </c>
       <c r="I1647">
-        <v>0.1569860547141868</v>
+        <v>0.2295209179287192</v>
       </c>
       <c r="J1647">
         <v>1.130139452858125</v>
       </c>
       <c r="K1647">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="L1647">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="M1647">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
       <c r="N1647">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="O1647">
         <v>1</v>
@@ -84349,60 +84349,60 @@
     </row>
     <row r="1648" spans="1:16">
       <c r="A1648" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1648" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C1648">
-        <v>1.121405183498271</v>
+        <v>1.26526630161123</v>
       </c>
       <c r="D1648" t="s">
-        <v>231</v>
+        <v>427</v>
       </c>
       <c r="E1648">
-        <v>1.333205254505096</v>
+        <v>1.422252356325417</v>
       </c>
       <c r="F1648">
         <v>1</v>
       </c>
       <c r="G1648">
-        <v>0.00961859481650173</v>
+        <v>0.008294733698388771</v>
       </c>
       <c r="H1648">
-        <v>0.009946794745494904</v>
+        <v>0.008677747643674582</v>
       </c>
       <c r="I1648">
-        <v>0.2118000710068246</v>
+        <v>0.1569860547141868</v>
       </c>
       <c r="J1648">
-        <v>1.163998579863488</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1648">
-        <v>3.65</v>
+        <v>3.11</v>
       </c>
       <c r="L1648">
-        <v>5.37</v>
+        <v>4.78</v>
       </c>
       <c r="M1648">
-        <v>3.7</v>
+        <v>3.21</v>
       </c>
       <c r="N1648">
-        <v>5.64</v>
+        <v>5.05</v>
       </c>
       <c r="O1648">
         <v>1</v>
       </c>
       <c r="P1648" t="s">
-        <v>541</v>
+        <v>248</v>
       </c>
     </row>
     <row r="1649" spans="1:16">
       <c r="A1649" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1649" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C1649">
         <v>1.446165055685984</v>
@@ -84449,7 +84449,7 @@
     </row>
     <row r="1650" spans="1:16">
       <c r="A1650" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1650" t="s">
         <v>241</v>
@@ -84499,7 +84499,7 @@
     </row>
     <row r="1651" spans="1:16">
       <c r="A1651" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1651" t="s">
         <v>245</v>
@@ -84549,7 +84549,7 @@
     </row>
     <row r="1652" spans="1:16">
       <c r="A1652" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1652" t="s">
         <v>233</v>
@@ -84599,7 +84599,7 @@
     </row>
     <row r="1653" spans="1:16">
       <c r="A1653" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1653" t="s">
         <v>249</v>
@@ -84649,7 +84649,7 @@
     </row>
     <row r="1654" spans="1:16">
       <c r="A1654" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1654" t="s">
         <v>242</v>
@@ -84699,7 +84699,7 @@
     </row>
     <row r="1655" spans="1:16">
       <c r="A1655" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1655" t="s">
         <v>247</v>
@@ -84749,7 +84749,7 @@
     </row>
     <row r="1656" spans="1:16">
       <c r="A1656" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1656" t="s">
         <v>246</v>
@@ -84799,10 +84799,10 @@
     </row>
     <row r="1657" spans="1:16">
       <c r="A1657" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1657" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C1657">
         <v>1.193564558638205</v>
@@ -84849,10 +84849,10 @@
     </row>
     <row r="1658" spans="1:16">
       <c r="A1658" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1658" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C1658">
         <v>1.159964416624554</v>
@@ -84902,7 +84902,7 @@
         <v>0</v>
       </c>
       <c r="B1659" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C1659">
         <v>1.284389949876279</v>
@@ -85302,7 +85302,7 @@
         <v>8</v>
       </c>
       <c r="B1667" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C1667">
         <v>1.047694308736757</v>
@@ -85352,7 +85352,7 @@
         <v>9</v>
       </c>
       <c r="B1668" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C1668">
         <v>1.018638411268323</v>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5025" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="547">
   <si>
     <t>trade_time</t>
   </si>
@@ -718,9 +718,6 @@
     <t>2021-05-20</t>
   </si>
   <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
     <t>2021-07-12</t>
   </si>
   <si>
@@ -742,31 +739,34 @@
     <t>2021-05-10</t>
   </si>
   <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
     <t>2021-07-06</t>
   </si>
   <si>
-    <t>2021-06-09</t>
+    <t>2021-04-01</t>
   </si>
   <si>
     <t>2021-06-16</t>
   </si>
   <si>
-    <t>2021-04-01</t>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2021-05-12</t>
   </si>
   <si>
+    <t>2021-06-11</t>
+  </si>
+  <si>
     <t>2021-06-21</t>
   </si>
   <si>
-    <t>2021-06-11</t>
+    <t>2021-07-27</t>
   </si>
   <si>
     <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
   </si>
   <si>
     <t>2021-06-18</t>
@@ -1270,40 +1270,40 @@
     <t>2021-03-22</t>
   </si>
   <si>
-    <t>2021-03-23</t>
-  </si>
-  <si>
     <t>2021-04-30</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-08-04</t>
   </si>
   <si>
     <t>2021-05-11</t>
   </si>
   <si>
-    <t>2021-07-08</t>
-  </si>
-  <si>
     <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>2021-05-17</t>
   </si>
   <si>
     <t>2021-07-20</t>
   </si>
   <si>
+    <t>2021-06-25</t>
+  </si>
+  <si>
+    <t>2021-07-08</t>
+  </si>
+  <si>
     <t>2021-04-09</t>
   </si>
   <si>
-    <t>2021-04-28</t>
+    <t>2021-05-17</t>
   </si>
   <si>
     <t>2021-06-01</t>
   </si>
   <si>
     <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
   </si>
   <si>
     <t>2016-08-24</t>
@@ -1639,10 +1639,16 @@
     <t>2021-01-25</t>
   </si>
   <si>
+    <t>2021-03-17</t>
+  </si>
+  <si>
     <t>2021-03-18</t>
   </si>
   <si>
     <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-03-23</t>
   </si>
   <si>
     <t>2021-03-30</t>
@@ -2006,7 +2012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1671"/>
+  <dimension ref="A1:P1664"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -79517,7 +79523,7 @@
         <v>3.008937146023147</v>
       </c>
       <c r="D1551" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E1551">
         <v>2.648164860871706</v>
@@ -79567,7 +79573,7 @@
         <v>2.987429820241319</v>
       </c>
       <c r="D1552" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E1552">
         <v>2.648164860871706</v>
@@ -79617,7 +79623,7 @@
         <v>2.973459123368629</v>
       </c>
       <c r="D1553" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E1553">
         <v>2.648164860871706</v>
@@ -79667,7 +79673,7 @@
         <v>3.020628231962571</v>
       </c>
       <c r="D1554" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E1554">
         <v>2.677981100714109</v>
@@ -79711,43 +79717,43 @@
         <v>0</v>
       </c>
       <c r="B1555" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C1555">
-        <v>2.621340383975996</v>
+        <v>2.986632807697001</v>
       </c>
       <c r="D1555" t="s">
         <v>418</v>
       </c>
       <c r="E1555">
-        <v>2.852589664057424</v>
+        <v>2.787882087778429</v>
       </c>
       <c r="F1555">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1555">
-        <v>0.008298659616024004</v>
+        <v>0.008093367192302999</v>
       </c>
       <c r="H1555">
-        <v>0.008287410335942576</v>
+        <v>0.007652117912221571</v>
       </c>
       <c r="I1555">
-        <v>0.2312492800814274</v>
+        <v>0.1987507199185727</v>
       </c>
       <c r="J1555">
         <v>0.7132310593025135</v>
       </c>
       <c r="K1555">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="L1555">
-        <v>5.46</v>
+        <v>5.54</v>
       </c>
       <c r="M1555">
-        <v>3.81</v>
+        <v>3.41</v>
       </c>
       <c r="N1555">
-        <v>5.57</v>
+        <v>5.22</v>
       </c>
       <c r="O1555">
         <v>1</v>
@@ -79761,43 +79767,43 @@
         <v>1</v>
       </c>
       <c r="B1556" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C1556">
-        <v>2.986632807697001</v>
+        <v>3.033765118290027</v>
       </c>
       <c r="D1556" t="s">
-        <v>419</v>
+        <v>250</v>
       </c>
       <c r="E1556">
-        <v>2.787882087778429</v>
+        <v>2.790897428883052</v>
       </c>
       <c r="F1556">
         <v>-1</v>
       </c>
       <c r="G1556">
-        <v>0.008093367192302999</v>
+        <v>0.008126234881709974</v>
       </c>
       <c r="H1556">
-        <v>0.007652117912221571</v>
+        <v>0.007869102571116948</v>
       </c>
       <c r="I1556">
-        <v>0.1987507199185727</v>
+        <v>0.242867689406975</v>
       </c>
       <c r="J1556">
         <v>0.7132310593025135</v>
       </c>
       <c r="K1556">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="L1556">
-        <v>5.54</v>
+        <v>5.58</v>
       </c>
       <c r="M1556">
-        <v>3.41</v>
+        <v>3.56</v>
       </c>
       <c r="N1556">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1556">
         <v>1</v>
@@ -79811,43 +79817,43 @@
         <v>2</v>
       </c>
       <c r="B1557" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1557">
-        <v>3.033765118290027</v>
+        <v>2.603248337348258</v>
       </c>
       <c r="D1557" t="s">
-        <v>249</v>
+        <v>419</v>
       </c>
       <c r="E1557">
-        <v>2.790897428883052</v>
+        <v>2.438614586918088</v>
       </c>
       <c r="F1557">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1557">
-        <v>0.008126234881709974</v>
+        <v>0.006996751662651741</v>
       </c>
       <c r="H1557">
-        <v>0.007869102571116948</v>
+        <v>0.006361385413081912</v>
       </c>
       <c r="I1557">
-        <v>0.242867689406975</v>
+        <v>-0.1646337504301698</v>
       </c>
       <c r="J1557">
         <v>0.7132310593025135</v>
       </c>
       <c r="K1557">
-        <v>3.57</v>
+        <v>3.08</v>
       </c>
       <c r="L1557">
-        <v>5.58</v>
+        <v>4.8</v>
       </c>
       <c r="M1557">
-        <v>3.56</v>
+        <v>2.75</v>
       </c>
       <c r="N1557">
-        <v>5.33</v>
+        <v>4.4</v>
       </c>
       <c r="O1557">
         <v>1</v>
@@ -79864,40 +79870,40 @@
         <v>235</v>
       </c>
       <c r="C1558">
-        <v>2.603248337348258</v>
+        <v>2.561851405569183</v>
       </c>
       <c r="D1558" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E1558">
-        <v>2.384423791580862</v>
+        <v>2.438614586918088</v>
       </c>
       <c r="F1558">
         <v>1</v>
       </c>
       <c r="G1558">
-        <v>0.006996751662651741</v>
+        <v>0.006998148594430817</v>
       </c>
       <c r="H1558">
-        <v>0.006435576208419139</v>
+        <v>0.006361385413081912</v>
       </c>
       <c r="I1558">
-        <v>-0.2188245457673963</v>
+        <v>-0.1232368186510953</v>
       </c>
       <c r="J1558">
         <v>0.7132310593025135</v>
       </c>
       <c r="K1558">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="L1558">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="M1558">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="N1558">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="O1558">
         <v>1</v>
@@ -79914,40 +79920,40 @@
         <v>236</v>
       </c>
       <c r="C1559">
-        <v>2.561851405569183</v>
+        <v>2.548762238615736</v>
       </c>
       <c r="D1559" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E1559">
-        <v>2.384423791580862</v>
+        <v>2.438614586918088</v>
       </c>
       <c r="F1559">
         <v>1</v>
       </c>
       <c r="G1559">
-        <v>0.006998148594430817</v>
+        <v>0.006671237761384265</v>
       </c>
       <c r="H1559">
-        <v>0.006435576208419139</v>
+        <v>0.006361385413081912</v>
       </c>
       <c r="I1559">
-        <v>-0.1774276139883217</v>
+        <v>-0.1101476516976478</v>
       </c>
       <c r="J1559">
         <v>0.7132310593025135</v>
       </c>
       <c r="K1559">
-        <v>3.11</v>
+        <v>2.89</v>
       </c>
       <c r="L1559">
-        <v>4.78</v>
+        <v>4.61</v>
       </c>
       <c r="M1559">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="N1559">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="O1559">
         <v>1</v>
@@ -79958,116 +79964,116 @@
     </row>
     <row r="1560" spans="1:16">
       <c r="A1560" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1560" t="s">
         <v>237</v>
       </c>
       <c r="C1560">
-        <v>2.548762238615736</v>
+        <v>2.140622595222724</v>
       </c>
       <c r="D1560" t="s">
-        <v>420</v>
+        <v>230</v>
       </c>
       <c r="E1560">
-        <v>2.384423791580862</v>
+        <v>2.470162479018722</v>
       </c>
       <c r="F1560">
         <v>1</v>
       </c>
       <c r="G1560">
-        <v>0.006671237761384265</v>
+        <v>0.008359377404777275</v>
       </c>
       <c r="H1560">
-        <v>0.006435576208419139</v>
+        <v>0.008809837520981278</v>
       </c>
       <c r="I1560">
-        <v>-0.1643384470348743</v>
+        <v>0.3295398837959973</v>
       </c>
       <c r="J1560">
-        <v>0.7132310593025135</v>
+        <v>0.8637159457714654</v>
       </c>
       <c r="K1560">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="L1560">
-        <v>4.61</v>
+        <v>5.25</v>
       </c>
       <c r="M1560">
-        <v>2.84</v>
+        <v>3.67</v>
       </c>
       <c r="N1560">
-        <v>4.41</v>
+        <v>5.64</v>
       </c>
       <c r="O1560">
         <v>1</v>
       </c>
       <c r="P1560" t="s">
-        <v>229</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1561" spans="1:16">
       <c r="A1561" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1561" t="s">
         <v>238</v>
       </c>
       <c r="C1561">
-        <v>2.140622595222724</v>
+        <v>2.49970236281472</v>
       </c>
       <c r="D1561" t="s">
-        <v>230</v>
+        <v>418</v>
       </c>
       <c r="E1561">
-        <v>2.470162479018722</v>
+        <v>2.274728624919303</v>
       </c>
       <c r="F1561">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1561">
-        <v>0.008359377404777275</v>
+        <v>0.008960297637185281</v>
       </c>
       <c r="H1561">
-        <v>0.008809837520981278</v>
+        <v>0.008165271375080696</v>
       </c>
       <c r="I1561">
-        <v>0.3295398837959973</v>
+        <v>0.2249737378954171</v>
       </c>
       <c r="J1561">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1561">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="L1561">
-        <v>5.25</v>
+        <v>5.73</v>
       </c>
       <c r="M1561">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="N1561">
-        <v>5.64</v>
+        <v>5.22</v>
       </c>
       <c r="O1561">
         <v>1</v>
       </c>
       <c r="P1561" t="s">
-        <v>234</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1562" spans="1:16">
       <c r="A1562" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1562" t="s">
         <v>239</v>
       </c>
       <c r="C1562">
-        <v>2.49970236281472</v>
+        <v>2.515171233053583</v>
       </c>
       <c r="D1562" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E1562">
         <v>2.274728624919303</v>
@@ -80076,22 +80082,22 @@
         <v>-1</v>
       </c>
       <c r="G1562">
-        <v>0.008960297637185281</v>
+        <v>0.008664828766946417</v>
       </c>
       <c r="H1562">
         <v>0.008165271375080696</v>
       </c>
       <c r="I1562">
-        <v>0.2249737378954171</v>
+        <v>0.2404426081342805</v>
       </c>
       <c r="J1562">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1562">
-        <v>3.74</v>
+        <v>3.56</v>
       </c>
       <c r="L1562">
-        <v>5.73</v>
+        <v>5.59</v>
       </c>
       <c r="M1562">
         <v>3.41</v>
@@ -80103,48 +80109,48 @@
         <v>1</v>
       </c>
       <c r="P1562" t="s">
-        <v>234</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1563" spans="1:16">
       <c r="A1563" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1563" t="s">
         <v>240</v>
       </c>
       <c r="C1563">
-        <v>2.515171233053583</v>
+        <v>2.146091465461588</v>
       </c>
       <c r="D1563" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E1563">
-        <v>2.274728624919303</v>
+        <v>2.309277262750161</v>
       </c>
       <c r="F1563">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1563">
-        <v>0.008664828766946417</v>
+        <v>0.008053908534538412</v>
       </c>
       <c r="H1563">
-        <v>0.008165271375080696</v>
+        <v>0.008130722737249839</v>
       </c>
       <c r="I1563">
-        <v>0.2404426081342805</v>
+        <v>0.1631857972885733</v>
       </c>
       <c r="J1563">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1563">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="L1563">
-        <v>5.59</v>
+        <v>5.1</v>
       </c>
       <c r="M1563">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="N1563">
         <v>5.22</v>
@@ -80153,398 +80159,398 @@
         <v>1</v>
       </c>
       <c r="P1563" t="s">
-        <v>234</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1564" spans="1:16">
       <c r="A1564" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1564" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C1564">
-        <v>2.146091465461588</v>
+        <v>2.496534073595869</v>
       </c>
       <c r="D1564" t="s">
-        <v>421</v>
+        <v>250</v>
       </c>
       <c r="E1564">
-        <v>2.309277262750161</v>
+        <v>2.255171233053583</v>
       </c>
       <c r="F1564">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1564">
-        <v>0.008053908534538412</v>
+        <v>0.008663465926404131</v>
       </c>
       <c r="H1564">
-        <v>0.008130722737249839</v>
+        <v>0.008404828766946416</v>
       </c>
       <c r="I1564">
-        <v>0.1631857972885733</v>
+        <v>0.2413628405422856</v>
       </c>
       <c r="J1564">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1564">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="L1564">
-        <v>5.1</v>
+        <v>5.58</v>
       </c>
       <c r="M1564">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="N1564">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1564">
         <v>1</v>
       </c>
       <c r="P1564" t="s">
-        <v>234</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1565" spans="1:16">
       <c r="A1565" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1565" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1565">
-        <v>2.496534073595869</v>
+        <v>2.139754887023886</v>
       </c>
       <c r="D1565" t="s">
-        <v>249</v>
+        <v>421</v>
       </c>
       <c r="E1565">
-        <v>2.255171233053583</v>
+        <v>2.311117727566173</v>
       </c>
       <c r="F1565">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1565">
-        <v>0.008663465926404131</v>
+        <v>0.007460245112976114</v>
       </c>
       <c r="H1565">
-        <v>0.008404828766946416</v>
+        <v>0.007648882272433829</v>
       </c>
       <c r="I1565">
-        <v>0.2413628405422856</v>
+        <v>0.1713628405422862</v>
       </c>
       <c r="J1565">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1565">
-        <v>3.57</v>
+        <v>3.08</v>
       </c>
       <c r="L1565">
-        <v>5.58</v>
+        <v>4.8</v>
       </c>
       <c r="M1565">
-        <v>3.56</v>
+        <v>3.09</v>
       </c>
       <c r="N1565">
-        <v>5.33</v>
+        <v>4.98</v>
       </c>
       <c r="O1565">
         <v>1</v>
       </c>
       <c r="P1565" t="s">
-        <v>234</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1566" spans="1:16">
       <c r="A1566" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1566" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C1566">
-        <v>2.157471814073596</v>
+        <v>2.093843408650743</v>
       </c>
       <c r="D1566" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E1566">
-        <v>2.347029205939316</v>
+        <v>2.311117727566173</v>
       </c>
       <c r="F1566">
         <v>1</v>
       </c>
       <c r="G1566">
-        <v>0.007702528185926405</v>
+        <v>0.007466156591349258</v>
       </c>
       <c r="H1566">
-        <v>0.007632970794060685</v>
+        <v>0.007648882272433829</v>
       </c>
       <c r="I1566">
-        <v>0.1895573918657205</v>
+        <v>0.2172743189154294</v>
       </c>
       <c r="J1566">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1566">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="L1566">
-        <v>4.93</v>
+        <v>4.78</v>
       </c>
       <c r="M1566">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="N1566">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
       <c r="O1566">
         <v>1</v>
       </c>
       <c r="P1566" t="s">
-        <v>234</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1567" spans="1:16">
       <c r="A1567" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1567" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C1567">
-        <v>2.139754887023886</v>
+        <v>2.113860916720465</v>
       </c>
       <c r="D1567" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E1567">
-        <v>2.311117727566173</v>
+        <v>2.02478114912847</v>
       </c>
       <c r="F1567">
         <v>1</v>
       </c>
       <c r="G1567">
-        <v>0.007460245112976114</v>
+        <v>0.007106139083279535</v>
       </c>
       <c r="H1567">
-        <v>0.007648882272433829</v>
+        <v>0.006775218850871531</v>
       </c>
       <c r="I1567">
-        <v>0.1713628405422862</v>
+        <v>-0.08907976759199476</v>
       </c>
       <c r="J1567">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1567">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="L1567">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="M1567">
-        <v>3.09</v>
+        <v>2.75</v>
       </c>
       <c r="N1567">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="O1567">
         <v>1</v>
       </c>
       <c r="P1567" t="s">
-        <v>234</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1568" spans="1:16">
       <c r="A1568" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1568" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1568">
-        <v>2.093843408650743</v>
+        <v>1.99772260130418</v>
       </c>
       <c r="D1568" t="s">
-        <v>423</v>
+        <v>230</v>
       </c>
       <c r="E1568">
-        <v>2.311117727566173</v>
+        <v>2.324483874107317</v>
       </c>
       <c r="F1568">
         <v>1</v>
       </c>
       <c r="G1568">
-        <v>0.007466156591349258</v>
+        <v>0.00850227739869582</v>
       </c>
       <c r="H1568">
-        <v>0.007648882272433829</v>
+        <v>0.008955516125892682</v>
       </c>
       <c r="I1568">
-        <v>0.2172743189154294</v>
+        <v>0.3267612728031368</v>
       </c>
       <c r="J1568">
-        <v>0.8637159457714654</v>
+        <v>0.9034103885266167</v>
       </c>
       <c r="K1568">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="L1568">
-        <v>4.78</v>
+        <v>5.25</v>
       </c>
       <c r="M1568">
-        <v>3.09</v>
+        <v>3.67</v>
       </c>
       <c r="N1568">
-        <v>4.98</v>
+        <v>5.64</v>
       </c>
       <c r="O1568">
         <v>1</v>
       </c>
       <c r="P1568" t="s">
-        <v>234</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1569" spans="1:16">
       <c r="A1569" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1569" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C1569">
-        <v>2.113860916720465</v>
+        <v>2.351245146910454</v>
       </c>
       <c r="D1569" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E1569">
-        <v>1.957046714009039</v>
+        <v>2.139370575124237</v>
       </c>
       <c r="F1569">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1569">
-        <v>0.007106139083279535</v>
+        <v>0.009108754853089547</v>
       </c>
       <c r="H1569">
-        <v>0.006862953285990962</v>
+        <v>0.008300629424875762</v>
       </c>
       <c r="I1569">
-        <v>-0.1568142027114265</v>
+        <v>0.2118745717862169</v>
       </c>
       <c r="J1569">
-        <v>0.8637159457714654</v>
+        <v>0.9034103885266167</v>
       </c>
       <c r="K1569">
-        <v>2.89</v>
+        <v>3.74</v>
       </c>
       <c r="L1569">
-        <v>4.61</v>
+        <v>5.73</v>
       </c>
       <c r="M1569">
-        <v>2.84</v>
+        <v>3.41</v>
       </c>
       <c r="N1569">
-        <v>4.41</v>
+        <v>5.22</v>
       </c>
       <c r="O1569">
         <v>1</v>
       </c>
       <c r="P1569" t="s">
-        <v>234</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1570" spans="1:16">
       <c r="A1570" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1570" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C1570">
-        <v>1.99772260130418</v>
+        <v>2.373859016845244</v>
       </c>
       <c r="D1570" t="s">
-        <v>230</v>
+        <v>418</v>
       </c>
       <c r="E1570">
-        <v>2.324483874107317</v>
+        <v>2.139370575124237</v>
       </c>
       <c r="F1570">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1570">
-        <v>0.00850227739869582</v>
+        <v>0.008806140983154756</v>
       </c>
       <c r="H1570">
-        <v>0.008955516125892682</v>
+        <v>0.008300629424875762</v>
       </c>
       <c r="I1570">
-        <v>0.3267612728031368</v>
+        <v>0.2344884417210076</v>
       </c>
       <c r="J1570">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1570">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="L1570">
-        <v>5.25</v>
+        <v>5.59</v>
       </c>
       <c r="M1570">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="N1570">
-        <v>5.64</v>
+        <v>5.22</v>
       </c>
       <c r="O1570">
         <v>1</v>
       </c>
       <c r="P1570" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1571" spans="1:16">
       <c r="A1571" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1571" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C1571">
-        <v>2.351245146910454</v>
+        <v>2.010336471238971</v>
       </c>
       <c r="D1571" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E1571">
-        <v>2.139370575124237</v>
+        <v>2.175506990665301</v>
       </c>
       <c r="F1571">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1571">
-        <v>0.009108754853089547</v>
+        <v>0.00818966352876103</v>
       </c>
       <c r="H1571">
-        <v>0.008300629424875762</v>
+        <v>0.008264493009334699</v>
       </c>
       <c r="I1571">
-        <v>0.2118745717862169</v>
+        <v>0.1651705194263307</v>
       </c>
       <c r="J1571">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1571">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="L1571">
-        <v>5.73</v>
+        <v>5.1</v>
       </c>
       <c r="M1571">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="N1571">
         <v>5.22</v>
@@ -80553,951 +80559,951 @@
         <v>1</v>
       </c>
       <c r="P1571" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1572" spans="1:16">
       <c r="A1572" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1572" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C1572">
-        <v>2.373859016845244</v>
+        <v>2.354824912959979</v>
       </c>
       <c r="D1572" t="s">
-        <v>419</v>
+        <v>250</v>
       </c>
       <c r="E1572">
-        <v>2.139370575124237</v>
+        <v>2.113859016845244</v>
       </c>
       <c r="F1572">
         <v>-1</v>
       </c>
       <c r="G1572">
-        <v>0.008806140983154756</v>
+        <v>0.008805175087040021</v>
       </c>
       <c r="H1572">
-        <v>0.008300629424875762</v>
+        <v>0.008546140983154756</v>
       </c>
       <c r="I1572">
-        <v>0.2344884417210076</v>
+        <v>0.2409658961147341</v>
       </c>
       <c r="J1572">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1572">
+        <v>3.57</v>
+      </c>
+      <c r="L1572">
+        <v>5.58</v>
+      </c>
+      <c r="M1572">
         <v>3.56</v>
       </c>
-      <c r="L1572">
-        <v>5.59</v>
-      </c>
-      <c r="M1572">
-        <v>3.41</v>
-      </c>
       <c r="N1572">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1572">
         <v>1</v>
       </c>
       <c r="P1572" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1573" spans="1:16">
       <c r="A1573" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1573" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C1573">
-        <v>2.010336471238971</v>
+        <v>2.01749600333802</v>
       </c>
       <c r="D1573" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E1573">
-        <v>2.175506990665301</v>
+        <v>2.168120860600093</v>
       </c>
       <c r="F1573">
         <v>1</v>
       </c>
       <c r="G1573">
-        <v>0.00818966352876103</v>
+        <v>0.007582503996661979</v>
       </c>
       <c r="H1573">
-        <v>0.008264493009334699</v>
+        <v>0.007931879139399908</v>
       </c>
       <c r="I1573">
-        <v>0.1651705194263307</v>
+        <v>0.1506248572620721</v>
       </c>
       <c r="J1573">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1573">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="L1573">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="M1573">
-        <v>3.37</v>
+        <v>3.19</v>
       </c>
       <c r="N1573">
-        <v>5.22</v>
+        <v>5.05</v>
       </c>
       <c r="O1573">
         <v>1</v>
       </c>
       <c r="P1573" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1574" spans="1:16">
       <c r="A1574" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1574" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C1574">
-        <v>2.354824912959979</v>
+        <v>1.970393691682222</v>
       </c>
       <c r="D1574" t="s">
-        <v>249</v>
+        <v>422</v>
       </c>
       <c r="E1574">
-        <v>2.113859016845244</v>
+        <v>2.168120860600093</v>
       </c>
       <c r="F1574">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1574">
-        <v>0.008805175087040021</v>
+        <v>0.007589606308317778</v>
       </c>
       <c r="H1574">
-        <v>0.008546140983154756</v>
+        <v>0.007931879139399908</v>
       </c>
       <c r="I1574">
-        <v>0.2409658961147341</v>
+        <v>0.1977271689178703</v>
       </c>
       <c r="J1574">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1574">
-        <v>3.57</v>
+        <v>3.11</v>
       </c>
       <c r="L1574">
-        <v>5.58</v>
+        <v>4.78</v>
       </c>
       <c r="M1574">
-        <v>3.56</v>
+        <v>3.19</v>
       </c>
       <c r="N1574">
-        <v>5.33</v>
+        <v>5.05</v>
       </c>
       <c r="O1574">
         <v>1</v>
       </c>
       <c r="P1574" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1575" spans="1:16">
       <c r="A1575" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1575" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C1575">
-        <v>2.027097744042107</v>
+        <v>1.999143977158078</v>
       </c>
       <c r="D1575" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E1575">
-        <v>2.225564211108553</v>
+        <v>1.915621431551804</v>
       </c>
       <c r="F1575">
         <v>1</v>
       </c>
       <c r="G1575">
-        <v>0.008332902255957892</v>
+        <v>0.007220856022841922</v>
       </c>
       <c r="H1575">
-        <v>0.007754435788891447</v>
+        <v>0.006884378568448197</v>
       </c>
       <c r="I1575">
-        <v>0.1984664670664458</v>
+        <v>-0.08352254560627381</v>
       </c>
       <c r="J1575">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1575">
-        <v>3.49</v>
+        <v>2.89</v>
       </c>
       <c r="L1575">
-        <v>5.18</v>
+        <v>4.61</v>
       </c>
       <c r="M1575">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="N1575">
-        <v>4.99</v>
+        <v>4.4</v>
       </c>
       <c r="O1575">
         <v>1</v>
       </c>
       <c r="P1575" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1576" spans="1:16">
       <c r="A1576" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1576" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C1576">
-        <v>2.03005265282956</v>
+        <v>1.893712084063664</v>
       </c>
       <c r="D1576" t="s">
-        <v>422</v>
+        <v>230</v>
       </c>
       <c r="E1576">
-        <v>2.225564211108553</v>
+        <v>2.218450930142679</v>
       </c>
       <c r="F1576">
         <v>1</v>
       </c>
       <c r="G1576">
-        <v>0.007829947347170439</v>
+        <v>0.008606287915936336</v>
       </c>
       <c r="H1576">
-        <v>0.007754435788891447</v>
+        <v>0.009061549069857322</v>
       </c>
       <c r="I1576">
-        <v>0.195511558278993</v>
+        <v>0.3247388460790153</v>
       </c>
       <c r="J1576">
-        <v>0.9034103885266167</v>
+        <v>0.9323021988712045</v>
       </c>
       <c r="K1576">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="L1576">
-        <v>4.93</v>
+        <v>5.25</v>
       </c>
       <c r="M1576">
-        <v>3.06</v>
+        <v>3.67</v>
       </c>
       <c r="N1576">
-        <v>4.99</v>
+        <v>5.64</v>
       </c>
       <c r="O1576">
         <v>1</v>
       </c>
       <c r="P1576" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1577" spans="1:16">
       <c r="A1577" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B1577" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C1577">
-        <v>2.01749600333802</v>
+        <v>2.243189776221695</v>
       </c>
       <c r="D1577" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="E1577">
-        <v>2.188461899452755</v>
+        <v>2.040849501849193</v>
       </c>
       <c r="F1577">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1577">
-        <v>0.007582503996661979</v>
+        <v>0.009216810223778306</v>
       </c>
       <c r="H1577">
-        <v>0.007771538100547246</v>
+        <v>0.008399150498150806</v>
       </c>
       <c r="I1577">
-        <v>0.1709658961147347</v>
+        <v>0.2023402743725029</v>
       </c>
       <c r="J1577">
-        <v>0.9034103885266167</v>
+        <v>0.9323021988712045</v>
       </c>
       <c r="K1577">
-        <v>3.08</v>
+        <v>3.74</v>
       </c>
       <c r="L1577">
-        <v>4.8</v>
+        <v>5.73</v>
       </c>
       <c r="M1577">
-        <v>3.09</v>
+        <v>3.41</v>
       </c>
       <c r="N1577">
-        <v>4.98</v>
+        <v>5.22</v>
       </c>
       <c r="O1577">
         <v>1</v>
       </c>
       <c r="P1577" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1578" spans="1:16">
       <c r="A1578" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B1578" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C1578">
-        <v>1.970393691682222</v>
+        <v>2.271004172018512</v>
       </c>
       <c r="D1578" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="E1578">
-        <v>2.188461899452755</v>
+        <v>2.040849501849193</v>
       </c>
       <c r="F1578">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1578">
-        <v>0.007589606308317778</v>
+        <v>0.008908995827981488</v>
       </c>
       <c r="H1578">
-        <v>0.007771538100547246</v>
+        <v>0.008399150498150806</v>
       </c>
       <c r="I1578">
-        <v>0.2180682077705329</v>
+        <v>0.2301546701693193</v>
       </c>
       <c r="J1578">
-        <v>0.9034103885266167</v>
+        <v>0.9323021988712045</v>
       </c>
       <c r="K1578">
-        <v>3.11</v>
+        <v>3.56</v>
       </c>
       <c r="L1578">
-        <v>4.78</v>
+        <v>5.59</v>
       </c>
       <c r="M1578">
-        <v>3.09</v>
+        <v>3.41</v>
       </c>
       <c r="N1578">
-        <v>4.98</v>
+        <v>5.22</v>
       </c>
       <c r="O1578">
         <v>1</v>
       </c>
       <c r="P1578" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1579" spans="1:16">
       <c r="A1579" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B1579" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C1579">
-        <v>1.999143977158078</v>
+        <v>1.911526479860481</v>
       </c>
       <c r="D1579" t="s">
         <v>420</v>
       </c>
       <c r="E1579">
-        <v>1.844314496584409</v>
+        <v>2.078141589804041</v>
       </c>
       <c r="F1579">
         <v>1</v>
       </c>
       <c r="G1579">
-        <v>0.007220856022841922</v>
+        <v>0.008288473520139519</v>
       </c>
       <c r="H1579">
-        <v>0.006975685503415592</v>
+        <v>0.008361858410195959</v>
       </c>
       <c r="I1579">
-        <v>-0.1548294805736692</v>
+        <v>0.1666151099435602</v>
       </c>
       <c r="J1579">
-        <v>0.9034103885266167</v>
+        <v>0.9323021988712045</v>
       </c>
       <c r="K1579">
-        <v>2.89</v>
+        <v>3.42</v>
       </c>
       <c r="L1579">
-        <v>4.61</v>
+        <v>5.1</v>
       </c>
       <c r="M1579">
-        <v>2.84</v>
+        <v>3.37</v>
       </c>
       <c r="N1579">
-        <v>4.41</v>
+        <v>5.22</v>
       </c>
       <c r="O1579">
         <v>1</v>
       </c>
       <c r="P1579" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1580" spans="1:16">
       <c r="A1580" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1580" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C1580">
-        <v>1.893712084063664</v>
+        <v>2.2516811500298</v>
       </c>
       <c r="D1580" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E1580">
-        <v>2.218450930142679</v>
+        <v>2.011004172018512</v>
       </c>
       <c r="F1580">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1580">
-        <v>0.008606287915936336</v>
+        <v>0.0089083188499702</v>
       </c>
       <c r="H1580">
-        <v>0.009061549069857322</v>
+        <v>0.008648995827981487</v>
       </c>
       <c r="I1580">
-        <v>0.3247388460790153</v>
+        <v>0.2406769780112881</v>
       </c>
       <c r="J1580">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1580">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="L1580">
-        <v>5.25</v>
+        <v>5.58</v>
       </c>
       <c r="M1580">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="N1580">
-        <v>5.64</v>
+        <v>5.33</v>
       </c>
       <c r="O1580">
         <v>1</v>
       </c>
       <c r="P1580" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1581" spans="1:16">
       <c r="A1581" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B1581" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C1581">
-        <v>2.243189776221695</v>
+        <v>1.926265325939496</v>
       </c>
       <c r="D1581" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E1581">
-        <v>2.040849501849193</v>
+        <v>2.076787633781465</v>
       </c>
       <c r="F1581">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1581">
-        <v>0.009216810223778306</v>
+        <v>0.008433734674060504</v>
       </c>
       <c r="H1581">
-        <v>0.008399150498150806</v>
+        <v>0.008323212366218535</v>
       </c>
       <c r="I1581">
-        <v>0.2023402743725029</v>
+        <v>0.1505223078419693</v>
       </c>
       <c r="J1581">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1581">
-        <v>3.74</v>
+        <v>3.49</v>
       </c>
       <c r="L1581">
-        <v>5.73</v>
+        <v>5.18</v>
       </c>
       <c r="M1581">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="N1581">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="O1581">
         <v>1</v>
       </c>
       <c r="P1581" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1582" spans="1:16">
       <c r="A1582" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B1582" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C1582">
-        <v>2.271004172018512</v>
+        <v>1.880540161510555</v>
       </c>
       <c r="D1582" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E1582">
-        <v>2.040849501849193</v>
+        <v>2.075955985600858</v>
       </c>
       <c r="F1582">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1582">
-        <v>0.008908995827981488</v>
+        <v>0.007679459838489447</v>
       </c>
       <c r="H1582">
-        <v>0.008399150498150806</v>
+        <v>0.008024044014399141</v>
       </c>
       <c r="I1582">
-        <v>0.2301546701693193</v>
+        <v>0.1954158240903032</v>
       </c>
       <c r="J1582">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1582">
-        <v>3.56</v>
+        <v>3.11</v>
       </c>
       <c r="L1582">
-        <v>5.59</v>
+        <v>4.78</v>
       </c>
       <c r="M1582">
-        <v>3.41</v>
+        <v>3.19</v>
       </c>
       <c r="N1582">
-        <v>5.22</v>
+        <v>5.05</v>
       </c>
       <c r="O1582">
         <v>1</v>
       </c>
       <c r="P1582" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1583" spans="1:16">
       <c r="A1583" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1583" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C1583">
-        <v>1.911526479860481</v>
+        <v>1.915646645262219</v>
       </c>
       <c r="D1583" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E1583">
-        <v>2.154234391905633</v>
+        <v>1.836168953104188</v>
       </c>
       <c r="F1583">
         <v>1</v>
       </c>
       <c r="G1583">
-        <v>0.008288473520139519</v>
+        <v>0.007304353354737781</v>
       </c>
       <c r="H1583">
-        <v>0.008605765608094368</v>
+        <v>0.006963831046895813</v>
       </c>
       <c r="I1583">
-        <v>0.2427079120451521</v>
+        <v>-0.07947769215803113</v>
       </c>
       <c r="J1583">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1583">
-        <v>3.42</v>
+        <v>2.89</v>
       </c>
       <c r="L1583">
-        <v>5.1</v>
+        <v>4.61</v>
       </c>
       <c r="M1583">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="N1583">
-        <v>5.38</v>
+        <v>4.4</v>
       </c>
       <c r="O1583">
         <v>1</v>
       </c>
       <c r="P1583" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1584" spans="1:16">
       <c r="A1584" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1584" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C1584">
-        <v>2.2516811500298</v>
+        <v>1.792368417943001</v>
       </c>
       <c r="D1584" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="E1584">
-        <v>2.011004172018512</v>
+        <v>2.115136692736337</v>
       </c>
       <c r="F1584">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1584">
-        <v>0.0089083188499702</v>
+        <v>0.008707631582056998</v>
       </c>
       <c r="H1584">
-        <v>0.008648995827981487</v>
+        <v>0.009164863307263663</v>
       </c>
       <c r="I1584">
-        <v>0.2406769780112881</v>
+        <v>0.322768274793336</v>
       </c>
       <c r="J1584">
-        <v>0.9323021988712045</v>
+        <v>0.9604532172380553</v>
       </c>
       <c r="K1584">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="L1584">
-        <v>5.58</v>
+        <v>5.25</v>
       </c>
       <c r="M1584">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="N1584">
-        <v>5.33</v>
+        <v>5.64</v>
       </c>
       <c r="O1584">
         <v>1</v>
       </c>
       <c r="P1584" t="s">
-        <v>542</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1585" spans="1:16">
       <c r="A1585" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1585" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C1585">
-        <v>1.926265325939496</v>
+        <v>2.137904967529674</v>
       </c>
       <c r="D1585" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E1585">
-        <v>2.137155271454115</v>
+        <v>1.944854529218231</v>
       </c>
       <c r="F1585">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1585">
-        <v>0.008433734674060504</v>
+        <v>0.009322095032470328</v>
       </c>
       <c r="H1585">
-        <v>0.007842844728545887</v>
+        <v>0.008495145470781769</v>
       </c>
       <c r="I1585">
-        <v>0.2108899455146189</v>
+        <v>0.1930504383114426</v>
       </c>
       <c r="J1585">
-        <v>0.9323021988712045</v>
+        <v>0.9604532172380553</v>
       </c>
       <c r="K1585">
-        <v>3.49</v>
+        <v>3.74</v>
       </c>
       <c r="L1585">
-        <v>5.18</v>
+        <v>5.73</v>
       </c>
       <c r="M1585">
-        <v>3.06</v>
+        <v>3.41</v>
       </c>
       <c r="N1585">
-        <v>4.99</v>
+        <v>5.22</v>
       </c>
       <c r="O1585">
         <v>1</v>
       </c>
       <c r="P1585" t="s">
-        <v>542</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1586" spans="1:16">
       <c r="A1586" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B1586" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C1586">
-        <v>1.937309941623433</v>
+        <v>2.170786546632523</v>
       </c>
       <c r="D1586" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E1586">
-        <v>2.137155271454115</v>
+        <v>1.944854529218231</v>
       </c>
       <c r="F1586">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1586">
-        <v>0.007922690058376567</v>
+        <v>0.009009213453367476</v>
       </c>
       <c r="H1586">
-        <v>0.007842844728545887</v>
+        <v>0.008495145470781769</v>
       </c>
       <c r="I1586">
-        <v>0.1998453298306813</v>
+        <v>0.225932017414292</v>
       </c>
       <c r="J1586">
-        <v>0.9323021988712045</v>
+        <v>0.9604532172380553</v>
       </c>
       <c r="K1586">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="L1586">
-        <v>4.93</v>
+        <v>5.59</v>
       </c>
       <c r="M1586">
-        <v>3.06</v>
+        <v>3.41</v>
       </c>
       <c r="N1586">
-        <v>4.99</v>
+        <v>5.22</v>
       </c>
       <c r="O1586">
         <v>1</v>
       </c>
       <c r="P1586" t="s">
-        <v>542</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1587" spans="1:16">
       <c r="A1587" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1587" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C1587">
-        <v>1.92850922747669</v>
+        <v>1.81524999704585</v>
       </c>
       <c r="D1587" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E1587">
-        <v>2.099186205487979</v>
+        <v>1.983272657907753</v>
       </c>
       <c r="F1587">
         <v>1</v>
       </c>
       <c r="G1587">
-        <v>0.00767149077252331</v>
+        <v>0.008384750002954149</v>
       </c>
       <c r="H1587">
-        <v>0.007860813794512023</v>
+        <v>0.008456727342092248</v>
       </c>
       <c r="I1587">
-        <v>0.1706769780112887</v>
+        <v>0.1680226608619027</v>
       </c>
       <c r="J1587">
-        <v>0.9323021988712045</v>
+        <v>0.9604532172380553</v>
       </c>
       <c r="K1587">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="L1587">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="M1587">
-        <v>3.09</v>
+        <v>3.37</v>
       </c>
       <c r="N1587">
-        <v>4.98</v>
+        <v>5.22</v>
       </c>
       <c r="O1587">
         <v>1</v>
       </c>
       <c r="P1587" t="s">
-        <v>542</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1588" spans="1:16">
       <c r="A1588" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1588" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C1588">
-        <v>1.880540161510555</v>
+        <v>2.151182014460143</v>
       </c>
       <c r="D1588" t="s">
-        <v>423</v>
+        <v>250</v>
       </c>
       <c r="E1588">
-        <v>2.099186205487979</v>
+        <v>1.910786546632523</v>
       </c>
       <c r="F1588">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1588">
-        <v>0.007679459838489447</v>
+        <v>0.009008817985539857</v>
       </c>
       <c r="H1588">
-        <v>0.007860813794512023</v>
+        <v>0.008749213453367478</v>
       </c>
       <c r="I1588">
-        <v>0.218646043977424</v>
+        <v>0.2403954678276197</v>
       </c>
       <c r="J1588">
-        <v>0.9323021988712045</v>
+        <v>0.9604532172380553</v>
       </c>
       <c r="K1588">
-        <v>3.11</v>
+        <v>3.57</v>
       </c>
       <c r="L1588">
-        <v>4.78</v>
+        <v>5.58</v>
       </c>
       <c r="M1588">
-        <v>3.09</v>
+        <v>3.56</v>
       </c>
       <c r="N1588">
-        <v>4.98</v>
+        <v>5.33</v>
       </c>
       <c r="O1588">
         <v>1</v>
       </c>
       <c r="P1588" t="s">
-        <v>542</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1589" spans="1:16">
       <c r="A1589" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B1589" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C1589">
-        <v>1.915646645262219</v>
+        <v>1.828018271839186</v>
       </c>
       <c r="D1589" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E1589">
-        <v>1.76226175520578</v>
+        <v>1.982481722252515</v>
       </c>
       <c r="F1589">
         <v>1</v>
       </c>
       <c r="G1589">
-        <v>0.007304353354737781</v>
+        <v>0.008531981728160814</v>
       </c>
       <c r="H1589">
-        <v>0.007057738244794221</v>
+        <v>0.008417518277747487</v>
       </c>
       <c r="I1589">
-        <v>-0.1533848900564396</v>
+        <v>0.1544634504133282</v>
       </c>
       <c r="J1589">
-        <v>0.9323021988712045</v>
+        <v>0.9604532172380553</v>
       </c>
       <c r="K1589">
-        <v>2.89</v>
+        <v>3.49</v>
       </c>
       <c r="L1589">
-        <v>4.61</v>
+        <v>5.18</v>
       </c>
       <c r="M1589">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="N1589">
-        <v>4.41</v>
+        <v>5.2</v>
       </c>
       <c r="O1589">
         <v>1</v>
       </c>
       <c r="P1589" t="s">
-        <v>542</v>
+        <v>417</v>
       </c>
     </row>
     <row r="1590" spans="1:16">
       <c r="A1590" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1590" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C1590">
-        <v>1.792368417943001</v>
+        <v>1.846945172665842</v>
       </c>
       <c r="D1590" t="s">
-        <v>230</v>
+        <v>424</v>
       </c>
       <c r="E1590">
-        <v>2.115136692736337</v>
+        <v>2.051013155251551</v>
       </c>
       <c r="F1590">
         <v>1</v>
       </c>
       <c r="G1590">
-        <v>0.008707631582056998</v>
+        <v>0.008013054827334156</v>
       </c>
       <c r="H1590">
-        <v>0.009164863307263663</v>
+        <v>0.007928986844748449</v>
       </c>
       <c r="I1590">
-        <v>0.322768274793336</v>
+        <v>0.2040679825857086</v>
       </c>
       <c r="J1590">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1590">
-        <v>3.6</v>
+        <v>3.21</v>
       </c>
       <c r="L1590">
-        <v>5.25</v>
+        <v>4.93</v>
       </c>
       <c r="M1590">
-        <v>3.67</v>
+        <v>3.06</v>
       </c>
       <c r="N1590">
-        <v>5.64</v>
+        <v>4.99</v>
       </c>
       <c r="O1590">
         <v>1</v>
@@ -81508,46 +81514,46 @@
     </row>
     <row r="1591" spans="1:16">
       <c r="A1591" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B1591" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C1591">
-        <v>2.137904967529674</v>
+        <v>1.792990494389648</v>
       </c>
       <c r="D1591" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E1591">
-        <v>1.944854529218231</v>
+        <v>1.986154237010604</v>
       </c>
       <c r="F1591">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1591">
-        <v>0.009322095032470328</v>
+        <v>0.007767009505610351</v>
       </c>
       <c r="H1591">
-        <v>0.008495145470781769</v>
+        <v>0.008113845762989395</v>
       </c>
       <c r="I1591">
-        <v>0.1930504383114426</v>
+        <v>0.1931637426209551</v>
       </c>
       <c r="J1591">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1591">
-        <v>3.74</v>
+        <v>3.11</v>
       </c>
       <c r="L1591">
-        <v>5.73</v>
+        <v>4.78</v>
       </c>
       <c r="M1591">
-        <v>3.41</v>
+        <v>3.19</v>
       </c>
       <c r="N1591">
-        <v>5.22</v>
+        <v>5.05</v>
       </c>
       <c r="O1591">
         <v>1</v>
@@ -81558,46 +81564,46 @@
     </row>
     <row r="1592" spans="1:16">
       <c r="A1592" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B1592" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C1592">
-        <v>2.170786546632523</v>
+        <v>1.83429020218202</v>
       </c>
       <c r="D1592" t="s">
         <v>419</v>
       </c>
       <c r="E1592">
-        <v>1.944854529218231</v>
+        <v>1.758753652595348</v>
       </c>
       <c r="F1592">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1592">
-        <v>0.009009213453367476</v>
+        <v>0.007385709797817981</v>
       </c>
       <c r="H1592">
-        <v>0.008495145470781769</v>
+        <v>0.007041246347404653</v>
       </c>
       <c r="I1592">
-        <v>0.225932017414292</v>
+        <v>-0.07553654958667222</v>
       </c>
       <c r="J1592">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1592">
-        <v>3.56</v>
+        <v>2.89</v>
       </c>
       <c r="L1592">
-        <v>5.59</v>
+        <v>4.61</v>
       </c>
       <c r="M1592">
-        <v>3.41</v>
+        <v>2.75</v>
       </c>
       <c r="N1592">
-        <v>5.22</v>
+        <v>4.4</v>
       </c>
       <c r="O1592">
         <v>1</v>
@@ -81608,1240 +81614,1240 @@
     </row>
     <row r="1593" spans="1:16">
       <c r="A1593" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1593" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C1593">
-        <v>1.81524999704585</v>
+        <v>1.676370302057997</v>
       </c>
       <c r="D1593" t="s">
-        <v>424</v>
+        <v>230</v>
       </c>
       <c r="E1593">
-        <v>2.056831868356328</v>
+        <v>1.996883057931346</v>
       </c>
       <c r="F1593">
         <v>1</v>
       </c>
       <c r="G1593">
-        <v>0.008384750002954149</v>
+        <v>0.008823629697942004</v>
       </c>
       <c r="H1593">
-        <v>0.008703168131643672</v>
+        <v>0.009283116942068651</v>
       </c>
       <c r="I1593">
-        <v>0.241581871310478</v>
+        <v>0.3205127558733496</v>
       </c>
       <c r="J1593">
-        <v>0.9604532172380553</v>
+        <v>0.9926749160950009</v>
       </c>
       <c r="K1593">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="L1593">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="M1593">
-        <v>3.46</v>
+        <v>3.67</v>
       </c>
       <c r="N1593">
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="O1593">
         <v>1</v>
       </c>
       <c r="P1593" t="s">
-        <v>417</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1594" spans="1:16">
       <c r="A1594" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1594" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C1594">
-        <v>2.151182014460143</v>
+        <v>1.746736556253247</v>
       </c>
       <c r="D1594" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E1594">
-        <v>1.910786546632523</v>
+        <v>1.967102810448496</v>
       </c>
       <c r="F1594">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1594">
-        <v>0.009008817985539857</v>
+        <v>0.008993263443746754</v>
       </c>
       <c r="H1594">
-        <v>0.008749213453367478</v>
+        <v>0.009312897189551504</v>
       </c>
       <c r="I1594">
-        <v>0.2403954678276197</v>
+        <v>0.2203662541952491</v>
       </c>
       <c r="J1594">
-        <v>0.9604532172380553</v>
+        <v>0.9926749160950009</v>
       </c>
       <c r="K1594">
-        <v>3.57</v>
+        <v>3.65</v>
       </c>
       <c r="L1594">
-        <v>5.58</v>
+        <v>5.37</v>
       </c>
       <c r="M1594">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N1594">
-        <v>5.33</v>
+        <v>5.64</v>
       </c>
       <c r="O1594">
         <v>1</v>
       </c>
       <c r="P1594" t="s">
-        <v>417</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1595" spans="1:16">
       <c r="A1595" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1595" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C1595">
-        <v>1.828018271839186</v>
+        <v>2.017395813804697</v>
       </c>
       <c r="D1595" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E1595">
-        <v>2.051013155251551</v>
+        <v>1.834978536116047</v>
       </c>
       <c r="F1595">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1595">
-        <v>0.008531981728160814</v>
+        <v>0.009442604186195304</v>
       </c>
       <c r="H1595">
-        <v>0.007928986844748449</v>
+        <v>0.008605021463883953</v>
       </c>
       <c r="I1595">
-        <v>0.2229948834123645</v>
+        <v>0.1824172776886503</v>
       </c>
       <c r="J1595">
-        <v>0.9604532172380553</v>
+        <v>0.9926749160950009</v>
       </c>
       <c r="K1595">
-        <v>3.49</v>
+        <v>3.74</v>
       </c>
       <c r="L1595">
-        <v>5.18</v>
+        <v>5.73</v>
       </c>
       <c r="M1595">
-        <v>3.06</v>
+        <v>3.41</v>
       </c>
       <c r="N1595">
-        <v>4.99</v>
+        <v>5.22</v>
       </c>
       <c r="O1595">
         <v>1</v>
       </c>
       <c r="P1595" t="s">
-        <v>417</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1596" spans="1:16">
       <c r="A1596" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1596" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C1596">
-        <v>1.853668125735373</v>
+        <v>2.056077298701796</v>
       </c>
       <c r="D1596" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E1596">
-        <v>2.051013155251551</v>
+        <v>1.834978536116047</v>
       </c>
       <c r="F1596">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1596">
-        <v>0.008346331874264626</v>
+        <v>0.009123922701298205</v>
       </c>
       <c r="H1596">
-        <v>0.007928986844748449</v>
+        <v>0.008605021463883953</v>
       </c>
       <c r="I1596">
-        <v>0.1973450295161783</v>
+        <v>0.2210987625857497</v>
       </c>
       <c r="J1596">
-        <v>0.9604532172380553</v>
+        <v>0.9926749160950009</v>
       </c>
       <c r="K1596">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="L1596">
-        <v>5.1</v>
+        <v>5.59</v>
       </c>
       <c r="M1596">
-        <v>3.06</v>
+        <v>3.41</v>
       </c>
       <c r="N1596">
-        <v>4.99</v>
+        <v>5.22</v>
       </c>
       <c r="O1596">
         <v>1</v>
       </c>
       <c r="P1596" t="s">
-        <v>417</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1597" spans="1:16">
       <c r="A1597" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1597" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C1597">
-        <v>1.846945172665842</v>
+        <v>1.705051786955097</v>
       </c>
       <c r="D1597" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E1597">
-        <v>2.051013155251551</v>
+        <v>1.874685532759846</v>
       </c>
       <c r="F1597">
         <v>1</v>
       </c>
       <c r="G1597">
-        <v>0.008013054827334156</v>
+        <v>0.008494948213044903</v>
       </c>
       <c r="H1597">
-        <v>0.007928986844748449</v>
+        <v>0.008565314467240154</v>
       </c>
       <c r="I1597">
-        <v>0.2040679825857086</v>
+        <v>0.1696337458047497</v>
       </c>
       <c r="J1597">
-        <v>0.9604532172380553</v>
+        <v>0.9926749160950009</v>
       </c>
       <c r="K1597">
-        <v>3.21</v>
+        <v>3.42</v>
       </c>
       <c r="L1597">
-        <v>4.93</v>
+        <v>5.1</v>
       </c>
       <c r="M1597">
-        <v>3.06</v>
+        <v>3.37</v>
       </c>
       <c r="N1597">
-        <v>4.99</v>
+        <v>5.22</v>
       </c>
       <c r="O1597">
         <v>1</v>
       </c>
       <c r="P1597" t="s">
-        <v>417</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1598" spans="1:16">
       <c r="A1598" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1598" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C1598">
-        <v>1.792990494389648</v>
+        <v>2.036150549540847</v>
       </c>
       <c r="D1598" t="s">
-        <v>423</v>
+        <v>250</v>
       </c>
       <c r="E1598">
-        <v>2.01219955873441</v>
+        <v>1.796077298701797</v>
       </c>
       <c r="F1598">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1598">
-        <v>0.007767009505610351</v>
+        <v>0.009123849450459152</v>
       </c>
       <c r="H1598">
-        <v>0.007947800441265591</v>
+        <v>0.008863922701298205</v>
       </c>
       <c r="I1598">
-        <v>0.2192090643447613</v>
+        <v>0.2400732508390506</v>
       </c>
       <c r="J1598">
-        <v>0.9604532172380553</v>
+        <v>0.9926749160950009</v>
       </c>
       <c r="K1598">
-        <v>3.11</v>
+        <v>3.57</v>
       </c>
       <c r="L1598">
-        <v>4.78</v>
+        <v>5.58</v>
       </c>
       <c r="M1598">
-        <v>3.09</v>
+        <v>3.56</v>
       </c>
       <c r="N1598">
-        <v>4.98</v>
+        <v>5.33</v>
       </c>
       <c r="O1598">
         <v>1</v>
       </c>
       <c r="P1598" t="s">
-        <v>417</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1599" spans="1:16">
       <c r="A1599" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1599" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C1599">
-        <v>1.83429020218202</v>
+        <v>1.715564542828446</v>
       </c>
       <c r="D1599" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E1599">
-        <v>1.682312863043923</v>
+        <v>1.874539031081747</v>
       </c>
       <c r="F1599">
         <v>1</v>
       </c>
       <c r="G1599">
-        <v>0.007385709797817981</v>
+        <v>0.008644435457171553</v>
       </c>
       <c r="H1599">
-        <v>0.007137687136956078</v>
+        <v>0.008525460968918253</v>
       </c>
       <c r="I1599">
-        <v>-0.1519773391380972</v>
+        <v>0.1589744882533006</v>
       </c>
       <c r="J1599">
-        <v>0.9604532172380553</v>
+        <v>0.9926749160950009</v>
       </c>
       <c r="K1599">
-        <v>2.89</v>
+        <v>3.49</v>
       </c>
       <c r="L1599">
-        <v>4.61</v>
+        <v>5.18</v>
       </c>
       <c r="M1599">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="N1599">
-        <v>4.41</v>
+        <v>5.2</v>
       </c>
       <c r="O1599">
         <v>1</v>
       </c>
       <c r="P1599" t="s">
-        <v>417</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1600" spans="1:16">
       <c r="A1600" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1600" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C1600">
-        <v>1.676370302057997</v>
+        <v>1.744758783598896</v>
       </c>
       <c r="D1600" t="s">
-        <v>230</v>
+        <v>423</v>
       </c>
       <c r="E1600">
-        <v>1.996883057931346</v>
+        <v>1.874539031081747</v>
       </c>
       <c r="F1600">
         <v>1</v>
       </c>
       <c r="G1600">
-        <v>0.008823629697942004</v>
+        <v>0.008455241216401102</v>
       </c>
       <c r="H1600">
-        <v>0.009283116942068651</v>
+        <v>0.008525460968918253</v>
       </c>
       <c r="I1600">
-        <v>0.3205127558733496</v>
+        <v>0.1297802474828504</v>
       </c>
       <c r="J1600">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1600">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="L1600">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="M1600">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="N1600">
-        <v>5.64</v>
+        <v>5.2</v>
       </c>
       <c r="O1600">
         <v>1</v>
       </c>
       <c r="P1600" t="s">
-        <v>418</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1601" spans="1:16">
       <c r="A1601" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B1601" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C1601">
-        <v>1.746736556253247</v>
+        <v>1.743513519335047</v>
       </c>
       <c r="D1601" t="s">
-        <v>231</v>
+        <v>424</v>
       </c>
       <c r="E1601">
-        <v>1.967102810448496</v>
+        <v>1.952414756749298</v>
       </c>
       <c r="F1601">
         <v>1</v>
       </c>
       <c r="G1601">
-        <v>0.008993263443746754</v>
+        <v>0.008116486480664953</v>
       </c>
       <c r="H1601">
-        <v>0.009312897189551504</v>
+        <v>0.008027585243250703</v>
       </c>
       <c r="I1601">
-        <v>0.2203662541952491</v>
+        <v>0.2089012374142509</v>
       </c>
       <c r="J1601">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1601">
-        <v>3.65</v>
+        <v>3.21</v>
       </c>
       <c r="L1601">
-        <v>5.37</v>
+        <v>4.93</v>
       </c>
       <c r="M1601">
-        <v>3.7</v>
+        <v>3.06</v>
       </c>
       <c r="N1601">
-        <v>5.64</v>
+        <v>4.99</v>
       </c>
       <c r="O1601">
         <v>1</v>
       </c>
       <c r="P1601" t="s">
-        <v>418</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1602" spans="1:16">
       <c r="A1602" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B1602" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C1602">
-        <v>2.017395813804697</v>
+        <v>1.692781010944548</v>
       </c>
       <c r="D1602" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E1602">
-        <v>1.834978536116047</v>
+        <v>1.883367017656947</v>
       </c>
       <c r="F1602">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1602">
-        <v>0.009442604186195304</v>
+        <v>0.007867218989055453</v>
       </c>
       <c r="H1602">
-        <v>0.008605021463883953</v>
+        <v>0.008216632982343054</v>
       </c>
       <c r="I1602">
-        <v>0.1824172776886503</v>
+        <v>0.1905860067123992</v>
       </c>
       <c r="J1602">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1602">
-        <v>3.74</v>
+        <v>3.11</v>
       </c>
       <c r="L1602">
-        <v>5.73</v>
+        <v>4.78</v>
       </c>
       <c r="M1602">
-        <v>3.41</v>
+        <v>3.19</v>
       </c>
       <c r="N1602">
-        <v>5.22</v>
+        <v>5.05</v>
       </c>
       <c r="O1602">
         <v>1</v>
       </c>
       <c r="P1602" t="s">
-        <v>418</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1603" spans="1:16">
       <c r="A1603" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B1603" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C1603">
-        <v>2.056077298701796</v>
+        <v>1.741169492485448</v>
       </c>
       <c r="D1603" t="s">
         <v>419</v>
       </c>
       <c r="E1603">
-        <v>1.834978536116047</v>
+        <v>1.670143980738748</v>
       </c>
       <c r="F1603">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1603">
-        <v>0.009123922701298205</v>
+        <v>0.007478830507514553</v>
       </c>
       <c r="H1603">
-        <v>0.008605021463883953</v>
+        <v>0.007129856019261253</v>
       </c>
       <c r="I1603">
-        <v>0.2210987625857497</v>
+        <v>-0.0710255117466998</v>
       </c>
       <c r="J1603">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1603">
-        <v>3.56</v>
+        <v>2.89</v>
       </c>
       <c r="L1603">
-        <v>5.59</v>
+        <v>4.61</v>
       </c>
       <c r="M1603">
-        <v>3.41</v>
+        <v>2.75</v>
       </c>
       <c r="N1603">
-        <v>5.22</v>
+        <v>4.4</v>
       </c>
       <c r="O1603">
         <v>1</v>
       </c>
       <c r="P1603" t="s">
-        <v>418</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1604" spans="1:16">
       <c r="A1604" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1604" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C1604">
-        <v>1.705051786955097</v>
+        <v>1.605356319289299</v>
       </c>
       <c r="D1604" t="s">
-        <v>424</v>
+        <v>231</v>
       </c>
       <c r="E1604">
-        <v>1.945344790311297</v>
+        <v>1.823785857909699</v>
       </c>
       <c r="F1604">
         <v>1</v>
       </c>
       <c r="G1604">
-        <v>0.008494948213044903</v>
+        <v>0.009134643680710703</v>
       </c>
       <c r="H1604">
-        <v>0.008814655209688702</v>
+        <v>0.009456214142090301</v>
       </c>
       <c r="I1604">
-        <v>0.2402930033562001</v>
+        <v>0.2184295386204007</v>
       </c>
       <c r="J1604">
-        <v>0.9926749160950009</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1604">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="L1604">
-        <v>5.1</v>
+        <v>5.37</v>
       </c>
       <c r="M1604">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="N1604">
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="O1604">
         <v>1</v>
       </c>
       <c r="P1604" t="s">
-        <v>418</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1605" spans="1:16">
       <c r="A1605" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1605" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C1605">
-        <v>1.754978536116047</v>
+        <v>1.872529488806021</v>
       </c>
       <c r="D1605" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E1605">
-        <v>1.945344790311297</v>
+        <v>1.702894533911371</v>
       </c>
       <c r="F1605">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1605">
-        <v>0.008525021463883953</v>
+        <v>0.00958747051119398</v>
       </c>
       <c r="H1605">
-        <v>0.008814655209688702</v>
+        <v>0.00873710546608863</v>
       </c>
       <c r="I1605">
-        <v>0.1903662541952502</v>
+        <v>0.1696349548946499</v>
       </c>
       <c r="J1605">
-        <v>0.9926749160950009</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1605">
+        <v>3.74</v>
+      </c>
+      <c r="L1605">
+        <v>5.73</v>
+      </c>
+      <c r="M1605">
         <v>3.41</v>
       </c>
-      <c r="L1605">
-        <v>5.14</v>
-      </c>
-      <c r="M1605">
-        <v>3.46</v>
-      </c>
       <c r="N1605">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="O1605">
         <v>1</v>
       </c>
       <c r="P1605" t="s">
-        <v>418</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1606" spans="1:16">
       <c r="A1606" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B1606" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C1606">
-        <v>2.036150549540847</v>
+        <v>1.918183149772576</v>
       </c>
       <c r="D1606" t="s">
-        <v>249</v>
+        <v>418</v>
       </c>
       <c r="E1606">
-        <v>1.796077298701797</v>
+        <v>1.702894533911371</v>
       </c>
       <c r="F1606">
         <v>-1</v>
       </c>
       <c r="G1606">
-        <v>0.009123849450459152</v>
+        <v>0.009261816850227424</v>
       </c>
       <c r="H1606">
-        <v>0.008863922701298205</v>
+        <v>0.00873710546608863</v>
       </c>
       <c r="I1606">
-        <v>0.2400732508390506</v>
+        <v>0.2152886158612044</v>
       </c>
       <c r="J1606">
-        <v>0.9926749160950009</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1606">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="L1606">
-        <v>5.58</v>
+        <v>5.59</v>
       </c>
       <c r="M1606">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="N1606">
-        <v>5.33</v>
+        <v>5.22</v>
       </c>
       <c r="O1606">
         <v>1</v>
       </c>
       <c r="P1606" t="s">
-        <v>418</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1607" spans="1:16">
       <c r="A1607" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1607" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C1607">
-        <v>1.715564542828446</v>
+        <v>1.572580441635452</v>
       </c>
       <c r="D1607" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E1607">
-        <v>1.952414756749298</v>
+        <v>1.744150903015051</v>
       </c>
       <c r="F1607">
         <v>1</v>
       </c>
       <c r="G1607">
-        <v>0.008644435457171553</v>
+        <v>0.008627419558364548</v>
       </c>
       <c r="H1607">
-        <v>0.008027585243250703</v>
+        <v>0.00869584909698495</v>
       </c>
       <c r="I1607">
-        <v>0.2368502139208513</v>
+        <v>0.171570461379599</v>
       </c>
       <c r="J1607">
-        <v>0.9926749160950009</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1607">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
       <c r="L1607">
-        <v>5.18</v>
+        <v>5.1</v>
       </c>
       <c r="M1607">
-        <v>3.06</v>
+        <v>3.37</v>
       </c>
       <c r="N1607">
-        <v>4.99</v>
+        <v>5.22</v>
       </c>
       <c r="O1607">
         <v>1</v>
       </c>
       <c r="P1607" t="s">
-        <v>418</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1608" spans="1:16">
       <c r="A1608" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1608" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C1608">
-        <v>1.744758783598896</v>
+        <v>1.897869057496656</v>
       </c>
       <c r="D1608" t="s">
-        <v>422</v>
+        <v>250</v>
       </c>
       <c r="E1608">
-        <v>1.952414756749298</v>
+        <v>1.658183149772576</v>
       </c>
       <c r="F1608">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1608">
-        <v>0.008455241216401102</v>
+        <v>0.009262130942503345</v>
       </c>
       <c r="H1608">
-        <v>0.008027585243250703</v>
+        <v>0.009001816850227424</v>
       </c>
       <c r="I1608">
-        <v>0.2076559731504011</v>
+        <v>0.2396859077240805</v>
       </c>
       <c r="J1608">
-        <v>0.9926749160950009</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1608">
-        <v>3.38</v>
+        <v>3.57</v>
       </c>
       <c r="L1608">
-        <v>5.1</v>
+        <v>5.58</v>
       </c>
       <c r="M1608">
-        <v>3.06</v>
+        <v>3.56</v>
       </c>
       <c r="N1608">
-        <v>4.99</v>
+        <v>5.33</v>
       </c>
       <c r="O1608">
         <v>1</v>
       </c>
       <c r="P1608" t="s">
-        <v>418</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1609" spans="1:16">
       <c r="A1609" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B1609" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C1609">
-        <v>1.755125037794147</v>
+        <v>1.580381795704013</v>
       </c>
       <c r="D1609" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1609">
-        <v>1.952414756749298</v>
+        <v>1.74477908756689</v>
       </c>
       <c r="F1609">
         <v>1</v>
       </c>
       <c r="G1609">
-        <v>0.008564874962205853</v>
+        <v>0.008779618204295986</v>
       </c>
       <c r="H1609">
-        <v>0.008027585243250703</v>
+        <v>0.00865522091243311</v>
       </c>
       <c r="I1609">
-        <v>0.1972897189551506</v>
+        <v>0.1643972918628771</v>
       </c>
       <c r="J1609">
-        <v>0.9926749160950009</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1609">
-        <v>3.43</v>
+        <v>3.49</v>
       </c>
       <c r="L1609">
-        <v>5.16</v>
+        <v>5.18</v>
       </c>
       <c r="M1609">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1609">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1609">
         <v>1</v>
       </c>
       <c r="P1609" t="s">
-        <v>418</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1610" spans="1:16">
       <c r="A1610" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B1610" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C1610">
-        <v>1.743513519335047</v>
+        <v>1.613836810739131</v>
       </c>
       <c r="D1610" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1610">
-        <v>1.952414756749298</v>
+        <v>1.74477908756689</v>
       </c>
       <c r="F1610">
         <v>1</v>
       </c>
       <c r="G1610">
-        <v>0.008116486480664953</v>
+        <v>0.00858616318926087</v>
       </c>
       <c r="H1610">
-        <v>0.008027585243250703</v>
+        <v>0.00865522091243311</v>
       </c>
       <c r="I1610">
-        <v>0.2089012374142509</v>
+        <v>0.1309422768277595</v>
       </c>
       <c r="J1610">
-        <v>0.9926749160950009</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1610">
-        <v>3.21</v>
+        <v>3.38</v>
       </c>
       <c r="L1610">
-        <v>4.93</v>
+        <v>5.1</v>
       </c>
       <c r="M1610">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1610">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1610">
         <v>1</v>
       </c>
       <c r="P1610" t="s">
-        <v>418</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1611" spans="1:16">
       <c r="A1611" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B1611" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C1611">
-        <v>1.692781010944548</v>
+        <v>1.619176379429766</v>
       </c>
       <c r="D1611" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E1611">
-        <v>1.883367017656947</v>
+        <v>1.833887763568562</v>
       </c>
       <c r="F1611">
         <v>1</v>
       </c>
       <c r="G1611">
-        <v>0.007867218989055453</v>
+        <v>0.008240823620570232</v>
       </c>
       <c r="H1611">
-        <v>0.008216632982343054</v>
+        <v>0.008146112236431439</v>
       </c>
       <c r="I1611">
-        <v>0.1905860067123992</v>
+        <v>0.2147113841387962</v>
       </c>
       <c r="J1611">
-        <v>0.9926749160950009</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1611">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="L1611">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="M1611">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="N1611">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="O1611">
         <v>1</v>
       </c>
       <c r="P1611" t="s">
-        <v>418</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1612" spans="1:16">
       <c r="A1612" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B1612" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1612">
+        <v>1.572317302188964</v>
+      </c>
+      <c r="D1612" t="s">
+        <v>422</v>
+      </c>
+      <c r="E1612">
+        <v>1.759804563981606</v>
+      </c>
+      <c r="F1612">
+        <v>1</v>
+      </c>
+      <c r="G1612">
+        <v>0.007987682697811038</v>
+      </c>
+      <c r="H1612">
+        <v>0.008340195436018395</v>
+      </c>
+      <c r="I1612">
+        <v>0.1874872617926417</v>
+      </c>
+      <c r="J1612">
+        <v>1.031409227591973</v>
+      </c>
+      <c r="K1612">
+        <v>3.11</v>
+      </c>
+      <c r="L1612">
+        <v>4.78</v>
+      </c>
+      <c r="M1612">
+        <v>3.19</v>
+      </c>
+      <c r="N1612">
+        <v>5.05</v>
+      </c>
+      <c r="O1612">
+        <v>1</v>
+      </c>
+      <c r="P1612" t="s">
         <v>237</v>
-      </c>
-      <c r="C1612">
-        <v>1.741169492485448</v>
-      </c>
-      <c r="D1612" t="s">
-        <v>420</v>
-      </c>
-      <c r="E1612">
-        <v>1.590803238290198</v>
-      </c>
-      <c r="F1612">
-        <v>1</v>
-      </c>
-      <c r="G1612">
-        <v>0.007478830507514553</v>
-      </c>
-      <c r="H1612">
-        <v>0.007229196761709803</v>
-      </c>
-      <c r="I1612">
-        <v>-0.1503662541952502</v>
-      </c>
-      <c r="J1612">
-        <v>0.9926749160950009</v>
-      </c>
-      <c r="K1612">
-        <v>2.89</v>
-      </c>
-      <c r="L1612">
-        <v>4.61</v>
-      </c>
-      <c r="M1612">
-        <v>2.84</v>
-      </c>
-      <c r="N1612">
-        <v>4.41</v>
-      </c>
-      <c r="O1612">
-        <v>1</v>
-      </c>
-      <c r="P1612" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="1613" spans="1:16">
       <c r="A1613" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1613" t="s">
         <v>245</v>
       </c>
       <c r="C1613">
-        <v>1.605356319289299</v>
+        <v>1.480797793638797</v>
       </c>
       <c r="D1613" t="s">
-        <v>231</v>
+        <v>419</v>
       </c>
       <c r="E1613">
-        <v>1.823785857909699</v>
+        <v>1.563624624122074</v>
       </c>
       <c r="F1613">
         <v>1</v>
       </c>
       <c r="G1613">
-        <v>0.009134643680710703</v>
+        <v>0.007339202206361204</v>
       </c>
       <c r="H1613">
-        <v>0.009456214142090301</v>
+        <v>0.007236375375877927</v>
       </c>
       <c r="I1613">
-        <v>0.2184295386204007</v>
+        <v>0.08282683048327755</v>
       </c>
       <c r="J1613">
         <v>1.031409227591973</v>
       </c>
       <c r="K1613">
-        <v>3.65</v>
+        <v>2.84</v>
       </c>
       <c r="L1613">
-        <v>5.37</v>
+        <v>4.41</v>
       </c>
       <c r="M1613">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="N1613">
-        <v>5.64</v>
+        <v>4.4</v>
       </c>
       <c r="O1613">
         <v>1</v>
       </c>
       <c r="P1613" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1614" spans="1:16">
       <c r="A1614" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1614" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C1614">
-        <v>1.872529488806021</v>
+        <v>1.516085437608808</v>
       </c>
       <c r="D1614" t="s">
-        <v>426</v>
+        <v>231</v>
       </c>
       <c r="E1614">
-        <v>1.744099950185619</v>
+        <v>1.733292087439065</v>
       </c>
       <c r="F1614">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1614">
-        <v>0.00958747051119398</v>
+        <v>0.009223914562391192</v>
       </c>
       <c r="H1614">
-        <v>0.00935590004981438</v>
+        <v>0.009546707912560935</v>
       </c>
       <c r="I1614">
-        <v>0.1284295386204017</v>
+        <v>0.2172066498302567</v>
       </c>
       <c r="J1614">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1614">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="L1614">
-        <v>5.73</v>
+        <v>5.37</v>
       </c>
       <c r="M1614">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="N1614">
-        <v>5.55</v>
+        <v>5.64</v>
       </c>
       <c r="O1614">
         <v>1</v>
       </c>
       <c r="P1614" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1615" spans="1:16">
       <c r="A1615" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1615" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C1615">
-        <v>1.918183149772576</v>
+        <v>1.781057407303272</v>
       </c>
       <c r="D1615" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E1615">
-        <v>1.702894533911371</v>
+        <v>1.653850757473014</v>
       </c>
       <c r="F1615">
         <v>-1</v>
       </c>
       <c r="G1615">
-        <v>0.009261816850227424</v>
+        <v>0.009678942592696728</v>
       </c>
       <c r="H1615">
-        <v>0.00873710546608863</v>
+        <v>0.009446149242526986</v>
       </c>
       <c r="I1615">
-        <v>0.2152886158612044</v>
+        <v>0.1272066498302578</v>
       </c>
       <c r="J1615">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1615">
-        <v>3.56</v>
+        <v>3.74</v>
       </c>
       <c r="L1615">
-        <v>5.59</v>
+        <v>5.73</v>
       </c>
       <c r="M1615">
-        <v>3.41</v>
+        <v>3.69</v>
       </c>
       <c r="N1615">
-        <v>5.22</v>
+        <v>5.55</v>
       </c>
       <c r="O1615">
         <v>1</v>
       </c>
       <c r="P1615" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1616" spans="1:16">
       <c r="A1616" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1616" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C1616">
-        <v>1.572580441635452</v>
+        <v>1.831113467914344</v>
       </c>
       <c r="D1616" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E1616">
-        <v>1.811324072531773</v>
+        <v>1.619493518423571</v>
       </c>
       <c r="F1616">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1616">
-        <v>0.008627419558364548</v>
+        <v>0.009348886532085656</v>
       </c>
       <c r="H1616">
-        <v>0.008948675927468227</v>
+        <v>0.008820506481576429</v>
       </c>
       <c r="I1616">
-        <v>0.2387436308963213</v>
+        <v>0.2116199494907733</v>
       </c>
       <c r="J1616">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1616">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="L1616">
-        <v>5.1</v>
+        <v>5.59</v>
       </c>
       <c r="M1616">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="N1616">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="O1616">
         <v>1</v>
       </c>
       <c r="P1616" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1617" spans="1:16">
       <c r="A1617" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1617" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C1617">
-        <v>1.622894533911371</v>
+        <v>1.488934848389623</v>
       </c>
       <c r="D1617" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E1617">
-        <v>1.811324072531773</v>
+        <v>1.726700168253829</v>
       </c>
       <c r="F1617">
         <v>1</v>
       </c>
       <c r="G1617">
-        <v>0.00865710546608863</v>
+        <v>0.008711065151610378</v>
       </c>
       <c r="H1617">
-        <v>0.008948675927468227</v>
+        <v>0.00903329983174617</v>
       </c>
       <c r="I1617">
-        <v>0.1884295386204018</v>
+        <v>0.2377653198642062</v>
       </c>
       <c r="J1617">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1617">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="L1617">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="M1617">
         <v>3.46</v>
@@ -82853,145 +82859,145 @@
         <v>1</v>
       </c>
       <c r="P1617" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1618" spans="1:16">
       <c r="A1618" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1618" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C1618">
-        <v>1.897869057496656</v>
+        <v>1.539493518423571</v>
       </c>
       <c r="D1618" t="s">
-        <v>249</v>
+        <v>426</v>
       </c>
       <c r="E1618">
-        <v>1.658183149772576</v>
+        <v>1.726700168253829</v>
       </c>
       <c r="F1618">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1618">
-        <v>0.009262130942503345</v>
+        <v>0.008740506481576428</v>
       </c>
       <c r="H1618">
-        <v>0.009001816850227424</v>
+        <v>0.00903329983174617</v>
       </c>
       <c r="I1618">
-        <v>0.2396859077240805</v>
+        <v>0.1872066498302583</v>
       </c>
       <c r="J1618">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1618">
-        <v>3.57</v>
+        <v>3.41</v>
       </c>
       <c r="L1618">
-        <v>5.58</v>
+        <v>5.14</v>
       </c>
       <c r="M1618">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="N1618">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="O1618">
         <v>1</v>
       </c>
       <c r="P1618" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1619" spans="1:16">
       <c r="A1619" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1619" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C1619">
-        <v>1.580381795704013</v>
+        <v>1.810554797880396</v>
       </c>
       <c r="D1619" t="s">
-        <v>422</v>
+        <v>250</v>
       </c>
       <c r="E1619">
-        <v>1.833887763568562</v>
+        <v>1.571113467914344</v>
       </c>
       <c r="F1619">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1619">
-        <v>0.008779618204295986</v>
+        <v>0.009349445202119604</v>
       </c>
       <c r="H1619">
-        <v>0.008146112236431439</v>
+        <v>0.009088886532085656</v>
       </c>
       <c r="I1619">
-        <v>0.253505967864549</v>
+        <v>0.2394413299660516</v>
       </c>
       <c r="J1619">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1619">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="L1619">
-        <v>5.18</v>
+        <v>5.58</v>
       </c>
       <c r="M1619">
-        <v>3.06</v>
+        <v>3.56</v>
       </c>
       <c r="N1619">
-        <v>4.99</v>
+        <v>5.33</v>
       </c>
       <c r="O1619">
         <v>1</v>
       </c>
       <c r="P1619" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1620" spans="1:16">
       <c r="A1620" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1620" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C1620">
-        <v>1.630067703428094</v>
+        <v>1.495024158151983</v>
       </c>
       <c r="D1620" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E1620">
-        <v>1.833887763568562</v>
+        <v>1.759046969611768</v>
       </c>
       <c r="F1620">
         <v>1</v>
       </c>
       <c r="G1620">
-        <v>0.008849932296571906</v>
+        <v>0.008864975841848017</v>
       </c>
       <c r="H1620">
-        <v>0.008146112236431439</v>
+        <v>0.008220953030388231</v>
       </c>
       <c r="I1620">
-        <v>0.2038200601404681</v>
+        <v>0.2640228114597849</v>
       </c>
       <c r="J1620">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1620">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="L1620">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="M1620">
         <v>3.06</v>
@@ -83003,45 +83009,45 @@
         <v>1</v>
       </c>
       <c r="P1620" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1621" spans="1:16">
       <c r="A1621" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1621" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C1621">
-        <v>1.613836810739131</v>
+        <v>1.544465488118035</v>
       </c>
       <c r="D1621" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E1621">
-        <v>1.833887763568562</v>
+        <v>1.759046969611768</v>
       </c>
       <c r="F1621">
         <v>1</v>
       </c>
       <c r="G1621">
-        <v>0.00858616318926087</v>
+        <v>0.008935534511881966</v>
       </c>
       <c r="H1621">
-        <v>0.008146112236431439</v>
+        <v>0.008220953030388231</v>
       </c>
       <c r="I1621">
-        <v>0.2200509528294314</v>
+        <v>0.2145814814937328</v>
       </c>
       <c r="J1621">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1621">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="L1621">
-        <v>5.1</v>
+        <v>5.24</v>
       </c>
       <c r="M1621">
         <v>3.06</v>
@@ -83053,45 +83059,45 @@
         <v>1</v>
       </c>
       <c r="P1621" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1622" spans="1:16">
       <c r="A1622" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1622" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C1622">
-        <v>1.622266349359532</v>
+        <v>1.531169528525416</v>
       </c>
       <c r="D1622" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E1622">
-        <v>1.833887763568562</v>
+        <v>1.759046969611768</v>
       </c>
       <c r="F1622">
         <v>1</v>
       </c>
       <c r="G1622">
-        <v>0.008697733650640469</v>
+        <v>0.008668830471474584</v>
       </c>
       <c r="H1622">
-        <v>0.008146112236431439</v>
+        <v>0.008220953030388231</v>
       </c>
       <c r="I1622">
-        <v>0.2116214142090302</v>
+        <v>0.2278774410863518</v>
       </c>
       <c r="J1622">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1622">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="L1622">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="M1622">
         <v>3.06</v>
@@ -83103,45 +83109,45 @@
         <v>1</v>
       </c>
       <c r="P1622" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1623" spans="1:16">
       <c r="A1623" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1623" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C1623">
-        <v>1.619176379429766</v>
+        <v>1.538376178355674</v>
       </c>
       <c r="D1623" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E1623">
-        <v>1.833887763568562</v>
+        <v>1.759046969611768</v>
       </c>
       <c r="F1623">
         <v>1</v>
       </c>
       <c r="G1623">
-        <v>0.008240823620570232</v>
+        <v>0.008781623821644326</v>
       </c>
       <c r="H1623">
-        <v>0.008146112236431439</v>
+        <v>0.008220953030388231</v>
       </c>
       <c r="I1623">
-        <v>0.2147113841387962</v>
+        <v>0.2206707912560937</v>
       </c>
       <c r="J1623">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1623">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="L1623">
-        <v>4.93</v>
+        <v>5.16</v>
       </c>
       <c r="M1623">
         <v>3.06</v>
@@ -83153,151 +83159,151 @@
         <v>1</v>
       </c>
       <c r="P1623" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1624" spans="1:16">
       <c r="A1624" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1624" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C1624">
-        <v>1.572317302188964</v>
+        <v>1.54066691910254</v>
       </c>
       <c r="D1624" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E1624">
-        <v>1.759804563981606</v>
+        <v>1.759046969611768</v>
       </c>
       <c r="F1624">
         <v>1</v>
       </c>
       <c r="G1624">
-        <v>0.007987682697811038</v>
+        <v>0.008319333080897461</v>
       </c>
       <c r="H1624">
-        <v>0.008340195436018395</v>
+        <v>0.008220953030388231</v>
       </c>
       <c r="I1624">
-        <v>0.1874872617926417</v>
+        <v>0.2183800505092277</v>
       </c>
       <c r="J1624">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1624">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="L1624">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="M1624">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="N1624">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="O1624">
         <v>1</v>
       </c>
       <c r="P1624" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1625" spans="1:16">
       <c r="A1625" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1625" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C1625">
-        <v>1.629227332259198</v>
+        <v>1.496253619442026</v>
       </c>
       <c r="D1625" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E1625">
-        <v>1.480797793638797</v>
+        <v>1.681784259170438</v>
       </c>
       <c r="F1625">
         <v>1</v>
       </c>
       <c r="G1625">
-        <v>0.007590772667740803</v>
+        <v>0.008063746380557974</v>
       </c>
       <c r="H1625">
-        <v>0.007339202206361204</v>
+        <v>0.008418215740829562</v>
       </c>
       <c r="I1625">
-        <v>-0.1484295386204013</v>
+        <v>0.185530639728412</v>
       </c>
       <c r="J1625">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1625">
-        <v>2.89</v>
+        <v>3.11</v>
       </c>
       <c r="L1625">
-        <v>4.61</v>
+        <v>4.78</v>
       </c>
       <c r="M1625">
-        <v>2.84</v>
+        <v>3.19</v>
       </c>
       <c r="N1625">
-        <v>4.41</v>
+        <v>5.05</v>
       </c>
       <c r="O1625">
         <v>1</v>
       </c>
       <c r="P1625" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1626" spans="1:16">
       <c r="A1626" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B1626" t="s">
         <v>245</v>
       </c>
       <c r="C1626">
-        <v>1.516085437608808</v>
+        <v>1.411337710358634</v>
       </c>
       <c r="D1626" t="s">
-        <v>231</v>
+        <v>419</v>
       </c>
       <c r="E1626">
-        <v>1.733292087439065</v>
+        <v>1.496365740664171</v>
       </c>
       <c r="F1626">
         <v>1</v>
       </c>
       <c r="G1626">
-        <v>0.009223914562391192</v>
+        <v>0.007408662289641366</v>
       </c>
       <c r="H1626">
-        <v>0.009546707912560935</v>
+        <v>0.00730363425933583</v>
       </c>
       <c r="I1626">
-        <v>0.2172066498302567</v>
+        <v>0.08502803030553663</v>
       </c>
       <c r="J1626">
         <v>1.055867003394847</v>
       </c>
       <c r="K1626">
-        <v>3.65</v>
+        <v>2.84</v>
       </c>
       <c r="L1626">
-        <v>5.37</v>
+        <v>4.41</v>
       </c>
       <c r="M1626">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="N1626">
-        <v>5.64</v>
+        <v>4.4</v>
       </c>
       <c r="O1626">
         <v>1</v>
@@ -83308,140 +83314,140 @@
     </row>
     <row r="1627" spans="1:16">
       <c r="A1627" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1627" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C1627">
-        <v>1.831113467914344</v>
+        <v>1.244990997067842</v>
       </c>
       <c r="D1627" t="s">
-        <v>419</v>
+        <v>231</v>
       </c>
       <c r="E1627">
-        <v>1.619493518423571</v>
+        <v>1.458484024424935</v>
       </c>
       <c r="F1627">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1627">
-        <v>0.009348886532085656</v>
+        <v>0.009495009002932157</v>
       </c>
       <c r="H1627">
-        <v>0.008820506481576429</v>
+        <v>0.009821515975575065</v>
       </c>
       <c r="I1627">
-        <v>0.2116199494907733</v>
+        <v>0.2134930273570932</v>
       </c>
       <c r="J1627">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1627">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="L1627">
-        <v>5.59</v>
+        <v>5.37</v>
       </c>
       <c r="M1627">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="N1627">
-        <v>5.22</v>
+        <v>5.64</v>
       </c>
       <c r="O1627">
         <v>1</v>
       </c>
       <c r="P1627" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1628" spans="1:16">
       <c r="A1628" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1628" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C1628">
-        <v>1.488934848389623</v>
+        <v>1.566703547825073</v>
       </c>
       <c r="D1628" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E1628">
-        <v>1.726700168253829</v>
+        <v>1.366224465753792</v>
       </c>
       <c r="F1628">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1628">
-        <v>0.008711065151610378</v>
+        <v>0.009613296452174926</v>
       </c>
       <c r="H1628">
-        <v>0.00903329983174617</v>
+        <v>0.009073775534246207</v>
       </c>
       <c r="I1628">
-        <v>0.2377653198642062</v>
+        <v>0.200479082071281</v>
       </c>
       <c r="J1628">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1628">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="L1628">
-        <v>5.1</v>
+        <v>5.59</v>
       </c>
       <c r="M1628">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="N1628">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="O1628">
         <v>1</v>
       </c>
       <c r="P1628" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1629" spans="1:16">
       <c r="A1629" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1629" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C1629">
-        <v>1.539493518423571</v>
+        <v>1.234923071225211</v>
       </c>
       <c r="D1629" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E1629">
-        <v>1.726700168253829</v>
+        <v>1.469717493110886</v>
       </c>
       <c r="F1629">
         <v>1</v>
       </c>
       <c r="G1629">
-        <v>0.008740506481576428</v>
+        <v>0.008965076928774789</v>
       </c>
       <c r="H1629">
-        <v>0.00903329983174617</v>
+        <v>0.009290282506889113</v>
       </c>
       <c r="I1629">
-        <v>0.1872066498302583</v>
+        <v>0.2347944218856752</v>
       </c>
       <c r="J1629">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1629">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="L1629">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="M1629">
         <v>3.46</v>
@@ -83453,795 +83459,795 @@
         <v>1</v>
       </c>
       <c r="P1629" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1630" spans="1:16">
       <c r="A1630" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1630" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C1630">
-        <v>1.810554797880396</v>
+        <v>1.286224465753792</v>
       </c>
       <c r="D1630" t="s">
-        <v>249</v>
+        <v>426</v>
       </c>
       <c r="E1630">
-        <v>1.571113467914344</v>
+        <v>1.469717493110886</v>
       </c>
       <c r="F1630">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1630">
-        <v>0.009349445202119604</v>
+        <v>0.008993775534246207</v>
       </c>
       <c r="H1630">
-        <v>0.009088886532085656</v>
+        <v>0.009290282506889113</v>
       </c>
       <c r="I1630">
-        <v>0.2394413299660516</v>
+        <v>0.1834930273570943</v>
       </c>
       <c r="J1630">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1630">
-        <v>3.57</v>
+        <v>3.41</v>
       </c>
       <c r="L1630">
-        <v>5.58</v>
+        <v>5.14</v>
       </c>
       <c r="M1630">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="N1630">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="O1630">
         <v>1</v>
       </c>
       <c r="P1630" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1631" spans="1:16">
       <c r="A1631" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1631" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C1631">
-        <v>1.495024158151983</v>
+        <v>1.545402153296492</v>
       </c>
       <c r="D1631" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E1631">
-        <v>1.759046969611768</v>
+        <v>1.411909125939398</v>
       </c>
       <c r="F1631">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1631">
-        <v>0.008864975841848017</v>
+        <v>0.009614597846703507</v>
       </c>
       <c r="H1631">
-        <v>0.008220953030388231</v>
+        <v>0.009368090874060602</v>
       </c>
       <c r="I1631">
-        <v>0.2640228114597849</v>
+        <v>0.133493027357094</v>
       </c>
       <c r="J1631">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1631">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="L1631">
-        <v>5.18</v>
+        <v>5.58</v>
       </c>
       <c r="M1631">
-        <v>3.06</v>
+        <v>3.52</v>
       </c>
       <c r="N1631">
-        <v>4.99</v>
+        <v>5.39</v>
       </c>
       <c r="O1631">
         <v>1</v>
       </c>
       <c r="P1631" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1632" spans="1:16">
       <c r="A1632" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1632" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C1632">
-        <v>1.544465488118035</v>
+        <v>1.235813309525142</v>
       </c>
       <c r="D1632" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1632">
-        <v>1.759046969611768</v>
+        <v>1.41403283292528</v>
       </c>
       <c r="F1632">
         <v>1</v>
       </c>
       <c r="G1632">
-        <v>0.008935534511881966</v>
+        <v>0.009124186690474857</v>
       </c>
       <c r="H1632">
-        <v>0.008220953030388231</v>
+        <v>0.008985967167074721</v>
       </c>
       <c r="I1632">
-        <v>0.2145814814937328</v>
+        <v>0.1782195234001382</v>
       </c>
       <c r="J1632">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1632">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="L1632">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="M1632">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1632">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1632">
         <v>1</v>
       </c>
       <c r="P1632" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1633" spans="1:16">
       <c r="A1633" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1633" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C1633">
-        <v>1.531169528525416</v>
+        <v>1.284511914996561</v>
       </c>
       <c r="D1633" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1633">
-        <v>1.759046969611768</v>
+        <v>1.41403283292528</v>
       </c>
       <c r="F1633">
         <v>1</v>
       </c>
       <c r="G1633">
-        <v>0.008668830471474584</v>
+        <v>0.00919548808500344</v>
       </c>
       <c r="H1633">
-        <v>0.008220953030388231</v>
+        <v>0.008985967167074721</v>
       </c>
       <c r="I1633">
-        <v>0.2278774410863518</v>
+        <v>0.1295209179287187</v>
       </c>
       <c r="J1633">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1633">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="L1633">
-        <v>5.1</v>
+        <v>5.24</v>
       </c>
       <c r="M1633">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1633">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1633">
         <v>1</v>
       </c>
       <c r="P1633" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1634" spans="1:16">
       <c r="A1634" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1634" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C1634">
-        <v>1.538376178355674</v>
+        <v>1.280128649339536</v>
       </c>
       <c r="D1634" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1634">
-        <v>1.759046969611768</v>
+        <v>1.41403283292528</v>
       </c>
       <c r="F1634">
         <v>1</v>
       </c>
       <c r="G1634">
-        <v>0.008781623821644326</v>
+        <v>0.008919871350660464</v>
       </c>
       <c r="H1634">
-        <v>0.008220953030388231</v>
+        <v>0.008985967167074721</v>
       </c>
       <c r="I1634">
-        <v>0.2206707912560937</v>
+        <v>0.1339041835857442</v>
       </c>
       <c r="J1634">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1634">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="L1634">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="M1634">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1634">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1634">
         <v>1</v>
       </c>
       <c r="P1634" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1635" spans="1:16">
       <c r="A1635" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1635" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C1635">
-        <v>1.54066691910254</v>
+        <v>1.28362167669663</v>
       </c>
       <c r="D1635" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1635">
-        <v>1.759046969611768</v>
+        <v>1.41403283292528</v>
       </c>
       <c r="F1635">
         <v>1</v>
       </c>
       <c r="G1635">
-        <v>0.008319333080897461</v>
+        <v>0.009036378323303371</v>
       </c>
       <c r="H1635">
-        <v>0.008220953030388231</v>
+        <v>0.008985967167074721</v>
       </c>
       <c r="I1635">
-        <v>0.2183800505092277</v>
+        <v>0.1304111562286505</v>
       </c>
       <c r="J1635">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1635">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="L1635">
-        <v>4.93</v>
+        <v>5.16</v>
       </c>
       <c r="M1635">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1635">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1635">
         <v>1</v>
       </c>
       <c r="P1635" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1636" spans="1:16">
       <c r="A1636" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1636" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C1636">
-        <v>1.496253619442026</v>
+        <v>1.302252356325417</v>
       </c>
       <c r="D1636" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E1636">
-        <v>1.681784259170438</v>
+        <v>1.531773274254136</v>
       </c>
       <c r="F1636">
         <v>1</v>
       </c>
       <c r="G1636">
-        <v>0.008063746380557974</v>
+        <v>0.008557747643674583</v>
       </c>
       <c r="H1636">
-        <v>0.008418215740829562</v>
+        <v>0.008448226725745866</v>
       </c>
       <c r="I1636">
-        <v>0.185530639728412</v>
+        <v>0.2295209179287192</v>
       </c>
       <c r="J1636">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1636">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="L1636">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="M1636">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="N1636">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="O1636">
         <v>1</v>
       </c>
       <c r="P1636" t="s">
-        <v>230</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1637" spans="1:16">
       <c r="A1637" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1637" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C1637">
-        <v>1.244990997067842</v>
+        <v>1.26526630161123</v>
       </c>
       <c r="D1637" t="s">
-        <v>231</v>
+        <v>428</v>
       </c>
       <c r="E1637">
-        <v>1.458484024424935</v>
+        <v>1.422252356325417</v>
       </c>
       <c r="F1637">
         <v>1</v>
       </c>
       <c r="G1637">
-        <v>0.009495009002932157</v>
+        <v>0.008294733698388771</v>
       </c>
       <c r="H1637">
-        <v>0.009821515975575065</v>
+        <v>0.008677747643674582</v>
       </c>
       <c r="I1637">
-        <v>0.2134930273570932</v>
+        <v>0.1569860547141868</v>
       </c>
       <c r="J1637">
         <v>1.130139452858125</v>
       </c>
       <c r="K1637">
-        <v>3.65</v>
+        <v>3.11</v>
       </c>
       <c r="L1637">
-        <v>5.37</v>
+        <v>4.78</v>
       </c>
       <c r="M1637">
-        <v>3.7</v>
+        <v>3.21</v>
       </c>
       <c r="N1637">
-        <v>5.64</v>
+        <v>5.05</v>
       </c>
       <c r="O1637">
         <v>1</v>
       </c>
       <c r="P1637" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1638" spans="1:16">
       <c r="A1638" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B1638" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C1638">
-        <v>1.566703547825073</v>
+        <v>1.565198375768599</v>
       </c>
       <c r="D1638" t="s">
-        <v>427</v>
+        <v>236</v>
       </c>
       <c r="E1638">
-        <v>1.415813309525142</v>
+        <v>1.343896981240018</v>
       </c>
       <c r="F1638">
         <v>-1</v>
       </c>
       <c r="G1638">
-        <v>0.009613296452174926</v>
+        <v>0.008074801624231402</v>
       </c>
       <c r="H1638">
-        <v>0.009304186690474857</v>
+        <v>0.007876103018759982</v>
       </c>
       <c r="I1638">
-        <v>0.1508902382999304</v>
+        <v>0.2213013945285813</v>
       </c>
       <c r="J1638">
         <v>1.130139452858125</v>
       </c>
       <c r="K1638">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="L1638">
-        <v>5.59</v>
+        <v>4.82</v>
       </c>
       <c r="M1638">
-        <v>3.49</v>
+        <v>2.89</v>
       </c>
       <c r="N1638">
-        <v>5.36</v>
+        <v>4.61</v>
       </c>
       <c r="O1638">
         <v>1</v>
       </c>
       <c r="P1638" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1639" spans="1:16">
       <c r="A1639" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B1639" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C1639">
-        <v>1.234923071225211</v>
+        <v>1.200403953882924</v>
       </c>
       <c r="D1639" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E1639">
-        <v>1.469717493110886</v>
+        <v>1.292116504640155</v>
       </c>
       <c r="F1639">
         <v>1</v>
       </c>
       <c r="G1639">
-        <v>0.008965076928774789</v>
+        <v>0.007619596046117076</v>
       </c>
       <c r="H1639">
-        <v>0.009290282506889113</v>
+        <v>0.007507883495359845</v>
       </c>
       <c r="I1639">
-        <v>0.2347944218856752</v>
+        <v>0.09171255075723161</v>
       </c>
       <c r="J1639">
         <v>1.130139452858125</v>
       </c>
       <c r="K1639">
-        <v>3.42</v>
+        <v>2.84</v>
       </c>
       <c r="L1639">
-        <v>5.1</v>
+        <v>4.41</v>
       </c>
       <c r="M1639">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="N1639">
-        <v>5.38</v>
+        <v>4.4</v>
       </c>
       <c r="O1639">
         <v>1</v>
       </c>
       <c r="P1639" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1640" spans="1:16">
       <c r="A1640" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1640" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C1640">
-        <v>1.286224465753792</v>
+        <v>1.121405183498271</v>
       </c>
       <c r="D1640" t="s">
-        <v>424</v>
+        <v>231</v>
       </c>
       <c r="E1640">
-        <v>1.469717493110886</v>
+        <v>1.333205254505096</v>
       </c>
       <c r="F1640">
         <v>1</v>
       </c>
       <c r="G1640">
-        <v>0.008993775534246207</v>
+        <v>0.00961859481650173</v>
       </c>
       <c r="H1640">
-        <v>0.009290282506889113</v>
+        <v>0.009946794745494904</v>
       </c>
       <c r="I1640">
-        <v>0.1834930273570943</v>
+        <v>0.2118000710068246</v>
       </c>
       <c r="J1640">
-        <v>1.130139452858125</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1640">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="L1640">
-        <v>5.14</v>
+        <v>5.37</v>
       </c>
       <c r="M1640">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="N1640">
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="O1640">
         <v>1</v>
       </c>
       <c r="P1640" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1641" spans="1:16">
       <c r="A1641" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1641" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C1641">
-        <v>1.545402153296492</v>
+        <v>1.446165055685984</v>
       </c>
       <c r="D1641" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E1641">
-        <v>1.411909125939398</v>
+        <v>1.297644956276429</v>
       </c>
       <c r="F1641">
         <v>-1</v>
       </c>
       <c r="G1641">
-        <v>0.009614597846703507</v>
+        <v>0.009733834944314016</v>
       </c>
       <c r="H1641">
-        <v>0.009368090874060602</v>
+        <v>0.009422355043723572</v>
       </c>
       <c r="I1641">
-        <v>0.133493027357094</v>
+        <v>0.1485200994095557</v>
       </c>
       <c r="J1641">
-        <v>1.130139452858125</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1641">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="L1641">
-        <v>5.58</v>
+        <v>5.59</v>
       </c>
       <c r="M1641">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="N1641">
-        <v>5.39</v>
+        <v>5.36</v>
       </c>
       <c r="O1641">
         <v>1</v>
       </c>
       <c r="P1641" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1642" spans="1:16">
       <c r="A1642" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1642" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C1642">
-        <v>1.306703547825073</v>
+        <v>1.119124856866872</v>
       </c>
       <c r="D1642" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E1642">
-        <v>1.531773274254136</v>
+        <v>1.352564913672333</v>
       </c>
       <c r="F1642">
         <v>1</v>
       </c>
       <c r="G1642">
-        <v>0.009353296452174927</v>
+        <v>0.009080875143133127</v>
       </c>
       <c r="H1642">
-        <v>0.008448226725745866</v>
+        <v>0.009407435086327666</v>
       </c>
       <c r="I1642">
-        <v>0.2250697264290631</v>
+        <v>0.2334400568054611</v>
       </c>
       <c r="J1642">
-        <v>1.130139452858125</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1642">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="L1642">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="M1642">
-        <v>3.06</v>
+        <v>3.46</v>
       </c>
       <c r="N1642">
-        <v>4.99</v>
+        <v>5.38</v>
       </c>
       <c r="O1642">
         <v>1</v>
       </c>
       <c r="P1642" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1643" spans="1:16">
       <c r="A1643" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1643" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C1643">
-        <v>1.235813309525142</v>
+        <v>1.170764842665507</v>
       </c>
       <c r="D1643" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E1643">
-        <v>1.531773274254136</v>
+        <v>1.352564913672333</v>
       </c>
       <c r="F1643">
         <v>1</v>
       </c>
       <c r="G1643">
-        <v>0.009124186690474857</v>
+        <v>0.009109235157334493</v>
       </c>
       <c r="H1643">
-        <v>0.008448226725745866</v>
+        <v>0.009407435086327666</v>
       </c>
       <c r="I1643">
-        <v>0.2959599647289943</v>
+        <v>0.1818000710068266</v>
       </c>
       <c r="J1643">
-        <v>1.130139452858125</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1643">
-        <v>3.49</v>
+        <v>3.41</v>
       </c>
       <c r="L1643">
-        <v>5.18</v>
+        <v>5.14</v>
       </c>
       <c r="M1643">
-        <v>3.06</v>
+        <v>3.46</v>
       </c>
       <c r="N1643">
-        <v>4.99</v>
+        <v>5.38</v>
       </c>
       <c r="O1643">
         <v>1</v>
       </c>
       <c r="P1643" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1644" spans="1:16">
       <c r="A1644" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1644" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="C1644">
-        <v>1.284511914996561</v>
+        <v>1.42452506988735</v>
       </c>
       <c r="D1644" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E1644">
-        <v>1.531773274254136</v>
+        <v>1.292724998880524</v>
       </c>
       <c r="F1644">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1644">
-        <v>0.00919548808500344</v>
+        <v>0.009735474930112651</v>
       </c>
       <c r="H1644">
-        <v>0.008448226725745866</v>
+        <v>0.009487275001119474</v>
       </c>
       <c r="I1644">
-        <v>0.2472613592575748</v>
+        <v>0.1318000710068263</v>
       </c>
       <c r="J1644">
-        <v>1.130139452858125</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1644">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="L1644">
-        <v>5.24</v>
+        <v>5.58</v>
       </c>
       <c r="M1644">
-        <v>3.06</v>
+        <v>3.52</v>
       </c>
       <c r="N1644">
-        <v>4.99</v>
+        <v>5.39</v>
       </c>
       <c r="O1644">
         <v>1</v>
       </c>
       <c r="P1644" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1645" spans="1:16">
       <c r="A1645" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1645" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C1645">
-        <v>1.28362167669663</v>
+        <v>1.186165055685985</v>
       </c>
       <c r="D1645" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E1645">
-        <v>1.531773274254136</v>
+        <v>1.428164345617728</v>
       </c>
       <c r="F1645">
         <v>1</v>
       </c>
       <c r="G1645">
-        <v>0.009036378323303371</v>
+        <v>0.009473834944314016</v>
       </c>
       <c r="H1645">
-        <v>0.008448226725745866</v>
+        <v>0.008551835654382271</v>
       </c>
       <c r="I1645">
-        <v>0.2481515975575066</v>
+        <v>0.2419992899317438</v>
       </c>
       <c r="J1645">
-        <v>1.130139452858125</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1645">
-        <v>3.43</v>
+        <v>3.56</v>
       </c>
       <c r="L1645">
-        <v>5.16</v>
+        <v>5.33</v>
       </c>
       <c r="M1645">
         <v>3.06</v>
@@ -84253,45 +84259,45 @@
         <v>1</v>
       </c>
       <c r="P1645" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1646" spans="1:16">
       <c r="A1646" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1646" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C1646">
-        <v>1.302252356325417</v>
+        <v>1.117644956276428</v>
       </c>
       <c r="D1646" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E1646">
-        <v>1.531773274254136</v>
+        <v>1.428164345617728</v>
       </c>
       <c r="F1646">
         <v>1</v>
       </c>
       <c r="G1646">
-        <v>0.008557747643674583</v>
+        <v>0.009242355043723571</v>
       </c>
       <c r="H1646">
-        <v>0.008448226725745866</v>
+        <v>0.008551835654382271</v>
       </c>
       <c r="I1646">
-        <v>0.2295209179287192</v>
+        <v>0.3105193893413003</v>
       </c>
       <c r="J1646">
-        <v>1.130139452858125</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1646">
-        <v>3.21</v>
+        <v>3.49</v>
       </c>
       <c r="L1646">
-        <v>4.93</v>
+        <v>5.18</v>
       </c>
       <c r="M1646">
         <v>3.06</v>
@@ -84303,545 +84309,545 @@
         <v>1</v>
       </c>
       <c r="P1646" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1647" spans="1:16">
       <c r="A1647" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B1647" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C1647">
-        <v>1.26526630161123</v>
+        <v>1.166004970477794</v>
       </c>
       <c r="D1647" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E1647">
-        <v>1.422252356325417</v>
+        <v>1.428164345617728</v>
       </c>
       <c r="F1647">
         <v>1</v>
       </c>
       <c r="G1647">
-        <v>0.008294733698388771</v>
+        <v>0.009313995029522208</v>
       </c>
       <c r="H1647">
-        <v>0.008677747643674582</v>
+        <v>0.008551835654382271</v>
       </c>
       <c r="I1647">
-        <v>0.1569860547141868</v>
+        <v>0.2621593751399343</v>
       </c>
       <c r="J1647">
-        <v>1.130139452858125</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1647">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="L1647">
-        <v>4.78</v>
+        <v>5.24</v>
       </c>
       <c r="M1647">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
       <c r="N1647">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="O1647">
         <v>1</v>
       </c>
       <c r="P1647" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1648" spans="1:16">
       <c r="A1648" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B1648" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C1648">
-        <v>1.565198375768599</v>
+        <v>1.167484871068238</v>
       </c>
       <c r="D1648" t="s">
-        <v>237</v>
+        <v>424</v>
       </c>
       <c r="E1648">
-        <v>1.343896981240018</v>
+        <v>1.428164345617728</v>
       </c>
       <c r="F1648">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1648">
-        <v>0.008074801624231402</v>
+        <v>0.009152515128931763</v>
       </c>
       <c r="H1648">
-        <v>0.007876103018759982</v>
+        <v>0.008551835654382271</v>
       </c>
       <c r="I1648">
-        <v>0.2213013945285813</v>
+        <v>0.2606794745494909</v>
       </c>
       <c r="J1648">
-        <v>1.130139452858125</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1648">
-        <v>2.88</v>
+        <v>3.43</v>
       </c>
       <c r="L1648">
-        <v>4.82</v>
+        <v>5.16</v>
       </c>
       <c r="M1648">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="N1648">
-        <v>4.61</v>
+        <v>4.99</v>
       </c>
       <c r="O1648">
         <v>1</v>
       </c>
       <c r="P1648" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1649" spans="1:16">
       <c r="A1649" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1649" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C1649">
-        <v>1.121405183498271</v>
+        <v>1.193564558638205</v>
       </c>
       <c r="D1649" t="s">
-        <v>231</v>
+        <v>424</v>
       </c>
       <c r="E1649">
-        <v>1.333205254505096</v>
+        <v>1.428164345617728</v>
       </c>
       <c r="F1649">
         <v>1</v>
       </c>
       <c r="G1649">
-        <v>0.00961859481650173</v>
+        <v>0.008666435441361794</v>
       </c>
       <c r="H1649">
-        <v>0.009946794745494904</v>
+        <v>0.008551835654382271</v>
       </c>
       <c r="I1649">
-        <v>0.2118000710068246</v>
+        <v>0.2345997869795236</v>
       </c>
       <c r="J1649">
         <v>1.163998579863488</v>
       </c>
       <c r="K1649">
-        <v>3.65</v>
+        <v>3.21</v>
       </c>
       <c r="L1649">
-        <v>5.37</v>
+        <v>4.93</v>
       </c>
       <c r="M1649">
-        <v>3.7</v>
+        <v>3.06</v>
       </c>
       <c r="N1649">
-        <v>5.64</v>
+        <v>4.99</v>
       </c>
       <c r="O1649">
         <v>1</v>
       </c>
       <c r="P1649" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1650" spans="1:16">
       <c r="A1650" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B1650" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C1650">
-        <v>1.446165055685984</v>
+        <v>1.159964416624554</v>
       </c>
       <c r="D1650" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E1650">
-        <v>1.297644956276429</v>
+        <v>1.313564558638205</v>
       </c>
       <c r="F1650">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1650">
-        <v>0.009733834944314016</v>
+        <v>0.008400035583375447</v>
       </c>
       <c r="H1650">
-        <v>0.009422355043723572</v>
+        <v>0.008786435441361795</v>
       </c>
       <c r="I1650">
-        <v>0.1485200994095557</v>
+        <v>0.153600142013651</v>
       </c>
       <c r="J1650">
         <v>1.163998579863488</v>
       </c>
       <c r="K1650">
-        <v>3.56</v>
+        <v>3.11</v>
       </c>
       <c r="L1650">
-        <v>5.59</v>
+        <v>4.78</v>
       </c>
       <c r="M1650">
-        <v>3.49</v>
+        <v>3.21</v>
       </c>
       <c r="N1650">
-        <v>5.36</v>
+        <v>5.05</v>
       </c>
       <c r="O1650">
         <v>1</v>
       </c>
       <c r="P1650" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1651" spans="1:16">
       <c r="A1651" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B1651" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C1651">
-        <v>1.119124856866872</v>
+        <v>1.467684089993156</v>
       </c>
       <c r="D1651" t="s">
-        <v>424</v>
+        <v>236</v>
       </c>
       <c r="E1651">
-        <v>1.352564913672333</v>
+        <v>1.246044104194521</v>
       </c>
       <c r="F1651">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1651">
-        <v>0.009080875143133127</v>
+        <v>0.008172315910006844</v>
       </c>
       <c r="H1651">
-        <v>0.009407435086327666</v>
+        <v>0.00797395589580548</v>
       </c>
       <c r="I1651">
-        <v>0.2334400568054611</v>
+        <v>0.2216399857986349</v>
       </c>
       <c r="J1651">
         <v>1.163998579863488</v>
       </c>
       <c r="K1651">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="L1651">
-        <v>5.1</v>
+        <v>4.82</v>
       </c>
       <c r="M1651">
-        <v>3.46</v>
+        <v>2.89</v>
       </c>
       <c r="N1651">
-        <v>5.38</v>
+        <v>4.61</v>
       </c>
       <c r="O1651">
         <v>1</v>
       </c>
       <c r="P1651" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1652" spans="1:16">
       <c r="A1652" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B1652" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C1652">
-        <v>1.170764842665507</v>
+        <v>1.104244033187696</v>
       </c>
       <c r="D1652" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E1652">
-        <v>1.352564913672333</v>
+        <v>1.19900390537541</v>
       </c>
       <c r="F1652">
         <v>1</v>
       </c>
       <c r="G1652">
-        <v>0.009109235157334493</v>
+        <v>0.007715755966812305</v>
       </c>
       <c r="H1652">
-        <v>0.009407435086327666</v>
+        <v>0.007600996094624592</v>
       </c>
       <c r="I1652">
-        <v>0.1818000710068266</v>
+        <v>0.09475987218771387</v>
       </c>
       <c r="J1652">
         <v>1.163998579863488</v>
       </c>
       <c r="K1652">
-        <v>3.41</v>
+        <v>2.84</v>
       </c>
       <c r="L1652">
-        <v>5.14</v>
+        <v>4.41</v>
       </c>
       <c r="M1652">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="N1652">
-        <v>5.38</v>
+        <v>4.4</v>
       </c>
       <c r="O1652">
         <v>1</v>
       </c>
       <c r="P1652" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1653" spans="1:16">
       <c r="A1653" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1653" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C1653">
-        <v>1.42452506988735</v>
+        <v>1.284389949876279</v>
       </c>
       <c r="D1653" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E1653">
-        <v>1.292724998880524</v>
+        <v>1.139050821648374</v>
       </c>
       <c r="F1653">
         <v>-1</v>
       </c>
       <c r="G1653">
-        <v>0.009735474930112651</v>
+        <v>0.009895610050123722</v>
       </c>
       <c r="H1653">
-        <v>0.009487275001119474</v>
+        <v>0.009580949178351627</v>
       </c>
       <c r="I1653">
-        <v>0.1318000710068263</v>
+        <v>0.1453391282279046</v>
       </c>
       <c r="J1653">
-        <v>1.163998579863488</v>
+        <v>1.209441025315652</v>
       </c>
       <c r="K1653">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="L1653">
-        <v>5.58</v>
+        <v>5.59</v>
       </c>
       <c r="M1653">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="N1653">
-        <v>5.39</v>
+        <v>5.36</v>
       </c>
       <c r="O1653">
         <v>1</v>
       </c>
       <c r="P1653" t="s">
-        <v>544</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1654" spans="1:16">
       <c r="A1654" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1654" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C1654">
-        <v>1.186165055685985</v>
+        <v>0.9637116934204695</v>
       </c>
       <c r="D1654" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E1654">
-        <v>1.428164345617728</v>
+        <v>1.195334052407844</v>
       </c>
       <c r="F1654">
         <v>1</v>
       </c>
       <c r="G1654">
-        <v>0.009473834944314016</v>
+        <v>0.00923628830657953</v>
       </c>
       <c r="H1654">
-        <v>0.008551835654382271</v>
+        <v>0.009564665947592156</v>
       </c>
       <c r="I1654">
-        <v>0.2419992899317438</v>
+        <v>0.2316223589873747</v>
       </c>
       <c r="J1654">
-        <v>1.163998579863488</v>
+        <v>1.209441025315652</v>
       </c>
       <c r="K1654">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="L1654">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="M1654">
-        <v>3.06</v>
+        <v>3.46</v>
       </c>
       <c r="N1654">
-        <v>4.99</v>
+        <v>5.38</v>
       </c>
       <c r="O1654">
         <v>1</v>
       </c>
       <c r="P1654" t="s">
-        <v>544</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1655" spans="1:16">
       <c r="A1655" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B1655" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C1655">
-        <v>1.117644956276428</v>
+        <v>1.015806103673627</v>
       </c>
       <c r="D1655" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E1655">
-        <v>1.428164345617728</v>
+        <v>1.195334052407844</v>
       </c>
       <c r="F1655">
         <v>1</v>
       </c>
       <c r="G1655">
-        <v>0.009242355043723571</v>
+        <v>0.009264193896326373</v>
       </c>
       <c r="H1655">
-        <v>0.008551835654382271</v>
+        <v>0.009564665947592156</v>
       </c>
       <c r="I1655">
-        <v>0.3105193893413003</v>
+        <v>0.1795279487342176</v>
       </c>
       <c r="J1655">
-        <v>1.163998579863488</v>
+        <v>1.209441025315652</v>
       </c>
       <c r="K1655">
-        <v>3.49</v>
+        <v>3.41</v>
       </c>
       <c r="L1655">
-        <v>5.18</v>
+        <v>5.14</v>
       </c>
       <c r="M1655">
-        <v>3.06</v>
+        <v>3.46</v>
       </c>
       <c r="N1655">
-        <v>4.99</v>
+        <v>5.38</v>
       </c>
       <c r="O1655">
         <v>1</v>
       </c>
       <c r="P1655" t="s">
-        <v>544</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1656" spans="1:16">
       <c r="A1656" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1656" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="C1656">
-        <v>1.166004970477794</v>
+        <v>1.262295539623123</v>
       </c>
       <c r="D1656" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E1656">
-        <v>1.428164345617728</v>
+        <v>1.132767590888904</v>
       </c>
       <c r="F1656">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1656">
-        <v>0.009313995029522208</v>
+        <v>0.009897704460376877</v>
       </c>
       <c r="H1656">
-        <v>0.008551835654382271</v>
+        <v>0.009647232409111094</v>
       </c>
       <c r="I1656">
-        <v>0.2621593751399343</v>
+        <v>0.1295279487342187</v>
       </c>
       <c r="J1656">
-        <v>1.163998579863488</v>
+        <v>1.209441025315652</v>
       </c>
       <c r="K1656">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="L1656">
-        <v>5.24</v>
+        <v>5.58</v>
       </c>
       <c r="M1656">
-        <v>3.06</v>
+        <v>3.52</v>
       </c>
       <c r="N1656">
-        <v>4.99</v>
+        <v>5.39</v>
       </c>
       <c r="O1656">
         <v>1</v>
       </c>
       <c r="P1656" t="s">
-        <v>544</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1657" spans="1:16">
       <c r="A1657" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1657" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C1657">
-        <v>1.167484871068238</v>
+        <v>1.024389949876279</v>
       </c>
       <c r="D1657" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E1657">
-        <v>1.428164345617728</v>
+        <v>1.289110462534105</v>
       </c>
       <c r="F1657">
         <v>1</v>
       </c>
       <c r="G1657">
-        <v>0.009152515128931763</v>
+        <v>0.00963561005012372</v>
       </c>
       <c r="H1657">
-        <v>0.008551835654382271</v>
+        <v>0.008690889537465897</v>
       </c>
       <c r="I1657">
-        <v>0.2606794745494909</v>
+        <v>0.264720512657826</v>
       </c>
       <c r="J1657">
-        <v>1.163998579863488</v>
+        <v>1.209441025315652</v>
       </c>
       <c r="K1657">
-        <v>3.43</v>
+        <v>3.56</v>
       </c>
       <c r="L1657">
-        <v>5.16</v>
+        <v>5.33</v>
       </c>
       <c r="M1657">
         <v>3.06</v>
@@ -84853,45 +84859,45 @@
         <v>1</v>
       </c>
       <c r="P1657" t="s">
-        <v>544</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1658" spans="1:16">
       <c r="A1658" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B1658" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C1658">
-        <v>1.193564558638205</v>
+        <v>0.9590508216483737</v>
       </c>
       <c r="D1658" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E1658">
-        <v>1.428164345617728</v>
+        <v>1.289110462534105</v>
       </c>
       <c r="F1658">
         <v>1</v>
       </c>
       <c r="G1658">
-        <v>0.008666435441361794</v>
+        <v>0.009400949178351626</v>
       </c>
       <c r="H1658">
-        <v>0.008551835654382271</v>
+        <v>0.008690889537465897</v>
       </c>
       <c r="I1658">
-        <v>0.2345997869795236</v>
+        <v>0.3300596408857315</v>
       </c>
       <c r="J1658">
-        <v>1.163998579863488</v>
+        <v>1.209441025315652</v>
       </c>
       <c r="K1658">
-        <v>3.21</v>
+        <v>3.49</v>
       </c>
       <c r="L1658">
-        <v>4.93</v>
+        <v>5.18</v>
       </c>
       <c r="M1658">
         <v>3.06</v>
@@ -84903,151 +84909,151 @@
         <v>1</v>
       </c>
       <c r="P1658" t="s">
-        <v>544</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1659" spans="1:16">
       <c r="A1659" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B1659" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C1659">
-        <v>1.159964416624554</v>
+        <v>1.006956411395218</v>
       </c>
       <c r="D1659" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E1659">
-        <v>1.313564558638205</v>
+        <v>1.289110462534105</v>
       </c>
       <c r="F1659">
         <v>1</v>
       </c>
       <c r="G1659">
-        <v>0.008400035583375447</v>
+        <v>0.009473043588604782</v>
       </c>
       <c r="H1659">
-        <v>0.008786435441361795</v>
+        <v>0.008690889537465897</v>
       </c>
       <c r="I1659">
-        <v>0.153600142013651</v>
+        <v>0.2821540511388871</v>
       </c>
       <c r="J1659">
-        <v>1.163998579863488</v>
+        <v>1.209441025315652</v>
       </c>
       <c r="K1659">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="L1659">
-        <v>4.78</v>
+        <v>5.24</v>
       </c>
       <c r="M1659">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
       <c r="N1659">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="O1659">
         <v>1</v>
       </c>
       <c r="P1659" t="s">
-        <v>544</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1660" spans="1:16">
       <c r="A1660" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B1660" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C1660">
-        <v>1.467684089993156</v>
+        <v>1.045334052407845</v>
       </c>
       <c r="D1660" t="s">
-        <v>237</v>
+        <v>424</v>
       </c>
       <c r="E1660">
-        <v>1.246044104194521</v>
+        <v>1.289110462534105</v>
       </c>
       <c r="F1660">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1660">
-        <v>0.008172315910006844</v>
+        <v>0.009414665947592155</v>
       </c>
       <c r="H1660">
-        <v>0.00797395589580548</v>
+        <v>0.008690889537465897</v>
       </c>
       <c r="I1660">
-        <v>0.2216399857986349</v>
+        <v>0.2437764101262605</v>
       </c>
       <c r="J1660">
-        <v>1.163998579863488</v>
+        <v>1.209441025315652</v>
       </c>
       <c r="K1660">
-        <v>2.88</v>
+        <v>3.46</v>
       </c>
       <c r="L1660">
-        <v>4.82</v>
+        <v>5.23</v>
       </c>
       <c r="M1660">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="N1660">
-        <v>4.61</v>
+        <v>4.99</v>
       </c>
       <c r="O1660">
         <v>1</v>
       </c>
       <c r="P1660" t="s">
-        <v>544</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1661" spans="1:16">
       <c r="A1661" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1661" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C1661">
-        <v>1.284389949876279</v>
+        <v>1.047694308736757</v>
       </c>
       <c r="D1661" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E1661">
-        <v>1.139050821648374</v>
+        <v>1.289110462534105</v>
       </c>
       <c r="F1661">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1661">
-        <v>0.009895610050123722</v>
+        <v>0.008812305691263242</v>
       </c>
       <c r="H1661">
-        <v>0.009580949178351627</v>
+        <v>0.008690889537465897</v>
       </c>
       <c r="I1661">
-        <v>0.1453391282279046</v>
+        <v>0.2414161537973483</v>
       </c>
       <c r="J1661">
         <v>1.209441025315652</v>
       </c>
       <c r="K1661">
-        <v>3.56</v>
+        <v>3.21</v>
       </c>
       <c r="L1661">
-        <v>5.59</v>
+        <v>4.93</v>
       </c>
       <c r="M1661">
-        <v>3.49</v>
+        <v>3.06</v>
       </c>
       <c r="N1661">
-        <v>5.36</v>
+        <v>4.99</v>
       </c>
       <c r="O1661">
         <v>1</v>
@@ -85058,46 +85064,46 @@
     </row>
     <row r="1662" spans="1:16">
       <c r="A1662" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B1662" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C1662">
-        <v>0.9637116934204695</v>
+        <v>1.018638411268323</v>
       </c>
       <c r="D1662" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E1662">
-        <v>1.195334052407844</v>
+        <v>1.167694308736757</v>
       </c>
       <c r="F1662">
         <v>1</v>
       </c>
       <c r="G1662">
-        <v>0.00923628830657953</v>
+        <v>0.008541361588731679</v>
       </c>
       <c r="H1662">
-        <v>0.009564665947592156</v>
+        <v>0.008932305691263243</v>
       </c>
       <c r="I1662">
-        <v>0.2316223589873747</v>
+        <v>0.1490558974684344</v>
       </c>
       <c r="J1662">
         <v>1.209441025315652</v>
       </c>
       <c r="K1662">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="L1662">
-        <v>5.1</v>
+        <v>4.78</v>
       </c>
       <c r="M1662">
-        <v>3.46</v>
+        <v>3.21</v>
       </c>
       <c r="N1662">
-        <v>5.38</v>
+        <v>5.05</v>
       </c>
       <c r="O1662">
         <v>1</v>
@@ -85108,46 +85114,46 @@
     </row>
     <row r="1663" spans="1:16">
       <c r="A1663" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B1663" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C1663">
-        <v>1.015806103673627</v>
+        <v>1.336809847090922</v>
       </c>
       <c r="D1663" t="s">
-        <v>424</v>
+        <v>236</v>
       </c>
       <c r="E1663">
-        <v>1.195334052407844</v>
+        <v>1.114715436837766</v>
       </c>
       <c r="F1663">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1663">
-        <v>0.009264193896326373</v>
+        <v>0.008303190152909078</v>
       </c>
       <c r="H1663">
-        <v>0.009564665947592156</v>
+        <v>0.008105284563162235</v>
       </c>
       <c r="I1663">
-        <v>0.1795279487342176</v>
+        <v>0.2220944102531566</v>
       </c>
       <c r="J1663">
         <v>1.209441025315652</v>
       </c>
       <c r="K1663">
-        <v>3.41</v>
+        <v>2.88</v>
       </c>
       <c r="L1663">
-        <v>5.14</v>
+        <v>4.82</v>
       </c>
       <c r="M1663">
-        <v>3.46</v>
+        <v>2.89</v>
       </c>
       <c r="N1663">
-        <v>5.38</v>
+        <v>4.61</v>
       </c>
       <c r="O1663">
         <v>1</v>
@@ -85158,401 +85164,51 @@
     </row>
     <row r="1664" spans="1:16">
       <c r="A1664" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B1664" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C1664">
-        <v>1.262295539623123</v>
+        <v>0.9751874881035487</v>
       </c>
       <c r="D1664" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="E1664">
-        <v>1.132767590888904</v>
+        <v>1.074037180381958</v>
       </c>
       <c r="F1664">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1664">
-        <v>0.009897704460376877</v>
+        <v>0.007844812511896452</v>
       </c>
       <c r="H1664">
-        <v>0.009647232409111094</v>
+        <v>0.007725962819618044</v>
       </c>
       <c r="I1664">
-        <v>0.1295279487342187</v>
+        <v>0.09884969227840879</v>
       </c>
       <c r="J1664">
         <v>1.209441025315652</v>
       </c>
       <c r="K1664">
-        <v>3.57</v>
+        <v>2.84</v>
       </c>
       <c r="L1664">
-        <v>5.58</v>
+        <v>4.41</v>
       </c>
       <c r="M1664">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="N1664">
-        <v>5.39</v>
+        <v>4.4</v>
       </c>
       <c r="O1664">
         <v>1</v>
       </c>
       <c r="P1664" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="1665" spans="1:16">
-      <c r="A1665" s="1">
-        <v>4</v>
-      </c>
-      <c r="B1665" t="s">
-        <v>249</v>
-      </c>
-      <c r="C1665">
-        <v>1.024389949876279</v>
-      </c>
-      <c r="D1665" t="s">
-        <v>422</v>
-      </c>
-      <c r="E1665">
-        <v>1.289110462534105</v>
-      </c>
-      <c r="F1665">
-        <v>1</v>
-      </c>
-      <c r="G1665">
-        <v>0.00963561005012372</v>
-      </c>
-      <c r="H1665">
-        <v>0.008690889537465897</v>
-      </c>
-      <c r="I1665">
-        <v>0.264720512657826</v>
-      </c>
-      <c r="J1665">
-        <v>1.209441025315652</v>
-      </c>
-      <c r="K1665">
-        <v>3.56</v>
-      </c>
-      <c r="L1665">
-        <v>5.33</v>
-      </c>
-      <c r="M1665">
-        <v>3.06</v>
-      </c>
-      <c r="N1665">
-        <v>4.99</v>
-      </c>
-      <c r="O1665">
-        <v>1</v>
-      </c>
-      <c r="P1665" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="1666" spans="1:16">
-      <c r="A1666" s="1">
-        <v>5</v>
-      </c>
-      <c r="B1666" t="s">
-        <v>243</v>
-      </c>
-      <c r="C1666">
-        <v>0.9590508216483737</v>
-      </c>
-      <c r="D1666" t="s">
-        <v>422</v>
-      </c>
-      <c r="E1666">
-        <v>1.289110462534105</v>
-      </c>
-      <c r="F1666">
-        <v>1</v>
-      </c>
-      <c r="G1666">
-        <v>0.009400949178351626</v>
-      </c>
-      <c r="H1666">
-        <v>0.008690889537465897</v>
-      </c>
-      <c r="I1666">
-        <v>0.3300596408857315</v>
-      </c>
-      <c r="J1666">
-        <v>1.209441025315652</v>
-      </c>
-      <c r="K1666">
-        <v>3.49</v>
-      </c>
-      <c r="L1666">
-        <v>5.18</v>
-      </c>
-      <c r="M1666">
-        <v>3.06</v>
-      </c>
-      <c r="N1666">
-        <v>4.99</v>
-      </c>
-      <c r="O1666">
-        <v>1</v>
-      </c>
-      <c r="P1666" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="1667" spans="1:16">
-      <c r="A1667" s="1">
-        <v>6</v>
-      </c>
-      <c r="B1667" t="s">
-        <v>248</v>
-      </c>
-      <c r="C1667">
-        <v>1.006956411395218</v>
-      </c>
-      <c r="D1667" t="s">
-        <v>422</v>
-      </c>
-      <c r="E1667">
-        <v>1.289110462534105</v>
-      </c>
-      <c r="F1667">
-        <v>1</v>
-      </c>
-      <c r="G1667">
-        <v>0.009473043588604782</v>
-      </c>
-      <c r="H1667">
-        <v>0.008690889537465897</v>
-      </c>
-      <c r="I1667">
-        <v>0.2821540511388871</v>
-      </c>
-      <c r="J1667">
-        <v>1.209441025315652</v>
-      </c>
-      <c r="K1667">
-        <v>3.5</v>
-      </c>
-      <c r="L1667">
-        <v>5.24</v>
-      </c>
-      <c r="M1667">
-        <v>3.06</v>
-      </c>
-      <c r="N1667">
-        <v>4.99</v>
-      </c>
-      <c r="O1667">
-        <v>1</v>
-      </c>
-      <c r="P1667" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="1668" spans="1:16">
-      <c r="A1668" s="1">
-        <v>7</v>
-      </c>
-      <c r="B1668" t="s">
-        <v>251</v>
-      </c>
-      <c r="C1668">
-        <v>1.045334052407845</v>
-      </c>
-      <c r="D1668" t="s">
-        <v>422</v>
-      </c>
-      <c r="E1668">
-        <v>1.289110462534105</v>
-      </c>
-      <c r="F1668">
-        <v>1</v>
-      </c>
-      <c r="G1668">
-        <v>0.009414665947592155</v>
-      </c>
-      <c r="H1668">
-        <v>0.008690889537465897</v>
-      </c>
-      <c r="I1668">
-        <v>0.2437764101262605</v>
-      </c>
-      <c r="J1668">
-        <v>1.209441025315652</v>
-      </c>
-      <c r="K1668">
-        <v>3.46</v>
-      </c>
-      <c r="L1668">
-        <v>5.23</v>
-      </c>
-      <c r="M1668">
-        <v>3.06</v>
-      </c>
-      <c r="N1668">
-        <v>4.99</v>
-      </c>
-      <c r="O1668">
-        <v>1</v>
-      </c>
-      <c r="P1668" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="1669" spans="1:16">
-      <c r="A1669" s="1">
-        <v>8</v>
-      </c>
-      <c r="B1669" t="s">
-        <v>242</v>
-      </c>
-      <c r="C1669">
-        <v>1.047694308736757</v>
-      </c>
-      <c r="D1669" t="s">
-        <v>422</v>
-      </c>
-      <c r="E1669">
-        <v>1.289110462534105</v>
-      </c>
-      <c r="F1669">
-        <v>1</v>
-      </c>
-      <c r="G1669">
-        <v>0.008812305691263242</v>
-      </c>
-      <c r="H1669">
-        <v>0.008690889537465897</v>
-      </c>
-      <c r="I1669">
-        <v>0.2414161537973483</v>
-      </c>
-      <c r="J1669">
-        <v>1.209441025315652</v>
-      </c>
-      <c r="K1669">
-        <v>3.21</v>
-      </c>
-      <c r="L1669">
-        <v>4.93</v>
-      </c>
-      <c r="M1669">
-        <v>3.06</v>
-      </c>
-      <c r="N1669">
-        <v>4.99</v>
-      </c>
-      <c r="O1669">
-        <v>1</v>
-      </c>
-      <c r="P1669" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="1670" spans="1:16">
-      <c r="A1670" s="1">
-        <v>9</v>
-      </c>
-      <c r="B1670" t="s">
-        <v>236</v>
-      </c>
-      <c r="C1670">
-        <v>1.018638411268323</v>
-      </c>
-      <c r="D1670" t="s">
-        <v>429</v>
-      </c>
-      <c r="E1670">
-        <v>1.167694308736757</v>
-      </c>
-      <c r="F1670">
-        <v>1</v>
-      </c>
-      <c r="G1670">
-        <v>0.008541361588731679</v>
-      </c>
-      <c r="H1670">
-        <v>0.008932305691263243</v>
-      </c>
-      <c r="I1670">
-        <v>0.1490558974684344</v>
-      </c>
-      <c r="J1670">
-        <v>1.209441025315652</v>
-      </c>
-      <c r="K1670">
-        <v>3.11</v>
-      </c>
-      <c r="L1670">
-        <v>4.78</v>
-      </c>
-      <c r="M1670">
-        <v>3.21</v>
-      </c>
-      <c r="N1670">
-        <v>5.05</v>
-      </c>
-      <c r="O1670">
-        <v>1</v>
-      </c>
-      <c r="P1670" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="1671" spans="1:16">
-      <c r="A1671" s="1">
-        <v>10</v>
-      </c>
-      <c r="B1671" t="s">
-        <v>250</v>
-      </c>
-      <c r="C1671">
-        <v>1.336809847090922</v>
-      </c>
-      <c r="D1671" t="s">
-        <v>237</v>
-      </c>
-      <c r="E1671">
-        <v>1.114715436837766</v>
-      </c>
-      <c r="F1671">
-        <v>-1</v>
-      </c>
-      <c r="G1671">
-        <v>0.008303190152909078</v>
-      </c>
-      <c r="H1671">
-        <v>0.008105284563162235</v>
-      </c>
-      <c r="I1671">
-        <v>0.2220944102531566</v>
-      </c>
-      <c r="J1671">
-        <v>1.209441025315652</v>
-      </c>
-      <c r="K1671">
-        <v>2.88</v>
-      </c>
-      <c r="L1671">
-        <v>4.82</v>
-      </c>
-      <c r="M1671">
-        <v>2.89</v>
-      </c>
-      <c r="N1671">
-        <v>4.61</v>
-      </c>
-      <c r="O1671">
-        <v>1</v>
-      </c>
-      <c r="P1671" t="s">
         <v>231</v>
       </c>
     </row>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -724,10 +724,10 @@
     <t>2021-07-29</t>
   </si>
   <si>
-    <t>2021-04-08</t>
+    <t>2021-03-24</t>
   </si>
   <si>
-    <t>2021-03-24</t>
+    <t>2021-04-08</t>
   </si>
   <si>
     <t>2021-04-15</t>
@@ -736,10 +736,10 @@
     <t>2021-05-10</t>
   </si>
   <si>
-    <t>2021-06-09</t>
+    <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-06-09</t>
   </si>
   <si>
     <t>2021-04-01</t>
@@ -748,31 +748,31 @@
     <t>2021-06-16</t>
   </si>
   <si>
-    <t>2021-06-21</t>
-  </si>
-  <si>
     <t>2021-07-27</t>
   </si>
   <si>
     <t>2021-06-11</t>
   </si>
   <si>
+    <t>2021-06-21</t>
+  </si>
+  <si>
     <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>2021-08-06</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
   </si>
   <si>
     <t>2021-06-02</t>
   </si>
   <si>
-    <t>2021-08-06</t>
-  </si>
-  <si>
     <t>2021-05-12</t>
   </si>
   <si>
-    <t>2021-06-18</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
+    <t>2021-07-26</t>
   </si>
   <si>
     <t>2016-10-20</t>
@@ -1285,19 +1285,22 @@
     <t>2021-07-20</t>
   </si>
   <si>
+    <t>2021-08-11</t>
+  </si>
+  <si>
     <t>2021-05-11</t>
   </si>
   <si>
     <t>2021-06-10</t>
   </si>
   <si>
-    <t>2021-06-25</t>
-  </si>
-  <si>
     <t>2021-07-19</t>
   </si>
   <si>
     <t>2021-04-09</t>
+  </si>
+  <si>
+    <t>2021-06-25</t>
   </si>
   <si>
     <t>2021-07-28</t>
@@ -1313,9 +1316,6 @@
   </si>
   <si>
     <t>2021-05-17</t>
-  </si>
-  <si>
-    <t>2021-07-08</t>
   </si>
   <si>
     <t>2016-08-24</t>
@@ -79685,7 +79685,7 @@
         <v>3.020628231962571</v>
       </c>
       <c r="D1554" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E1554">
         <v>2.677981100714109</v>
@@ -79785,7 +79785,7 @@
         <v>3.033765118290027</v>
       </c>
       <c r="D1556" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E1556">
         <v>2.690823603034227</v>
@@ -79929,10 +79929,10 @@
         <v>0</v>
       </c>
       <c r="B1559" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C1559">
-        <v>2.49970236281472</v>
+        <v>2.447896914138154</v>
       </c>
       <c r="D1559" t="s">
         <v>421</v>
@@ -79944,22 +79944,22 @@
         <v>-1</v>
       </c>
       <c r="G1559">
-        <v>0.008960297637185281</v>
+        <v>0.008632103085861846</v>
       </c>
       <c r="H1559">
         <v>0.008165271375080696</v>
       </c>
       <c r="I1559">
-        <v>0.2249737378954171</v>
+        <v>0.1731682892188515</v>
       </c>
       <c r="J1559">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1559">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="L1559">
-        <v>5.73</v>
+        <v>5.54</v>
       </c>
       <c r="M1559">
         <v>3.41</v>
@@ -79979,43 +79979,43 @@
         <v>1</v>
       </c>
       <c r="B1560" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C1560">
-        <v>2.447896914138154</v>
+        <v>2.496534073595869</v>
       </c>
       <c r="D1560" t="s">
-        <v>421</v>
+        <v>250</v>
       </c>
       <c r="E1560">
-        <v>2.274728624919303</v>
+        <v>2.255171233053583</v>
       </c>
       <c r="F1560">
         <v>-1</v>
       </c>
       <c r="G1560">
-        <v>0.008632103085861846</v>
+        <v>0.008663465926404131</v>
       </c>
       <c r="H1560">
-        <v>0.008165271375080696</v>
+        <v>0.008404828766946416</v>
       </c>
       <c r="I1560">
-        <v>0.1731682892188515</v>
+        <v>0.2413628405422856</v>
       </c>
       <c r="J1560">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1560">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="L1560">
-        <v>5.54</v>
+        <v>5.58</v>
       </c>
       <c r="M1560">
-        <v>3.41</v>
+        <v>3.56</v>
       </c>
       <c r="N1560">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1560">
         <v>1</v>
@@ -80029,43 +80029,43 @@
         <v>2</v>
       </c>
       <c r="B1561" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1561">
-        <v>2.496534073595869</v>
+        <v>2.093843408650743</v>
       </c>
       <c r="D1561" t="s">
-        <v>248</v>
+        <v>422</v>
       </c>
       <c r="E1561">
-        <v>2.255171233053583</v>
+        <v>2.294746132989026</v>
       </c>
       <c r="F1561">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1561">
-        <v>0.008663465926404131</v>
+        <v>0.007466156591349258</v>
       </c>
       <c r="H1561">
-        <v>0.008404828766946416</v>
+        <v>0.007805253867010974</v>
       </c>
       <c r="I1561">
-        <v>0.2413628405422856</v>
+        <v>0.2009027243382824</v>
       </c>
       <c r="J1561">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1561">
-        <v>3.57</v>
+        <v>3.11</v>
       </c>
       <c r="L1561">
-        <v>5.58</v>
+        <v>4.78</v>
       </c>
       <c r="M1561">
-        <v>3.56</v>
+        <v>3.19</v>
       </c>
       <c r="N1561">
-        <v>5.33</v>
+        <v>5.05</v>
       </c>
       <c r="O1561">
         <v>1</v>
@@ -80079,43 +80079,43 @@
         <v>3</v>
       </c>
       <c r="B1562" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C1562">
-        <v>2.093843408650743</v>
+        <v>2.113860916720465</v>
       </c>
       <c r="D1562" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1562">
-        <v>2.294746132989026</v>
+        <v>2.005683873466753</v>
       </c>
       <c r="F1562">
         <v>1</v>
       </c>
       <c r="G1562">
-        <v>0.007466156591349258</v>
+        <v>0.007106139083279535</v>
       </c>
       <c r="H1562">
-        <v>0.007805253867010974</v>
+        <v>0.006894316126533248</v>
       </c>
       <c r="I1562">
-        <v>0.2009027243382824</v>
+        <v>-0.1081770432537121</v>
       </c>
       <c r="J1562">
         <v>0.8637159457714654</v>
       </c>
       <c r="K1562">
-        <v>3.11</v>
+        <v>2.89</v>
       </c>
       <c r="L1562">
-        <v>4.78</v>
+        <v>4.61</v>
       </c>
       <c r="M1562">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="N1562">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="O1562">
         <v>1</v>
@@ -80126,96 +80126,96 @@
     </row>
     <row r="1563" spans="1:16">
       <c r="A1563" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1563" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C1563">
-        <v>2.113860916720465</v>
+        <v>1.99772260130418</v>
       </c>
       <c r="D1563" t="s">
-        <v>420</v>
+        <v>230</v>
       </c>
       <c r="E1563">
-        <v>2.03478114912847</v>
+        <v>2.324483874107317</v>
       </c>
       <c r="F1563">
         <v>1</v>
       </c>
       <c r="G1563">
-        <v>0.007106139083279535</v>
+        <v>0.00850227739869582</v>
       </c>
       <c r="H1563">
-        <v>0.00678521885087153</v>
+        <v>0.008955516125892682</v>
       </c>
       <c r="I1563">
-        <v>-0.07907976759199498</v>
+        <v>0.3267612728031368</v>
       </c>
       <c r="J1563">
-        <v>0.8637159457714654</v>
+        <v>0.9034103885266167</v>
       </c>
       <c r="K1563">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="L1563">
-        <v>4.61</v>
+        <v>5.25</v>
       </c>
       <c r="M1563">
-        <v>2.75</v>
+        <v>3.67</v>
       </c>
       <c r="N1563">
-        <v>4.41</v>
+        <v>5.64</v>
       </c>
       <c r="O1563">
         <v>1</v>
       </c>
       <c r="P1563" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1564" spans="1:16">
       <c r="A1564" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1564" t="s">
         <v>237</v>
       </c>
       <c r="C1564">
-        <v>1.99772260130418</v>
+        <v>2.351245146910454</v>
       </c>
       <c r="D1564" t="s">
-        <v>230</v>
+        <v>421</v>
       </c>
       <c r="E1564">
-        <v>2.324483874107317</v>
+        <v>2.139370575124237</v>
       </c>
       <c r="F1564">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1564">
-        <v>0.00850227739869582</v>
+        <v>0.009108754853089547</v>
       </c>
       <c r="H1564">
-        <v>0.008955516125892682</v>
+        <v>0.008300629424875762</v>
       </c>
       <c r="I1564">
-        <v>0.3267612728031368</v>
+        <v>0.2118745717862169</v>
       </c>
       <c r="J1564">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1564">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="L1564">
-        <v>5.25</v>
+        <v>5.73</v>
       </c>
       <c r="M1564">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="N1564">
-        <v>5.64</v>
+        <v>5.22</v>
       </c>
       <c r="O1564">
         <v>1</v>
@@ -80226,13 +80226,13 @@
     </row>
     <row r="1565" spans="1:16">
       <c r="A1565" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1565" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C1565">
-        <v>2.351245146910454</v>
+        <v>2.305790809074712</v>
       </c>
       <c r="D1565" t="s">
         <v>421</v>
@@ -80244,22 +80244,22 @@
         <v>-1</v>
       </c>
       <c r="G1565">
-        <v>0.009108754853089547</v>
+        <v>0.008774209190925288</v>
       </c>
       <c r="H1565">
         <v>0.008300629424875762</v>
       </c>
       <c r="I1565">
-        <v>0.2118745717862169</v>
+        <v>0.1664202339504754</v>
       </c>
       <c r="J1565">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1565">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="L1565">
-        <v>5.73</v>
+        <v>5.54</v>
       </c>
       <c r="M1565">
         <v>3.41</v>
@@ -80276,46 +80276,46 @@
     </row>
     <row r="1566" spans="1:16">
       <c r="A1566" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1566" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C1566">
-        <v>2.373859016845244</v>
+        <v>2.354824912959979</v>
       </c>
       <c r="D1566" t="s">
-        <v>421</v>
+        <v>250</v>
       </c>
       <c r="E1566">
-        <v>2.139370575124237</v>
+        <v>2.113859016845244</v>
       </c>
       <c r="F1566">
         <v>-1</v>
       </c>
       <c r="G1566">
-        <v>0.008806140983154756</v>
+        <v>0.008805175087040021</v>
       </c>
       <c r="H1566">
-        <v>0.008300629424875762</v>
+        <v>0.008546140983154756</v>
       </c>
       <c r="I1566">
-        <v>0.2344884417210076</v>
+        <v>0.2409658961147341</v>
       </c>
       <c r="J1566">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1566">
+        <v>3.57</v>
+      </c>
+      <c r="L1566">
+        <v>5.58</v>
+      </c>
+      <c r="M1566">
         <v>3.56</v>
       </c>
-      <c r="L1566">
-        <v>5.59</v>
-      </c>
-      <c r="M1566">
-        <v>3.41</v>
-      </c>
       <c r="N1566">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1566">
         <v>1</v>
@@ -80326,46 +80326,46 @@
     </row>
     <row r="1567" spans="1:16">
       <c r="A1567" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1567" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1567">
-        <v>2.354824912959979</v>
+        <v>1.970393691682222</v>
       </c>
       <c r="D1567" t="s">
-        <v>248</v>
+        <v>422</v>
       </c>
       <c r="E1567">
-        <v>2.113859016845244</v>
+        <v>2.168120860600093</v>
       </c>
       <c r="F1567">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1567">
-        <v>0.008805175087040021</v>
+        <v>0.007589606308317778</v>
       </c>
       <c r="H1567">
-        <v>0.008546140983154756</v>
+        <v>0.007931879139399908</v>
       </c>
       <c r="I1567">
-        <v>0.2409658961147341</v>
+        <v>0.1977271689178703</v>
       </c>
       <c r="J1567">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1567">
-        <v>3.57</v>
+        <v>3.11</v>
       </c>
       <c r="L1567">
-        <v>5.58</v>
+        <v>4.78</v>
       </c>
       <c r="M1567">
-        <v>3.56</v>
+        <v>3.19</v>
       </c>
       <c r="N1567">
-        <v>5.33</v>
+        <v>5.05</v>
       </c>
       <c r="O1567">
         <v>1</v>
@@ -80376,46 +80376,46 @@
     </row>
     <row r="1568" spans="1:16">
       <c r="A1568" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1568" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C1568">
-        <v>1.970393691682222</v>
+        <v>1.999143977158078</v>
       </c>
       <c r="D1568" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1568">
-        <v>2.168120860600093</v>
+        <v>1.893348600469675</v>
       </c>
       <c r="F1568">
         <v>1</v>
       </c>
       <c r="G1568">
-        <v>0.007589606308317778</v>
+        <v>0.007220856022841922</v>
       </c>
       <c r="H1568">
-        <v>0.007931879139399908</v>
+        <v>0.007006651399530326</v>
       </c>
       <c r="I1568">
-        <v>0.1977271689178703</v>
+        <v>-0.1057953766884032</v>
       </c>
       <c r="J1568">
         <v>0.9034103885266167</v>
       </c>
       <c r="K1568">
-        <v>3.11</v>
+        <v>2.89</v>
       </c>
       <c r="L1568">
-        <v>4.78</v>
+        <v>4.61</v>
       </c>
       <c r="M1568">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="N1568">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="O1568">
         <v>1</v>
@@ -80426,96 +80426,96 @@
     </row>
     <row r="1569" spans="1:16">
       <c r="A1569" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1569" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C1569">
-        <v>1.999143977158078</v>
+        <v>1.893712084063664</v>
       </c>
       <c r="D1569" t="s">
-        <v>420</v>
+        <v>230</v>
       </c>
       <c r="E1569">
-        <v>1.925621431551804</v>
+        <v>2.218450930142679</v>
       </c>
       <c r="F1569">
         <v>1</v>
       </c>
       <c r="G1569">
-        <v>0.007220856022841922</v>
+        <v>0.008606287915936336</v>
       </c>
       <c r="H1569">
-        <v>0.006894378568448197</v>
+        <v>0.009061549069857322</v>
       </c>
       <c r="I1569">
-        <v>-0.07352254560627403</v>
+        <v>0.3247388460790153</v>
       </c>
       <c r="J1569">
-        <v>0.9034103885266167</v>
+        <v>0.9323021988712045</v>
       </c>
       <c r="K1569">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="L1569">
-        <v>4.61</v>
+        <v>5.25</v>
       </c>
       <c r="M1569">
-        <v>2.75</v>
+        <v>3.67</v>
       </c>
       <c r="N1569">
-        <v>4.41</v>
+        <v>5.64</v>
       </c>
       <c r="O1569">
         <v>1</v>
       </c>
       <c r="P1569" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1570" spans="1:16">
       <c r="A1570" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1570" t="s">
         <v>237</v>
       </c>
       <c r="C1570">
-        <v>1.893712084063664</v>
+        <v>2.243189776221695</v>
       </c>
       <c r="D1570" t="s">
-        <v>230</v>
+        <v>421</v>
       </c>
       <c r="E1570">
-        <v>2.218450930142679</v>
+        <v>2.040849501849193</v>
       </c>
       <c r="F1570">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1570">
-        <v>0.008606287915936336</v>
+        <v>0.009216810223778306</v>
       </c>
       <c r="H1570">
-        <v>0.009061549069857322</v>
+        <v>0.008399150498150806</v>
       </c>
       <c r="I1570">
-        <v>0.3247388460790153</v>
+        <v>0.2023402743725029</v>
       </c>
       <c r="J1570">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1570">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="L1570">
-        <v>5.25</v>
+        <v>5.73</v>
       </c>
       <c r="M1570">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="N1570">
-        <v>5.64</v>
+        <v>5.22</v>
       </c>
       <c r="O1570">
         <v>1</v>
@@ -80526,13 +80526,13 @@
     </row>
     <row r="1571" spans="1:16">
       <c r="A1571" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1571" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C1571">
-        <v>2.243189776221695</v>
+        <v>2.271004172018512</v>
       </c>
       <c r="D1571" t="s">
         <v>421</v>
@@ -80544,22 +80544,22 @@
         <v>-1</v>
       </c>
       <c r="G1571">
-        <v>0.009216810223778306</v>
+        <v>0.008908995827981488</v>
       </c>
       <c r="H1571">
         <v>0.008399150498150806</v>
       </c>
       <c r="I1571">
-        <v>0.2023402743725029</v>
+        <v>0.2301546701693193</v>
       </c>
       <c r="J1571">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1571">
-        <v>3.74</v>
+        <v>3.56</v>
       </c>
       <c r="L1571">
-        <v>5.73</v>
+        <v>5.59</v>
       </c>
       <c r="M1571">
         <v>3.41</v>
@@ -80576,43 +80576,43 @@
     </row>
     <row r="1572" spans="1:16">
       <c r="A1572" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1572" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C1572">
-        <v>2.271004172018512</v>
+        <v>1.911526479860481</v>
       </c>
       <c r="D1572" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E1572">
-        <v>2.040849501849193</v>
+        <v>2.078141589804041</v>
       </c>
       <c r="F1572">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1572">
-        <v>0.008908995827981488</v>
+        <v>0.008288473520139519</v>
       </c>
       <c r="H1572">
-        <v>0.008399150498150806</v>
+        <v>0.008361858410195959</v>
       </c>
       <c r="I1572">
-        <v>0.2301546701693193</v>
+        <v>0.1666151099435602</v>
       </c>
       <c r="J1572">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1572">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="L1572">
-        <v>5.59</v>
+        <v>5.1</v>
       </c>
       <c r="M1572">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="N1572">
         <v>5.22</v>
@@ -80626,46 +80626,46 @@
     </row>
     <row r="1573" spans="1:16">
       <c r="A1573" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1573" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C1573">
-        <v>1.911526479860481</v>
+        <v>2.2516811500298</v>
       </c>
       <c r="D1573" t="s">
-        <v>423</v>
+        <v>250</v>
       </c>
       <c r="E1573">
-        <v>2.078141589804041</v>
+        <v>2.011004172018512</v>
       </c>
       <c r="F1573">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1573">
-        <v>0.008288473520139519</v>
+        <v>0.0089083188499702</v>
       </c>
       <c r="H1573">
-        <v>0.008361858410195959</v>
+        <v>0.008648995827981487</v>
       </c>
       <c r="I1573">
-        <v>0.1666151099435602</v>
+        <v>0.2406769780112881</v>
       </c>
       <c r="J1573">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1573">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="L1573">
-        <v>5.1</v>
+        <v>5.58</v>
       </c>
       <c r="M1573">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="N1573">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1573">
         <v>1</v>
@@ -80676,46 +80676,46 @@
     </row>
     <row r="1574" spans="1:16">
       <c r="A1574" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1574" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1574">
-        <v>2.2516811500298</v>
+        <v>1.880540161510555</v>
       </c>
       <c r="D1574" t="s">
-        <v>248</v>
+        <v>422</v>
       </c>
       <c r="E1574">
-        <v>2.011004172018512</v>
+        <v>2.075955985600858</v>
       </c>
       <c r="F1574">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1574">
-        <v>0.0089083188499702</v>
+        <v>0.007679459838489447</v>
       </c>
       <c r="H1574">
-        <v>0.008648995827981487</v>
+        <v>0.008024044014399141</v>
       </c>
       <c r="I1574">
-        <v>0.2406769780112881</v>
+        <v>0.1954158240903032</v>
       </c>
       <c r="J1574">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1574">
-        <v>3.57</v>
+        <v>3.11</v>
       </c>
       <c r="L1574">
-        <v>5.58</v>
+        <v>4.78</v>
       </c>
       <c r="M1574">
-        <v>3.56</v>
+        <v>3.19</v>
       </c>
       <c r="N1574">
-        <v>5.33</v>
+        <v>5.05</v>
       </c>
       <c r="O1574">
         <v>1</v>
@@ -80726,46 +80726,46 @@
     </row>
     <row r="1575" spans="1:16">
       <c r="A1575" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1575" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C1575">
-        <v>1.880540161510555</v>
+        <v>1.76226175520578</v>
       </c>
       <c r="D1575" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1575">
-        <v>2.075955985600858</v>
+        <v>1.811584777194491</v>
       </c>
       <c r="F1575">
         <v>1</v>
       </c>
       <c r="G1575">
-        <v>0.007679459838489447</v>
+        <v>0.007057738244794221</v>
       </c>
       <c r="H1575">
-        <v>0.008024044014399141</v>
+        <v>0.007088415222805509</v>
       </c>
       <c r="I1575">
-        <v>0.1954158240903032</v>
+        <v>0.04932302198871152</v>
       </c>
       <c r="J1575">
         <v>0.9323021988712045</v>
       </c>
       <c r="K1575">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="L1575">
-        <v>4.78</v>
+        <v>4.41</v>
       </c>
       <c r="M1575">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="N1575">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="O1575">
         <v>1</v>
@@ -80776,96 +80776,96 @@
     </row>
     <row r="1576" spans="1:16">
       <c r="A1576" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1576" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C1576">
-        <v>1.915646645262219</v>
+        <v>1.792368417943001</v>
       </c>
       <c r="D1576" t="s">
-        <v>420</v>
+        <v>230</v>
       </c>
       <c r="E1576">
-        <v>1.846168953104188</v>
+        <v>2.115136692736337</v>
       </c>
       <c r="F1576">
         <v>1</v>
       </c>
       <c r="G1576">
-        <v>0.007304353354737781</v>
+        <v>0.008707631582056998</v>
       </c>
       <c r="H1576">
-        <v>0.006973831046895813</v>
+        <v>0.009164863307263663</v>
       </c>
       <c r="I1576">
-        <v>-0.06947769215803135</v>
+        <v>0.322768274793336</v>
       </c>
       <c r="J1576">
-        <v>0.9323021988712045</v>
+        <v>0.9604532172380553</v>
       </c>
       <c r="K1576">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="L1576">
-        <v>4.61</v>
+        <v>5.25</v>
       </c>
       <c r="M1576">
-        <v>2.75</v>
+        <v>3.67</v>
       </c>
       <c r="N1576">
-        <v>4.41</v>
+        <v>5.64</v>
       </c>
       <c r="O1576">
         <v>1</v>
       </c>
       <c r="P1576" t="s">
-        <v>547</v>
+        <v>418</v>
       </c>
     </row>
     <row r="1577" spans="1:16">
       <c r="A1577" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1577" t="s">
         <v>237</v>
       </c>
       <c r="C1577">
-        <v>1.792368417943001</v>
+        <v>2.137904967529674</v>
       </c>
       <c r="D1577" t="s">
-        <v>230</v>
+        <v>421</v>
       </c>
       <c r="E1577">
-        <v>2.115136692736337</v>
+        <v>1.944854529218231</v>
       </c>
       <c r="F1577">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1577">
-        <v>0.008707631582056998</v>
+        <v>0.009322095032470328</v>
       </c>
       <c r="H1577">
-        <v>0.009164863307263663</v>
+        <v>0.008495145470781769</v>
       </c>
       <c r="I1577">
-        <v>0.322768274793336</v>
+        <v>0.1930504383114426</v>
       </c>
       <c r="J1577">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1577">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="L1577">
-        <v>5.25</v>
+        <v>5.73</v>
       </c>
       <c r="M1577">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="N1577">
-        <v>5.64</v>
+        <v>5.22</v>
       </c>
       <c r="O1577">
         <v>1</v>
@@ -80876,13 +80876,13 @@
     </row>
     <row r="1578" spans="1:16">
       <c r="A1578" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1578" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C1578">
-        <v>2.137904967529674</v>
+        <v>2.170786546632523</v>
       </c>
       <c r="D1578" t="s">
         <v>421</v>
@@ -80894,22 +80894,22 @@
         <v>-1</v>
       </c>
       <c r="G1578">
-        <v>0.009322095032470328</v>
+        <v>0.009009213453367476</v>
       </c>
       <c r="H1578">
         <v>0.008495145470781769</v>
       </c>
       <c r="I1578">
-        <v>0.1930504383114426</v>
+        <v>0.225932017414292</v>
       </c>
       <c r="J1578">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1578">
-        <v>3.74</v>
+        <v>3.56</v>
       </c>
       <c r="L1578">
-        <v>5.73</v>
+        <v>5.59</v>
       </c>
       <c r="M1578">
         <v>3.41</v>
@@ -80926,43 +80926,43 @@
     </row>
     <row r="1579" spans="1:16">
       <c r="A1579" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1579" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C1579">
-        <v>2.170786546632523</v>
+        <v>1.81524999704585</v>
       </c>
       <c r="D1579" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E1579">
-        <v>1.944854529218231</v>
+        <v>1.983272657907753</v>
       </c>
       <c r="F1579">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1579">
-        <v>0.009009213453367476</v>
+        <v>0.008384750002954149</v>
       </c>
       <c r="H1579">
-        <v>0.008495145470781769</v>
+        <v>0.008456727342092248</v>
       </c>
       <c r="I1579">
-        <v>0.225932017414292</v>
+        <v>0.1680226608619027</v>
       </c>
       <c r="J1579">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1579">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="L1579">
-        <v>5.59</v>
+        <v>5.1</v>
       </c>
       <c r="M1579">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="N1579">
         <v>5.22</v>
@@ -80976,46 +80976,46 @@
     </row>
     <row r="1580" spans="1:16">
       <c r="A1580" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1580" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C1580">
-        <v>1.81524999704585</v>
+        <v>2.151182014460143</v>
       </c>
       <c r="D1580" t="s">
-        <v>423</v>
+        <v>250</v>
       </c>
       <c r="E1580">
-        <v>1.983272657907753</v>
+        <v>1.910786546632523</v>
       </c>
       <c r="F1580">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1580">
-        <v>0.008384750002954149</v>
+        <v>0.009008817985539857</v>
       </c>
       <c r="H1580">
-        <v>0.008456727342092248</v>
+        <v>0.008749213453367478</v>
       </c>
       <c r="I1580">
-        <v>0.1680226608619027</v>
+        <v>0.2403954678276197</v>
       </c>
       <c r="J1580">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1580">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="L1580">
-        <v>5.1</v>
+        <v>5.58</v>
       </c>
       <c r="M1580">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="N1580">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1580">
         <v>1</v>
@@ -81026,46 +81026,46 @@
     </row>
     <row r="1581" spans="1:16">
       <c r="A1581" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1581" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C1581">
-        <v>2.151182014460143</v>
+        <v>1.828018271839186</v>
       </c>
       <c r="D1581" t="s">
-        <v>248</v>
+        <v>425</v>
       </c>
       <c r="E1581">
-        <v>1.910786546632523</v>
+        <v>1.974854529218231</v>
       </c>
       <c r="F1581">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1581">
-        <v>0.009008817985539857</v>
+        <v>0.008531981728160814</v>
       </c>
       <c r="H1581">
-        <v>0.008749213453367478</v>
+        <v>0.008525145470781769</v>
       </c>
       <c r="I1581">
-        <v>0.2403954678276197</v>
+        <v>0.1468362573790447</v>
       </c>
       <c r="J1581">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1581">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="L1581">
-        <v>5.58</v>
+        <v>5.18</v>
       </c>
       <c r="M1581">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="N1581">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="O1581">
         <v>1</v>
@@ -81076,46 +81076,46 @@
     </row>
     <row r="1582" spans="1:16">
       <c r="A1582" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1582" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C1582">
-        <v>1.828018271839186</v>
+        <v>1.792990494389648</v>
       </c>
       <c r="D1582" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E1582">
-        <v>1.974854529218231</v>
+        <v>1.966945172665842</v>
       </c>
       <c r="F1582">
         <v>1</v>
       </c>
       <c r="G1582">
-        <v>0.008531981728160814</v>
+        <v>0.007767009505610351</v>
       </c>
       <c r="H1582">
-        <v>0.008525145470781769</v>
+        <v>0.008133054827334157</v>
       </c>
       <c r="I1582">
-        <v>0.1468362573790447</v>
+        <v>0.173954678276194</v>
       </c>
       <c r="J1582">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1582">
-        <v>3.49</v>
+        <v>3.11</v>
       </c>
       <c r="L1582">
-        <v>5.18</v>
+        <v>4.78</v>
       </c>
       <c r="M1582">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="N1582">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="O1582">
         <v>1</v>
@@ -81126,46 +81126,46 @@
     </row>
     <row r="1583" spans="1:16">
       <c r="A1583" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1583" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C1583">
-        <v>1.792990494389648</v>
+        <v>1.682312863043923</v>
       </c>
       <c r="D1583" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1583">
-        <v>1.986154237010604</v>
+        <v>1.731917395216303</v>
       </c>
       <c r="F1583">
         <v>1</v>
       </c>
       <c r="G1583">
-        <v>0.007767009505610351</v>
+        <v>0.007137687136956078</v>
       </c>
       <c r="H1583">
-        <v>0.008113845762989395</v>
+        <v>0.007168082604783697</v>
       </c>
       <c r="I1583">
-        <v>0.1931637426209551</v>
+        <v>0.04960453217238037</v>
       </c>
       <c r="J1583">
         <v>0.9604532172380553</v>
       </c>
       <c r="K1583">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="L1583">
-        <v>4.78</v>
+        <v>4.41</v>
       </c>
       <c r="M1583">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="N1583">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="O1583">
         <v>1</v>
@@ -81176,96 +81176,96 @@
     </row>
     <row r="1584" spans="1:16">
       <c r="A1584" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1584" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C1584">
-        <v>1.83429020218202</v>
+        <v>1.676370302057997</v>
       </c>
       <c r="D1584" t="s">
-        <v>420</v>
+        <v>230</v>
       </c>
       <c r="E1584">
-        <v>1.768753652595348</v>
+        <v>1.996883057931346</v>
       </c>
       <c r="F1584">
         <v>1</v>
       </c>
       <c r="G1584">
-        <v>0.007385709797817981</v>
+        <v>0.008823629697942004</v>
       </c>
       <c r="H1584">
-        <v>0.007051246347404653</v>
+        <v>0.009283116942068651</v>
       </c>
       <c r="I1584">
-        <v>-0.06553654958667243</v>
+        <v>0.3205127558733496</v>
       </c>
       <c r="J1584">
-        <v>0.9604532172380553</v>
+        <v>0.9926749160950009</v>
       </c>
       <c r="K1584">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="L1584">
-        <v>4.61</v>
+        <v>5.25</v>
       </c>
       <c r="M1584">
-        <v>2.75</v>
+        <v>3.67</v>
       </c>
       <c r="N1584">
-        <v>4.41</v>
+        <v>5.64</v>
       </c>
       <c r="O1584">
         <v>1</v>
       </c>
       <c r="P1584" t="s">
-        <v>418</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1585" spans="1:16">
       <c r="A1585" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1585" t="s">
         <v>237</v>
       </c>
       <c r="C1585">
-        <v>1.676370302057997</v>
+        <v>2.017395813804697</v>
       </c>
       <c r="D1585" t="s">
-        <v>230</v>
+        <v>421</v>
       </c>
       <c r="E1585">
-        <v>1.996883057931346</v>
+        <v>1.834978536116047</v>
       </c>
       <c r="F1585">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1585">
-        <v>0.008823629697942004</v>
+        <v>0.009442604186195304</v>
       </c>
       <c r="H1585">
-        <v>0.009283116942068651</v>
+        <v>0.008605021463883953</v>
       </c>
       <c r="I1585">
-        <v>0.3205127558733496</v>
+        <v>0.1824172776886503</v>
       </c>
       <c r="J1585">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1585">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="L1585">
-        <v>5.25</v>
+        <v>5.73</v>
       </c>
       <c r="M1585">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="N1585">
-        <v>5.64</v>
+        <v>5.22</v>
       </c>
       <c r="O1585">
         <v>1</v>
@@ -81276,13 +81276,13 @@
     </row>
     <row r="1586" spans="1:16">
       <c r="A1586" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1586" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C1586">
-        <v>2.017395813804697</v>
+        <v>2.056077298701796</v>
       </c>
       <c r="D1586" t="s">
         <v>421</v>
@@ -81294,22 +81294,22 @@
         <v>-1</v>
       </c>
       <c r="G1586">
-        <v>0.009442604186195304</v>
+        <v>0.009123922701298205</v>
       </c>
       <c r="H1586">
         <v>0.008605021463883953</v>
       </c>
       <c r="I1586">
-        <v>0.1824172776886503</v>
+        <v>0.2210987625857497</v>
       </c>
       <c r="J1586">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1586">
-        <v>3.74</v>
+        <v>3.56</v>
       </c>
       <c r="L1586">
-        <v>5.73</v>
+        <v>5.59</v>
       </c>
       <c r="M1586">
         <v>3.41</v>
@@ -81326,43 +81326,43 @@
     </row>
     <row r="1587" spans="1:16">
       <c r="A1587" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1587" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C1587">
-        <v>2.056077298701796</v>
+        <v>1.705051786955097</v>
       </c>
       <c r="D1587" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E1587">
-        <v>1.834978536116047</v>
+        <v>1.874685532759846</v>
       </c>
       <c r="F1587">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1587">
-        <v>0.009123922701298205</v>
+        <v>0.008494948213044903</v>
       </c>
       <c r="H1587">
-        <v>0.008605021463883953</v>
+        <v>0.008565314467240154</v>
       </c>
       <c r="I1587">
-        <v>0.2210987625857497</v>
+        <v>0.1696337458047497</v>
       </c>
       <c r="J1587">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1587">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="L1587">
-        <v>5.59</v>
+        <v>5.1</v>
       </c>
       <c r="M1587">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="N1587">
         <v>5.22</v>
@@ -81376,46 +81376,46 @@
     </row>
     <row r="1588" spans="1:16">
       <c r="A1588" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1588" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C1588">
-        <v>1.705051786955097</v>
+        <v>2.036150549540847</v>
       </c>
       <c r="D1588" t="s">
-        <v>423</v>
+        <v>250</v>
       </c>
       <c r="E1588">
-        <v>1.874685532759846</v>
+        <v>1.796077298701797</v>
       </c>
       <c r="F1588">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1588">
-        <v>0.008494948213044903</v>
+        <v>0.009123849450459152</v>
       </c>
       <c r="H1588">
-        <v>0.008565314467240154</v>
+        <v>0.008863922701298205</v>
       </c>
       <c r="I1588">
-        <v>0.1696337458047497</v>
+        <v>0.2400732508390506</v>
       </c>
       <c r="J1588">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1588">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="L1588">
-        <v>5.1</v>
+        <v>5.58</v>
       </c>
       <c r="M1588">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="N1588">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1588">
         <v>1</v>
@@ -81426,46 +81426,46 @@
     </row>
     <row r="1589" spans="1:16">
       <c r="A1589" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1589" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C1589">
-        <v>2.036150549540847</v>
+        <v>1.715564542828446</v>
       </c>
       <c r="D1589" t="s">
-        <v>248</v>
+        <v>425</v>
       </c>
       <c r="E1589">
-        <v>1.796077298701797</v>
+        <v>1.864978536116047</v>
       </c>
       <c r="F1589">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1589">
-        <v>0.009123849450459152</v>
+        <v>0.008644435457171553</v>
       </c>
       <c r="H1589">
-        <v>0.008863922701298205</v>
+        <v>0.008635021463883953</v>
       </c>
       <c r="I1589">
-        <v>0.2400732508390506</v>
+        <v>0.1494139932876006</v>
       </c>
       <c r="J1589">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1589">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="L1589">
-        <v>5.58</v>
+        <v>5.18</v>
       </c>
       <c r="M1589">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="N1589">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="O1589">
         <v>1</v>
@@ -81476,46 +81476,46 @@
     </row>
     <row r="1590" spans="1:16">
       <c r="A1590" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1590" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C1590">
-        <v>1.715564542828446</v>
+        <v>1.692781010944548</v>
       </c>
       <c r="D1590" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E1590">
-        <v>1.874539031081747</v>
+        <v>1.863513519335047</v>
       </c>
       <c r="F1590">
         <v>1</v>
       </c>
       <c r="G1590">
-        <v>0.008644435457171553</v>
+        <v>0.007867218989055453</v>
       </c>
       <c r="H1590">
-        <v>0.008525460968918253</v>
+        <v>0.008236486480664953</v>
       </c>
       <c r="I1590">
-        <v>0.1589744882533006</v>
+        <v>0.1707325083904991</v>
       </c>
       <c r="J1590">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1590">
-        <v>3.49</v>
+        <v>3.11</v>
       </c>
       <c r="L1590">
-        <v>5.18</v>
+        <v>4.78</v>
       </c>
       <c r="M1590">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N1590">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="O1590">
         <v>1</v>
@@ -81526,46 +81526,46 @@
     </row>
     <row r="1591" spans="1:16">
       <c r="A1591" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1591" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C1591">
-        <v>1.692781010944548</v>
+        <v>1.590803238290198</v>
       </c>
       <c r="D1591" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1591">
-        <v>1.883367017656947</v>
+        <v>1.640729987451147</v>
       </c>
       <c r="F1591">
         <v>1</v>
       </c>
       <c r="G1591">
-        <v>0.007867218989055453</v>
+        <v>0.007229196761709803</v>
       </c>
       <c r="H1591">
-        <v>0.008216632982343054</v>
+        <v>0.007259270012548853</v>
       </c>
       <c r="I1591">
-        <v>0.1905860067123992</v>
+        <v>0.04992674916094986</v>
       </c>
       <c r="J1591">
         <v>0.9926749160950009</v>
       </c>
       <c r="K1591">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="L1591">
-        <v>4.78</v>
+        <v>4.41</v>
       </c>
       <c r="M1591">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="N1591">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="O1591">
         <v>1</v>
@@ -81576,113 +81576,113 @@
     </row>
     <row r="1592" spans="1:16">
       <c r="A1592" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1592" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C1592">
-        <v>1.590803238290198</v>
+        <v>1.605356319289299</v>
       </c>
       <c r="D1592" t="s">
-        <v>420</v>
+        <v>231</v>
       </c>
       <c r="E1592">
-        <v>1.680143980738748</v>
+        <v>1.823785857909699</v>
       </c>
       <c r="F1592">
         <v>1</v>
       </c>
       <c r="G1592">
-        <v>0.007229196761709803</v>
+        <v>0.009134643680710703</v>
       </c>
       <c r="H1592">
-        <v>0.007139856019261252</v>
+        <v>0.009456214142090301</v>
       </c>
       <c r="I1592">
-        <v>0.08934074244855017</v>
+        <v>0.2184295386204007</v>
       </c>
       <c r="J1592">
-        <v>0.9926749160950009</v>
+        <v>1.031409227591973</v>
       </c>
       <c r="K1592">
-        <v>2.84</v>
+        <v>3.65</v>
       </c>
       <c r="L1592">
-        <v>4.41</v>
+        <v>5.37</v>
       </c>
       <c r="M1592">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="N1592">
-        <v>4.41</v>
+        <v>5.64</v>
       </c>
       <c r="O1592">
         <v>1</v>
       </c>
       <c r="P1592" t="s">
-        <v>548</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1593" spans="1:16">
       <c r="A1593" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1593" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C1593">
-        <v>1.605356319289299</v>
+        <v>1.872529488806021</v>
       </c>
       <c r="D1593" t="s">
-        <v>231</v>
+        <v>421</v>
       </c>
       <c r="E1593">
-        <v>1.823785857909699</v>
+        <v>1.702894533911371</v>
       </c>
       <c r="F1593">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1593">
-        <v>0.009134643680710703</v>
+        <v>0.00958747051119398</v>
       </c>
       <c r="H1593">
-        <v>0.009456214142090301</v>
+        <v>0.00873710546608863</v>
       </c>
       <c r="I1593">
-        <v>0.2184295386204007</v>
+        <v>0.1696349548946499</v>
       </c>
       <c r="J1593">
         <v>1.031409227591973</v>
       </c>
       <c r="K1593">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="L1593">
-        <v>5.37</v>
+        <v>5.73</v>
       </c>
       <c r="M1593">
-        <v>3.7</v>
+        <v>3.41</v>
       </c>
       <c r="N1593">
-        <v>5.64</v>
+        <v>5.22</v>
       </c>
       <c r="O1593">
         <v>1</v>
       </c>
       <c r="P1593" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1594" spans="1:16">
       <c r="A1594" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1594" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C1594">
-        <v>1.872529488806021</v>
+        <v>1.918183149772576</v>
       </c>
       <c r="D1594" t="s">
         <v>421</v>
@@ -81694,22 +81694,22 @@
         <v>-1</v>
       </c>
       <c r="G1594">
-        <v>0.00958747051119398</v>
+        <v>0.009261816850227424</v>
       </c>
       <c r="H1594">
         <v>0.00873710546608863</v>
       </c>
       <c r="I1594">
-        <v>0.1696349548946499</v>
+        <v>0.2152886158612044</v>
       </c>
       <c r="J1594">
         <v>1.031409227591973</v>
       </c>
       <c r="K1594">
-        <v>3.74</v>
+        <v>3.56</v>
       </c>
       <c r="L1594">
-        <v>5.73</v>
+        <v>5.59</v>
       </c>
       <c r="M1594">
         <v>3.41</v>
@@ -81721,48 +81721,48 @@
         <v>1</v>
       </c>
       <c r="P1594" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1595" spans="1:16">
       <c r="A1595" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1595" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C1595">
-        <v>1.918183149772576</v>
+        <v>1.572580441635452</v>
       </c>
       <c r="D1595" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E1595">
-        <v>1.702894533911371</v>
+        <v>1.744150903015051</v>
       </c>
       <c r="F1595">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1595">
-        <v>0.009261816850227424</v>
+        <v>0.008627419558364548</v>
       </c>
       <c r="H1595">
-        <v>0.00873710546608863</v>
+        <v>0.00869584909698495</v>
       </c>
       <c r="I1595">
-        <v>0.2152886158612044</v>
+        <v>0.171570461379599</v>
       </c>
       <c r="J1595">
         <v>1.031409227591973</v>
       </c>
       <c r="K1595">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="L1595">
-        <v>5.59</v>
+        <v>5.1</v>
       </c>
       <c r="M1595">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="N1595">
         <v>5.22</v>
@@ -81771,301 +81771,301 @@
         <v>1</v>
       </c>
       <c r="P1595" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1596" spans="1:16">
       <c r="A1596" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1596" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C1596">
-        <v>1.572580441635452</v>
+        <v>1.897869057496656</v>
       </c>
       <c r="D1596" t="s">
-        <v>423</v>
+        <v>250</v>
       </c>
       <c r="E1596">
-        <v>1.744150903015051</v>
+        <v>1.658183149772576</v>
       </c>
       <c r="F1596">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1596">
-        <v>0.008627419558364548</v>
+        <v>0.009262130942503345</v>
       </c>
       <c r="H1596">
-        <v>0.00869584909698495</v>
+        <v>0.009001816850227424</v>
       </c>
       <c r="I1596">
-        <v>0.171570461379599</v>
+        <v>0.2396859077240805</v>
       </c>
       <c r="J1596">
         <v>1.031409227591973</v>
       </c>
       <c r="K1596">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="L1596">
-        <v>5.1</v>
+        <v>5.58</v>
       </c>
       <c r="M1596">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="N1596">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1596">
         <v>1</v>
       </c>
       <c r="P1596" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1597" spans="1:16">
       <c r="A1597" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1597" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C1597">
-        <v>1.897869057496656</v>
+        <v>1.580381795704013</v>
       </c>
       <c r="D1597" t="s">
-        <v>248</v>
+        <v>425</v>
       </c>
       <c r="E1597">
-        <v>1.658183149772576</v>
+        <v>1.732894533911371</v>
       </c>
       <c r="F1597">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1597">
-        <v>0.009262130942503345</v>
+        <v>0.008779618204295986</v>
       </c>
       <c r="H1597">
-        <v>0.009001816850227424</v>
+        <v>0.008767105466088628</v>
       </c>
       <c r="I1597">
-        <v>0.2396859077240805</v>
+        <v>0.1525127382073581</v>
       </c>
       <c r="J1597">
         <v>1.031409227591973</v>
       </c>
       <c r="K1597">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="L1597">
-        <v>5.58</v>
+        <v>5.18</v>
       </c>
       <c r="M1597">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="N1597">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="O1597">
         <v>1</v>
       </c>
       <c r="P1597" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1598" spans="1:16">
       <c r="A1598" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1598" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C1598">
-        <v>1.580381795704013</v>
+        <v>1.572317302188964</v>
       </c>
       <c r="D1598" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E1598">
-        <v>1.74477908756689</v>
+        <v>1.739176379429766</v>
       </c>
       <c r="F1598">
         <v>1</v>
       </c>
       <c r="G1598">
-        <v>0.008779618204295986</v>
+        <v>0.007987682697811038</v>
       </c>
       <c r="H1598">
-        <v>0.00865522091243311</v>
+        <v>0.008360823620570234</v>
       </c>
       <c r="I1598">
-        <v>0.1643972918628771</v>
+        <v>0.1668590772408023</v>
       </c>
       <c r="J1598">
         <v>1.031409227591973</v>
       </c>
       <c r="K1598">
-        <v>3.49</v>
+        <v>3.11</v>
       </c>
       <c r="L1598">
-        <v>5.18</v>
+        <v>4.78</v>
       </c>
       <c r="M1598">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N1598">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="O1598">
         <v>1</v>
       </c>
       <c r="P1598" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1599" spans="1:16">
       <c r="A1599" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1599" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C1599">
-        <v>1.572317302188964</v>
+        <v>1.480797793638797</v>
       </c>
       <c r="D1599" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E1599">
-        <v>1.739176379429766</v>
+        <v>1.531111885914716</v>
       </c>
       <c r="F1599">
         <v>1</v>
       </c>
       <c r="G1599">
-        <v>0.007987682697811038</v>
+        <v>0.007339202206361204</v>
       </c>
       <c r="H1599">
-        <v>0.008360823620570234</v>
+        <v>0.007368888114085283</v>
       </c>
       <c r="I1599">
-        <v>0.1668590772408023</v>
+        <v>0.05031409227591954</v>
       </c>
       <c r="J1599">
         <v>1.031409227591973</v>
       </c>
       <c r="K1599">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="L1599">
-        <v>4.78</v>
+        <v>4.41</v>
       </c>
       <c r="M1599">
-        <v>3.21</v>
+        <v>2.83</v>
       </c>
       <c r="N1599">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="O1599">
         <v>1</v>
       </c>
       <c r="P1599" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1600" spans="1:16">
       <c r="A1600" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1600" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C1600">
-        <v>1.480797793638797</v>
+        <v>1.516085437608808</v>
       </c>
       <c r="D1600" t="s">
-        <v>420</v>
+        <v>231</v>
       </c>
       <c r="E1600">
-        <v>1.573624624122074</v>
+        <v>1.733292087439065</v>
       </c>
       <c r="F1600">
         <v>1</v>
       </c>
       <c r="G1600">
-        <v>0.007339202206361204</v>
+        <v>0.009223914562391192</v>
       </c>
       <c r="H1600">
-        <v>0.007246375375877927</v>
+        <v>0.009546707912560935</v>
       </c>
       <c r="I1600">
-        <v>0.09282683048327733</v>
+        <v>0.2172066498302567</v>
       </c>
       <c r="J1600">
-        <v>1.031409227591973</v>
+        <v>1.055867003394847</v>
       </c>
       <c r="K1600">
-        <v>2.84</v>
+        <v>3.65</v>
       </c>
       <c r="L1600">
-        <v>4.41</v>
+        <v>5.37</v>
       </c>
       <c r="M1600">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="N1600">
-        <v>4.41</v>
+        <v>5.64</v>
       </c>
       <c r="O1600">
         <v>1</v>
       </c>
       <c r="P1600" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1601" spans="1:16">
       <c r="A1601" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1601" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C1601">
-        <v>1.516085437608808</v>
+        <v>1.781057407303272</v>
       </c>
       <c r="D1601" t="s">
-        <v>231</v>
+        <v>427</v>
       </c>
       <c r="E1601">
-        <v>1.733292087439065</v>
+        <v>1.653850757473014</v>
       </c>
       <c r="F1601">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1601">
-        <v>0.009223914562391192</v>
+        <v>0.009678942592696728</v>
       </c>
       <c r="H1601">
-        <v>0.009546707912560935</v>
+        <v>0.009446149242526986</v>
       </c>
       <c r="I1601">
-        <v>0.2172066498302567</v>
+        <v>0.1272066498302578</v>
       </c>
       <c r="J1601">
         <v>1.055867003394847</v>
       </c>
       <c r="K1601">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="L1601">
-        <v>5.37</v>
+        <v>5.73</v>
       </c>
       <c r="M1601">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="N1601">
-        <v>5.64</v>
+        <v>5.55</v>
       </c>
       <c r="O1601">
         <v>1</v>
@@ -82076,46 +82076,46 @@
     </row>
     <row r="1602" spans="1:16">
       <c r="A1602" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1602" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C1602">
-        <v>1.781057407303272</v>
+        <v>1.831113467914344</v>
       </c>
       <c r="D1602" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E1602">
-        <v>1.653850757473014</v>
+        <v>1.619493518423571</v>
       </c>
       <c r="F1602">
         <v>-1</v>
       </c>
       <c r="G1602">
-        <v>0.009678942592696728</v>
+        <v>0.009348886532085656</v>
       </c>
       <c r="H1602">
-        <v>0.009446149242526986</v>
+        <v>0.008820506481576429</v>
       </c>
       <c r="I1602">
-        <v>0.1272066498302578</v>
+        <v>0.2116199494907733</v>
       </c>
       <c r="J1602">
         <v>1.055867003394847</v>
       </c>
       <c r="K1602">
-        <v>3.74</v>
+        <v>3.56</v>
       </c>
       <c r="L1602">
-        <v>5.73</v>
+        <v>5.59</v>
       </c>
       <c r="M1602">
-        <v>3.69</v>
+        <v>3.41</v>
       </c>
       <c r="N1602">
-        <v>5.55</v>
+        <v>5.22</v>
       </c>
       <c r="O1602">
         <v>1</v>
@@ -82126,43 +82126,43 @@
     </row>
     <row r="1603" spans="1:16">
       <c r="A1603" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1603" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C1603">
-        <v>1.831113467914344</v>
+        <v>1.488934848389623</v>
       </c>
       <c r="D1603" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E1603">
-        <v>1.619493518423571</v>
+        <v>1.661728198559365</v>
       </c>
       <c r="F1603">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1603">
-        <v>0.009348886532085656</v>
+        <v>0.008711065151610378</v>
       </c>
       <c r="H1603">
-        <v>0.008820506481576429</v>
+        <v>0.008778271801440635</v>
       </c>
       <c r="I1603">
-        <v>0.2116199494907733</v>
+        <v>0.1727933501697421</v>
       </c>
       <c r="J1603">
         <v>1.055867003394847</v>
       </c>
       <c r="K1603">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="L1603">
-        <v>5.59</v>
+        <v>5.1</v>
       </c>
       <c r="M1603">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="N1603">
         <v>5.22</v>
@@ -82176,46 +82176,46 @@
     </row>
     <row r="1604" spans="1:16">
       <c r="A1604" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1604" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C1604">
-        <v>1.488934848389623</v>
+        <v>1.810554797880396</v>
       </c>
       <c r="D1604" t="s">
-        <v>423</v>
+        <v>250</v>
       </c>
       <c r="E1604">
-        <v>1.661728198559365</v>
+        <v>1.571113467914344</v>
       </c>
       <c r="F1604">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1604">
-        <v>0.008711065151610378</v>
+        <v>0.009349445202119604</v>
       </c>
       <c r="H1604">
-        <v>0.008778271801440635</v>
+        <v>0.009088886532085656</v>
       </c>
       <c r="I1604">
-        <v>0.1727933501697421</v>
+        <v>0.2394413299660516</v>
       </c>
       <c r="J1604">
         <v>1.055867003394847</v>
       </c>
       <c r="K1604">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="L1604">
-        <v>5.1</v>
+        <v>5.58</v>
       </c>
       <c r="M1604">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="N1604">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1604">
         <v>1</v>
@@ -82226,46 +82226,46 @@
     </row>
     <row r="1605" spans="1:16">
       <c r="A1605" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1605" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C1605">
-        <v>1.810554797880396</v>
+        <v>1.495024158151983</v>
       </c>
       <c r="D1605" t="s">
-        <v>248</v>
+        <v>428</v>
       </c>
       <c r="E1605">
-        <v>1.571113467914344</v>
+        <v>1.662845538627262</v>
       </c>
       <c r="F1605">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1605">
-        <v>0.009349445202119604</v>
+        <v>0.008864975841848017</v>
       </c>
       <c r="H1605">
-        <v>0.009088886532085656</v>
+        <v>0.008737154461372739</v>
       </c>
       <c r="I1605">
-        <v>0.2394413299660516</v>
+        <v>0.1678213804752788</v>
       </c>
       <c r="J1605">
         <v>1.055867003394847</v>
       </c>
       <c r="K1605">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="L1605">
-        <v>5.58</v>
+        <v>5.18</v>
       </c>
       <c r="M1605">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="N1605">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="O1605">
         <v>1</v>
@@ -82276,16 +82276,16 @@
     </row>
     <row r="1606" spans="1:16">
       <c r="A1606" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1606" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C1606">
-        <v>1.495024158151983</v>
+        <v>1.531169528525416</v>
       </c>
       <c r="D1606" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E1606">
         <v>1.662845538627262</v>
@@ -82294,22 +82294,22 @@
         <v>1</v>
       </c>
       <c r="G1606">
-        <v>0.008864975841848017</v>
+        <v>0.008668830471474584</v>
       </c>
       <c r="H1606">
         <v>0.008737154461372739</v>
       </c>
       <c r="I1606">
-        <v>0.1678213804752788</v>
+        <v>0.1316760101018457</v>
       </c>
       <c r="J1606">
         <v>1.055867003394847</v>
       </c>
       <c r="K1606">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="L1606">
-        <v>5.18</v>
+        <v>5.1</v>
       </c>
       <c r="M1606">
         <v>3.35</v>
@@ -82326,46 +82326,46 @@
     </row>
     <row r="1607" spans="1:16">
       <c r="A1607" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1607" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C1607">
-        <v>1.531169528525416</v>
+        <v>1.496253619442026</v>
       </c>
       <c r="D1607" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E1607">
-        <v>1.662845538627262</v>
+        <v>1.66066691910254</v>
       </c>
       <c r="F1607">
         <v>1</v>
       </c>
       <c r="G1607">
-        <v>0.008668830471474584</v>
+        <v>0.008063746380557974</v>
       </c>
       <c r="H1607">
-        <v>0.008737154461372739</v>
+        <v>0.008439333080897459</v>
       </c>
       <c r="I1607">
-        <v>0.1316760101018457</v>
+        <v>0.1644132996605148</v>
       </c>
       <c r="J1607">
         <v>1.055867003394847</v>
       </c>
       <c r="K1607">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="L1607">
-        <v>5.1</v>
+        <v>4.78</v>
       </c>
       <c r="M1607">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N1607">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="O1607">
         <v>1</v>
@@ -82376,46 +82376,46 @@
     </row>
     <row r="1608" spans="1:16">
       <c r="A1608" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1608" t="s">
         <v>244</v>
       </c>
       <c r="C1608">
-        <v>1.538376178355674</v>
+        <v>1.77910303022284</v>
       </c>
       <c r="D1608" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E1608">
-        <v>1.662845538627262</v>
+        <v>1.647985690154943</v>
       </c>
       <c r="F1608">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1608">
-        <v>0.008781623821644326</v>
+        <v>0.007860896969777161</v>
       </c>
       <c r="H1608">
-        <v>0.008737154461372739</v>
+        <v>0.007772014309845057</v>
       </c>
       <c r="I1608">
-        <v>0.1244693602715876</v>
+        <v>0.1311173400678971</v>
       </c>
       <c r="J1608">
         <v>1.055867003394847</v>
       </c>
       <c r="K1608">
-        <v>3.43</v>
+        <v>2.88</v>
       </c>
       <c r="L1608">
-        <v>5.16</v>
+        <v>4.82</v>
       </c>
       <c r="M1608">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N1608">
-        <v>5.2</v>
+        <v>4.71</v>
       </c>
       <c r="O1608">
         <v>1</v>
@@ -82426,46 +82426,46 @@
     </row>
     <row r="1609" spans="1:16">
       <c r="A1609" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1609" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C1609">
-        <v>1.496253619442026</v>
+        <v>1.411337710358634</v>
       </c>
       <c r="D1609" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E1609">
-        <v>1.66066691910254</v>
+        <v>1.461896380392583</v>
       </c>
       <c r="F1609">
         <v>1</v>
       </c>
       <c r="G1609">
-        <v>0.008063746380557974</v>
+        <v>0.007408662289641366</v>
       </c>
       <c r="H1609">
-        <v>0.008439333080897459</v>
+        <v>0.007438103619607418</v>
       </c>
       <c r="I1609">
-        <v>0.1644132996605148</v>
+        <v>0.05055867003394843</v>
       </c>
       <c r="J1609">
         <v>1.055867003394847</v>
       </c>
       <c r="K1609">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="L1609">
-        <v>4.78</v>
+        <v>4.41</v>
       </c>
       <c r="M1609">
-        <v>3.21</v>
+        <v>2.83</v>
       </c>
       <c r="N1609">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="O1609">
         <v>1</v>
@@ -82476,146 +82476,146 @@
     </row>
     <row r="1610" spans="1:16">
       <c r="A1610" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B1610" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C1610">
-        <v>1.77910303022284</v>
+        <v>1.244990997067842</v>
       </c>
       <c r="D1610" t="s">
-        <v>428</v>
+        <v>231</v>
       </c>
       <c r="E1610">
-        <v>1.647985690154943</v>
+        <v>1.458484024424935</v>
       </c>
       <c r="F1610">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1610">
-        <v>0.007860896969777161</v>
+        <v>0.009495009002932157</v>
       </c>
       <c r="H1610">
-        <v>0.007772014309845057</v>
+        <v>0.009821515975575065</v>
       </c>
       <c r="I1610">
-        <v>0.1311173400678971</v>
+        <v>0.2134930273570932</v>
       </c>
       <c r="J1610">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1610">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="L1610">
-        <v>4.82</v>
+        <v>5.37</v>
       </c>
       <c r="M1610">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="N1610">
-        <v>4.71</v>
+        <v>5.64</v>
       </c>
       <c r="O1610">
         <v>1</v>
       </c>
       <c r="P1610" t="s">
-        <v>230</v>
+        <v>549</v>
       </c>
     </row>
     <row r="1611" spans="1:16">
       <c r="A1611" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B1611" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C1611">
-        <v>1.411337710358634</v>
+        <v>1.566703547825073</v>
       </c>
       <c r="D1611" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E1611">
-        <v>1.506365740664171</v>
+        <v>1.366224465753792</v>
       </c>
       <c r="F1611">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1611">
-        <v>0.007408662289641366</v>
+        <v>0.009613296452174926</v>
       </c>
       <c r="H1611">
-        <v>0.00731363425933583</v>
+        <v>0.009073775534246207</v>
       </c>
       <c r="I1611">
-        <v>0.09502803030553642</v>
+        <v>0.200479082071281</v>
       </c>
       <c r="J1611">
-        <v>1.055867003394847</v>
+        <v>1.130139452858125</v>
       </c>
       <c r="K1611">
-        <v>2.84</v>
+        <v>3.56</v>
       </c>
       <c r="L1611">
-        <v>4.41</v>
+        <v>5.59</v>
       </c>
       <c r="M1611">
-        <v>2.75</v>
+        <v>3.41</v>
       </c>
       <c r="N1611">
-        <v>4.41</v>
+        <v>5.22</v>
       </c>
       <c r="O1611">
         <v>1</v>
       </c>
       <c r="P1611" t="s">
-        <v>230</v>
+        <v>549</v>
       </c>
     </row>
     <row r="1612" spans="1:16">
       <c r="A1612" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1612" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C1612">
-        <v>1.244990997067842</v>
+        <v>1.234923071225211</v>
       </c>
       <c r="D1612" t="s">
-        <v>231</v>
+        <v>424</v>
       </c>
       <c r="E1612">
-        <v>1.458484024424935</v>
+        <v>1.411430043868117</v>
       </c>
       <c r="F1612">
         <v>1</v>
       </c>
       <c r="G1612">
-        <v>0.009495009002932157</v>
+        <v>0.008965076928774789</v>
       </c>
       <c r="H1612">
-        <v>0.009821515975575065</v>
+        <v>0.009028569956131882</v>
       </c>
       <c r="I1612">
-        <v>0.2134930273570932</v>
+        <v>0.176506972642906</v>
       </c>
       <c r="J1612">
         <v>1.130139452858125</v>
       </c>
       <c r="K1612">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="L1612">
-        <v>5.37</v>
+        <v>5.1</v>
       </c>
       <c r="M1612">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
       <c r="N1612">
-        <v>5.64</v>
+        <v>5.22</v>
       </c>
       <c r="O1612">
         <v>1</v>
@@ -82626,46 +82626,46 @@
     </row>
     <row r="1613" spans="1:16">
       <c r="A1613" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1613" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C1613">
-        <v>1.566703547825073</v>
+        <v>1.545402153296492</v>
       </c>
       <c r="D1613" t="s">
-        <v>421</v>
+        <v>250</v>
       </c>
       <c r="E1613">
-        <v>1.366224465753792</v>
+        <v>1.306703547825073</v>
       </c>
       <c r="F1613">
         <v>-1</v>
       </c>
       <c r="G1613">
-        <v>0.009613296452174926</v>
+        <v>0.009614597846703507</v>
       </c>
       <c r="H1613">
-        <v>0.009073775534246207</v>
+        <v>0.009353296452174927</v>
       </c>
       <c r="I1613">
-        <v>0.200479082071281</v>
+        <v>0.2386986054714191</v>
       </c>
       <c r="J1613">
         <v>1.130139452858125</v>
       </c>
       <c r="K1613">
+        <v>3.57</v>
+      </c>
+      <c r="L1613">
+        <v>5.58</v>
+      </c>
+      <c r="M1613">
         <v>3.56</v>
       </c>
-      <c r="L1613">
-        <v>5.59</v>
-      </c>
-      <c r="M1613">
-        <v>3.41</v>
-      </c>
       <c r="N1613">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="O1613">
         <v>1</v>
@@ -82676,46 +82676,46 @@
     </row>
     <row r="1614" spans="1:16">
       <c r="A1614" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1614" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C1614">
-        <v>1.234923071225211</v>
+        <v>1.235813309525142</v>
       </c>
       <c r="D1614" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E1614">
-        <v>1.411430043868117</v>
+        <v>1.41403283292528</v>
       </c>
       <c r="F1614">
         <v>1</v>
       </c>
       <c r="G1614">
-        <v>0.008965076928774789</v>
+        <v>0.009124186690474857</v>
       </c>
       <c r="H1614">
-        <v>0.009028569956131882</v>
+        <v>0.008985967167074721</v>
       </c>
       <c r="I1614">
-        <v>0.176506972642906</v>
+        <v>0.1782195234001382</v>
       </c>
       <c r="J1614">
         <v>1.130139452858125</v>
       </c>
       <c r="K1614">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="L1614">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="M1614">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N1614">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="O1614">
         <v>1</v>
@@ -82726,46 +82726,46 @@
     </row>
     <row r="1615" spans="1:16">
       <c r="A1615" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1615" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C1615">
-        <v>1.545402153296492</v>
+        <v>1.284511914996561</v>
       </c>
       <c r="D1615" t="s">
-        <v>248</v>
+        <v>428</v>
       </c>
       <c r="E1615">
-        <v>1.306703547825073</v>
+        <v>1.41403283292528</v>
       </c>
       <c r="F1615">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1615">
-        <v>0.009614597846703507</v>
+        <v>0.00919548808500344</v>
       </c>
       <c r="H1615">
-        <v>0.009353296452174927</v>
+        <v>0.008985967167074721</v>
       </c>
       <c r="I1615">
-        <v>0.2386986054714191</v>
+        <v>0.1295209179287187</v>
       </c>
       <c r="J1615">
         <v>1.130139452858125</v>
       </c>
       <c r="K1615">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="L1615">
-        <v>5.58</v>
+        <v>5.24</v>
       </c>
       <c r="M1615">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="N1615">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="O1615">
         <v>1</v>
@@ -82776,16 +82776,16 @@
     </row>
     <row r="1616" spans="1:16">
       <c r="A1616" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1616" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C1616">
-        <v>1.235813309525142</v>
+        <v>1.280128649339536</v>
       </c>
       <c r="D1616" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E1616">
         <v>1.41403283292528</v>
@@ -82794,22 +82794,22 @@
         <v>1</v>
       </c>
       <c r="G1616">
-        <v>0.009124186690474857</v>
+        <v>0.008919871350660464</v>
       </c>
       <c r="H1616">
         <v>0.008985967167074721</v>
       </c>
       <c r="I1616">
-        <v>0.1782195234001382</v>
+        <v>0.1339041835857442</v>
       </c>
       <c r="J1616">
         <v>1.130139452858125</v>
       </c>
       <c r="K1616">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="L1616">
-        <v>5.18</v>
+        <v>5.1</v>
       </c>
       <c r="M1616">
         <v>3.35</v>
@@ -82826,16 +82826,16 @@
     </row>
     <row r="1617" spans="1:16">
       <c r="A1617" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1617" t="s">
         <v>246</v>
       </c>
       <c r="C1617">
-        <v>1.284511914996561</v>
+        <v>1.28362167669663</v>
       </c>
       <c r="D1617" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E1617">
         <v>1.41403283292528</v>
@@ -82844,22 +82844,22 @@
         <v>1</v>
       </c>
       <c r="G1617">
-        <v>0.00919548808500344</v>
+        <v>0.009036378323303371</v>
       </c>
       <c r="H1617">
         <v>0.008985967167074721</v>
       </c>
       <c r="I1617">
-        <v>0.1295209179287187</v>
+        <v>0.1304111562286505</v>
       </c>
       <c r="J1617">
         <v>1.130139452858125</v>
       </c>
       <c r="K1617">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="L1617">
-        <v>5.24</v>
+        <v>5.16</v>
       </c>
       <c r="M1617">
         <v>3.35</v>
@@ -82876,46 +82876,46 @@
     </row>
     <row r="1618" spans="1:16">
       <c r="A1618" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1618" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C1618">
-        <v>1.280128649339536</v>
+        <v>1.26526630161123</v>
       </c>
       <c r="D1618" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E1618">
-        <v>1.41403283292528</v>
+        <v>1.422252356325417</v>
       </c>
       <c r="F1618">
         <v>1</v>
       </c>
       <c r="G1618">
-        <v>0.008919871350660464</v>
+        <v>0.008294733698388771</v>
       </c>
       <c r="H1618">
-        <v>0.008985967167074721</v>
+        <v>0.008677747643674582</v>
       </c>
       <c r="I1618">
-        <v>0.1339041835857442</v>
+        <v>0.1569860547141868</v>
       </c>
       <c r="J1618">
         <v>1.130139452858125</v>
       </c>
       <c r="K1618">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="L1618">
-        <v>5.1</v>
+        <v>4.78</v>
       </c>
       <c r="M1618">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N1618">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="O1618">
         <v>1</v>
@@ -82926,46 +82926,46 @@
     </row>
     <row r="1619" spans="1:16">
       <c r="A1619" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B1619" t="s">
         <v>244</v>
       </c>
       <c r="C1619">
-        <v>1.28362167669663</v>
+        <v>1.565198375768599</v>
       </c>
       <c r="D1619" t="s">
-        <v>425</v>
+        <v>235</v>
       </c>
       <c r="E1619">
-        <v>1.41403283292528</v>
+        <v>1.343896981240018</v>
       </c>
       <c r="F1619">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1619">
-        <v>0.009036378323303371</v>
+        <v>0.008074801624231402</v>
       </c>
       <c r="H1619">
-        <v>0.008985967167074721</v>
+        <v>0.007876103018759982</v>
       </c>
       <c r="I1619">
-        <v>0.1304111562286505</v>
+        <v>0.2213013945285813</v>
       </c>
       <c r="J1619">
         <v>1.130139452858125</v>
       </c>
       <c r="K1619">
-        <v>3.43</v>
+        <v>2.88</v>
       </c>
       <c r="L1619">
-        <v>5.16</v>
+        <v>4.82</v>
       </c>
       <c r="M1619">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="N1619">
-        <v>5.2</v>
+        <v>4.61</v>
       </c>
       <c r="O1619">
         <v>1</v>
@@ -82976,46 +82976,46 @@
     </row>
     <row r="1620" spans="1:16">
       <c r="A1620" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B1620" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C1620">
-        <v>1.26526630161123</v>
+        <v>1.200403953882924</v>
       </c>
       <c r="D1620" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E1620">
-        <v>1.422252356325417</v>
+        <v>1.251705348411505</v>
       </c>
       <c r="F1620">
         <v>1</v>
       </c>
       <c r="G1620">
-        <v>0.008294733698388771</v>
+        <v>0.007619596046117076</v>
       </c>
       <c r="H1620">
-        <v>0.008677747643674582</v>
+        <v>0.007648294651588495</v>
       </c>
       <c r="I1620">
-        <v>0.1569860547141868</v>
+        <v>0.0513013945285814</v>
       </c>
       <c r="J1620">
         <v>1.130139452858125</v>
       </c>
       <c r="K1620">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="L1620">
-        <v>4.78</v>
+        <v>4.41</v>
       </c>
       <c r="M1620">
-        <v>3.21</v>
+        <v>2.83</v>
       </c>
       <c r="N1620">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="O1620">
         <v>1</v>
@@ -83026,46 +83026,46 @@
     </row>
     <row r="1621" spans="1:16">
       <c r="A1621" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B1621" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C1621">
-        <v>1.565198375768599</v>
+        <v>1.292116504640155</v>
       </c>
       <c r="D1621" t="s">
-        <v>235</v>
+        <v>423</v>
       </c>
       <c r="E1621">
-        <v>1.343896981240018</v>
+        <v>1.251705348411505</v>
       </c>
       <c r="F1621">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1621">
-        <v>0.008074801624231402</v>
+        <v>0.007507883495359845</v>
       </c>
       <c r="H1621">
-        <v>0.007876103018759982</v>
+        <v>0.007648294651588495</v>
       </c>
       <c r="I1621">
-        <v>0.2213013945285813</v>
+        <v>-0.04041115622865021</v>
       </c>
       <c r="J1621">
         <v>1.130139452858125</v>
       </c>
       <c r="K1621">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="L1621">
-        <v>4.82</v>
+        <v>4.4</v>
       </c>
       <c r="M1621">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="N1621">
-        <v>4.61</v>
+        <v>4.45</v>
       </c>
       <c r="O1621">
         <v>1</v>
@@ -83076,46 +83076,46 @@
     </row>
     <row r="1622" spans="1:16">
       <c r="A1622" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1622" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C1622">
-        <v>1.200403953882924</v>
+        <v>1.268623477283061</v>
       </c>
       <c r="D1622" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E1622">
-        <v>1.302116504640155</v>
+        <v>1.251705348411505</v>
       </c>
       <c r="F1622">
         <v>1</v>
       </c>
       <c r="G1622">
-        <v>0.007619596046117076</v>
+        <v>0.00737137652271694</v>
       </c>
       <c r="H1622">
-        <v>0.007517883495359846</v>
+        <v>0.007648294651588495</v>
       </c>
       <c r="I1622">
-        <v>0.1017125507572314</v>
+        <v>-0.01691812887155608</v>
       </c>
       <c r="J1622">
         <v>1.130139452858125</v>
       </c>
       <c r="K1622">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="L1622">
-        <v>4.41</v>
+        <v>4.32</v>
       </c>
       <c r="M1622">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="N1622">
-        <v>4.41</v>
+        <v>4.45</v>
       </c>
       <c r="O1622">
         <v>1</v>
@@ -83126,46 +83126,46 @@
     </row>
     <row r="1623" spans="1:16">
       <c r="A1623" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B1623" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C1623">
-        <v>1.292116504640155</v>
+        <v>1.279513715582993</v>
       </c>
       <c r="D1623" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E1623">
-        <v>1.302116504640155</v>
+        <v>1.251705348411505</v>
       </c>
       <c r="F1623">
         <v>1</v>
       </c>
       <c r="G1623">
-        <v>0.007507883495359845</v>
+        <v>0.007540486284417008</v>
       </c>
       <c r="H1623">
-        <v>0.007517883495359846</v>
+        <v>0.007648294651588495</v>
       </c>
       <c r="I1623">
-        <v>0.009999999999999787</v>
+        <v>-0.02780836717148727</v>
       </c>
       <c r="J1623">
         <v>1.130139452858125</v>
       </c>
       <c r="K1623">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="L1623">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="M1623">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="N1623">
-        <v>4.41</v>
+        <v>4.45</v>
       </c>
       <c r="O1623">
         <v>1</v>
@@ -83285,7 +83285,7 @@
         <v>1.119124856866872</v>
       </c>
       <c r="D1626" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E1626">
         <v>1.297324785860047</v>
@@ -83335,7 +83335,7 @@
         <v>1.42452506988735</v>
       </c>
       <c r="D1627" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E1627">
         <v>1.292724998880524</v>
@@ -83379,13 +83379,13 @@
         <v>4</v>
       </c>
       <c r="B1628" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C1628">
         <v>1.186165055685985</v>
       </c>
       <c r="D1628" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E1628">
         <v>1.297484871068237</v>
@@ -83429,13 +83429,13 @@
         <v>5</v>
       </c>
       <c r="B1629" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C1629">
         <v>1.117644956276428</v>
       </c>
       <c r="D1629" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E1629">
         <v>1.300604757457317</v>
@@ -83479,13 +83479,13 @@
         <v>6</v>
       </c>
       <c r="B1630" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C1630">
         <v>1.166004970477794</v>
       </c>
       <c r="D1630" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E1630">
         <v>1.300604757457317</v>
@@ -83535,7 +83535,7 @@
         <v>1.165684800061412</v>
       </c>
       <c r="D1631" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E1631">
         <v>1.300604757457317</v>
@@ -83579,13 +83579,13 @@
         <v>8</v>
       </c>
       <c r="B1632" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C1632">
         <v>1.167484871068238</v>
       </c>
       <c r="D1632" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E1632">
         <v>1.300604757457317</v>
@@ -83679,7 +83679,7 @@
         <v>10</v>
       </c>
       <c r="B1634" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C1634">
         <v>1.467684089993156</v>
@@ -83729,16 +83729,16 @@
         <v>11</v>
       </c>
       <c r="B1635" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C1635">
         <v>1.104244033187696</v>
       </c>
       <c r="D1635" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E1635">
-        <v>1.209003905375409</v>
+        <v>1.15588401898633</v>
       </c>
       <c r="F1635">
         <v>1</v>
@@ -83747,10 +83747,10 @@
         <v>0.007715755966812305</v>
       </c>
       <c r="H1635">
-        <v>0.007610996094624591</v>
+        <v>0.007744115981013671</v>
       </c>
       <c r="I1635">
-        <v>0.1047598721877137</v>
+        <v>0.05163998579863449</v>
       </c>
       <c r="J1635">
         <v>1.163998579863488</v>
@@ -83762,10 +83762,10 @@
         <v>4.41</v>
       </c>
       <c r="M1635">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="N1635">
-        <v>4.41</v>
+        <v>4.45</v>
       </c>
       <c r="O1635">
         <v>1</v>
@@ -83779,16 +83779,16 @@
         <v>12</v>
       </c>
       <c r="B1636" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C1636">
         <v>1.177203834368584</v>
       </c>
       <c r="D1636" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E1636">
-        <v>1.209003905375409</v>
+        <v>1.15588401898633</v>
       </c>
       <c r="F1636">
         <v>1</v>
@@ -83797,10 +83797,10 @@
         <v>0.007462796165631417</v>
       </c>
       <c r="H1636">
-        <v>0.007610996094624591</v>
+        <v>0.007744115981013671</v>
       </c>
       <c r="I1636">
-        <v>0.0318000710068258</v>
+        <v>-0.02131981538225336</v>
       </c>
       <c r="J1636">
         <v>1.163998579863488</v>
@@ -83812,10 +83812,10 @@
         <v>4.32</v>
       </c>
       <c r="M1636">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="N1636">
-        <v>4.41</v>
+        <v>4.45</v>
       </c>
       <c r="O1636">
         <v>1</v>
@@ -83826,96 +83826,96 @@
     </row>
     <row r="1637" spans="1:16">
       <c r="A1637" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1637" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C1637">
-        <v>1.284389949876279</v>
+        <v>1.18572393377814</v>
       </c>
       <c r="D1637" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="E1637">
-        <v>1.139050821648374</v>
+        <v>1.15588401898633</v>
       </c>
       <c r="F1637">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1637">
-        <v>0.009895610050123722</v>
+        <v>0.007634276066221861</v>
       </c>
       <c r="H1637">
-        <v>0.009580949178351627</v>
+        <v>0.007744115981013671</v>
       </c>
       <c r="I1637">
-        <v>0.1453391282279046</v>
+        <v>-0.02983991479180936</v>
       </c>
       <c r="J1637">
-        <v>1.209441025315652</v>
+        <v>1.163998579863488</v>
       </c>
       <c r="K1637">
-        <v>3.56</v>
+        <v>2.77</v>
       </c>
       <c r="L1637">
-        <v>5.59</v>
+        <v>4.41</v>
       </c>
       <c r="M1637">
-        <v>3.49</v>
+        <v>2.83</v>
       </c>
       <c r="N1637">
-        <v>5.36</v>
+        <v>4.45</v>
       </c>
       <c r="O1637">
         <v>1</v>
       </c>
       <c r="P1637" t="s">
-        <v>231</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1638" spans="1:16">
       <c r="A1638" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1638" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C1638">
-        <v>0.9637116934204695</v>
+        <v>1.284389949876279</v>
       </c>
       <c r="D1638" t="s">
         <v>432</v>
       </c>
       <c r="E1638">
-        <v>1.195334052407844</v>
+        <v>1.139050821648374</v>
       </c>
       <c r="F1638">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1638">
-        <v>0.00923628830657953</v>
+        <v>0.009895610050123722</v>
       </c>
       <c r="H1638">
-        <v>0.009564665947592156</v>
+        <v>0.009580949178351627</v>
       </c>
       <c r="I1638">
-        <v>0.2316223589873747</v>
+        <v>0.1453391282279046</v>
       </c>
       <c r="J1638">
         <v>1.209441025315652</v>
       </c>
       <c r="K1638">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="L1638">
-        <v>5.1</v>
+        <v>5.59</v>
       </c>
       <c r="M1638">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="N1638">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="O1638">
         <v>1</v>
@@ -83926,16 +83926,16 @@
     </row>
     <row r="1639" spans="1:16">
       <c r="A1639" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1639" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C1639">
-        <v>1.015806103673627</v>
+        <v>0.9637116934204695</v>
       </c>
       <c r="D1639" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E1639">
         <v>1.195334052407844</v>
@@ -83944,22 +83944,22 @@
         <v>1</v>
       </c>
       <c r="G1639">
-        <v>0.009264193896326373</v>
+        <v>0.00923628830657953</v>
       </c>
       <c r="H1639">
         <v>0.009564665947592156</v>
       </c>
       <c r="I1639">
-        <v>0.1795279487342176</v>
+        <v>0.2316223589873747</v>
       </c>
       <c r="J1639">
         <v>1.209441025315652</v>
       </c>
       <c r="K1639">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="L1639">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="M1639">
         <v>3.46</v>
@@ -83976,46 +83976,46 @@
     </row>
     <row r="1640" spans="1:16">
       <c r="A1640" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1640" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C1640">
-        <v>1.262295539623123</v>
+        <v>1.015806103673627</v>
       </c>
       <c r="D1640" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E1640">
-        <v>1.132767590888904</v>
+        <v>1.195334052407844</v>
       </c>
       <c r="F1640">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1640">
-        <v>0.009897704460376877</v>
+        <v>0.009264193896326373</v>
       </c>
       <c r="H1640">
-        <v>0.009647232409111094</v>
+        <v>0.009564665947592156</v>
       </c>
       <c r="I1640">
-        <v>0.1295279487342187</v>
+        <v>0.1795279487342176</v>
       </c>
       <c r="J1640">
         <v>1.209441025315652</v>
       </c>
       <c r="K1640">
-        <v>3.57</v>
+        <v>3.41</v>
       </c>
       <c r="L1640">
-        <v>5.58</v>
+        <v>5.14</v>
       </c>
       <c r="M1640">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="N1640">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="O1640">
         <v>1</v>
@@ -84026,46 +84026,46 @@
     </row>
     <row r="1641" spans="1:16">
       <c r="A1641" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1641" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="C1641">
-        <v>1.024389949876279</v>
+        <v>1.262295539623123</v>
       </c>
       <c r="D1641" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E1641">
-        <v>1.289110462534105</v>
+        <v>1.132767590888904</v>
       </c>
       <c r="F1641">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1641">
-        <v>0.00963561005012372</v>
+        <v>0.009897704460376877</v>
       </c>
       <c r="H1641">
-        <v>0.008690889537465897</v>
+        <v>0.009647232409111094</v>
       </c>
       <c r="I1641">
-        <v>0.264720512657826</v>
+        <v>0.1295279487342187</v>
       </c>
       <c r="J1641">
         <v>1.209441025315652</v>
       </c>
       <c r="K1641">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="L1641">
-        <v>5.33</v>
+        <v>5.58</v>
       </c>
       <c r="M1641">
-        <v>3.06</v>
+        <v>3.52</v>
       </c>
       <c r="N1641">
-        <v>4.99</v>
+        <v>5.39</v>
       </c>
       <c r="O1641">
         <v>1</v>
@@ -84076,46 +84076,46 @@
     </row>
     <row r="1642" spans="1:16">
       <c r="A1642" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1642" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C1642">
-        <v>0.9590508216483737</v>
+        <v>1.024389949876279</v>
       </c>
       <c r="D1642" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E1642">
-        <v>1.289110462534105</v>
+        <v>1.148372565192566</v>
       </c>
       <c r="F1642">
         <v>1</v>
       </c>
       <c r="G1642">
-        <v>0.009400949178351626</v>
+        <v>0.00963561005012372</v>
       </c>
       <c r="H1642">
-        <v>0.008690889537465897</v>
+        <v>0.009251627434807435</v>
       </c>
       <c r="I1642">
-        <v>0.3300596408857315</v>
+        <v>0.1239826153162866</v>
       </c>
       <c r="J1642">
         <v>1.209441025315652</v>
       </c>
       <c r="K1642">
-        <v>3.49</v>
+        <v>3.56</v>
       </c>
       <c r="L1642">
-        <v>5.18</v>
+        <v>5.33</v>
       </c>
       <c r="M1642">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1642">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1642">
         <v>1</v>
@@ -84126,46 +84126,46 @@
     </row>
     <row r="1643" spans="1:16">
       <c r="A1643" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1643" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C1643">
-        <v>1.006956411395218</v>
+        <v>0.9590508216483737</v>
       </c>
       <c r="D1643" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E1643">
-        <v>1.289110462534105</v>
+        <v>1.148372565192566</v>
       </c>
       <c r="F1643">
         <v>1</v>
       </c>
       <c r="G1643">
-        <v>0.009473043588604782</v>
+        <v>0.009400949178351626</v>
       </c>
       <c r="H1643">
-        <v>0.008690889537465897</v>
+        <v>0.009251627434807435</v>
       </c>
       <c r="I1643">
-        <v>0.2821540511388871</v>
+        <v>0.1893217435441921</v>
       </c>
       <c r="J1643">
         <v>1.209441025315652</v>
       </c>
       <c r="K1643">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="L1643">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="M1643">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1643">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1643">
         <v>1</v>
@@ -84176,46 +84176,46 @@
     </row>
     <row r="1644" spans="1:16">
       <c r="A1644" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1644" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C1644">
-        <v>1.045334052407845</v>
+        <v>1.006956411395218</v>
       </c>
       <c r="D1644" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E1644">
-        <v>1.289110462534105</v>
+        <v>1.148372565192566</v>
       </c>
       <c r="F1644">
         <v>1</v>
       </c>
       <c r="G1644">
-        <v>0.009414665947592155</v>
+        <v>0.009473043588604782</v>
       </c>
       <c r="H1644">
-        <v>0.008690889537465897</v>
+        <v>0.009251627434807435</v>
       </c>
       <c r="I1644">
-        <v>0.2437764101262605</v>
+        <v>0.1414161537973477</v>
       </c>
       <c r="J1644">
         <v>1.209441025315652</v>
       </c>
       <c r="K1644">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="L1644">
-        <v>5.23</v>
+        <v>5.24</v>
       </c>
       <c r="M1644">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1644">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1644">
         <v>1</v>
@@ -84226,46 +84226,46 @@
     </row>
     <row r="1645" spans="1:16">
       <c r="A1645" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1645" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C1645">
-        <v>1.047694308736757</v>
+        <v>1.011617283167314</v>
       </c>
       <c r="D1645" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E1645">
-        <v>1.289110462534105</v>
+        <v>1.148372565192566</v>
       </c>
       <c r="F1645">
         <v>1</v>
       </c>
       <c r="G1645">
-        <v>0.008812305691263242</v>
+        <v>0.009308382716832686</v>
       </c>
       <c r="H1645">
-        <v>0.008690889537465897</v>
+        <v>0.009251627434807435</v>
       </c>
       <c r="I1645">
-        <v>0.2414161537973483</v>
+        <v>0.136755282025252</v>
       </c>
       <c r="J1645">
         <v>1.209441025315652</v>
       </c>
       <c r="K1645">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="L1645">
-        <v>4.93</v>
+        <v>5.16</v>
       </c>
       <c r="M1645">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N1645">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="O1645">
         <v>1</v>
@@ -84276,7 +84276,7 @@
     </row>
     <row r="1646" spans="1:16">
       <c r="A1646" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1646" t="s">
         <v>234</v>
@@ -84326,13 +84326,13 @@
     </row>
     <row r="1647" spans="1:16">
       <c r="A1647" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1647" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C1647">
-        <v>1.336809847090922</v>
+        <v>1.247960154812513</v>
       </c>
       <c r="D1647" t="s">
         <v>235</v>
@@ -84344,22 +84344,22 @@
         <v>-1</v>
       </c>
       <c r="G1647">
-        <v>0.008303190152909078</v>
+        <v>0.008432039845187487</v>
       </c>
       <c r="H1647">
         <v>0.008105284563162235</v>
       </c>
       <c r="I1647">
-        <v>0.2220944102531566</v>
+        <v>0.1332447179747471</v>
       </c>
       <c r="J1647">
         <v>1.209441025315652</v>
       </c>
       <c r="K1647">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="L1647">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
       <c r="M1647">
         <v>2.89</v>
@@ -84376,19 +84376,19 @@
     </row>
     <row r="1648" spans="1:16">
       <c r="A1648" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1648" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C1648">
         <v>0.9751874881035487</v>
       </c>
       <c r="D1648" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E1648">
-        <v>1.084037180381957</v>
+        <v>1.027281898356705</v>
       </c>
       <c r="F1648">
         <v>1</v>
@@ -84397,10 +84397,10 @@
         <v>0.007844812511896452</v>
       </c>
       <c r="H1648">
-        <v>0.007735962819618043</v>
+        <v>0.007872718101643295</v>
       </c>
       <c r="I1648">
-        <v>0.1088496922784086</v>
+        <v>0.0520944102531562</v>
       </c>
       <c r="J1648">
         <v>1.209441025315652</v>
@@ -84412,10 +84412,10 @@
         <v>4.41</v>
       </c>
       <c r="M1648">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="N1648">
-        <v>4.41</v>
+        <v>4.45</v>
       </c>
       <c r="O1648">
         <v>1</v>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -84394,10 +84394,10 @@
         <v>0</v>
       </c>
       <c r="B1648" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C1648">
-        <v>1.692400984783762</v>
+        <v>1.608934335394003</v>
       </c>
       <c r="D1648" t="s">
         <v>436</v>
@@ -84409,22 +84409,22 @@
         <v>-1</v>
       </c>
       <c r="G1648">
-        <v>0.007787599015216239</v>
+        <v>0.007811065664605997</v>
       </c>
       <c r="H1648">
         <v>0.007732452324361901</v>
       </c>
       <c r="I1648">
-        <v>0.2048533091456619</v>
+        <v>0.121386659755903</v>
       </c>
       <c r="J1648">
         <v>1.069332987795171</v>
       </c>
       <c r="K1648">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="L1648">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="M1648">
         <v>2.92</v>
@@ -84444,10 +84444,10 @@
         <v>0</v>
       </c>
       <c r="B1649" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C1649">
-        <v>1.630825248599586</v>
+        <v>1.546278323136421</v>
       </c>
       <c r="D1649" t="s">
         <v>436</v>
@@ -84459,22 +84459,22 @@
         <v>-1</v>
       </c>
       <c r="G1649">
-        <v>0.007849174751400415</v>
+        <v>0.007873721676863579</v>
       </c>
       <c r="H1649">
         <v>0.007795540447048846</v>
       </c>
       <c r="I1649">
-        <v>0.2063656956484312</v>
+        <v>0.121818770185266</v>
       </c>
       <c r="J1649">
         <v>1.090938509263303</v>
       </c>
       <c r="K1649">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="L1649">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="M1649">
         <v>2.92</v>
@@ -84500,10 +84500,10 @@
         <v>1.562310563546519</v>
       </c>
       <c r="D1650" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E1650">
-        <v>1.418861201057535</v>
+        <v>1.354262051072224</v>
       </c>
       <c r="F1650">
         <v>-1</v>
@@ -84512,10 +84512,10 @@
         <v>0.007917689436453481</v>
       </c>
       <c r="H1650">
-        <v>0.007841138798942465</v>
+        <v>0.007865737948927776</v>
       </c>
       <c r="I1650">
-        <v>0.1434493624889841</v>
+        <v>0.2080485124742957</v>
       </c>
       <c r="J1650">
         <v>1.1149787496328</v>
@@ -84527,10 +84527,10 @@
         <v>4.74</v>
       </c>
       <c r="M1650">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="N1650">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="O1650">
         <v>1</v>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4971" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4974" uniqueCount="558">
   <si>
     <t>trade_time</t>
   </si>
@@ -772,9 +772,6 @@
     <t>2021-06-02</t>
   </si>
   <si>
-    <t>2021-06-18</t>
-  </si>
-  <si>
     <t>2021-07-21</t>
   </si>
   <si>
@@ -788,6 +785,9 @@
   </si>
   <si>
     <t>2021-08-23</t>
+  </si>
+  <si>
+    <t>2021-08-31</t>
   </si>
   <si>
     <t>2016-10-20</t>
@@ -1327,6 +1327,9 @@
     <t>2021-08-24</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2016-08-24</t>
   </si>
   <si>
@@ -1682,6 +1685,9 @@
   </si>
   <si>
     <t>2021-08-13</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
   </si>
 </sst>
 </file>
@@ -2039,7 +2045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1653"/>
+  <dimension ref="A1:P1654"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2136,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2186,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2236,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2286,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2336,7 +2342,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2386,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2436,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2486,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2536,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2586,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2636,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2686,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2736,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2786,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2836,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2936,7 +2942,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2986,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3036,7 +3042,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3086,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3136,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3186,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3236,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3286,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3336,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3386,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3586,7 +3592,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3636,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3686,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3736,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3786,7 +3792,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3836,7 +3842,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3886,7 +3892,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3936,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4186,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4236,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4286,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4336,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4386,7 +4392,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4436,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4486,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4536,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4586,7 +4592,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4636,7 +4642,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4686,7 +4692,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4736,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4786,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4836,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4886,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4936,7 +4942,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4986,7 +4992,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5036,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5086,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5136,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5186,7 +5192,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5236,7 +5242,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5286,7 +5292,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5336,7 +5342,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5386,7 +5392,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5436,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5486,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5536,7 +5542,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5586,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5636,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5686,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5736,7 +5742,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5786,7 +5792,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5836,7 +5842,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5886,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5936,7 +5942,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5986,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6036,7 +6042,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6086,7 +6092,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6136,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6536,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6586,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6636,7 +6642,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6686,7 +6692,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6736,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6786,7 +6792,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6836,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6886,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6936,7 +6942,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6986,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -7036,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -7086,7 +7092,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7136,7 +7142,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7186,7 +7192,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7236,7 +7242,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7286,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7336,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7386,7 +7392,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7436,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7486,7 +7492,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7536,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7586,7 +7592,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7636,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7686,7 +7692,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7736,7 +7742,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7786,7 +7792,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7836,7 +7842,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7886,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7936,7 +7942,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7986,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8036,7 +8042,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8086,7 +8092,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8136,7 +8142,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8186,7 +8192,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8236,7 +8242,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8286,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8336,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8386,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8436,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8486,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8536,7 +8542,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8586,7 +8592,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8636,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8686,7 +8692,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8736,7 +8742,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8786,7 +8792,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8836,7 +8842,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8886,7 +8892,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8936,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8986,7 +8992,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9036,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9086,7 +9092,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9136,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9186,7 +9192,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9236,7 +9242,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9286,7 +9292,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9336,7 +9342,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9386,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9436,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9486,7 +9492,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9536,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9586,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9636,7 +9642,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9686,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9736,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9786,7 +9792,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9836,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9886,7 +9892,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9936,7 +9942,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9986,7 +9992,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -10036,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10086,7 +10092,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10136,7 +10142,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10186,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10236,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10286,7 +10292,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10336,7 +10342,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10386,7 +10392,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10436,7 +10442,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10486,7 +10492,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10536,7 +10542,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10586,7 +10592,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10636,7 +10642,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10686,7 +10692,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10736,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10786,7 +10792,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10836,7 +10842,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10886,7 +10892,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10936,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10986,7 +10992,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11036,7 +11042,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11086,7 +11092,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -11136,7 +11142,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11186,7 +11192,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11236,7 +11242,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11286,7 +11292,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11336,7 +11342,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11386,7 +11392,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11436,7 +11442,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11486,7 +11492,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11536,7 +11542,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11586,7 +11592,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11636,7 +11642,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11686,7 +11692,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11736,7 +11742,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11786,7 +11792,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11836,7 +11842,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11886,7 +11892,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11936,7 +11942,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11986,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -12036,7 +12042,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -12086,7 +12092,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12136,7 +12142,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12186,7 +12192,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12236,7 +12242,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12286,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12336,7 +12342,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12386,7 +12392,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12436,7 +12442,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12486,7 +12492,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12536,7 +12542,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12586,7 +12592,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12636,7 +12642,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12686,7 +12692,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12736,7 +12742,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12786,7 +12792,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12836,7 +12842,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12886,7 +12892,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12936,7 +12942,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12986,7 +12992,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13036,7 +13042,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13086,7 +13092,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -13136,7 +13142,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13186,7 +13192,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -13236,7 +13242,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13286,7 +13292,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13736,7 +13742,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13786,7 +13792,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13836,7 +13842,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13886,7 +13892,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13936,7 +13942,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13986,7 +13992,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -14036,7 +14042,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -14086,7 +14092,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -14136,7 +14142,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14186,7 +14192,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14236,7 +14242,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14286,7 +14292,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14336,7 +14342,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14386,7 +14392,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14436,7 +14442,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14486,7 +14492,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14536,7 +14542,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -15136,7 +15142,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15186,7 +15192,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15236,7 +15242,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15286,7 +15292,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15336,7 +15342,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15386,7 +15392,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15536,7 +15542,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15586,7 +15592,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15636,7 +15642,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15686,7 +15692,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15736,7 +15742,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15786,7 +15792,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15836,7 +15842,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -16436,7 +16442,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16486,7 +16492,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16536,7 +16542,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16586,7 +16592,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16636,7 +16642,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16686,7 +16692,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16736,7 +16742,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16786,7 +16792,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16836,7 +16842,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16886,7 +16892,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16936,7 +16942,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16986,7 +16992,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17036,7 +17042,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17086,7 +17092,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17136,7 +17142,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17486,7 +17492,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17536,7 +17542,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17586,7 +17592,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17636,7 +17642,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17686,7 +17692,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17736,7 +17742,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17786,7 +17792,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17836,7 +17842,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17886,7 +17892,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17936,7 +17942,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17986,7 +17992,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -18036,7 +18042,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18086,7 +18092,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -18136,7 +18142,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18186,7 +18192,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -18236,7 +18242,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18286,7 +18292,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18336,7 +18342,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18386,7 +18392,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18436,7 +18442,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18486,7 +18492,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18536,7 +18542,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18586,7 +18592,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18636,7 +18642,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18686,7 +18692,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18736,7 +18742,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18786,7 +18792,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18836,7 +18842,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18886,7 +18892,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18936,7 +18942,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18986,7 +18992,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19036,7 +19042,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19086,7 +19092,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19136,7 +19142,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19186,7 +19192,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19236,7 +19242,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19286,7 +19292,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19336,7 +19342,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19386,7 +19392,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19436,7 +19442,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19486,7 +19492,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19536,7 +19542,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19586,7 +19592,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19636,7 +19642,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -21186,7 +21192,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21236,7 +21242,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21286,7 +21292,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21336,7 +21342,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21386,7 +21392,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21436,7 +21442,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21786,7 +21792,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21836,7 +21842,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21886,7 +21892,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21936,7 +21942,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21986,7 +21992,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22036,7 +22042,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22086,7 +22092,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22136,7 +22142,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22186,7 +22192,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22236,7 +22242,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22286,7 +22292,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22336,7 +22342,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22986,7 +22992,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23036,7 +23042,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23086,7 +23092,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23136,7 +23142,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23186,7 +23192,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23236,7 +23242,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23286,7 +23292,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -25036,7 +25042,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -25086,7 +25092,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25136,7 +25142,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25186,7 +25192,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25236,7 +25242,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25286,7 +25292,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25336,7 +25342,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25386,7 +25392,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25436,7 +25442,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25486,7 +25492,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25536,7 +25542,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25586,7 +25592,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25636,7 +25642,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25686,7 +25692,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25736,7 +25742,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25786,7 +25792,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -28086,7 +28092,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28136,7 +28142,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28186,7 +28192,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28236,7 +28242,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28286,7 +28292,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28336,7 +28342,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28386,7 +28392,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28436,7 +28442,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -29286,7 +29292,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29336,7 +29342,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29386,7 +29392,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29436,7 +29442,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29486,7 +29492,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29536,7 +29542,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29586,7 +29592,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29636,7 +29642,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -30486,7 +30492,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30536,7 +30542,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30586,7 +30592,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30636,7 +30642,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30686,7 +30692,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30736,7 +30742,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30786,7 +30792,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30836,7 +30842,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30886,7 +30892,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30936,7 +30942,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30986,7 +30992,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -31036,7 +31042,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -31086,7 +31092,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -31136,7 +31142,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31186,7 +31192,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31236,7 +31242,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31286,7 +31292,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31336,7 +31342,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31386,7 +31392,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31436,7 +31442,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31486,7 +31492,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31536,7 +31542,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31586,7 +31592,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31636,7 +31642,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31686,7 +31692,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31736,7 +31742,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31786,7 +31792,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31836,7 +31842,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31886,7 +31892,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31936,7 +31942,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31986,7 +31992,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32036,7 +32042,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32086,7 +32092,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32136,7 +32142,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32186,7 +32192,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32236,7 +32242,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32286,7 +32292,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32336,7 +32342,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32386,7 +32392,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32436,7 +32442,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32486,7 +32492,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32536,7 +32542,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32586,7 +32592,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32636,7 +32642,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32686,7 +32692,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32736,7 +32742,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32786,7 +32792,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32836,7 +32842,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32886,7 +32892,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32936,7 +32942,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -36036,7 +36042,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36086,7 +36092,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36136,7 +36142,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36186,7 +36192,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36236,7 +36242,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36286,7 +36292,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36336,7 +36342,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36386,7 +36392,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36436,7 +36442,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36486,7 +36492,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36536,7 +36542,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36586,7 +36592,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36636,7 +36642,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -38786,7 +38792,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38836,7 +38842,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38886,7 +38892,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38936,7 +38942,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38986,7 +38992,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39036,7 +39042,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39086,7 +39092,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39136,7 +39142,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39186,7 +39192,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39236,7 +39242,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39286,7 +39292,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39336,7 +39342,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39386,7 +39392,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39436,7 +39442,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39486,7 +39492,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39536,7 +39542,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39586,7 +39592,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39636,7 +39642,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -42286,7 +42292,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42336,7 +42342,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42386,7 +42392,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42436,7 +42442,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42486,7 +42492,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42536,7 +42542,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42586,7 +42592,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42636,7 +42642,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42686,7 +42692,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -47636,7 +47642,7 @@
         <v>1</v>
       </c>
       <c r="P912" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="913" spans="1:16">
@@ -47686,7 +47692,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -47736,7 +47742,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -48036,7 +48042,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48086,7 +48092,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48136,7 +48142,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48186,7 +48192,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48236,7 +48242,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -49386,7 +49392,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49436,7 +49442,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49486,7 +49492,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49536,7 +49542,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49586,7 +49592,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49636,7 +49642,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49686,7 +49692,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49736,7 +49742,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49786,7 +49792,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49836,7 +49842,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49886,7 +49892,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -49936,7 +49942,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50786,7 +50792,7 @@
         <v>1</v>
       </c>
       <c r="P975" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="976" spans="1:16">
@@ -50836,7 +50842,7 @@
         <v>1</v>
       </c>
       <c r="P976" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="977" spans="1:16">
@@ -50886,7 +50892,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -50936,7 +50942,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -51136,7 +51142,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51186,7 +51192,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51236,7 +51242,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51436,7 +51442,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51486,7 +51492,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51536,7 +51542,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51586,7 +51592,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51636,7 +51642,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51686,7 +51692,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51736,7 +51742,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51786,7 +51792,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -51836,7 +51842,7 @@
         <v>1</v>
       </c>
       <c r="P996" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="997" spans="1:16">
@@ -51886,7 +51892,7 @@
         <v>1</v>
       </c>
       <c r="P997" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="998" spans="1:16">
@@ -51936,7 +51942,7 @@
         <v>1</v>
       </c>
       <c r="P998" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="999" spans="1:16">
@@ -51986,7 +51992,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -52036,7 +52042,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52086,7 +52092,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -52286,7 +52292,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52336,7 +52342,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52386,7 +52392,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52436,7 +52442,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -52636,7 +52642,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52686,7 +52692,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52736,7 +52742,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -54686,7 +54692,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54736,7 +54742,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54786,7 +54792,7 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
@@ -54836,7 +54842,7 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -54886,7 +54892,7 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -54936,7 +54942,7 @@
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -54986,7 +54992,7 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
@@ -55036,7 +55042,7 @@
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
@@ -55086,7 +55092,7 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
@@ -55136,7 +55142,7 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -55186,7 +55192,7 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -55236,7 +55242,7 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -55286,7 +55292,7 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55336,7 +55342,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55386,7 +55392,7 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55436,7 +55442,7 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55486,7 +55492,7 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
@@ -55536,7 +55542,7 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
@@ -55586,7 +55592,7 @@
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55636,7 +55642,7 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55686,7 +55692,7 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -55736,7 +55742,7 @@
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1075" spans="1:16">
@@ -55786,7 +55792,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55836,7 +55842,7 @@
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -55886,7 +55892,7 @@
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
@@ -55936,7 +55942,7 @@
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
@@ -55986,7 +55992,7 @@
         <v>1</v>
       </c>
       <c r="P1079" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1080" spans="1:16">
@@ -56036,7 +56042,7 @@
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
@@ -56086,7 +56092,7 @@
         <v>1</v>
       </c>
       <c r="P1081" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1082" spans="1:16">
@@ -56136,7 +56142,7 @@
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
@@ -56186,7 +56192,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56236,7 +56242,7 @@
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56286,7 +56292,7 @@
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56336,7 +56342,7 @@
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56386,7 +56392,7 @@
         <v>1</v>
       </c>
       <c r="P1087" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1088" spans="1:16">
@@ -56436,7 +56442,7 @@
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56486,7 +56492,7 @@
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56536,7 +56542,7 @@
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56586,7 +56592,7 @@
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -56636,7 +56642,7 @@
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1093" spans="1:16">
@@ -56686,7 +56692,7 @@
         <v>1</v>
       </c>
       <c r="P1093" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1094" spans="1:16">
@@ -56736,7 +56742,7 @@
         <v>1</v>
       </c>
       <c r="P1094" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1095" spans="1:16">
@@ -56786,7 +56792,7 @@
         <v>1</v>
       </c>
       <c r="P1095" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1096" spans="1:16">
@@ -56836,7 +56842,7 @@
         <v>1</v>
       </c>
       <c r="P1096" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="1097" spans="1:16">
@@ -56886,7 +56892,7 @@
         <v>1</v>
       </c>
       <c r="P1097" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1098" spans="1:16">
@@ -56936,7 +56942,7 @@
         <v>1</v>
       </c>
       <c r="P1098" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1099" spans="1:16">
@@ -56986,7 +56992,7 @@
         <v>1</v>
       </c>
       <c r="P1099" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1100" spans="1:16">
@@ -57036,7 +57042,7 @@
         <v>1</v>
       </c>
       <c r="P1100" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1101" spans="1:16">
@@ -57086,7 +57092,7 @@
         <v>1</v>
       </c>
       <c r="P1101" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1102" spans="1:16">
@@ -57136,7 +57142,7 @@
         <v>1</v>
       </c>
       <c r="P1102" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1103" spans="1:16">
@@ -57186,7 +57192,7 @@
         <v>1</v>
       </c>
       <c r="P1103" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1104" spans="1:16">
@@ -57236,7 +57242,7 @@
         <v>1</v>
       </c>
       <c r="P1104" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1105" spans="1:16">
@@ -57286,7 +57292,7 @@
         <v>1</v>
       </c>
       <c r="P1105" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1106" spans="1:16">
@@ -57336,7 +57342,7 @@
         <v>1</v>
       </c>
       <c r="P1106" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1107" spans="1:16">
@@ -57386,7 +57392,7 @@
         <v>1</v>
       </c>
       <c r="P1107" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1108" spans="1:16">
@@ -57436,7 +57442,7 @@
         <v>1</v>
       </c>
       <c r="P1108" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="1109" spans="1:16">
@@ -57486,7 +57492,7 @@
         <v>1</v>
       </c>
       <c r="P1109" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1110" spans="1:16">
@@ -57536,7 +57542,7 @@
         <v>1</v>
       </c>
       <c r="P1110" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1111" spans="1:16">
@@ -57586,7 +57592,7 @@
         <v>1</v>
       </c>
       <c r="P1111" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1112" spans="1:16">
@@ -57636,7 +57642,7 @@
         <v>1</v>
       </c>
       <c r="P1112" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1113" spans="1:16">
@@ -57686,7 +57692,7 @@
         <v>1</v>
       </c>
       <c r="P1113" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1114" spans="1:16">
@@ -57736,7 +57742,7 @@
         <v>1</v>
       </c>
       <c r="P1114" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1115" spans="1:16">
@@ -57786,7 +57792,7 @@
         <v>1</v>
       </c>
       <c r="P1115" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1116" spans="1:16">
@@ -57836,7 +57842,7 @@
         <v>1</v>
       </c>
       <c r="P1116" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1117" spans="1:16">
@@ -57886,7 +57892,7 @@
         <v>1</v>
       </c>
       <c r="P1117" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1118" spans="1:16">
@@ -57936,7 +57942,7 @@
         <v>1</v>
       </c>
       <c r="P1118" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1119" spans="1:16">
@@ -57986,7 +57992,7 @@
         <v>1</v>
       </c>
       <c r="P1119" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1120" spans="1:16">
@@ -58036,7 +58042,7 @@
         <v>1</v>
       </c>
       <c r="P1120" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="1121" spans="1:16">
@@ -59236,7 +59242,7 @@
         <v>1</v>
       </c>
       <c r="P1144" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1145" spans="1:16">
@@ -59286,7 +59292,7 @@
         <v>1</v>
       </c>
       <c r="P1145" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1146" spans="1:16">
@@ -59336,7 +59342,7 @@
         <v>1</v>
       </c>
       <c r="P1146" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1147" spans="1:16">
@@ -59386,7 +59392,7 @@
         <v>1</v>
       </c>
       <c r="P1147" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1148" spans="1:16">
@@ -59436,7 +59442,7 @@
         <v>1</v>
       </c>
       <c r="P1148" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1149" spans="1:16">
@@ -59486,7 +59492,7 @@
         <v>1</v>
       </c>
       <c r="P1149" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1150" spans="1:16">
@@ -59536,7 +59542,7 @@
         <v>1</v>
       </c>
       <c r="P1150" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1151" spans="1:16">
@@ -59586,7 +59592,7 @@
         <v>1</v>
       </c>
       <c r="P1151" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1152" spans="1:16">
@@ -59636,7 +59642,7 @@
         <v>1</v>
       </c>
       <c r="P1152" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1153" spans="1:16">
@@ -59686,7 +59692,7 @@
         <v>1</v>
       </c>
       <c r="P1153" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1154" spans="1:16">
@@ -59736,7 +59742,7 @@
         <v>1</v>
       </c>
       <c r="P1154" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1155" spans="1:16">
@@ -59786,7 +59792,7 @@
         <v>1</v>
       </c>
       <c r="P1155" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1156" spans="1:16">
@@ -59836,7 +59842,7 @@
         <v>1</v>
       </c>
       <c r="P1156" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1157" spans="1:16">
@@ -59886,7 +59892,7 @@
         <v>1</v>
       </c>
       <c r="P1157" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1158" spans="1:16">
@@ -59936,7 +59942,7 @@
         <v>1</v>
       </c>
       <c r="P1158" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1159" spans="1:16">
@@ -59986,7 +59992,7 @@
         <v>1</v>
       </c>
       <c r="P1159" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1160" spans="1:16">
@@ -60036,7 +60042,7 @@
         <v>1</v>
       </c>
       <c r="P1160" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1161" spans="1:16">
@@ -60086,7 +60092,7 @@
         <v>1</v>
       </c>
       <c r="P1161" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1162" spans="1:16">
@@ -60136,7 +60142,7 @@
         <v>1</v>
       </c>
       <c r="P1162" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1163" spans="1:16">
@@ -60186,7 +60192,7 @@
         <v>1</v>
       </c>
       <c r="P1163" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1164" spans="1:16">
@@ -60236,7 +60242,7 @@
         <v>1</v>
       </c>
       <c r="P1164" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1165" spans="1:16">
@@ -60286,7 +60292,7 @@
         <v>1</v>
       </c>
       <c r="P1165" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1166" spans="1:16">
@@ -60336,7 +60342,7 @@
         <v>1</v>
       </c>
       <c r="P1166" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1167" spans="1:16">
@@ -60386,7 +60392,7 @@
         <v>1</v>
       </c>
       <c r="P1167" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1168" spans="1:16">
@@ -60436,7 +60442,7 @@
         <v>1</v>
       </c>
       <c r="P1168" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1169" spans="1:16">
@@ -60486,7 +60492,7 @@
         <v>1</v>
       </c>
       <c r="P1169" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1170" spans="1:16">
@@ -60936,7 +60942,7 @@
         <v>1</v>
       </c>
       <c r="P1178" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1179" spans="1:16">
@@ -60986,7 +60992,7 @@
         <v>1</v>
       </c>
       <c r="P1179" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1180" spans="1:16">
@@ -61036,7 +61042,7 @@
         <v>1</v>
       </c>
       <c r="P1180" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1181" spans="1:16">
@@ -61086,7 +61092,7 @@
         <v>1</v>
       </c>
       <c r="P1181" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1182" spans="1:16">
@@ -61136,7 +61142,7 @@
         <v>1</v>
       </c>
       <c r="P1182" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1183" spans="1:16">
@@ -61186,7 +61192,7 @@
         <v>1</v>
       </c>
       <c r="P1183" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1184" spans="1:16">
@@ -61236,7 +61242,7 @@
         <v>1</v>
       </c>
       <c r="P1184" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1185" spans="1:16">
@@ -61286,7 +61292,7 @@
         <v>1</v>
       </c>
       <c r="P1185" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1186" spans="1:16">
@@ -61736,7 +61742,7 @@
         <v>1</v>
       </c>
       <c r="P1194" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1195" spans="1:16">
@@ -61786,7 +61792,7 @@
         <v>1</v>
       </c>
       <c r="P1195" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1196" spans="1:16">
@@ -61836,7 +61842,7 @@
         <v>1</v>
       </c>
       <c r="P1196" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1197" spans="1:16">
@@ -61886,7 +61892,7 @@
         <v>1</v>
       </c>
       <c r="P1197" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1198" spans="1:16">
@@ -61936,7 +61942,7 @@
         <v>1</v>
       </c>
       <c r="P1198" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1199" spans="1:16">
@@ -61986,7 +61992,7 @@
         <v>1</v>
       </c>
       <c r="P1199" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1200" spans="1:16">
@@ -62036,7 +62042,7 @@
         <v>1</v>
       </c>
       <c r="P1200" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1201" spans="1:16">
@@ -62086,7 +62092,7 @@
         <v>1</v>
       </c>
       <c r="P1201" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1202" spans="1:16">
@@ -62136,7 +62142,7 @@
         <v>1</v>
       </c>
       <c r="P1202" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1203" spans="1:16">
@@ -62186,7 +62192,7 @@
         <v>1</v>
       </c>
       <c r="P1203" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1204" spans="1:16">
@@ -62236,7 +62242,7 @@
         <v>1</v>
       </c>
       <c r="P1204" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1205" spans="1:16">
@@ -62286,7 +62292,7 @@
         <v>1</v>
       </c>
       <c r="P1205" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1206" spans="1:16">
@@ -62336,7 +62342,7 @@
         <v>1</v>
       </c>
       <c r="P1206" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1207" spans="1:16">
@@ -62386,7 +62392,7 @@
         <v>1</v>
       </c>
       <c r="P1207" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1208" spans="1:16">
@@ -62436,7 +62442,7 @@
         <v>1</v>
       </c>
       <c r="P1208" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1209" spans="1:16">
@@ -62486,7 +62492,7 @@
         <v>1</v>
       </c>
       <c r="P1209" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1210" spans="1:16">
@@ -62536,7 +62542,7 @@
         <v>1</v>
       </c>
       <c r="P1210" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1211" spans="1:16">
@@ -62586,7 +62592,7 @@
         <v>1</v>
       </c>
       <c r="P1211" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1212" spans="1:16">
@@ -62636,7 +62642,7 @@
         <v>1</v>
       </c>
       <c r="P1212" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1213" spans="1:16">
@@ -62686,7 +62692,7 @@
         <v>1</v>
       </c>
       <c r="P1213" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1214" spans="1:16">
@@ -62736,7 +62742,7 @@
         <v>1</v>
       </c>
       <c r="P1214" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1215" spans="1:16">
@@ -62786,7 +62792,7 @@
         <v>1</v>
       </c>
       <c r="P1215" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1216" spans="1:16">
@@ -62836,7 +62842,7 @@
         <v>1</v>
       </c>
       <c r="P1216" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1217" spans="1:16">
@@ -62886,7 +62892,7 @@
         <v>1</v>
       </c>
       <c r="P1217" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1218" spans="1:16">
@@ -62936,7 +62942,7 @@
         <v>1</v>
       </c>
       <c r="P1218" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1219" spans="1:16">
@@ -62986,7 +62992,7 @@
         <v>1</v>
       </c>
       <c r="P1219" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1220" spans="1:16">
@@ -64686,7 +64692,7 @@
         <v>1</v>
       </c>
       <c r="P1253" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1254" spans="1:16">
@@ -64736,7 +64742,7 @@
         <v>1</v>
       </c>
       <c r="P1254" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1255" spans="1:16">
@@ -64786,7 +64792,7 @@
         <v>1</v>
       </c>
       <c r="P1255" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1256" spans="1:16">
@@ -64836,7 +64842,7 @@
         <v>1</v>
       </c>
       <c r="P1256" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1257" spans="1:16">
@@ -64886,7 +64892,7 @@
         <v>1</v>
       </c>
       <c r="P1257" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1258" spans="1:16">
@@ -64936,7 +64942,7 @@
         <v>1</v>
       </c>
       <c r="P1258" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1259" spans="1:16">
@@ -64986,7 +64992,7 @@
         <v>1</v>
       </c>
       <c r="P1259" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1260" spans="1:16">
@@ -65036,7 +65042,7 @@
         <v>1</v>
       </c>
       <c r="P1260" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1261" spans="1:16">
@@ -65086,7 +65092,7 @@
         <v>1</v>
       </c>
       <c r="P1261" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1262" spans="1:16">
@@ -65136,7 +65142,7 @@
         <v>1</v>
       </c>
       <c r="P1262" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1263" spans="1:16">
@@ -65186,7 +65192,7 @@
         <v>1</v>
       </c>
       <c r="P1263" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1264" spans="1:16">
@@ -65836,7 +65842,7 @@
         <v>1</v>
       </c>
       <c r="P1276" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1277" spans="1:16">
@@ -65886,7 +65892,7 @@
         <v>1</v>
       </c>
       <c r="P1277" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1278" spans="1:16">
@@ -65936,7 +65942,7 @@
         <v>1</v>
       </c>
       <c r="P1278" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1279" spans="1:16">
@@ -65986,7 +65992,7 @@
         <v>1</v>
       </c>
       <c r="P1279" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1280" spans="1:16">
@@ -66036,7 +66042,7 @@
         <v>1</v>
       </c>
       <c r="P1280" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1281" spans="1:16">
@@ -66086,7 +66092,7 @@
         <v>1</v>
       </c>
       <c r="P1281" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1282" spans="1:16">
@@ -66136,7 +66142,7 @@
         <v>1</v>
       </c>
       <c r="P1282" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1283" spans="1:16">
@@ -66186,7 +66192,7 @@
         <v>1</v>
       </c>
       <c r="P1283" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1284" spans="1:16">
@@ -66236,7 +66242,7 @@
         <v>1</v>
       </c>
       <c r="P1284" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1285" spans="1:16">
@@ -66286,7 +66292,7 @@
         <v>1</v>
       </c>
       <c r="P1285" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1286" spans="1:16">
@@ -66336,7 +66342,7 @@
         <v>1</v>
       </c>
       <c r="P1286" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1287" spans="1:16">
@@ -66386,7 +66392,7 @@
         <v>1</v>
       </c>
       <c r="P1287" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1288" spans="1:16">
@@ -66436,7 +66442,7 @@
         <v>1</v>
       </c>
       <c r="P1288" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1289" spans="1:16">
@@ -66486,7 +66492,7 @@
         <v>1</v>
       </c>
       <c r="P1289" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1290" spans="1:16">
@@ -66536,7 +66542,7 @@
         <v>1</v>
       </c>
       <c r="P1290" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1291" spans="1:16">
@@ -66586,7 +66592,7 @@
         <v>1</v>
       </c>
       <c r="P1291" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1292" spans="1:16">
@@ -66636,7 +66642,7 @@
         <v>1</v>
       </c>
       <c r="P1292" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1293" spans="1:16">
@@ -66686,7 +66692,7 @@
         <v>1</v>
       </c>
       <c r="P1293" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1294" spans="1:16">
@@ -66736,7 +66742,7 @@
         <v>1</v>
       </c>
       <c r="P1294" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1295" spans="1:16">
@@ -66786,7 +66792,7 @@
         <v>1</v>
       </c>
       <c r="P1295" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1296" spans="1:16">
@@ -66836,7 +66842,7 @@
         <v>1</v>
       </c>
       <c r="P1296" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1297" spans="1:16">
@@ -66886,7 +66892,7 @@
         <v>1</v>
       </c>
       <c r="P1297" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1298" spans="1:16">
@@ -66936,7 +66942,7 @@
         <v>1</v>
       </c>
       <c r="P1298" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1299" spans="1:16">
@@ -66986,7 +66992,7 @@
         <v>1</v>
       </c>
       <c r="P1299" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1300" spans="1:16">
@@ -67036,7 +67042,7 @@
         <v>1</v>
       </c>
       <c r="P1300" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1301" spans="1:16">
@@ -67086,7 +67092,7 @@
         <v>1</v>
       </c>
       <c r="P1301" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1302" spans="1:16">
@@ -67136,7 +67142,7 @@
         <v>1</v>
       </c>
       <c r="P1302" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1303" spans="1:16">
@@ -67186,7 +67192,7 @@
         <v>1</v>
       </c>
       <c r="P1303" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1304" spans="1:16">
@@ -67236,7 +67242,7 @@
         <v>1</v>
       </c>
       <c r="P1304" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1305" spans="1:16">
@@ -67286,7 +67292,7 @@
         <v>1</v>
       </c>
       <c r="P1305" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1306" spans="1:16">
@@ -67336,7 +67342,7 @@
         <v>1</v>
       </c>
       <c r="P1306" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1307" spans="1:16">
@@ -67386,7 +67392,7 @@
         <v>1</v>
       </c>
       <c r="P1307" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1308" spans="1:16">
@@ -67436,7 +67442,7 @@
         <v>1</v>
       </c>
       <c r="P1308" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1309" spans="1:16">
@@ -67486,7 +67492,7 @@
         <v>1</v>
       </c>
       <c r="P1309" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1310" spans="1:16">
@@ -67536,7 +67542,7 @@
         <v>1</v>
       </c>
       <c r="P1310" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1311" spans="1:16">
@@ -67586,7 +67592,7 @@
         <v>1</v>
       </c>
       <c r="P1311" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="1312" spans="1:16">
@@ -67636,7 +67642,7 @@
         <v>1</v>
       </c>
       <c r="P1312" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1313" spans="1:16">
@@ -67686,7 +67692,7 @@
         <v>1</v>
       </c>
       <c r="P1313" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1314" spans="1:16">
@@ -67736,7 +67742,7 @@
         <v>1</v>
       </c>
       <c r="P1314" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1315" spans="1:16">
@@ -67786,7 +67792,7 @@
         <v>1</v>
       </c>
       <c r="P1315" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1316" spans="1:16">
@@ -67836,7 +67842,7 @@
         <v>1</v>
       </c>
       <c r="P1316" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1317" spans="1:16">
@@ -67886,7 +67892,7 @@
         <v>1</v>
       </c>
       <c r="P1317" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1318" spans="1:16">
@@ -67936,7 +67942,7 @@
         <v>1</v>
       </c>
       <c r="P1318" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1319" spans="1:16">
@@ -67986,7 +67992,7 @@
         <v>1</v>
       </c>
       <c r="P1319" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1320" spans="1:16">
@@ -68036,7 +68042,7 @@
         <v>1</v>
       </c>
       <c r="P1320" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1321" spans="1:16">
@@ -68086,7 +68092,7 @@
         <v>1</v>
       </c>
       <c r="P1321" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1322" spans="1:16">
@@ -68136,7 +68142,7 @@
         <v>1</v>
       </c>
       <c r="P1322" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1323" spans="1:16">
@@ -68186,7 +68192,7 @@
         <v>1</v>
       </c>
       <c r="P1323" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1324" spans="1:16">
@@ -68836,7 +68842,7 @@
         <v>1</v>
       </c>
       <c r="P1336" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1337" spans="1:16">
@@ -68886,7 +68892,7 @@
         <v>1</v>
       </c>
       <c r="P1337" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1338" spans="1:16">
@@ -68936,7 +68942,7 @@
         <v>1</v>
       </c>
       <c r="P1338" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1339" spans="1:16">
@@ -68986,7 +68992,7 @@
         <v>1</v>
       </c>
       <c r="P1339" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1340" spans="1:16">
@@ -69036,7 +69042,7 @@
         <v>1</v>
       </c>
       <c r="P1340" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1341" spans="1:16">
@@ -69086,7 +69092,7 @@
         <v>1</v>
       </c>
       <c r="P1341" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1342" spans="1:16">
@@ -69136,7 +69142,7 @@
         <v>1</v>
       </c>
       <c r="P1342" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1343" spans="1:16">
@@ -69186,7 +69192,7 @@
         <v>1</v>
       </c>
       <c r="P1343" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1344" spans="1:16">
@@ -69236,7 +69242,7 @@
         <v>1</v>
       </c>
       <c r="P1344" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1345" spans="1:16">
@@ -69286,7 +69292,7 @@
         <v>1</v>
       </c>
       <c r="P1345" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1346" spans="1:16">
@@ -69336,7 +69342,7 @@
         <v>1</v>
       </c>
       <c r="P1346" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1347" spans="1:16">
@@ -69386,7 +69392,7 @@
         <v>1</v>
       </c>
       <c r="P1347" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="1348" spans="1:16">
@@ -70036,7 +70042,7 @@
         <v>1</v>
       </c>
       <c r="P1360" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1361" spans="1:16">
@@ -70086,7 +70092,7 @@
         <v>1</v>
       </c>
       <c r="P1361" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1362" spans="1:16">
@@ -70136,7 +70142,7 @@
         <v>1</v>
       </c>
       <c r="P1362" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1363" spans="1:16">
@@ -70186,7 +70192,7 @@
         <v>1</v>
       </c>
       <c r="P1363" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1364" spans="1:16">
@@ -70236,7 +70242,7 @@
         <v>1</v>
       </c>
       <c r="P1364" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1365" spans="1:16">
@@ -70286,7 +70292,7 @@
         <v>1</v>
       </c>
       <c r="P1365" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1366" spans="1:16">
@@ -70336,7 +70342,7 @@
         <v>1</v>
       </c>
       <c r="P1366" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1367" spans="1:16">
@@ -70386,7 +70392,7 @@
         <v>1</v>
       </c>
       <c r="P1367" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1368" spans="1:16">
@@ -70436,7 +70442,7 @@
         <v>1</v>
       </c>
       <c r="P1368" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1369" spans="1:16">
@@ -70486,7 +70492,7 @@
         <v>1</v>
       </c>
       <c r="P1369" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1370" spans="1:16">
@@ -70536,7 +70542,7 @@
         <v>1</v>
       </c>
       <c r="P1370" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="1371" spans="1:16">
@@ -71186,7 +71192,7 @@
         <v>1</v>
       </c>
       <c r="P1383" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1384" spans="1:16">
@@ -71236,7 +71242,7 @@
         <v>1</v>
       </c>
       <c r="P1384" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1385" spans="1:16">
@@ -71286,7 +71292,7 @@
         <v>1</v>
       </c>
       <c r="P1385" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1386" spans="1:16">
@@ -71336,7 +71342,7 @@
         <v>1</v>
       </c>
       <c r="P1386" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1387" spans="1:16">
@@ -71386,7 +71392,7 @@
         <v>1</v>
       </c>
       <c r="P1387" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1388" spans="1:16">
@@ -71436,7 +71442,7 @@
         <v>1</v>
       </c>
       <c r="P1388" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1389" spans="1:16">
@@ -71486,7 +71492,7 @@
         <v>1</v>
       </c>
       <c r="P1389" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1390" spans="1:16">
@@ -71536,7 +71542,7 @@
         <v>1</v>
       </c>
       <c r="P1390" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1391" spans="1:16">
@@ -71586,7 +71592,7 @@
         <v>1</v>
       </c>
       <c r="P1391" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1392" spans="1:16">
@@ -71636,7 +71642,7 @@
         <v>1</v>
       </c>
       <c r="P1392" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1393" spans="1:16">
@@ -71686,7 +71692,7 @@
         <v>1</v>
       </c>
       <c r="P1393" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1394" spans="1:16">
@@ -72836,7 +72842,7 @@
         <v>1</v>
       </c>
       <c r="P1416" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1417" spans="1:16">
@@ -72886,7 +72892,7 @@
         <v>1</v>
       </c>
       <c r="P1417" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1418" spans="1:16">
@@ -72936,7 +72942,7 @@
         <v>1</v>
       </c>
       <c r="P1418" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1419" spans="1:16">
@@ -72986,7 +72992,7 @@
         <v>1</v>
       </c>
       <c r="P1419" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1420" spans="1:16">
@@ -73036,7 +73042,7 @@
         <v>1</v>
       </c>
       <c r="P1420" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1421" spans="1:16">
@@ -73086,7 +73092,7 @@
         <v>1</v>
       </c>
       <c r="P1421" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1422" spans="1:16">
@@ -73136,7 +73142,7 @@
         <v>1</v>
       </c>
       <c r="P1422" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1423" spans="1:16">
@@ -73186,7 +73192,7 @@
         <v>1</v>
       </c>
       <c r="P1423" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1424" spans="1:16">
@@ -73236,7 +73242,7 @@
         <v>1</v>
       </c>
       <c r="P1424" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1425" spans="1:16">
@@ -73286,7 +73292,7 @@
         <v>1</v>
       </c>
       <c r="P1425" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1426" spans="1:16">
@@ -73336,7 +73342,7 @@
         <v>1</v>
       </c>
       <c r="P1426" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1427" spans="1:16">
@@ -73386,7 +73392,7 @@
         <v>1</v>
       </c>
       <c r="P1427" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="1428" spans="1:16">
@@ -74536,7 +74542,7 @@
         <v>1</v>
       </c>
       <c r="P1450" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1451" spans="1:16">
@@ -74586,7 +74592,7 @@
         <v>1</v>
       </c>
       <c r="P1451" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1452" spans="1:16">
@@ -74636,7 +74642,7 @@
         <v>1</v>
       </c>
       <c r="P1452" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1453" spans="1:16">
@@ -74686,7 +74692,7 @@
         <v>1</v>
       </c>
       <c r="P1453" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1454" spans="1:16">
@@ -74736,7 +74742,7 @@
         <v>1</v>
       </c>
       <c r="P1454" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1455" spans="1:16">
@@ -74786,7 +74792,7 @@
         <v>1</v>
       </c>
       <c r="P1455" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1456" spans="1:16">
@@ -74836,7 +74842,7 @@
         <v>1</v>
       </c>
       <c r="P1456" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1457" spans="1:16">
@@ -74886,7 +74892,7 @@
         <v>1</v>
       </c>
       <c r="P1457" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1458" spans="1:16">
@@ -74936,7 +74942,7 @@
         <v>1</v>
       </c>
       <c r="P1458" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1459" spans="1:16">
@@ -75386,7 +75392,7 @@
         <v>1</v>
       </c>
       <c r="P1467" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1468" spans="1:16">
@@ -75436,7 +75442,7 @@
         <v>1</v>
       </c>
       <c r="P1468" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1469" spans="1:16">
@@ -75486,7 +75492,7 @@
         <v>1</v>
       </c>
       <c r="P1469" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1470" spans="1:16">
@@ -75536,7 +75542,7 @@
         <v>1</v>
       </c>
       <c r="P1470" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1471" spans="1:16">
@@ -75586,7 +75592,7 @@
         <v>1</v>
       </c>
       <c r="P1471" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1472" spans="1:16">
@@ -75636,7 +75642,7 @@
         <v>1</v>
       </c>
       <c r="P1472" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="1473" spans="1:16">
@@ -75686,7 +75692,7 @@
         <v>1</v>
       </c>
       <c r="P1473" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="1474" spans="1:16">
@@ -75736,7 +75742,7 @@
         <v>1</v>
       </c>
       <c r="P1474" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="1475" spans="1:16">
@@ -75786,7 +75792,7 @@
         <v>1</v>
       </c>
       <c r="P1475" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="1476" spans="1:16">
@@ -75836,7 +75842,7 @@
         <v>1</v>
       </c>
       <c r="P1476" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="1477" spans="1:16">
@@ -75886,7 +75892,7 @@
         <v>1</v>
       </c>
       <c r="P1477" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="1478" spans="1:16">
@@ -75936,7 +75942,7 @@
         <v>1</v>
       </c>
       <c r="P1478" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1479" spans="1:16">
@@ -75986,7 +75992,7 @@
         <v>1</v>
       </c>
       <c r="P1479" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1480" spans="1:16">
@@ -76036,7 +76042,7 @@
         <v>1</v>
       </c>
       <c r="P1480" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1481" spans="1:16">
@@ -76086,7 +76092,7 @@
         <v>1</v>
       </c>
       <c r="P1481" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="1482" spans="1:16">
@@ -76136,7 +76142,7 @@
         <v>1</v>
       </c>
       <c r="P1482" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1483" spans="1:16">
@@ -76186,7 +76192,7 @@
         <v>1</v>
       </c>
       <c r="P1483" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1484" spans="1:16">
@@ -76236,7 +76242,7 @@
         <v>1</v>
       </c>
       <c r="P1484" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1485" spans="1:16">
@@ -76286,7 +76292,7 @@
         <v>1</v>
       </c>
       <c r="P1485" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1486" spans="1:16">
@@ -76336,7 +76342,7 @@
         <v>1</v>
       </c>
       <c r="P1486" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1487" spans="1:16">
@@ -76386,7 +76392,7 @@
         <v>1</v>
       </c>
       <c r="P1487" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1488" spans="1:16">
@@ -76436,7 +76442,7 @@
         <v>1</v>
       </c>
       <c r="P1488" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1489" spans="1:16">
@@ -76486,7 +76492,7 @@
         <v>1</v>
       </c>
       <c r="P1489" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1490" spans="1:16">
@@ -76536,7 +76542,7 @@
         <v>1</v>
       </c>
       <c r="P1490" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1491" spans="1:16">
@@ -76586,7 +76592,7 @@
         <v>1</v>
       </c>
       <c r="P1491" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1492" spans="1:16">
@@ -76636,7 +76642,7 @@
         <v>1</v>
       </c>
       <c r="P1492" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1493" spans="1:16">
@@ -76686,7 +76692,7 @@
         <v>1</v>
       </c>
       <c r="P1493" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1494" spans="1:16">
@@ -76736,7 +76742,7 @@
         <v>1</v>
       </c>
       <c r="P1494" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1495" spans="1:16">
@@ -76786,7 +76792,7 @@
         <v>1</v>
       </c>
       <c r="P1495" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1496" spans="1:16">
@@ -76836,7 +76842,7 @@
         <v>1</v>
       </c>
       <c r="P1496" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1497" spans="1:16">
@@ -76886,7 +76892,7 @@
         <v>1</v>
       </c>
       <c r="P1497" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1498" spans="1:16">
@@ -76936,7 +76942,7 @@
         <v>1</v>
       </c>
       <c r="P1498" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="1499" spans="1:16">
@@ -76986,7 +76992,7 @@
         <v>1</v>
       </c>
       <c r="P1499" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1500" spans="1:16">
@@ -77036,7 +77042,7 @@
         <v>1</v>
       </c>
       <c r="P1500" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1501" spans="1:16">
@@ -77086,7 +77092,7 @@
         <v>1</v>
       </c>
       <c r="P1501" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1502" spans="1:16">
@@ -77136,7 +77142,7 @@
         <v>1</v>
       </c>
       <c r="P1502" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1503" spans="1:16">
@@ -77186,7 +77192,7 @@
         <v>1</v>
       </c>
       <c r="P1503" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1504" spans="1:16">
@@ -77236,7 +77242,7 @@
         <v>1</v>
       </c>
       <c r="P1504" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1505" spans="1:16">
@@ -77286,7 +77292,7 @@
         <v>1</v>
       </c>
       <c r="P1505" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1506" spans="1:16">
@@ -77336,7 +77342,7 @@
         <v>1</v>
       </c>
       <c r="P1506" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1507" spans="1:16">
@@ -77386,7 +77392,7 @@
         <v>1</v>
       </c>
       <c r="P1507" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1508" spans="1:16">
@@ -77436,7 +77442,7 @@
         <v>1</v>
       </c>
       <c r="P1508" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1509" spans="1:16">
@@ -77486,7 +77492,7 @@
         <v>1</v>
       </c>
       <c r="P1509" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1510" spans="1:16">
@@ -77536,7 +77542,7 @@
         <v>1</v>
       </c>
       <c r="P1510" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1511" spans="1:16">
@@ -77586,7 +77592,7 @@
         <v>1</v>
       </c>
       <c r="P1511" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1512" spans="1:16">
@@ -77636,7 +77642,7 @@
         <v>1</v>
       </c>
       <c r="P1512" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="1513" spans="1:16">
@@ -78036,7 +78042,7 @@
         <v>1</v>
       </c>
       <c r="P1520" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1521" spans="1:16">
@@ -78086,7 +78092,7 @@
         <v>1</v>
       </c>
       <c r="P1521" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1522" spans="1:16">
@@ -78136,7 +78142,7 @@
         <v>1</v>
       </c>
       <c r="P1522" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1523" spans="1:16">
@@ -78186,7 +78192,7 @@
         <v>1</v>
       </c>
       <c r="P1523" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1524" spans="1:16">
@@ -78236,7 +78242,7 @@
         <v>1</v>
       </c>
       <c r="P1524" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1525" spans="1:16">
@@ -78286,7 +78292,7 @@
         <v>1</v>
       </c>
       <c r="P1525" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1526" spans="1:16">
@@ -78336,7 +78342,7 @@
         <v>1</v>
       </c>
       <c r="P1526" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1527" spans="1:16">
@@ -78386,7 +78392,7 @@
         <v>1</v>
       </c>
       <c r="P1527" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="1528" spans="1:16">
@@ -78436,7 +78442,7 @@
         <v>1</v>
       </c>
       <c r="P1528" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1529" spans="1:16">
@@ -78486,7 +78492,7 @@
         <v>1</v>
       </c>
       <c r="P1529" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1530" spans="1:16">
@@ -78536,7 +78542,7 @@
         <v>1</v>
       </c>
       <c r="P1530" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1531" spans="1:16">
@@ -78586,7 +78592,7 @@
         <v>1</v>
       </c>
       <c r="P1531" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1532" spans="1:16">
@@ -78636,7 +78642,7 @@
         <v>1</v>
       </c>
       <c r="P1532" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1533" spans="1:16">
@@ -78686,7 +78692,7 @@
         <v>1</v>
       </c>
       <c r="P1533" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1534" spans="1:16">
@@ -78736,7 +78742,7 @@
         <v>1</v>
       </c>
       <c r="P1534" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1535" spans="1:16">
@@ -78786,7 +78792,7 @@
         <v>1</v>
       </c>
       <c r="P1535" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1536" spans="1:16">
@@ -78836,7 +78842,7 @@
         <v>1</v>
       </c>
       <c r="P1536" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1537" spans="1:16">
@@ -78886,7 +78892,7 @@
         <v>1</v>
       </c>
       <c r="P1537" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1538" spans="1:16">
@@ -78936,7 +78942,7 @@
         <v>1</v>
       </c>
       <c r="P1538" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1539" spans="1:16">
@@ -78986,7 +78992,7 @@
         <v>1</v>
       </c>
       <c r="P1539" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="1540" spans="1:16">
@@ -79036,7 +79042,7 @@
         <v>1</v>
       </c>
       <c r="P1540" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1541" spans="1:16">
@@ -79086,7 +79092,7 @@
         <v>1</v>
       </c>
       <c r="P1541" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1542" spans="1:16">
@@ -79136,7 +79142,7 @@
         <v>1</v>
       </c>
       <c r="P1542" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1543" spans="1:16">
@@ -79186,7 +79192,7 @@
         <v>1</v>
       </c>
       <c r="P1543" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1544" spans="1:16">
@@ -79236,7 +79242,7 @@
         <v>1</v>
       </c>
       <c r="P1544" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1545" spans="1:16">
@@ -79286,7 +79292,7 @@
         <v>1</v>
       </c>
       <c r="P1545" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1546" spans="1:16">
@@ -79336,7 +79342,7 @@
         <v>1</v>
       </c>
       <c r="P1546" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1547" spans="1:16">
@@ -79386,7 +79392,7 @@
         <v>1</v>
       </c>
       <c r="P1547" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1548" spans="1:16">
@@ -79436,7 +79442,7 @@
         <v>1</v>
       </c>
       <c r="P1548" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1549" spans="1:16">
@@ -79486,7 +79492,7 @@
         <v>1</v>
       </c>
       <c r="P1549" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1550" spans="1:16">
@@ -79536,7 +79542,7 @@
         <v>1</v>
       </c>
       <c r="P1550" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1551" spans="1:16">
@@ -79586,7 +79592,7 @@
         <v>1</v>
       </c>
       <c r="P1551" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1552" spans="1:16">
@@ -79636,7 +79642,7 @@
         <v>1</v>
       </c>
       <c r="P1552" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1553" spans="1:16">
@@ -79686,7 +79692,7 @@
         <v>1</v>
       </c>
       <c r="P1553" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1554" spans="1:16">
@@ -79736,7 +79742,7 @@
         <v>1</v>
       </c>
       <c r="P1554" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="1555" spans="1:16">
@@ -79986,7 +79992,7 @@
         <v>1</v>
       </c>
       <c r="P1559" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="1560" spans="1:16">
@@ -80036,7 +80042,7 @@
         <v>1</v>
       </c>
       <c r="P1560" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="1561" spans="1:16">
@@ -80086,7 +80092,7 @@
         <v>1</v>
       </c>
       <c r="P1561" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="1562" spans="1:16">
@@ -80136,7 +80142,7 @@
         <v>1</v>
       </c>
       <c r="P1562" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="1563" spans="1:16">
@@ -80186,7 +80192,7 @@
         <v>1</v>
       </c>
       <c r="P1563" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1564" spans="1:16">
@@ -80236,7 +80242,7 @@
         <v>1</v>
       </c>
       <c r="P1564" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1565" spans="1:16">
@@ -80286,7 +80292,7 @@
         <v>1</v>
       </c>
       <c r="P1565" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1566" spans="1:16">
@@ -80336,7 +80342,7 @@
         <v>1</v>
       </c>
       <c r="P1566" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1567" spans="1:16">
@@ -80386,7 +80392,7 @@
         <v>1</v>
       </c>
       <c r="P1567" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="1568" spans="1:16">
@@ -80436,7 +80442,7 @@
         <v>1</v>
       </c>
       <c r="P1568" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1569" spans="1:16">
@@ -80486,7 +80492,7 @@
         <v>1</v>
       </c>
       <c r="P1569" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1570" spans="1:16">
@@ -80536,7 +80542,7 @@
         <v>1</v>
       </c>
       <c r="P1570" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1571" spans="1:16">
@@ -80586,7 +80592,7 @@
         <v>1</v>
       </c>
       <c r="P1571" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1572" spans="1:16">
@@ -80636,7 +80642,7 @@
         <v>1</v>
       </c>
       <c r="P1572" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1573" spans="1:16">
@@ -80650,7 +80656,7 @@
         <v>1.76226175520578</v>
       </c>
       <c r="D1573" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E1573">
         <v>2.006323623273507</v>
@@ -80686,7 +80692,7 @@
         <v>1</v>
       </c>
       <c r="P1573" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1574" spans="1:16">
@@ -81086,7 +81092,7 @@
         <v>1</v>
       </c>
       <c r="P1581" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1582" spans="1:16">
@@ -81136,7 +81142,7 @@
         <v>1</v>
       </c>
       <c r="P1582" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1583" spans="1:16">
@@ -81186,7 +81192,7 @@
         <v>1</v>
       </c>
       <c r="P1583" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1584" spans="1:16">
@@ -81236,7 +81242,7 @@
         <v>1</v>
       </c>
       <c r="P1584" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1585" spans="1:16">
@@ -81286,7 +81292,7 @@
         <v>1</v>
       </c>
       <c r="P1585" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1586" spans="1:16">
@@ -81336,7 +81342,7 @@
         <v>1</v>
       </c>
       <c r="P1586" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1587" spans="1:16">
@@ -81386,7 +81392,7 @@
         <v>1</v>
       </c>
       <c r="P1587" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1588" spans="1:16">
@@ -81436,7 +81442,7 @@
         <v>1</v>
       </c>
       <c r="P1588" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1589" spans="1:16">
@@ -82200,7 +82206,7 @@
         <v>1.411337710358634</v>
       </c>
       <c r="D1604" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E1604">
         <v>1.647985690154943</v>
@@ -82286,7 +82292,7 @@
         <v>1</v>
       </c>
       <c r="P1605" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1606" spans="1:16">
@@ -82336,7 +82342,7 @@
         <v>1</v>
       </c>
       <c r="P1606" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1607" spans="1:16">
@@ -82386,7 +82392,7 @@
         <v>1</v>
       </c>
       <c r="P1607" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1608" spans="1:16">
@@ -82436,7 +82442,7 @@
         <v>1</v>
       </c>
       <c r="P1608" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1609" spans="1:16">
@@ -82486,7 +82492,7 @@
         <v>1</v>
       </c>
       <c r="P1609" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1610" spans="1:16">
@@ -82536,7 +82542,7 @@
         <v>1</v>
       </c>
       <c r="P1610" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1611" spans="1:16">
@@ -82586,7 +82592,7 @@
         <v>1</v>
       </c>
       <c r="P1611" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1612" spans="1:16">
@@ -82636,7 +82642,7 @@
         <v>1</v>
       </c>
       <c r="P1612" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1613" spans="1:16">
@@ -82686,7 +82692,7 @@
         <v>1</v>
       </c>
       <c r="P1613" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1614" spans="1:16">
@@ -82736,7 +82742,7 @@
         <v>1</v>
       </c>
       <c r="P1614" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1615" spans="1:16">
@@ -82786,7 +82792,7 @@
         <v>1</v>
       </c>
       <c r="P1615" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1616" spans="1:16">
@@ -82836,7 +82842,7 @@
         <v>1</v>
       </c>
       <c r="P1616" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1617" spans="1:16">
@@ -82886,7 +82892,7 @@
         <v>1</v>
       </c>
       <c r="P1617" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1618" spans="1:16">
@@ -82936,7 +82942,7 @@
         <v>1</v>
       </c>
       <c r="P1618" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1619" spans="1:16">
@@ -82986,7 +82992,7 @@
         <v>1</v>
       </c>
       <c r="P1619" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1620" spans="1:16">
@@ -83036,7 +83042,7 @@
         <v>1</v>
       </c>
       <c r="P1620" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1621" spans="1:16">
@@ -83086,7 +83092,7 @@
         <v>1</v>
       </c>
       <c r="P1621" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1622" spans="1:16">
@@ -83136,7 +83142,7 @@
         <v>1</v>
       </c>
       <c r="P1622" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1623" spans="1:16">
@@ -83186,7 +83192,7 @@
         <v>1</v>
       </c>
       <c r="P1623" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1624" spans="1:16">
@@ -83236,7 +83242,7 @@
         <v>1</v>
       </c>
       <c r="P1624" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1625" spans="1:16">
@@ -83286,7 +83292,7 @@
         <v>1</v>
       </c>
       <c r="P1625" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1626" spans="1:16">
@@ -83336,7 +83342,7 @@
         <v>1</v>
       </c>
       <c r="P1626" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1627" spans="1:16">
@@ -83386,7 +83392,7 @@
         <v>1</v>
       </c>
       <c r="P1627" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1628" spans="1:16">
@@ -83436,7 +83442,7 @@
         <v>1</v>
       </c>
       <c r="P1628" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1629" spans="1:16">
@@ -83486,7 +83492,7 @@
         <v>1</v>
       </c>
       <c r="P1629" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1630" spans="1:16">
@@ -83536,7 +83542,7 @@
         <v>1</v>
       </c>
       <c r="P1630" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1631" spans="1:16">
@@ -83586,7 +83592,7 @@
         <v>1</v>
       </c>
       <c r="P1631" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1632" spans="1:16">
@@ -83636,7 +83642,7 @@
         <v>1</v>
       </c>
       <c r="P1632" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1633" spans="1:16">
@@ -83686,7 +83692,7 @@
         <v>1</v>
       </c>
       <c r="P1633" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1634" spans="1:16">
@@ -83994,10 +84000,10 @@
         <v>6</v>
       </c>
       <c r="B1640" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C1640">
-        <v>1.045334052407845</v>
+        <v>1.011617283167314</v>
       </c>
       <c r="D1640" t="s">
         <v>432</v>
@@ -84009,22 +84015,22 @@
         <v>1</v>
       </c>
       <c r="G1640">
-        <v>0.009414665947592155</v>
+        <v>0.009308382716832686</v>
       </c>
       <c r="H1640">
         <v>0.009251627434807435</v>
       </c>
       <c r="I1640">
-        <v>0.1030385127847211</v>
+        <v>0.136755282025252</v>
       </c>
       <c r="J1640">
         <v>1.209441025315652</v>
       </c>
       <c r="K1640">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="L1640">
-        <v>5.23</v>
+        <v>5.16</v>
       </c>
       <c r="M1640">
         <v>3.35</v>
@@ -84094,7 +84100,7 @@
         <v>8</v>
       </c>
       <c r="B1642" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C1642">
         <v>1.242827231774636</v>
@@ -84144,7 +84150,7 @@
         <v>9</v>
       </c>
       <c r="B1643" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C1643">
         <v>1.247960154812513</v>
@@ -84244,7 +84250,7 @@
         <v>11</v>
       </c>
       <c r="B1645" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C1645">
         <v>1.027281898356705</v>
@@ -84344,7 +84350,7 @@
         <v>0</v>
       </c>
       <c r="B1647" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1647">
         <v>1.670182610065094</v>
@@ -84386,7 +84392,7 @@
         <v>1</v>
       </c>
       <c r="P1647" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="1648" spans="1:16">
@@ -84394,7 +84400,7 @@
         <v>0</v>
       </c>
       <c r="B1648" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1648">
         <v>1.608934335394003</v>
@@ -84436,7 +84442,7 @@
         <v>1</v>
       </c>
       <c r="P1648" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="1649" spans="1:16">
@@ -84444,7 +84450,7 @@
         <v>0</v>
       </c>
       <c r="B1649" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1649">
         <v>1.546278323136421</v>
@@ -84486,7 +84492,7 @@
         <v>1</v>
       </c>
       <c r="P1649" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="1650" spans="1:16">
@@ -84494,10 +84500,10 @@
         <v>0</v>
       </c>
       <c r="B1650" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C1650">
-        <v>1.562310563546519</v>
+        <v>1.476561626064879</v>
       </c>
       <c r="D1650" t="s">
         <v>436</v>
@@ -84509,22 +84515,22 @@
         <v>-1</v>
       </c>
       <c r="G1650">
-        <v>0.007917689436453481</v>
+        <v>0.007943438373935121</v>
       </c>
       <c r="H1650">
         <v>0.007865737948927776</v>
       </c>
       <c r="I1650">
-        <v>0.2080485124742957</v>
+        <v>0.1222995749926556</v>
       </c>
       <c r="J1650">
         <v>1.1149787496328</v>
       </c>
       <c r="K1650">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="L1650">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="M1650">
         <v>2.92</v>
@@ -84550,10 +84556,10 @@
         <v>1.468962598106643</v>
       </c>
       <c r="D1651" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E1651">
-        <v>1.324530625455134</v>
+        <v>1.258621328586455</v>
       </c>
       <c r="F1651">
         <v>-1</v>
@@ -84562,10 +84568,10 @@
         <v>0.008011037401893358</v>
       </c>
       <c r="H1651">
-        <v>0.007935469374544866</v>
+        <v>0.007961378671413544</v>
       </c>
       <c r="I1651">
-        <v>0.1444319726515091</v>
+        <v>0.2103412695201876</v>
       </c>
       <c r="J1651">
         <v>1.147732421716968</v>
@@ -84577,10 +84583,10 @@
         <v>4.74</v>
       </c>
       <c r="M1651">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="N1651">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="O1651">
         <v>1</v>
@@ -84600,10 +84606,10 @@
         <v>1.395473830733309</v>
       </c>
       <c r="D1652" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E1652">
-        <v>1.250268292109449</v>
+        <v>1.183327573944303</v>
       </c>
       <c r="F1652">
         <v>-1</v>
@@ -84612,10 +84618,10 @@
         <v>0.008084526169266693</v>
       </c>
       <c r="H1652">
-        <v>0.008009731707890553</v>
+        <v>0.008036672426055699</v>
       </c>
       <c r="I1652">
-        <v>0.14520553862386</v>
+        <v>0.2121462567890058</v>
       </c>
       <c r="J1652">
         <v>1.173517954128664</v>
@@ -84627,16 +84633,16 @@
         <v>4.74</v>
       </c>
       <c r="M1652">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="N1652">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="O1652">
         <v>1</v>
       </c>
       <c r="P1652" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1653" spans="1:16">
@@ -84644,7 +84650,7 @@
         <v>0</v>
       </c>
       <c r="B1653" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1653">
         <v>1.148290651113722</v>
@@ -84687,6 +84693,56 @@
       </c>
       <c r="P1653" t="s">
         <v>433</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:16">
+      <c r="A1654" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1654">
+        <v>0.8926945616666919</v>
+      </c>
+      <c r="D1654" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1654">
+        <v>0.8349326342058419</v>
+      </c>
+      <c r="F1654">
+        <v>-1</v>
+      </c>
+      <c r="G1654">
+        <v>0.008507305438333309</v>
+      </c>
+      <c r="H1654">
+        <v>0.008705067365794157</v>
+      </c>
+      <c r="I1654">
+        <v>0.05776192746085007</v>
+      </c>
+      <c r="J1654">
+        <v>1.277619274608493</v>
+      </c>
+      <c r="K1654">
+        <v>2.98</v>
+      </c>
+      <c r="L1654">
+        <v>4.7</v>
+      </c>
+      <c r="M1654">
+        <v>3.08</v>
+      </c>
+      <c r="N1654">
+        <v>4.77</v>
+      </c>
+      <c r="O1654">
+        <v>1</v>
+      </c>
+      <c r="P1654" t="s">
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4974" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4998" uniqueCount="559">
   <si>
     <t>trade_time</t>
   </si>
@@ -784,10 +784,10 @@
     <t>2021-08-18</t>
   </si>
   <si>
-    <t>2021-08-23</t>
+    <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-08-31</t>
+    <t>2021-08-23</t>
   </si>
   <si>
     <t>2016-10-20</t>
@@ -1327,7 +1327,7 @@
     <t>2021-08-24</t>
   </si>
   <si>
-    <t>2021-09-01</t>
+    <t>2021-09-02</t>
   </si>
   <si>
     <t>2016-08-24</t>
@@ -1687,7 +1687,10 @@
     <t>2021-08-13</t>
   </si>
   <si>
-    <t>2021-08-30</t>
+    <t>2021-08-25</t>
+  </si>
+  <si>
+    <t>2021-08-26</t>
   </si>
 </sst>
 </file>
@@ -2045,7 +2048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1654"/>
+  <dimension ref="A1:P1662"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -84547,52 +84550,52 @@
     </row>
     <row r="1651" spans="1:16">
       <c r="A1651" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1651" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C1651">
-        <v>1.468962598106643</v>
+        <v>1.335865451130974</v>
       </c>
       <c r="D1651" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E1651">
-        <v>1.258621328586455</v>
+        <v>1.389314813619959</v>
       </c>
       <c r="F1651">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1651">
-        <v>0.008011037401893358</v>
+        <v>0.008204134548869025</v>
       </c>
       <c r="H1651">
-        <v>0.007961378671413544</v>
+        <v>0.008190685186380041</v>
       </c>
       <c r="I1651">
-        <v>0.2103412695201876</v>
+        <v>0.05344936248898469</v>
       </c>
       <c r="J1651">
-        <v>1.147732421716968</v>
+        <v>1.1149787496328</v>
       </c>
       <c r="K1651">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="L1651">
-        <v>4.74</v>
+        <v>4.77</v>
       </c>
       <c r="M1651">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N1651">
-        <v>4.61</v>
+        <v>4.79</v>
       </c>
       <c r="O1651">
         <v>1</v>
       </c>
       <c r="P1651" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1652" spans="1:16">
@@ -84603,28 +84606,28 @@
         <v>250</v>
       </c>
       <c r="C1652">
-        <v>1.395473830733309</v>
+        <v>1.468962598106643</v>
       </c>
       <c r="D1652" t="s">
         <v>436</v>
       </c>
       <c r="E1652">
-        <v>1.183327573944303</v>
+        <v>1.258621328586455</v>
       </c>
       <c r="F1652">
         <v>-1</v>
       </c>
       <c r="G1652">
-        <v>0.008084526169266693</v>
+        <v>0.008011037401893358</v>
       </c>
       <c r="H1652">
-        <v>0.008036672426055699</v>
+        <v>0.007961378671413544</v>
       </c>
       <c r="I1652">
-        <v>0.2121462567890058</v>
+        <v>0.2103412695201876</v>
       </c>
       <c r="J1652">
-        <v>1.173517954128664</v>
+        <v>1.147732421716968</v>
       </c>
       <c r="K1652">
         <v>2.85</v>
@@ -84642,57 +84645,57 @@
         <v>1</v>
       </c>
       <c r="P1652" t="s">
-        <v>255</v>
+        <v>429</v>
       </c>
     </row>
     <row r="1653" spans="1:16">
       <c r="A1653" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1653" t="s">
         <v>256</v>
       </c>
       <c r="C1653">
-        <v>1.148290651113722</v>
+        <v>1.234984141111739</v>
       </c>
       <c r="D1653" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E1653">
-        <v>1.027882933304618</v>
+        <v>1.289416113763249</v>
       </c>
       <c r="F1653">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1653">
-        <v>0.008091709348886278</v>
+        <v>0.00830501585888826</v>
       </c>
       <c r="H1653">
-        <v>0.008192117066695381</v>
+        <v>0.008290583886236751</v>
       </c>
       <c r="I1653">
-        <v>0.1204077178091039</v>
+        <v>0.05443197265150967</v>
       </c>
       <c r="J1653">
-        <v>1.226752420101158</v>
+        <v>1.147732421716968</v>
       </c>
       <c r="K1653">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1653">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1653">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N1653">
-        <v>4.61</v>
+        <v>4.79</v>
       </c>
       <c r="O1653">
         <v>1</v>
       </c>
       <c r="P1653" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="1654" spans="1:16">
@@ -84700,49 +84703,449 @@
         <v>0</v>
       </c>
       <c r="B1654" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C1654">
-        <v>0.8926945616666919</v>
+        <v>1.395473830733309</v>
       </c>
       <c r="D1654" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E1654">
-        <v>0.8349326342058419</v>
+        <v>1.183327573944303</v>
       </c>
       <c r="F1654">
         <v>-1</v>
       </c>
       <c r="G1654">
-        <v>0.008507305438333309</v>
+        <v>0.008084526169266693</v>
       </c>
       <c r="H1654">
-        <v>0.008705067365794157</v>
+        <v>0.008036672426055699</v>
       </c>
       <c r="I1654">
-        <v>0.05776192746085007</v>
+        <v>0.2121462567890058</v>
       </c>
       <c r="J1654">
-        <v>1.277619274608493</v>
+        <v>1.173517954128664</v>
       </c>
       <c r="K1654">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="L1654">
-        <v>4.7</v>
+        <v>4.74</v>
       </c>
       <c r="M1654">
+        <v>2.92</v>
+      </c>
+      <c r="N1654">
+        <v>4.61</v>
+      </c>
+      <c r="O1654">
+        <v>1</v>
+      </c>
+      <c r="P1654" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:16">
+      <c r="A1655" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1655">
+        <v>1.155564701283716</v>
+      </c>
+      <c r="D1655" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1655">
+        <v>1.210770239907577</v>
+      </c>
+      <c r="F1655">
+        <v>1</v>
+      </c>
+      <c r="G1655">
+        <v>0.008384435298716283</v>
+      </c>
+      <c r="H1655">
+        <v>0.008369229760092424</v>
+      </c>
+      <c r="I1655">
+        <v>0.05520553862386102</v>
+      </c>
+      <c r="J1655">
+        <v>1.173517954128664</v>
+      </c>
+      <c r="K1655">
         <v>3.08</v>
       </c>
-      <c r="N1654">
+      <c r="L1655">
         <v>4.77</v>
       </c>
-      <c r="O1654">
-        <v>1</v>
-      </c>
-      <c r="P1654" t="s">
+      <c r="M1655">
+        <v>3.05</v>
+      </c>
+      <c r="N1655">
+        <v>4.79</v>
+      </c>
+      <c r="O1655">
+        <v>1</v>
+      </c>
+      <c r="P1655" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:16">
+      <c r="A1656" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1656">
+        <v>1.199709616662221</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>436</v>
+      </c>
+      <c r="E1656">
+        <v>1.080937130973034</v>
+      </c>
+      <c r="F1656">
+        <v>-1</v>
+      </c>
+      <c r="G1656">
+        <v>0.00804029038333778</v>
+      </c>
+      <c r="H1656">
+        <v>0.008139062869026967</v>
+      </c>
+      <c r="I1656">
+        <v>0.118772485689187</v>
+      </c>
+      <c r="J1656">
+        <v>1.208583174324304</v>
+      </c>
+      <c r="K1656">
+        <v>2.83</v>
+      </c>
+      <c r="L1656">
+        <v>4.62</v>
+      </c>
+      <c r="M1656">
+        <v>2.92</v>
+      </c>
+      <c r="N1656">
+        <v>4.61</v>
+      </c>
+      <c r="O1656">
+        <v>1</v>
+      </c>
+      <c r="P1656" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:16">
+      <c r="A1657" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1657">
+        <v>1.047563823081144</v>
+      </c>
+      <c r="D1657" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1657">
+        <v>1.103821318310874</v>
+      </c>
+      <c r="F1657">
+        <v>1</v>
+      </c>
+      <c r="G1657">
+        <v>0.008492436176918855</v>
+      </c>
+      <c r="H1657">
+        <v>0.008476178681689126</v>
+      </c>
+      <c r="I1657">
+        <v>0.05625749522972967</v>
+      </c>
+      <c r="J1657">
+        <v>1.208583174324304</v>
+      </c>
+      <c r="K1657">
+        <v>3.08</v>
+      </c>
+      <c r="L1657">
+        <v>4.77</v>
+      </c>
+      <c r="M1657">
+        <v>3.05</v>
+      </c>
+      <c r="N1657">
+        <v>4.79</v>
+      </c>
+      <c r="O1657">
+        <v>1</v>
+      </c>
+      <c r="P1657" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:16">
+      <c r="A1658" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1658">
+        <v>1.148290651113722</v>
+      </c>
+      <c r="D1658" t="s">
+        <v>436</v>
+      </c>
+      <c r="E1658">
+        <v>1.027882933304618</v>
+      </c>
+      <c r="F1658">
+        <v>-1</v>
+      </c>
+      <c r="G1658">
+        <v>0.008091709348886278</v>
+      </c>
+      <c r="H1658">
+        <v>0.008192117066695381</v>
+      </c>
+      <c r="I1658">
+        <v>0.1204077178091039</v>
+      </c>
+      <c r="J1658">
+        <v>1.226752420101158</v>
+      </c>
+      <c r="K1658">
+        <v>2.83</v>
+      </c>
+      <c r="L1658">
+        <v>4.62</v>
+      </c>
+      <c r="M1658">
+        <v>2.92</v>
+      </c>
+      <c r="N1658">
+        <v>4.61</v>
+      </c>
+      <c r="O1658">
+        <v>1</v>
+      </c>
+      <c r="P1658" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:16">
+      <c r="A1659" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1659">
+        <v>0.9916025460884326</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1659">
+        <v>1.048405118691468</v>
+      </c>
+      <c r="F1659">
+        <v>1</v>
+      </c>
+      <c r="G1659">
+        <v>0.008548397453911566</v>
+      </c>
+      <c r="H1659">
+        <v>0.008531594881308533</v>
+      </c>
+      <c r="I1659">
+        <v>0.05680257260303545</v>
+      </c>
+      <c r="J1659">
+        <v>1.226752420101158</v>
+      </c>
+      <c r="K1659">
+        <v>3.08</v>
+      </c>
+      <c r="L1659">
+        <v>4.77</v>
+      </c>
+      <c r="M1659">
+        <v>3.05</v>
+      </c>
+      <c r="N1659">
+        <v>4.79</v>
+      </c>
+      <c r="O1659">
+        <v>1</v>
+      </c>
+      <c r="P1659" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:16">
+      <c r="A1660" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1660">
+        <v>0.9133372588035056</v>
+      </c>
+      <c r="D1660" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1660">
+        <v>0.9709021556333424</v>
+      </c>
+      <c r="F1660">
+        <v>1</v>
+      </c>
+      <c r="G1660">
+        <v>0.008626662741196495</v>
+      </c>
+      <c r="H1660">
+        <v>0.00860909784436666</v>
+      </c>
+      <c r="I1660">
+        <v>0.05756489682983679</v>
+      </c>
+      <c r="J1660">
+        <v>1.252163227661199</v>
+      </c>
+      <c r="K1660">
+        <v>3.08</v>
+      </c>
+      <c r="L1660">
+        <v>4.77</v>
+      </c>
+      <c r="M1660">
+        <v>3.05</v>
+      </c>
+      <c r="N1660">
+        <v>4.79</v>
+      </c>
+      <c r="O1660">
+        <v>1</v>
+      </c>
+      <c r="P1660" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:16">
+      <c r="A1661" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1661">
+        <v>0.8640876530634416</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1661">
+        <v>0.9221322538452918</v>
+      </c>
+      <c r="F1661">
+        <v>1</v>
+      </c>
+      <c r="G1661">
+        <v>0.008675912346936559</v>
+      </c>
+      <c r="H1661">
+        <v>0.008657867746154707</v>
+      </c>
+      <c r="I1661">
+        <v>0.05804460078185025</v>
+      </c>
+      <c r="J1661">
+        <v>1.268153359394986</v>
+      </c>
+      <c r="K1661">
+        <v>3.08</v>
+      </c>
+      <c r="L1661">
+        <v>4.77</v>
+      </c>
+      <c r="M1661">
+        <v>3.05</v>
+      </c>
+      <c r="N1661">
+        <v>4.79</v>
+      </c>
+      <c r="O1661">
+        <v>1</v>
+      </c>
+      <c r="P1661" t="s">
         <v>557</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:16">
+      <c r="A1662" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1662">
+        <v>0.8361486892860226</v>
+      </c>
+      <c r="D1662" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1662">
+        <v>0.8944654228319386</v>
+      </c>
+      <c r="F1662">
+        <v>1</v>
+      </c>
+      <c r="G1662">
+        <v>0.008703851310713976</v>
+      </c>
+      <c r="H1662">
+        <v>0.008685534577168062</v>
+      </c>
+      <c r="I1662">
+        <v>0.05831673354591604</v>
+      </c>
+      <c r="J1662">
+        <v>1.277224451530512</v>
+      </c>
+      <c r="K1662">
+        <v>3.08</v>
+      </c>
+      <c r="L1662">
+        <v>4.77</v>
+      </c>
+      <c r="M1662">
+        <v>3.05</v>
+      </c>
+      <c r="N1662">
+        <v>4.79</v>
+      </c>
+      <c r="O1662">
+        <v>1</v>
+      </c>
+      <c r="P1662" t="s">
+        <v>558</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5019" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5022" uniqueCount="566">
   <si>
     <t>trade_time</t>
   </si>
@@ -2069,7 +2069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1669"/>
+  <dimension ref="A1:P1670"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -84774,43 +84774,43 @@
         <v>1</v>
       </c>
       <c r="B1655" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1655">
-        <v>1.335865451130974</v>
+        <v>1.464610138539175</v>
       </c>
       <c r="D1655" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E1655">
-        <v>1.415865451130975</v>
+        <v>1.354262051072224</v>
       </c>
       <c r="F1655">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1655">
-        <v>0.008204134548869025</v>
+        <v>0.007775389861460825</v>
       </c>
       <c r="H1655">
-        <v>0.008284134548869025</v>
+        <v>0.007865737948927776</v>
       </c>
       <c r="I1655">
-        <v>0.08000000000000007</v>
+        <v>0.1103480874669516</v>
       </c>
       <c r="J1655">
         <v>1.1149787496328</v>
       </c>
       <c r="K1655">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1655">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1655">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1655">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1655">
         <v>1</v>
@@ -84821,63 +84821,63 @@
     </row>
     <row r="1656" spans="1:16">
       <c r="A1656" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1656" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C1656">
-        <v>1.381575977020794</v>
+        <v>1.335865451130974</v>
       </c>
       <c r="D1656" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E1656">
-        <v>1.258621328586455</v>
+        <v>1.415865451130975</v>
       </c>
       <c r="F1656">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1656">
-        <v>0.008038424022979206</v>
+        <v>0.008204134548869025</v>
       </c>
       <c r="H1656">
-        <v>0.007961378671413544</v>
+        <v>0.008284134548869025</v>
       </c>
       <c r="I1656">
-        <v>0.1229546484343391</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1656">
-        <v>1.147732421716968</v>
+        <v>1.1149787496328</v>
       </c>
       <c r="K1656">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="L1656">
-        <v>4.71</v>
+        <v>4.77</v>
       </c>
       <c r="M1656">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1656">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1656">
         <v>1</v>
       </c>
       <c r="P1656" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1657" spans="1:16">
       <c r="A1657" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1657" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C1657">
-        <v>1.371917246540982</v>
+        <v>1.381575977020794</v>
       </c>
       <c r="D1657" t="s">
         <v>438</v>
@@ -84889,22 +84889,22 @@
         <v>-1</v>
       </c>
       <c r="G1657">
-        <v>0.007868082753459019</v>
+        <v>0.008038424022979206</v>
       </c>
       <c r="H1657">
         <v>0.007961378671413544</v>
       </c>
       <c r="I1657">
-        <v>0.1132959179545265</v>
+        <v>0.1229546484343391</v>
       </c>
       <c r="J1657">
         <v>1.147732421716968</v>
       </c>
       <c r="K1657">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="L1657">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="M1657">
         <v>2.92</v>
@@ -84921,46 +84921,46 @@
     </row>
     <row r="1658" spans="1:16">
       <c r="A1658" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1658" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1658">
-        <v>1.234984141111739</v>
+        <v>1.371917246540982</v>
       </c>
       <c r="D1658" t="s">
-        <v>259</v>
+        <v>438</v>
       </c>
       <c r="E1658">
-        <v>1.329074844243061</v>
+        <v>1.258621328586455</v>
       </c>
       <c r="F1658">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1658">
-        <v>0.00830501585888826</v>
+        <v>0.007868082753459019</v>
       </c>
       <c r="H1658">
-        <v>0.008490925155756938</v>
+        <v>0.007961378671413544</v>
       </c>
       <c r="I1658">
-        <v>0.09409070313132162</v>
+        <v>0.1132959179545265</v>
       </c>
       <c r="J1658">
         <v>1.147732421716968</v>
       </c>
       <c r="K1658">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1658">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1658">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="N1658">
-        <v>4.91</v>
+        <v>4.61</v>
       </c>
       <c r="O1658">
         <v>1</v>
@@ -84971,96 +84971,96 @@
     </row>
     <row r="1659" spans="1:16">
       <c r="A1659" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1659" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1659">
-        <v>1.298944189815882</v>
+        <v>1.234984141111739</v>
       </c>
       <c r="D1659" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E1659">
-        <v>1.183327573944303</v>
+        <v>1.31498414111174</v>
       </c>
       <c r="F1659">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1659">
-        <v>0.007941055810184118</v>
+        <v>0.00830501585888826</v>
       </c>
       <c r="H1659">
-        <v>0.008036672426055699</v>
+        <v>0.00838501585888826</v>
       </c>
       <c r="I1659">
-        <v>0.1156166158715792</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1659">
-        <v>1.173517954128664</v>
+        <v>1.147732421716968</v>
       </c>
       <c r="K1659">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1659">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1659">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1659">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1659">
         <v>1</v>
       </c>
       <c r="P1659" t="s">
-        <v>255</v>
+        <v>431</v>
       </c>
     </row>
     <row r="1660" spans="1:16">
       <c r="A1660" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1660" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1660">
-        <v>1.155564701283716</v>
+        <v>1.298944189815882</v>
       </c>
       <c r="D1660" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E1660">
-        <v>1.235564701283716</v>
+        <v>1.183327573944303</v>
       </c>
       <c r="F1660">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1660">
-        <v>0.008384435298716283</v>
+        <v>0.007941055810184118</v>
       </c>
       <c r="H1660">
-        <v>0.008464435298716284</v>
+        <v>0.008036672426055699</v>
       </c>
       <c r="I1660">
-        <v>0.08000000000000007</v>
+        <v>0.1156166158715792</v>
       </c>
       <c r="J1660">
         <v>1.173517954128664</v>
       </c>
       <c r="K1660">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1660">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1660">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1660">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1660">
         <v>1</v>
@@ -85071,96 +85071,96 @@
     </row>
     <row r="1661" spans="1:16">
       <c r="A1661" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1661" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1661">
-        <v>1.199709616662221</v>
+        <v>1.155564701283716</v>
       </c>
       <c r="D1661" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E1661">
-        <v>1.080937130973034</v>
+        <v>1.235564701283716</v>
       </c>
       <c r="F1661">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1661">
-        <v>0.00804029038333778</v>
+        <v>0.008384435298716283</v>
       </c>
       <c r="H1661">
-        <v>0.008139062869026967</v>
+        <v>0.008464435298716284</v>
       </c>
       <c r="I1661">
-        <v>0.118772485689187</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1661">
-        <v>1.208583174324304</v>
+        <v>1.173517954128664</v>
       </c>
       <c r="K1661">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1661">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1661">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1661">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1661">
         <v>1</v>
       </c>
       <c r="P1661" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1662" spans="1:16">
       <c r="A1662" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1662" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1662">
-        <v>1.047563823081144</v>
+        <v>1.199709616662221</v>
       </c>
       <c r="D1662" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E1662">
-        <v>1.127563823081144</v>
+        <v>1.080937130973034</v>
       </c>
       <c r="F1662">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1662">
-        <v>0.008492436176918855</v>
+        <v>0.00804029038333778</v>
       </c>
       <c r="H1662">
-        <v>0.008572436176918854</v>
+        <v>0.008139062869026967</v>
       </c>
       <c r="I1662">
-        <v>0.08000000000000007</v>
+        <v>0.118772485689187</v>
       </c>
       <c r="J1662">
         <v>1.208583174324304</v>
       </c>
       <c r="K1662">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1662">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1662">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1662">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1662">
         <v>1</v>
@@ -85171,96 +85171,96 @@
     </row>
     <row r="1663" spans="1:16">
       <c r="A1663" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1663" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C1663">
-        <v>1.148290651113722</v>
+        <v>1.047563823081144</v>
       </c>
       <c r="D1663" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E1663">
-        <v>1.027882933304618</v>
+        <v>1.127563823081144</v>
       </c>
       <c r="F1663">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1663">
-        <v>0.008091709348886278</v>
+        <v>0.008492436176918855</v>
       </c>
       <c r="H1663">
-        <v>0.008192117066695381</v>
+        <v>0.008572436176918854</v>
       </c>
       <c r="I1663">
-        <v>0.1204077178091039</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1663">
-        <v>1.226752420101158</v>
+        <v>1.208583174324304</v>
       </c>
       <c r="K1663">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1663">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1663">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1663">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1663">
         <v>1</v>
       </c>
       <c r="P1663" t="s">
-        <v>435</v>
+        <v>250</v>
       </c>
     </row>
     <row r="1664" spans="1:16">
       <c r="A1664" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1664" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1664">
-        <v>0.9916025460884326</v>
+        <v>1.148290651113722</v>
       </c>
       <c r="D1664" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E1664">
-        <v>1.071602546088433</v>
+        <v>1.027882933304618</v>
       </c>
       <c r="F1664">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1664">
-        <v>0.008548397453911566</v>
+        <v>0.008091709348886278</v>
       </c>
       <c r="H1664">
-        <v>0.008628397453911568</v>
+        <v>0.008192117066695381</v>
       </c>
       <c r="I1664">
-        <v>0.08000000000000007</v>
+        <v>0.1204077178091039</v>
       </c>
       <c r="J1664">
         <v>1.226752420101158</v>
       </c>
       <c r="K1664">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1664">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1664">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1664">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1664">
         <v>1</v>
@@ -85271,34 +85271,34 @@
     </row>
     <row r="1665" spans="1:16">
       <c r="A1665" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1665" t="s">
         <v>257</v>
       </c>
       <c r="C1665">
-        <v>0.9133372588035056</v>
+        <v>0.9916025460884326</v>
       </c>
       <c r="D1665" t="s">
         <v>440</v>
       </c>
       <c r="E1665">
-        <v>0.9933372588035057</v>
+        <v>1.071602546088433</v>
       </c>
       <c r="F1665">
         <v>1</v>
       </c>
       <c r="G1665">
-        <v>0.008626662741196495</v>
+        <v>0.008548397453911566</v>
       </c>
       <c r="H1665">
-        <v>0.008706662741196493</v>
+        <v>0.008628397453911568</v>
       </c>
       <c r="I1665">
         <v>0.08000000000000007</v>
       </c>
       <c r="J1665">
-        <v>1.252163227661199</v>
+        <v>1.226752420101158</v>
       </c>
       <c r="K1665">
         <v>3.08</v>
@@ -85316,7 +85316,7 @@
         <v>1</v>
       </c>
       <c r="P1665" t="s">
-        <v>258</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1666" spans="1:16">
@@ -85327,28 +85327,28 @@
         <v>257</v>
       </c>
       <c r="C1666">
-        <v>0.8640876530634416</v>
+        <v>0.9133372588035056</v>
       </c>
       <c r="D1666" t="s">
         <v>440</v>
       </c>
       <c r="E1666">
-        <v>0.9440876530634417</v>
+        <v>0.9933372588035057</v>
       </c>
       <c r="F1666">
         <v>1</v>
       </c>
       <c r="G1666">
-        <v>0.008675912346936559</v>
+        <v>0.008626662741196495</v>
       </c>
       <c r="H1666">
-        <v>0.008755912346936559</v>
+        <v>0.008706662741196493</v>
       </c>
       <c r="I1666">
         <v>0.08000000000000007</v>
       </c>
       <c r="J1666">
-        <v>1.268153359394986</v>
+        <v>1.252163227661199</v>
       </c>
       <c r="K1666">
         <v>3.08</v>
@@ -85366,7 +85366,7 @@
         <v>1</v>
       </c>
       <c r="P1666" t="s">
-        <v>562</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1667" spans="1:16">
@@ -85377,28 +85377,28 @@
         <v>257</v>
       </c>
       <c r="C1667">
-        <v>0.8361486892860226</v>
+        <v>0.8640876530634416</v>
       </c>
       <c r="D1667" t="s">
         <v>440</v>
       </c>
       <c r="E1667">
-        <v>0.9161486892860227</v>
+        <v>0.9440876530634417</v>
       </c>
       <c r="F1667">
         <v>1</v>
       </c>
       <c r="G1667">
-        <v>0.008703851310713976</v>
+        <v>0.008675912346936559</v>
       </c>
       <c r="H1667">
-        <v>0.008783851310713978</v>
+        <v>0.008755912346936559</v>
       </c>
       <c r="I1667">
         <v>0.08000000000000007</v>
       </c>
       <c r="J1667">
-        <v>1.277224451530512</v>
+        <v>1.268153359394986</v>
       </c>
       <c r="K1667">
         <v>3.08</v>
@@ -85416,7 +85416,7 @@
         <v>1</v>
       </c>
       <c r="P1667" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="1668" spans="1:16">
@@ -85427,28 +85427,28 @@
         <v>257</v>
       </c>
       <c r="C1668">
-        <v>0.8463446294858961</v>
+        <v>0.8361486892860226</v>
       </c>
       <c r="D1668" t="s">
         <v>440</v>
       </c>
       <c r="E1668">
-        <v>0.9263446294858961</v>
+        <v>0.9161486892860227</v>
       </c>
       <c r="F1668">
         <v>1</v>
       </c>
       <c r="G1668">
-        <v>0.008693655370514104</v>
+        <v>0.008703851310713976</v>
       </c>
       <c r="H1668">
-        <v>0.008773655370514102</v>
+        <v>0.008783851310713978</v>
       </c>
       <c r="I1668">
         <v>0.08000000000000007</v>
       </c>
       <c r="J1668">
-        <v>1.273914081335748</v>
+        <v>1.277224451530512</v>
       </c>
       <c r="K1668">
         <v>3.08</v>
@@ -85466,7 +85466,7 @@
         <v>1</v>
       </c>
       <c r="P1668" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="1669" spans="1:16">
@@ -85474,48 +85474,98 @@
         <v>0</v>
       </c>
       <c r="B1669" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1669">
+        <v>0.8463446294858961</v>
+      </c>
+      <c r="D1669" t="s">
+        <v>440</v>
+      </c>
+      <c r="E1669">
+        <v>0.9263446294858961</v>
+      </c>
+      <c r="F1669">
+        <v>1</v>
+      </c>
+      <c r="G1669">
+        <v>0.008693655370514104</v>
+      </c>
+      <c r="H1669">
+        <v>0.008773655370514102</v>
+      </c>
+      <c r="I1669">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="J1669">
+        <v>1.273914081335748</v>
+      </c>
+      <c r="K1669">
+        <v>3.08</v>
+      </c>
+      <c r="L1669">
+        <v>4.77</v>
+      </c>
+      <c r="M1669">
+        <v>3.08</v>
+      </c>
+      <c r="N1669">
+        <v>4.85</v>
+      </c>
+      <c r="O1669">
+        <v>1</v>
+      </c>
+      <c r="P1669" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:16">
+      <c r="A1670" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1670" t="s">
         <v>259</v>
       </c>
-      <c r="C1669">
+      <c r="C1670">
         <v>0.9238278632215029</v>
       </c>
-      <c r="D1669" t="s">
+      <c r="D1670" t="s">
         <v>442</v>
       </c>
-      <c r="E1669">
+      <c r="E1670">
         <v>0.881618321252823</v>
       </c>
-      <c r="F1669">
+      <c r="F1670">
         <v>-1</v>
       </c>
-      <c r="G1669">
+      <c r="G1670">
         <v>0.008896172136778497</v>
       </c>
-      <c r="H1669">
+      <c r="H1670">
         <v>0.009058381678747177</v>
       </c>
-      <c r="I1669">
+      <c r="I1670">
         <v>0.04220954196867988</v>
       </c>
-      <c r="J1669">
+      <c r="J1670">
         <v>1.277619274608493</v>
       </c>
-      <c r="K1669">
+      <c r="K1670">
         <v>3.12</v>
       </c>
-      <c r="L1669">
+      <c r="L1670">
         <v>4.91</v>
       </c>
-      <c r="M1669">
+      <c r="M1670">
         <v>3.2</v>
       </c>
-      <c r="N1669">
+      <c r="N1670">
         <v>4.97</v>
       </c>
-      <c r="O1669">
-        <v>1</v>
-      </c>
-      <c r="P1669" t="s">
+      <c r="O1670">
+        <v>1</v>
+      </c>
+      <c r="P1670" t="s">
         <v>565</v>
       </c>
     </row>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5148" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5139" uniqueCount="577">
   <si>
     <t>trade_time</t>
   </si>
@@ -790,19 +790,19 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-16</t>
+    <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-09-01</t>
+    <t>2021-09-16</t>
   </si>
   <si>
     <t>2021-09-24</t>
   </si>
   <si>
-    <t>2021-09-17</t>
+    <t>2021-09-07</t>
   </si>
   <si>
-    <t>2021-09-07</t>
+    <t>2021-09-17</t>
   </si>
   <si>
     <t>2016-10-20</t>
@@ -1348,16 +1348,16 @@
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-09-10</t>
-  </si>
-  <si>
     <t>2021-09-27</t>
   </si>
   <si>
-    <t>2021-09-23</t>
+    <t>2021-09-28</t>
   </si>
   <si>
     <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2016-08-24</t>
@@ -1738,6 +1738,9 @@
     <t>2021-09-06</t>
   </si>
   <si>
+    <t>2021-09-10</t>
+  </si>
+  <si>
     <t>2021-09-13</t>
   </si>
   <si>
@@ -2099,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1712"/>
+  <dimension ref="A1:P1709"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -84701,63 +84704,63 @@
     </row>
     <row r="1653" spans="1:16">
       <c r="A1653" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1653" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C1653">
-        <v>1.467547675638099</v>
+        <v>1.546278323136421</v>
       </c>
       <c r="D1653" t="s">
-        <v>260</v>
+        <v>441</v>
       </c>
       <c r="E1653">
-        <v>1.563387696370389</v>
+        <v>1.424459552951155</v>
       </c>
       <c r="F1653">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1653">
-        <v>0.0077124523243619</v>
+        <v>0.007873721676863579</v>
       </c>
       <c r="H1653">
-        <v>0.00793661230362961</v>
+        <v>0.007795540447048846</v>
       </c>
       <c r="I1653">
-        <v>0.09584002073229003</v>
+        <v>0.121818770185266</v>
       </c>
       <c r="J1653">
-        <v>1.069332987795171</v>
+        <v>1.090938509263303</v>
       </c>
       <c r="K1653">
+        <v>2.9</v>
+      </c>
+      <c r="L1653">
+        <v>4.71</v>
+      </c>
+      <c r="M1653">
         <v>2.92</v>
       </c>
-      <c r="L1653">
-        <v>4.59</v>
-      </c>
-      <c r="M1653">
-        <v>2.98</v>
-      </c>
       <c r="N1653">
-        <v>4.75</v>
+        <v>4.61</v>
       </c>
       <c r="O1653">
         <v>1</v>
       </c>
       <c r="P1653" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="1654" spans="1:16">
       <c r="A1654" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1654" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1654">
-        <v>1.546278323136421</v>
+        <v>1.532644018784852</v>
       </c>
       <c r="D1654" t="s">
         <v>441</v>
@@ -84769,22 +84772,22 @@
         <v>-1</v>
       </c>
       <c r="G1654">
-        <v>0.007873721676863579</v>
+        <v>0.007707355981215148</v>
       </c>
       <c r="H1654">
         <v>0.007795540447048846</v>
       </c>
       <c r="I1654">
-        <v>0.121818770185266</v>
+        <v>0.108184465833697</v>
       </c>
       <c r="J1654">
         <v>1.090938509263303</v>
       </c>
       <c r="K1654">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="L1654">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="M1654">
         <v>2.92</v>
@@ -84801,46 +84804,46 @@
     </row>
     <row r="1655" spans="1:16">
       <c r="A1655" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1655" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C1655">
-        <v>1.532644018784852</v>
+        <v>1.409909391469025</v>
       </c>
       <c r="D1655" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E1655">
-        <v>1.424459552951155</v>
+        <v>1.489909391469026</v>
       </c>
       <c r="F1655">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1655">
-        <v>0.007707355981215148</v>
+        <v>0.008130090608530973</v>
       </c>
       <c r="H1655">
-        <v>0.007795540447048846</v>
+        <v>0.008210090608530974</v>
       </c>
       <c r="I1655">
-        <v>0.108184465833697</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1655">
         <v>1.090938509263303</v>
       </c>
       <c r="K1655">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1655">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1655">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1655">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1655">
         <v>1</v>
@@ -84851,46 +84854,46 @@
     </row>
     <row r="1656" spans="1:16">
       <c r="A1656" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1656" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C1656">
-        <v>1.409909391469025</v>
+        <v>1.548087385264796</v>
       </c>
       <c r="D1656" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E1656">
-        <v>1.489909391469026</v>
+        <v>1.418090621283759</v>
       </c>
       <c r="F1656">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1656">
-        <v>0.008130090608530973</v>
+        <v>0.008551912614735204</v>
       </c>
       <c r="H1656">
-        <v>0.008210090608530974</v>
+        <v>0.00818190937871624</v>
       </c>
       <c r="I1656">
-        <v>0.08000000000000007</v>
+        <v>0.1299967639810369</v>
       </c>
       <c r="J1656">
         <v>1.090938509263303</v>
       </c>
       <c r="K1656">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="L1656">
-        <v>4.77</v>
+        <v>5.05</v>
       </c>
       <c r="M1656">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N1656">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="O1656">
         <v>1</v>
@@ -84901,46 +84904,46 @@
     </row>
     <row r="1657" spans="1:16">
       <c r="A1657" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1657" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C1657">
-        <v>1.548087385264796</v>
+        <v>1.404459552951154</v>
       </c>
       <c r="D1657" t="s">
-        <v>444</v>
+        <v>260</v>
       </c>
       <c r="E1657">
-        <v>1.471721689616365</v>
+        <v>1.499003242395356</v>
       </c>
       <c r="F1657">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1657">
-        <v>0.008551912614735204</v>
+        <v>0.007775540447048846</v>
       </c>
       <c r="H1657">
-        <v>0.008628278310383635</v>
+        <v>0.008000996757604644</v>
       </c>
       <c r="I1657">
-        <v>0.07636569564843088</v>
+        <v>0.09454368944420199</v>
       </c>
       <c r="J1657">
         <v>1.090938509263303</v>
       </c>
       <c r="K1657">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
       <c r="L1657">
-        <v>5.05</v>
+        <v>4.59</v>
       </c>
       <c r="M1657">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="N1657">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="O1657">
         <v>1</v>
@@ -84951,96 +84954,96 @@
     </row>
     <row r="1658" spans="1:16">
       <c r="A1658" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1658" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C1658">
-        <v>1.404459552951154</v>
+        <v>1.476561626064879</v>
       </c>
       <c r="D1658" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E1658">
-        <v>1.499003242395356</v>
+        <v>1.562310563546519</v>
       </c>
       <c r="F1658">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1658">
-        <v>0.007775540447048846</v>
+        <v>0.007943438373935121</v>
       </c>
       <c r="H1658">
-        <v>0.008000996757604644</v>
+        <v>0.007917689436453481</v>
       </c>
       <c r="I1658">
-        <v>0.09454368944420199</v>
+        <v>-0.08574893748164003</v>
       </c>
       <c r="J1658">
-        <v>1.090938509263303</v>
+        <v>1.1149787496328</v>
       </c>
       <c r="K1658">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="L1658">
-        <v>4.59</v>
+        <v>4.71</v>
       </c>
       <c r="M1658">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="N1658">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="O1658">
         <v>1</v>
       </c>
       <c r="P1658" t="s">
-        <v>566</v>
+        <v>433</v>
       </c>
     </row>
     <row r="1659" spans="1:16">
       <c r="A1659" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1659" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1659">
-        <v>1.476561626064879</v>
+        <v>1.464610138539175</v>
       </c>
       <c r="D1659" t="s">
-        <v>250</v>
+        <v>441</v>
       </c>
       <c r="E1659">
-        <v>1.562310563546519</v>
+        <v>1.354262051072224</v>
       </c>
       <c r="F1659">
         <v>-1</v>
       </c>
       <c r="G1659">
-        <v>0.007943438373935121</v>
+        <v>0.007775389861460825</v>
       </c>
       <c r="H1659">
-        <v>0.007917689436453481</v>
+        <v>0.007865737948927776</v>
       </c>
       <c r="I1659">
-        <v>-0.08574893748164003</v>
+        <v>0.1103480874669516</v>
       </c>
       <c r="J1659">
         <v>1.1149787496328</v>
       </c>
       <c r="K1659">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="L1659">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="M1659">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="N1659">
-        <v>4.74</v>
+        <v>4.61</v>
       </c>
       <c r="O1659">
         <v>1</v>
@@ -85051,46 +85054,46 @@
     </row>
     <row r="1660" spans="1:16">
       <c r="A1660" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1660" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C1660">
-        <v>1.464610138539175</v>
+        <v>1.335865451130974</v>
       </c>
       <c r="D1660" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E1660">
-        <v>1.354262051072224</v>
+        <v>1.415865451130975</v>
       </c>
       <c r="F1660">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1660">
-        <v>0.007775389861460825</v>
+        <v>0.008204134548869025</v>
       </c>
       <c r="H1660">
-        <v>0.007865737948927776</v>
+        <v>0.008284134548869025</v>
       </c>
       <c r="I1660">
-        <v>0.1103480874669516</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1660">
         <v>1.1149787496328</v>
       </c>
       <c r="K1660">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1660">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1660">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1660">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1660">
         <v>1</v>
@@ -85101,46 +85104,46 @@
     </row>
     <row r="1661" spans="1:16">
       <c r="A1661" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1661" t="s">
         <v>259</v>
       </c>
       <c r="C1661">
-        <v>1.335865451130974</v>
+        <v>1.334262051072223</v>
       </c>
       <c r="D1661" t="s">
-        <v>443</v>
+        <v>260</v>
       </c>
       <c r="E1661">
-        <v>1.415865451130975</v>
+        <v>1.427363326094255</v>
       </c>
       <c r="F1661">
         <v>1</v>
       </c>
       <c r="G1661">
-        <v>0.008204134548869025</v>
+        <v>0.007845737948927777</v>
       </c>
       <c r="H1661">
-        <v>0.008284134548869025</v>
+        <v>0.008072636673905745</v>
       </c>
       <c r="I1661">
-        <v>0.08000000000000007</v>
+        <v>0.09310127502203214</v>
       </c>
       <c r="J1661">
         <v>1.1149787496328</v>
       </c>
       <c r="K1661">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="L1661">
-        <v>4.77</v>
+        <v>4.59</v>
       </c>
       <c r="M1661">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="N1661">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="O1661">
         <v>1</v>
@@ -85151,96 +85154,96 @@
     </row>
     <row r="1662" spans="1:16">
       <c r="A1662" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1662" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C1662">
-        <v>1.334262051072223</v>
+        <v>1.381575977020794</v>
       </c>
       <c r="D1662" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E1662">
-        <v>1.427363326094255</v>
+        <v>1.468962598106643</v>
       </c>
       <c r="F1662">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1662">
-        <v>0.007845737948927777</v>
+        <v>0.008038424022979206</v>
       </c>
       <c r="H1662">
-        <v>0.008072636673905745</v>
+        <v>0.008011037401893358</v>
       </c>
       <c r="I1662">
-        <v>0.09310127502203214</v>
+        <v>-0.08738662108584849</v>
       </c>
       <c r="J1662">
-        <v>1.1149787496328</v>
+        <v>1.147732421716968</v>
       </c>
       <c r="K1662">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="L1662">
-        <v>4.59</v>
+        <v>4.71</v>
       </c>
       <c r="M1662">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="N1662">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="O1662">
         <v>1</v>
       </c>
       <c r="P1662" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1663" spans="1:16">
       <c r="A1663" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1663" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1663">
-        <v>1.381575977020794</v>
+        <v>1.371917246540982</v>
       </c>
       <c r="D1663" t="s">
-        <v>250</v>
+        <v>441</v>
       </c>
       <c r="E1663">
-        <v>1.468962598106643</v>
+        <v>1.258621328586455</v>
       </c>
       <c r="F1663">
         <v>-1</v>
       </c>
       <c r="G1663">
-        <v>0.008038424022979206</v>
+        <v>0.007868082753459019</v>
       </c>
       <c r="H1663">
-        <v>0.008011037401893358</v>
+        <v>0.007961378671413544</v>
       </c>
       <c r="I1663">
-        <v>-0.08738662108584849</v>
+        <v>0.1132959179545265</v>
       </c>
       <c r="J1663">
         <v>1.147732421716968</v>
       </c>
       <c r="K1663">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="L1663">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="M1663">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="N1663">
-        <v>4.74</v>
+        <v>4.61</v>
       </c>
       <c r="O1663">
         <v>1</v>
@@ -85251,46 +85254,46 @@
     </row>
     <row r="1664" spans="1:16">
       <c r="A1664" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1664" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C1664">
-        <v>1.371917246540982</v>
+        <v>1.234984141111739</v>
       </c>
       <c r="D1664" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E1664">
-        <v>1.258621328586455</v>
+        <v>1.31498414111174</v>
       </c>
       <c r="F1664">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1664">
-        <v>0.007868082753459019</v>
+        <v>0.00830501585888826</v>
       </c>
       <c r="H1664">
-        <v>0.007961378671413544</v>
+        <v>0.00838501585888826</v>
       </c>
       <c r="I1664">
-        <v>0.1132959179545265</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1664">
         <v>1.147732421716968</v>
       </c>
       <c r="K1664">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1664">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1664">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1664">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1664">
         <v>1</v>
@@ -85301,46 +85304,46 @@
     </row>
     <row r="1665" spans="1:16">
       <c r="A1665" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1665" t="s">
         <v>259</v>
       </c>
       <c r="C1665">
-        <v>1.234984141111739</v>
+        <v>1.238621328586455</v>
       </c>
       <c r="D1665" t="s">
-        <v>443</v>
+        <v>260</v>
       </c>
       <c r="E1665">
-        <v>1.31498414111174</v>
+        <v>1.329757383283437</v>
       </c>
       <c r="F1665">
         <v>1</v>
       </c>
       <c r="G1665">
-        <v>0.00830501585888826</v>
+        <v>0.007941378671413545</v>
       </c>
       <c r="H1665">
-        <v>0.00838501585888826</v>
+        <v>0.008170242616716564</v>
       </c>
       <c r="I1665">
-        <v>0.08000000000000007</v>
+        <v>0.09113605469698216</v>
       </c>
       <c r="J1665">
         <v>1.147732421716968</v>
       </c>
       <c r="K1665">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="L1665">
-        <v>4.77</v>
+        <v>4.59</v>
       </c>
       <c r="M1665">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="N1665">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="O1665">
         <v>1</v>
@@ -85351,96 +85354,96 @@
     </row>
     <row r="1666" spans="1:16">
       <c r="A1666" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1666" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C1666">
-        <v>1.238621328586455</v>
+        <v>1.298944189815882</v>
       </c>
       <c r="D1666" t="s">
-        <v>260</v>
+        <v>441</v>
       </c>
       <c r="E1666">
-        <v>1.329757383283437</v>
+        <v>1.183327573944303</v>
       </c>
       <c r="F1666">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1666">
-        <v>0.007941378671413545</v>
+        <v>0.007941055810184118</v>
       </c>
       <c r="H1666">
-        <v>0.008170242616716564</v>
+        <v>0.008036672426055699</v>
       </c>
       <c r="I1666">
-        <v>0.09113605469698216</v>
+        <v>0.1156166158715792</v>
       </c>
       <c r="J1666">
-        <v>1.147732421716968</v>
+        <v>1.173517954128664</v>
       </c>
       <c r="K1666">
+        <v>2.83</v>
+      </c>
+      <c r="L1666">
+        <v>4.62</v>
+      </c>
+      <c r="M1666">
         <v>2.92</v>
       </c>
-      <c r="L1666">
-        <v>4.59</v>
-      </c>
-      <c r="M1666">
-        <v>2.98</v>
-      </c>
       <c r="N1666">
-        <v>4.75</v>
+        <v>4.61</v>
       </c>
       <c r="O1666">
         <v>1</v>
       </c>
       <c r="P1666" t="s">
-        <v>434</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1667" spans="1:16">
       <c r="A1667" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1667" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C1667">
-        <v>1.298944189815882</v>
+        <v>1.155564701283716</v>
       </c>
       <c r="D1667" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E1667">
-        <v>1.183327573944303</v>
+        <v>1.235564701283716</v>
       </c>
       <c r="F1667">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1667">
-        <v>0.007941055810184118</v>
+        <v>0.008384435298716283</v>
       </c>
       <c r="H1667">
-        <v>0.008036672426055699</v>
+        <v>0.008464435298716284</v>
       </c>
       <c r="I1667">
-        <v>0.1156166158715792</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1667">
         <v>1.173517954128664</v>
       </c>
       <c r="K1667">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1667">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1667">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1667">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1667">
         <v>1</v>
@@ -85451,46 +85454,46 @@
     </row>
     <row r="1668" spans="1:16">
       <c r="A1668" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1668" t="s">
         <v>259</v>
       </c>
       <c r="C1668">
-        <v>1.155564701283716</v>
+        <v>1.163327573944303</v>
       </c>
       <c r="D1668" t="s">
-        <v>443</v>
+        <v>260</v>
       </c>
       <c r="E1668">
-        <v>1.235564701283716</v>
+        <v>1.252916496696582</v>
       </c>
       <c r="F1668">
         <v>1</v>
       </c>
       <c r="G1668">
-        <v>0.008384435298716283</v>
+        <v>0.008016672426055697</v>
       </c>
       <c r="H1668">
-        <v>0.008464435298716284</v>
+        <v>0.008247083503303419</v>
       </c>
       <c r="I1668">
-        <v>0.08000000000000007</v>
+        <v>0.08958892275227992</v>
       </c>
       <c r="J1668">
         <v>1.173517954128664</v>
       </c>
       <c r="K1668">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="L1668">
-        <v>4.77</v>
+        <v>4.59</v>
       </c>
       <c r="M1668">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="N1668">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="O1668">
         <v>1</v>
@@ -85501,96 +85504,96 @@
     </row>
     <row r="1669" spans="1:16">
       <c r="A1669" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1669" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C1669">
-        <v>1.163327573944303</v>
+        <v>1.199709616662221</v>
       </c>
       <c r="D1669" t="s">
-        <v>260</v>
+        <v>441</v>
       </c>
       <c r="E1669">
-        <v>1.252916496696582</v>
+        <v>1.080937130973034</v>
       </c>
       <c r="F1669">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1669">
-        <v>0.008016672426055697</v>
+        <v>0.00804029038333778</v>
       </c>
       <c r="H1669">
-        <v>0.008247083503303419</v>
+        <v>0.008139062869026967</v>
       </c>
       <c r="I1669">
-        <v>0.08958892275227992</v>
+        <v>0.118772485689187</v>
       </c>
       <c r="J1669">
-        <v>1.173517954128664</v>
+        <v>1.208583174324304</v>
       </c>
       <c r="K1669">
+        <v>2.83</v>
+      </c>
+      <c r="L1669">
+        <v>4.62</v>
+      </c>
+      <c r="M1669">
         <v>2.92</v>
       </c>
-      <c r="L1669">
-        <v>4.59</v>
-      </c>
-      <c r="M1669">
-        <v>2.98</v>
-      </c>
       <c r="N1669">
-        <v>4.75</v>
+        <v>4.61</v>
       </c>
       <c r="O1669">
         <v>1</v>
       </c>
       <c r="P1669" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="1670" spans="1:16">
       <c r="A1670" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1670" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C1670">
-        <v>1.199709616662221</v>
+        <v>1.047563823081144</v>
       </c>
       <c r="D1670" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E1670">
-        <v>1.080937130973034</v>
+        <v>1.127563823081144</v>
       </c>
       <c r="F1670">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1670">
-        <v>0.00804029038333778</v>
+        <v>0.008492436176918855</v>
       </c>
       <c r="H1670">
-        <v>0.008139062869026967</v>
+        <v>0.008572436176918854</v>
       </c>
       <c r="I1670">
-        <v>0.118772485689187</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1670">
         <v>1.208583174324304</v>
       </c>
       <c r="K1670">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1670">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1670">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1670">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1670">
         <v>1</v>
@@ -85601,46 +85604,46 @@
     </row>
     <row r="1671" spans="1:16">
       <c r="A1671" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1671" t="s">
         <v>259</v>
       </c>
       <c r="C1671">
-        <v>1.047563823081144</v>
+        <v>1.060937130973033</v>
       </c>
       <c r="D1671" t="s">
-        <v>443</v>
+        <v>260</v>
       </c>
       <c r="E1671">
-        <v>1.127563823081144</v>
+        <v>1.148422140513575</v>
       </c>
       <c r="F1671">
         <v>1</v>
       </c>
       <c r="G1671">
-        <v>0.008492436176918855</v>
+        <v>0.008119062869026967</v>
       </c>
       <c r="H1671">
-        <v>0.008572436176918854</v>
+        <v>0.008351577859486425</v>
       </c>
       <c r="I1671">
-        <v>0.08000000000000007</v>
+        <v>0.08748500954054172</v>
       </c>
       <c r="J1671">
         <v>1.208583174324304</v>
       </c>
       <c r="K1671">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="L1671">
-        <v>4.77</v>
+        <v>4.59</v>
       </c>
       <c r="M1671">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="N1671">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="O1671">
         <v>1</v>
@@ -85651,52 +85654,52 @@
     </row>
     <row r="1672" spans="1:16">
       <c r="A1672" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1672" t="s">
         <v>258</v>
       </c>
       <c r="C1672">
-        <v>1.060937130973033</v>
+        <v>0.9916025460884326</v>
       </c>
       <c r="D1672" t="s">
-        <v>260</v>
+        <v>443</v>
       </c>
       <c r="E1672">
-        <v>1.148422140513575</v>
+        <v>1.071602546088433</v>
       </c>
       <c r="F1672">
         <v>1</v>
       </c>
       <c r="G1672">
-        <v>0.008119062869026967</v>
+        <v>0.008548397453911566</v>
       </c>
       <c r="H1672">
-        <v>0.008351577859486425</v>
+        <v>0.008628397453911568</v>
       </c>
       <c r="I1672">
-        <v>0.08748500954054172</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1672">
-        <v>1.208583174324304</v>
+        <v>1.226752420101158</v>
       </c>
       <c r="K1672">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="L1672">
-        <v>4.59</v>
+        <v>4.77</v>
       </c>
       <c r="M1672">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="N1672">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="O1672">
         <v>1</v>
       </c>
       <c r="P1672" t="s">
-        <v>250</v>
+        <v>438</v>
       </c>
     </row>
     <row r="1673" spans="1:16">
@@ -85704,31 +85707,31 @@
         <v>0</v>
       </c>
       <c r="B1673" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1673">
-        <v>0.9916025460884326</v>
+        <v>0.9133372588035056</v>
       </c>
       <c r="D1673" t="s">
         <v>443</v>
       </c>
       <c r="E1673">
-        <v>1.071602546088433</v>
+        <v>0.9933372588035057</v>
       </c>
       <c r="F1673">
         <v>1</v>
       </c>
       <c r="G1673">
-        <v>0.008548397453911566</v>
+        <v>0.008626662741196495</v>
       </c>
       <c r="H1673">
-        <v>0.008628397453911568</v>
+        <v>0.008706662741196493</v>
       </c>
       <c r="I1673">
         <v>0.08000000000000007</v>
       </c>
       <c r="J1673">
-        <v>1.226752420101158</v>
+        <v>1.252163227661199</v>
       </c>
       <c r="K1673">
         <v>3.08</v>
@@ -85746,51 +85749,51 @@
         <v>1</v>
       </c>
       <c r="P1673" t="s">
-        <v>438</v>
+        <v>256</v>
       </c>
     </row>
     <row r="1674" spans="1:16">
       <c r="A1674" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1674" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1674">
-        <v>0.9133372588035056</v>
+        <v>1.018553581569626</v>
       </c>
       <c r="D1674" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E1674">
-        <v>0.9933372588035057</v>
+        <v>0.971075213846238</v>
       </c>
       <c r="F1674">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1674">
-        <v>0.008626662741196495</v>
+        <v>0.008481446418430374</v>
       </c>
       <c r="H1674">
-        <v>0.008706662741196493</v>
+        <v>0.008408924786153764</v>
       </c>
       <c r="I1674">
-        <v>0.08000000000000007</v>
+        <v>0.04747836772338809</v>
       </c>
       <c r="J1674">
         <v>1.252163227661199</v>
       </c>
       <c r="K1674">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="L1674">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="M1674">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="N1674">
-        <v>4.85</v>
+        <v>4.69</v>
       </c>
       <c r="O1674">
         <v>1</v>
@@ -85801,96 +85804,96 @@
     </row>
     <row r="1675" spans="1:16">
       <c r="A1675" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1675" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C1675">
-        <v>1.018553581569626</v>
+        <v>0.8640876530634416</v>
       </c>
       <c r="D1675" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E1675">
-        <v>0.971075213846238</v>
+        <v>0.9440876530634417</v>
       </c>
       <c r="F1675">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1675">
-        <v>0.008481446418430374</v>
+        <v>0.008675912346936559</v>
       </c>
       <c r="H1675">
-        <v>0.008408924786153764</v>
+        <v>0.008755912346936559</v>
       </c>
       <c r="I1675">
-        <v>0.04747836772338809</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1675">
-        <v>1.252163227661199</v>
+        <v>1.268153359394986</v>
       </c>
       <c r="K1675">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="L1675">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="M1675">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="N1675">
-        <v>4.69</v>
+        <v>4.85</v>
       </c>
       <c r="O1675">
         <v>1</v>
       </c>
       <c r="P1675" t="s">
-        <v>256</v>
+        <v>567</v>
       </c>
     </row>
     <row r="1676" spans="1:16">
       <c r="A1676" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1676" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1676">
-        <v>0.8640876530634416</v>
+        <v>0.970902989002941</v>
       </c>
       <c r="D1676" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E1676">
-        <v>0.9440876530634417</v>
+        <v>0.9235845225968906</v>
       </c>
       <c r="F1676">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1676">
-        <v>0.008675912346936559</v>
+        <v>0.00852909701099706</v>
       </c>
       <c r="H1676">
-        <v>0.008755912346936559</v>
+        <v>0.00845641547740311</v>
       </c>
       <c r="I1676">
-        <v>0.08000000000000007</v>
+        <v>0.04731846640605042</v>
       </c>
       <c r="J1676">
         <v>1.268153359394986</v>
       </c>
       <c r="K1676">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="L1676">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="M1676">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="N1676">
-        <v>4.85</v>
+        <v>4.69</v>
       </c>
       <c r="O1676">
         <v>1</v>
@@ -85901,96 +85904,96 @@
     </row>
     <row r="1677" spans="1:16">
       <c r="A1677" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1677" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C1677">
-        <v>0.970902989002941</v>
+        <v>0.8361486892860226</v>
       </c>
       <c r="D1677" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E1677">
-        <v>0.9235845225968906</v>
+        <v>0.9161486892860227</v>
       </c>
       <c r="F1677">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1677">
-        <v>0.00852909701099706</v>
+        <v>0.008703851310713976</v>
       </c>
       <c r="H1677">
-        <v>0.00845641547740311</v>
+        <v>0.008783851310713978</v>
       </c>
       <c r="I1677">
-        <v>0.04731846640605042</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1677">
-        <v>1.268153359394986</v>
+        <v>1.277224451530512</v>
       </c>
       <c r="K1677">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="L1677">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="M1677">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="N1677">
-        <v>4.69</v>
+        <v>4.85</v>
       </c>
       <c r="O1677">
         <v>1</v>
       </c>
       <c r="P1677" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="1678" spans="1:16">
       <c r="A1678" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1678" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1678">
-        <v>0.8361486892860226</v>
+        <v>0.9438711344390742</v>
       </c>
       <c r="D1678" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E1678">
-        <v>0.9161486892860227</v>
+        <v>0.8966433789543795</v>
       </c>
       <c r="F1678">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1678">
-        <v>0.008703851310713976</v>
+        <v>0.008556128865560925</v>
       </c>
       <c r="H1678">
-        <v>0.008783851310713978</v>
+        <v>0.00848335662104562</v>
       </c>
       <c r="I1678">
-        <v>0.08000000000000007</v>
+        <v>0.04722775548469471</v>
       </c>
       <c r="J1678">
         <v>1.277224451530512</v>
       </c>
       <c r="K1678">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="L1678">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="M1678">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="N1678">
-        <v>4.85</v>
+        <v>4.69</v>
       </c>
       <c r="O1678">
         <v>1</v>
@@ -86001,96 +86004,96 @@
     </row>
     <row r="1679" spans="1:16">
       <c r="A1679" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1679" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C1679">
-        <v>0.9438711344390742</v>
+        <v>0.8463446294858961</v>
       </c>
       <c r="D1679" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E1679">
-        <v>0.8966433789543795</v>
+        <v>0.9263446294858961</v>
       </c>
       <c r="F1679">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1679">
-        <v>0.008556128865560925</v>
+        <v>0.008693655370514104</v>
       </c>
       <c r="H1679">
-        <v>0.00848335662104562</v>
+        <v>0.008773655370514102</v>
       </c>
       <c r="I1679">
-        <v>0.04722775548469471</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1679">
-        <v>1.277224451530512</v>
+        <v>1.273914081335748</v>
       </c>
       <c r="K1679">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="L1679">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="M1679">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="N1679">
-        <v>4.69</v>
+        <v>4.85</v>
       </c>
       <c r="O1679">
         <v>1</v>
       </c>
       <c r="P1679" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="1680" spans="1:16">
       <c r="A1680" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1680" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1680">
-        <v>0.8463446294858961</v>
+        <v>0.9537360376194712</v>
       </c>
       <c r="D1680" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E1680">
-        <v>0.9263446294858961</v>
+        <v>0.9027794743660413</v>
       </c>
       <c r="F1680">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1680">
-        <v>0.008693655370514104</v>
+        <v>0.00854626396238053</v>
       </c>
       <c r="H1680">
-        <v>0.008773655370514102</v>
+        <v>0.008597220525633957</v>
       </c>
       <c r="I1680">
-        <v>0.08000000000000007</v>
+        <v>0.0509565632534299</v>
       </c>
       <c r="J1680">
         <v>1.273914081335748</v>
       </c>
       <c r="K1680">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="L1680">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="M1680">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="N1680">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="O1680">
         <v>1</v>
@@ -86101,146 +86104,146 @@
     </row>
     <row r="1681" spans="1:16">
       <c r="A1681" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1681" t="s">
         <v>261</v>
       </c>
       <c r="C1681">
-        <v>0.8509968968061137</v>
+        <v>0.9238278632215029</v>
       </c>
       <c r="D1681" t="s">
         <v>446</v>
       </c>
       <c r="E1681">
-        <v>0.9182577559927565</v>
+        <v>0.881618321252823</v>
       </c>
       <c r="F1681">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1681">
-        <v>0.008469003103193887</v>
+        <v>0.008896172136778497</v>
       </c>
       <c r="H1681">
-        <v>0.008561742244007244</v>
+        <v>0.009058381678747177</v>
       </c>
       <c r="I1681">
-        <v>0.06726085918664282</v>
+        <v>0.04220954196867988</v>
       </c>
       <c r="J1681">
-        <v>1.273914081335748</v>
+        <v>1.277619274608493</v>
       </c>
       <c r="K1681">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="L1681">
-        <v>4.66</v>
+        <v>4.91</v>
       </c>
       <c r="M1681">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N1681">
-        <v>4.74</v>
+        <v>4.97</v>
       </c>
       <c r="O1681">
         <v>1</v>
       </c>
       <c r="P1681" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="1682" spans="1:16">
       <c r="A1682" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1682" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C1682">
-        <v>0.9537360376194712</v>
+        <v>0.8399183689206069</v>
       </c>
       <c r="D1682" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E1682">
-        <v>0.9064751784328289</v>
+        <v>0.9071421761745224</v>
       </c>
       <c r="F1682">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1682">
-        <v>0.00854626396238053</v>
+        <v>0.008480081631079394</v>
       </c>
       <c r="H1682">
-        <v>0.008473524821567172</v>
+        <v>0.008572857823825478</v>
       </c>
       <c r="I1682">
-        <v>0.04726085918664236</v>
+        <v>0.06722380725391552</v>
       </c>
       <c r="J1682">
-        <v>1.273914081335748</v>
+        <v>1.277619274608493</v>
       </c>
       <c r="K1682">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1682">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1682">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N1682">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1682">
         <v>1</v>
       </c>
       <c r="P1682" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="1683" spans="1:16">
       <c r="A1683" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1683" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C1683">
-        <v>0.9238278632215029</v>
+        <v>0.9426945616666917</v>
       </c>
       <c r="D1683" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E1683">
-        <v>0.881618321252823</v>
+        <v>0.8915897906823522</v>
       </c>
       <c r="F1683">
         <v>-1</v>
       </c>
       <c r="G1683">
-        <v>0.008896172136778497</v>
+        <v>0.008557305438333308</v>
       </c>
       <c r="H1683">
-        <v>0.009058381678747177</v>
+        <v>0.008608410209317647</v>
       </c>
       <c r="I1683">
-        <v>0.04220954196867988</v>
+        <v>0.05110477098433952</v>
       </c>
       <c r="J1683">
         <v>1.277619274608493</v>
       </c>
       <c r="K1683">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="L1683">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="M1683">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="N1683">
-        <v>4.97</v>
+        <v>4.75</v>
       </c>
       <c r="O1683">
         <v>1</v>
@@ -86251,34 +86254,34 @@
     </row>
     <row r="1684" spans="1:16">
       <c r="A1684" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1684" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1684">
-        <v>0.8399183689206069</v>
+        <v>0.8064988749071667</v>
       </c>
       <c r="D1684" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1684">
-        <v>0.9071421761745224</v>
+        <v>0.8736109112780941</v>
       </c>
       <c r="F1684">
         <v>1</v>
       </c>
       <c r="G1684">
-        <v>0.008480081631079394</v>
+        <v>0.008513501125092833</v>
       </c>
       <c r="H1684">
-        <v>0.008572857823825478</v>
+        <v>0.008606389088721907</v>
       </c>
       <c r="I1684">
-        <v>0.06722380725391552</v>
+        <v>0.06711203637092744</v>
       </c>
       <c r="J1684">
-        <v>1.277619274608493</v>
+        <v>1.288796362907302</v>
       </c>
       <c r="K1684">
         <v>2.99</v>
@@ -86296,39 +86299,39 @@
         <v>1</v>
       </c>
       <c r="P1684" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1685" spans="1:16">
       <c r="A1685" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1685" t="s">
         <v>260</v>
       </c>
       <c r="C1685">
-        <v>0.9426945616666917</v>
+        <v>0.90938683853624</v>
       </c>
       <c r="D1685" t="s">
         <v>445</v>
       </c>
       <c r="E1685">
-        <v>0.8954707544127771</v>
+        <v>0.8578349840199477</v>
       </c>
       <c r="F1685">
         <v>-1</v>
       </c>
       <c r="G1685">
-        <v>0.008557305438333308</v>
+        <v>0.008590613161463761</v>
       </c>
       <c r="H1685">
-        <v>0.008484529245587224</v>
+        <v>0.008642165015980051</v>
       </c>
       <c r="I1685">
-        <v>0.04722380725391462</v>
+        <v>0.05155185451629229</v>
       </c>
       <c r="J1685">
-        <v>1.277619274608493</v>
+        <v>1.288796362907302</v>
       </c>
       <c r="K1685">
         <v>2.98</v>
@@ -86337,16 +86340,16 @@
         <v>4.75</v>
       </c>
       <c r="M1685">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1685">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1685">
         <v>1</v>
       </c>
       <c r="P1685" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1686" spans="1:16">
@@ -86354,31 +86357,31 @@
         <v>0</v>
       </c>
       <c r="B1686" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1686">
-        <v>0.8064988749071667</v>
+        <v>0.7862584850929837</v>
       </c>
       <c r="D1686" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1686">
-        <v>0.8736109112780941</v>
+        <v>0.8533028278524921</v>
       </c>
       <c r="F1686">
         <v>1</v>
       </c>
       <c r="G1686">
-        <v>0.008513501125092833</v>
+        <v>0.008533741514907017</v>
       </c>
       <c r="H1686">
-        <v>0.008606389088721907</v>
+        <v>0.008626697172147509</v>
       </c>
       <c r="I1686">
-        <v>0.06711203637092744</v>
+        <v>0.06704434275950844</v>
       </c>
       <c r="J1686">
-        <v>1.288796362907302</v>
+        <v>1.295565724049169</v>
       </c>
       <c r="K1686">
         <v>2.99</v>
@@ -86396,7 +86399,7 @@
         <v>1</v>
       </c>
       <c r="P1686" t="s">
-        <v>571</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1687" spans="1:16">
@@ -86407,28 +86410,28 @@
         <v>260</v>
       </c>
       <c r="C1687">
-        <v>0.90938683853624</v>
+        <v>0.8892141423334752</v>
       </c>
       <c r="D1687" t="s">
         <v>445</v>
       </c>
       <c r="E1687">
-        <v>0.862274802165313</v>
+        <v>0.8373915133715086</v>
       </c>
       <c r="F1687">
         <v>-1</v>
       </c>
       <c r="G1687">
-        <v>0.008590613161463761</v>
+        <v>0.008610785857666524</v>
       </c>
       <c r="H1687">
-        <v>0.008517725197834688</v>
+        <v>0.008662608486628491</v>
       </c>
       <c r="I1687">
-        <v>0.04711203637092698</v>
+        <v>0.05182262896196654</v>
       </c>
       <c r="J1687">
-        <v>1.288796362907302</v>
+        <v>1.295565724049169</v>
       </c>
       <c r="K1687">
         <v>2.98</v>
@@ -86437,16 +86440,16 @@
         <v>4.75</v>
       </c>
       <c r="M1687">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1687">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1687">
         <v>1</v>
       </c>
       <c r="P1687" t="s">
-        <v>571</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1688" spans="1:16">
@@ -86454,31 +86457,31 @@
         <v>0</v>
       </c>
       <c r="B1688" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1688">
-        <v>0.7862584850929837</v>
+        <v>0.7524917367489325</v>
       </c>
       <c r="D1688" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1688">
-        <v>0.8533028278524921</v>
+        <v>0.819423147239732</v>
       </c>
       <c r="F1688">
         <v>1</v>
       </c>
       <c r="G1688">
-        <v>0.008533741514907017</v>
+        <v>0.008567508263251068</v>
       </c>
       <c r="H1688">
-        <v>0.008626697172147509</v>
+        <v>0.008660576852760268</v>
       </c>
       <c r="I1688">
-        <v>0.06704434275950844</v>
+        <v>0.06693141049079943</v>
       </c>
       <c r="J1688">
-        <v>1.295565724049169</v>
+        <v>1.306858950920089</v>
       </c>
       <c r="K1688">
         <v>2.99</v>
@@ -86496,7 +86499,7 @@
         <v>1</v>
       </c>
       <c r="P1688" t="s">
-        <v>259</v>
+        <v>572</v>
       </c>
     </row>
     <row r="1689" spans="1:16">
@@ -86507,28 +86510,28 @@
         <v>260</v>
       </c>
       <c r="C1689">
-        <v>0.8892141423334752</v>
+        <v>0.8555603262581335</v>
       </c>
       <c r="D1689" t="s">
         <v>445</v>
       </c>
       <c r="E1689">
-        <v>0.8421697995739672</v>
+        <v>0.80328596822133</v>
       </c>
       <c r="F1689">
         <v>-1</v>
       </c>
       <c r="G1689">
-        <v>0.008610785857666524</v>
+        <v>0.008644439673741866</v>
       </c>
       <c r="H1689">
-        <v>0.008537830200426033</v>
+        <v>0.008696714031778671</v>
       </c>
       <c r="I1689">
-        <v>0.04704434275950797</v>
+        <v>0.05227435803680347</v>
       </c>
       <c r="J1689">
-        <v>1.295565724049169</v>
+        <v>1.306858950920089</v>
       </c>
       <c r="K1689">
         <v>2.98</v>
@@ -86537,16 +86540,16 @@
         <v>4.75</v>
       </c>
       <c r="M1689">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1689">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1689">
         <v>1</v>
       </c>
       <c r="P1689" t="s">
-        <v>259</v>
+        <v>572</v>
       </c>
     </row>
     <row r="1690" spans="1:16">
@@ -86554,31 +86557,31 @@
         <v>0</v>
       </c>
       <c r="B1690" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1690">
-        <v>0.7524917367489325</v>
+        <v>0.747940275032922</v>
       </c>
       <c r="D1690" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1690">
-        <v>0.819423147239732</v>
+        <v>0.8148564632437347</v>
       </c>
       <c r="F1690">
         <v>1</v>
       </c>
       <c r="G1690">
-        <v>0.008567508263251068</v>
+        <v>0.008572059724967078</v>
       </c>
       <c r="H1690">
-        <v>0.008660576852760268</v>
+        <v>0.008665143536756265</v>
       </c>
       <c r="I1690">
-        <v>0.06693141049079943</v>
+        <v>0.06691618821081269</v>
       </c>
       <c r="J1690">
-        <v>1.306858950920089</v>
+        <v>1.308381178918755</v>
       </c>
       <c r="K1690">
         <v>2.99</v>
@@ -86596,7 +86599,7 @@
         <v>1</v>
       </c>
       <c r="P1690" t="s">
-        <v>572</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1691" spans="1:16">
@@ -86607,28 +86610,28 @@
         <v>260</v>
       </c>
       <c r="C1691">
-        <v>0.8555603262581335</v>
+        <v>0.8510240868221097</v>
       </c>
       <c r="D1691" t="s">
         <v>445</v>
       </c>
       <c r="E1691">
-        <v>0.8086289157673345</v>
+        <v>0.7986888396653593</v>
       </c>
       <c r="F1691">
         <v>-1</v>
       </c>
       <c r="G1691">
-        <v>0.008644439673741866</v>
+        <v>0.008648975913177891</v>
       </c>
       <c r="H1691">
-        <v>0.008571371084232667</v>
+        <v>0.008701311160334641</v>
       </c>
       <c r="I1691">
-        <v>0.04693141049079896</v>
+        <v>0.05233524715675042</v>
       </c>
       <c r="J1691">
-        <v>1.306858950920089</v>
+        <v>1.308381178918755</v>
       </c>
       <c r="K1691">
         <v>2.98</v>
@@ -86637,16 +86640,16 @@
         <v>4.75</v>
       </c>
       <c r="M1691">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1691">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1691">
         <v>1</v>
       </c>
       <c r="P1691" t="s">
-        <v>572</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1692" spans="1:16">
@@ -86654,31 +86657,31 @@
         <v>0</v>
       </c>
       <c r="B1692" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1692">
-        <v>0.747940275032922</v>
+        <v>0.7508817338992388</v>
       </c>
       <c r="D1692" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1692">
-        <v>0.8148564632437347</v>
+        <v>0.817807759765123</v>
       </c>
       <c r="F1692">
         <v>1</v>
       </c>
       <c r="G1692">
-        <v>0.008572059724967078</v>
+        <v>0.008569118266100762</v>
       </c>
       <c r="H1692">
-        <v>0.008665143536756265</v>
+        <v>0.008662192240234876</v>
       </c>
       <c r="I1692">
-        <v>0.06691618821081269</v>
+        <v>0.06692602586588414</v>
       </c>
       <c r="J1692">
-        <v>1.308381178918755</v>
+        <v>1.307397413411626</v>
       </c>
       <c r="K1692">
         <v>2.99</v>
@@ -86696,7 +86699,7 @@
         <v>1</v>
       </c>
       <c r="P1692" t="s">
-        <v>443</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1693" spans="1:16">
@@ -86707,28 +86710,28 @@
         <v>260</v>
       </c>
       <c r="C1693">
-        <v>0.8510240868221097</v>
+        <v>0.8539557080333555</v>
       </c>
       <c r="D1693" t="s">
         <v>445</v>
       </c>
       <c r="E1693">
-        <v>0.8041078986112975</v>
+        <v>0.80165981149689</v>
       </c>
       <c r="F1693">
         <v>-1</v>
       </c>
       <c r="G1693">
-        <v>0.008648975913177891</v>
+        <v>0.008646044291966644</v>
       </c>
       <c r="H1693">
-        <v>0.008575892101388703</v>
+        <v>0.00869834018850311</v>
       </c>
       <c r="I1693">
-        <v>0.04691618821081223</v>
+        <v>0.05229589653646549</v>
       </c>
       <c r="J1693">
-        <v>1.308381178918755</v>
+        <v>1.307397413411626</v>
       </c>
       <c r="K1693">
         <v>2.98</v>
@@ -86737,16 +86740,16 @@
         <v>4.75</v>
       </c>
       <c r="M1693">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1693">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1693">
         <v>1</v>
       </c>
       <c r="P1693" t="s">
-        <v>443</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1694" spans="1:16">
@@ -86754,31 +86757,31 @@
         <v>0</v>
       </c>
       <c r="B1694" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1694">
-        <v>0.7508817338992388</v>
+        <v>0.7342938724207762</v>
       </c>
       <c r="D1694" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1694">
-        <v>0.817807759765123</v>
+        <v>0.8011644204890738</v>
       </c>
       <c r="F1694">
         <v>1</v>
       </c>
       <c r="G1694">
-        <v>0.008569118266100762</v>
+        <v>0.008585706127579223</v>
       </c>
       <c r="H1694">
-        <v>0.008662192240234876</v>
+        <v>0.008678835579510928</v>
       </c>
       <c r="I1694">
-        <v>0.06692602586588414</v>
+        <v>0.06687054806829762</v>
       </c>
       <c r="J1694">
-        <v>1.307397413411626</v>
+        <v>1.312945193170309</v>
       </c>
       <c r="K1694">
         <v>2.99</v>
@@ -86796,7 +86799,7 @@
         <v>1</v>
       </c>
       <c r="P1694" t="s">
-        <v>573</v>
+        <v>261</v>
       </c>
     </row>
     <row r="1695" spans="1:16">
@@ -86807,28 +86810,28 @@
         <v>260</v>
       </c>
       <c r="C1695">
-        <v>0.8539557080333555</v>
+        <v>0.8374233243524793</v>
       </c>
       <c r="D1695" t="s">
         <v>445</v>
       </c>
       <c r="E1695">
-        <v>0.8070296821674718</v>
+        <v>0.7849055166256673</v>
       </c>
       <c r="F1695">
         <v>-1</v>
       </c>
       <c r="G1695">
-        <v>0.008646044291966644</v>
+        <v>0.008662576675647522</v>
       </c>
       <c r="H1695">
-        <v>0.008572970317832529</v>
+        <v>0.008715094483374333</v>
       </c>
       <c r="I1695">
-        <v>0.04692602586588368</v>
+        <v>0.05251780772681203</v>
       </c>
       <c r="J1695">
-        <v>1.307397413411626</v>
+        <v>1.312945193170309</v>
       </c>
       <c r="K1695">
         <v>2.98</v>
@@ -86837,16 +86840,16 @@
         <v>4.75</v>
       </c>
       <c r="M1695">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1695">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1695">
         <v>1</v>
       </c>
       <c r="P1695" t="s">
-        <v>573</v>
+        <v>261</v>
       </c>
     </row>
     <row r="1696" spans="1:16">
@@ -86854,31 +86857,31 @@
         <v>0</v>
       </c>
       <c r="B1696" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1696">
-        <v>0.7342938724207762</v>
+        <v>0.7280081951252568</v>
       </c>
       <c r="D1696" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1696">
-        <v>0.8011644204890738</v>
+        <v>0.7948577208614624</v>
       </c>
       <c r="F1696">
         <v>1</v>
       </c>
       <c r="G1696">
-        <v>0.008585706127579223</v>
+        <v>0.008591991804874743</v>
       </c>
       <c r="H1696">
-        <v>0.008678835579510928</v>
+        <v>0.008685142279138539</v>
       </c>
       <c r="I1696">
-        <v>0.06687054806829762</v>
+        <v>0.06684952573620562</v>
       </c>
       <c r="J1696">
-        <v>1.312945193170309</v>
+        <v>1.315047426379513</v>
       </c>
       <c r="K1696">
         <v>2.99</v>
@@ -86896,7 +86899,7 @@
         <v>1</v>
       </c>
       <c r="P1696" t="s">
-        <v>262</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1697" spans="1:16">
@@ -86907,28 +86910,28 @@
         <v>260</v>
       </c>
       <c r="C1697">
-        <v>0.8374233243524793</v>
+        <v>0.8311586693890525</v>
       </c>
       <c r="D1697" t="s">
         <v>445</v>
       </c>
       <c r="E1697">
-        <v>0.7905527762841826</v>
+        <v>0.7785567723338715</v>
       </c>
       <c r="F1697">
         <v>-1</v>
       </c>
       <c r="G1697">
-        <v>0.008662576675647522</v>
+        <v>0.008668841330610947</v>
       </c>
       <c r="H1697">
-        <v>0.008589447223715818</v>
+        <v>0.008721443227666128</v>
       </c>
       <c r="I1697">
-        <v>0.04687054806829671</v>
+        <v>0.05260189705518092</v>
       </c>
       <c r="J1697">
-        <v>1.312945193170309</v>
+        <v>1.315047426379513</v>
       </c>
       <c r="K1697">
         <v>2.98</v>
@@ -86937,16 +86940,16 @@
         <v>4.75</v>
       </c>
       <c r="M1697">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1697">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1697">
         <v>1</v>
       </c>
       <c r="P1697" t="s">
-        <v>262</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1698" spans="1:16">
@@ -86954,31 +86957,31 @@
         <v>0</v>
       </c>
       <c r="B1698" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1698">
-        <v>0.7280081951252568</v>
+        <v>0.7202147488435684</v>
       </c>
       <c r="D1698" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1698">
-        <v>0.7948577208614624</v>
+        <v>0.7870382095420423</v>
       </c>
       <c r="F1698">
         <v>1</v>
       </c>
       <c r="G1698">
-        <v>0.008591991804874743</v>
+        <v>0.008599785251156431</v>
       </c>
       <c r="H1698">
-        <v>0.008685142279138539</v>
+        <v>0.008692961790457957</v>
       </c>
       <c r="I1698">
-        <v>0.06684952573620562</v>
+        <v>0.06682346069847389</v>
       </c>
       <c r="J1698">
-        <v>1.315047426379513</v>
+        <v>1.317653930152653</v>
       </c>
       <c r="K1698">
         <v>2.99</v>
@@ -86996,7 +86999,7 @@
         <v>1</v>
       </c>
       <c r="P1698" t="s">
-        <v>447</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1699" spans="1:16">
@@ -87007,28 +87010,28 @@
         <v>260</v>
       </c>
       <c r="C1699">
-        <v>0.8311586693890525</v>
+        <v>0.8233912881450953</v>
       </c>
       <c r="D1699" t="s">
         <v>445</v>
       </c>
       <c r="E1699">
-        <v>0.7843091436528473</v>
+        <v>0.7706851309389888</v>
       </c>
       <c r="F1699">
         <v>-1</v>
       </c>
       <c r="G1699">
-        <v>0.008668841330610947</v>
+        <v>0.008676608711854904</v>
       </c>
       <c r="H1699">
-        <v>0.008595690856347154</v>
+        <v>0.008729314869061011</v>
       </c>
       <c r="I1699">
-        <v>0.04684952573620516</v>
+        <v>0.0527061572061065</v>
       </c>
       <c r="J1699">
-        <v>1.315047426379513</v>
+        <v>1.317653930152653</v>
       </c>
       <c r="K1699">
         <v>2.98</v>
@@ -87037,16 +87040,16 @@
         <v>4.75</v>
       </c>
       <c r="M1699">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1699">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1699">
         <v>1</v>
       </c>
       <c r="P1699" t="s">
-        <v>447</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1700" spans="1:16">
@@ -87054,31 +87057,31 @@
         <v>0</v>
       </c>
       <c r="B1700" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1700">
-        <v>0.7202147488435684</v>
+        <v>0.7246351928069408</v>
       </c>
       <c r="D1700" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1700">
-        <v>0.7870382095420423</v>
+        <v>0.7914734375989374</v>
       </c>
       <c r="F1700">
         <v>1</v>
       </c>
       <c r="G1700">
-        <v>0.008599785251156431</v>
+        <v>0.00859536480719306</v>
       </c>
       <c r="H1700">
-        <v>0.008692961790457957</v>
+        <v>0.008688526562401062</v>
       </c>
       <c r="I1700">
-        <v>0.06682346069847389</v>
+        <v>0.06683824479199663</v>
       </c>
       <c r="J1700">
-        <v>1.317653930152653</v>
+        <v>1.316175520800354</v>
       </c>
       <c r="K1700">
         <v>2.99</v>
@@ -87096,7 +87099,7 @@
         <v>1</v>
       </c>
       <c r="P1700" t="s">
-        <v>257</v>
+        <v>574</v>
       </c>
     </row>
     <row r="1701" spans="1:16">
@@ -87107,28 +87110,28 @@
         <v>260</v>
       </c>
       <c r="C1701">
-        <v>0.8233912881450953</v>
+        <v>0.8277969480149441</v>
       </c>
       <c r="D1701" t="s">
         <v>445</v>
       </c>
       <c r="E1701">
-        <v>0.7765678274466219</v>
+        <v>0.7751499271829303</v>
       </c>
       <c r="F1701">
         <v>-1</v>
       </c>
       <c r="G1701">
-        <v>0.008676608711854904</v>
+        <v>0.008672203051985057</v>
       </c>
       <c r="H1701">
-        <v>0.008603432172553379</v>
+        <v>0.008724850072817069</v>
       </c>
       <c r="I1701">
-        <v>0.04682346069847343</v>
+        <v>0.05264702083201378</v>
       </c>
       <c r="J1701">
-        <v>1.317653930152653</v>
+        <v>1.316175520800354</v>
       </c>
       <c r="K1701">
         <v>2.98</v>
@@ -87137,16 +87140,16 @@
         <v>4.75</v>
       </c>
       <c r="M1701">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1701">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1701">
         <v>1</v>
       </c>
       <c r="P1701" t="s">
-        <v>257</v>
+        <v>574</v>
       </c>
     </row>
     <row r="1702" spans="1:16">
@@ -87154,31 +87157,31 @@
         <v>0</v>
       </c>
       <c r="B1702" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1702">
-        <v>0.7246351928069408</v>
+        <v>0.7398440110333406</v>
       </c>
       <c r="D1702" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1702">
-        <v>0.7914734375989374</v>
+        <v>0.8067331214381346</v>
       </c>
       <c r="F1702">
         <v>1</v>
       </c>
       <c r="G1702">
-        <v>0.00859536480719306</v>
+        <v>0.008580155988966659</v>
       </c>
       <c r="H1702">
-        <v>0.008688526562401062</v>
+        <v>0.008673266878561865</v>
       </c>
       <c r="I1702">
-        <v>0.06683824479199663</v>
+        <v>0.06688911040479395</v>
       </c>
       <c r="J1702">
-        <v>1.316175520800354</v>
+        <v>1.311088959520622</v>
       </c>
       <c r="K1702">
         <v>2.99</v>
@@ -87196,7 +87199,7 @@
         <v>1</v>
       </c>
       <c r="P1702" t="s">
-        <v>444</v>
+        <v>575</v>
       </c>
     </row>
     <row r="1703" spans="1:16">
@@ -87207,28 +87210,28 @@
         <v>260</v>
       </c>
       <c r="C1703">
-        <v>0.8277969480149441</v>
+        <v>0.8429549006285466</v>
       </c>
       <c r="D1703" t="s">
         <v>445</v>
       </c>
       <c r="E1703">
-        <v>0.7809587032229479</v>
+        <v>0.7905113422477221</v>
       </c>
       <c r="F1703">
         <v>-1</v>
       </c>
       <c r="G1703">
-        <v>0.008672203051985057</v>
+        <v>0.008657045099371454</v>
       </c>
       <c r="H1703">
-        <v>0.008599041296777053</v>
+        <v>0.008709488657752278</v>
       </c>
       <c r="I1703">
-        <v>0.04683824479199616</v>
+        <v>0.05244355838082448</v>
       </c>
       <c r="J1703">
-        <v>1.316175520800354</v>
+        <v>1.311088959520622</v>
       </c>
       <c r="K1703">
         <v>2.98</v>
@@ -87237,16 +87240,16 @@
         <v>4.75</v>
       </c>
       <c r="M1703">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1703">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1703">
         <v>1</v>
       </c>
       <c r="P1703" t="s">
-        <v>444</v>
+        <v>575</v>
       </c>
     </row>
     <row r="1704" spans="1:16">
@@ -87254,31 +87257,31 @@
         <v>0</v>
       </c>
       <c r="B1704" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1704">
-        <v>0.7398440110333406</v>
+        <v>0.760654448446985</v>
       </c>
       <c r="D1704" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1704">
-        <v>0.8067331214381346</v>
+        <v>0.8276131589769085</v>
       </c>
       <c r="F1704">
         <v>1</v>
       </c>
       <c r="G1704">
-        <v>0.008580155988966659</v>
+        <v>0.008559345551553016</v>
       </c>
       <c r="H1704">
-        <v>0.008673266878561865</v>
+        <v>0.008652386841023091</v>
       </c>
       <c r="I1704">
-        <v>0.06688911040479395</v>
+        <v>0.06695871052992342</v>
       </c>
       <c r="J1704">
-        <v>1.311088959520622</v>
+        <v>1.304128947007697</v>
       </c>
       <c r="K1704">
         <v>2.99</v>
@@ -87296,7 +87299,7 @@
         <v>1</v>
       </c>
       <c r="P1704" t="s">
-        <v>574</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1705" spans="1:16">
@@ -87307,28 +87310,28 @@
         <v>260</v>
       </c>
       <c r="C1705">
-        <v>0.8429549006285466</v>
+        <v>0.863695737917062</v>
       </c>
       <c r="D1705" t="s">
         <v>445</v>
       </c>
       <c r="E1705">
-        <v>0.7960657902237531</v>
+        <v>0.811530580036754</v>
       </c>
       <c r="F1705">
         <v>-1</v>
       </c>
       <c r="G1705">
-        <v>0.008657045099371454</v>
+        <v>0.008636304262082938</v>
       </c>
       <c r="H1705">
-        <v>0.008583934209776248</v>
+        <v>0.008688469419963245</v>
       </c>
       <c r="I1705">
-        <v>0.04688911040479349</v>
+        <v>0.05216515788030796</v>
       </c>
       <c r="J1705">
-        <v>1.311088959520622</v>
+        <v>1.304128947007697</v>
       </c>
       <c r="K1705">
         <v>2.98</v>
@@ -87337,16 +87340,16 @@
         <v>4.75</v>
       </c>
       <c r="M1705">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1705">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1705">
         <v>1</v>
       </c>
       <c r="P1705" t="s">
-        <v>574</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1706" spans="1:16">
@@ -87354,181 +87357,181 @@
         <v>0</v>
       </c>
       <c r="B1706" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C1706">
-        <v>0.760654448446985</v>
+        <v>0.8943259526245027</v>
       </c>
       <c r="D1706" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E1706">
-        <v>0.8276131589769085</v>
+        <v>0.8425719385657708</v>
       </c>
       <c r="F1706">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1706">
-        <v>0.008559345551553016</v>
+        <v>0.008605674047375498</v>
       </c>
       <c r="H1706">
-        <v>0.008652386841023091</v>
+        <v>0.008657428061434229</v>
       </c>
       <c r="I1706">
-        <v>0.06695871052992342</v>
+        <v>0.05175401405873181</v>
       </c>
       <c r="J1706">
-        <v>1.304128947007697</v>
+        <v>1.293850351468288</v>
       </c>
       <c r="K1706">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1706">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1706">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="N1706">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="O1706">
         <v>1</v>
       </c>
       <c r="P1706" t="s">
-        <v>442</v>
+        <v>576</v>
       </c>
     </row>
     <row r="1707" spans="1:16">
       <c r="A1707" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1707" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C1707">
-        <v>0.863695737917062</v>
+        <v>0.8238855201820487</v>
       </c>
       <c r="D1707" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E1707">
-        <v>0.816737027387139</v>
+        <v>0.8910557058682764</v>
       </c>
       <c r="F1707">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1707">
-        <v>0.008636304262082938</v>
+        <v>0.008496114479817952</v>
       </c>
       <c r="H1707">
-        <v>0.008563262972612862</v>
+        <v>0.008588944294131725</v>
       </c>
       <c r="I1707">
-        <v>0.04695871052992295</v>
+        <v>0.06717018568622768</v>
       </c>
       <c r="J1707">
-        <v>1.304128947007697</v>
+        <v>1.282981431377241</v>
       </c>
       <c r="K1707">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1707">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1707">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N1707">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O1707">
         <v>1</v>
       </c>
       <c r="P1707" t="s">
-        <v>442</v>
+        <v>259</v>
       </c>
     </row>
     <row r="1708" spans="1:16">
       <c r="A1708" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1708" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C1708">
-        <v>0.7913874491098194</v>
+        <v>0.9267153344958214</v>
       </c>
       <c r="D1708" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E1708">
-        <v>0.858448945595137</v>
+        <v>0.8753960772407314</v>
       </c>
       <c r="F1708">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1708">
-        <v>0.00852861255089018</v>
+        <v>0.00857328466550418</v>
       </c>
       <c r="H1708">
-        <v>0.008621551054404862</v>
+        <v>0.008624603922759268</v>
       </c>
       <c r="I1708">
-        <v>0.06706149648531756</v>
+        <v>0.05131925725509001</v>
       </c>
       <c r="J1708">
-        <v>1.293850351468288</v>
+        <v>1.282981431377241</v>
       </c>
       <c r="K1708">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1708">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1708">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="N1708">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="O1708">
         <v>1</v>
       </c>
       <c r="P1708" t="s">
-        <v>575</v>
+        <v>259</v>
       </c>
     </row>
     <row r="1709" spans="1:16">
       <c r="A1709" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1709" t="s">
         <v>260</v>
       </c>
       <c r="C1709">
-        <v>0.8943259526245027</v>
+        <v>0.9437602885510952</v>
       </c>
       <c r="D1709" t="s">
         <v>445</v>
       </c>
       <c r="E1709">
-        <v>0.8472644561391856</v>
+        <v>0.8926698226256069</v>
       </c>
       <c r="F1709">
         <v>-1</v>
       </c>
       <c r="G1709">
-        <v>0.008605674047375498</v>
+        <v>0.008556239711448905</v>
       </c>
       <c r="H1709">
-        <v>0.008532735543860815</v>
+        <v>0.008607330177374395</v>
       </c>
       <c r="I1709">
-        <v>0.0470614964853171</v>
+        <v>0.05109046592548827</v>
       </c>
       <c r="J1709">
-        <v>1.293850351468288</v>
+        <v>1.277261648137216</v>
       </c>
       <c r="K1709">
         <v>2.98</v>
@@ -87537,166 +87540,16 @@
         <v>4.75</v>
       </c>
       <c r="M1709">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="N1709">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="O1709">
         <v>1</v>
       </c>
       <c r="P1709" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="1710" spans="1:16">
-      <c r="A1710" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1710" t="s">
-        <v>261</v>
-      </c>
-      <c r="C1710">
-        <v>0.8238855201820487</v>
-      </c>
-      <c r="D1710" t="s">
-        <v>446</v>
-      </c>
-      <c r="E1710">
-        <v>0.8910557058682764</v>
-      </c>
-      <c r="F1710">
-        <v>1</v>
-      </c>
-      <c r="G1710">
-        <v>0.008496114479817952</v>
-      </c>
-      <c r="H1710">
-        <v>0.008588944294131725</v>
-      </c>
-      <c r="I1710">
-        <v>0.06717018568622768</v>
-      </c>
-      <c r="J1710">
-        <v>1.282981431377241</v>
-      </c>
-      <c r="K1710">
-        <v>2.99</v>
-      </c>
-      <c r="L1710">
-        <v>4.66</v>
-      </c>
-      <c r="M1710">
-        <v>3</v>
-      </c>
-      <c r="N1710">
-        <v>4.74</v>
-      </c>
-      <c r="O1710">
-        <v>1</v>
-      </c>
-      <c r="P1710" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1711" spans="1:16">
-      <c r="A1711" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1711" t="s">
-        <v>260</v>
-      </c>
-      <c r="C1711">
-        <v>0.9267153344958214</v>
-      </c>
-      <c r="D1711" t="s">
-        <v>445</v>
-      </c>
-      <c r="E1711">
-        <v>0.8795451488095938</v>
-      </c>
-      <c r="F1711">
-        <v>-1</v>
-      </c>
-      <c r="G1711">
-        <v>0.00857328466550418</v>
-      </c>
-      <c r="H1711">
-        <v>0.008500454851190407</v>
-      </c>
-      <c r="I1711">
-        <v>0.04717018568622766</v>
-      </c>
-      <c r="J1711">
-        <v>1.282981431377241</v>
-      </c>
-      <c r="K1711">
-        <v>2.98</v>
-      </c>
-      <c r="L1711">
-        <v>4.75</v>
-      </c>
-      <c r="M1711">
-        <v>2.97</v>
-      </c>
-      <c r="N1711">
-        <v>4.69</v>
-      </c>
-      <c r="O1711">
-        <v>1</v>
-      </c>
-      <c r="P1711" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1712" spans="1:16">
-      <c r="A1712" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1712" t="s">
-        <v>260</v>
-      </c>
-      <c r="C1712">
-        <v>0.9437602885510952</v>
-      </c>
-      <c r="D1712" t="s">
-        <v>445</v>
-      </c>
-      <c r="E1712">
-        <v>0.8965329050324677</v>
-      </c>
-      <c r="F1712">
-        <v>-1</v>
-      </c>
-      <c r="G1712">
-        <v>0.008556239711448905</v>
-      </c>
-      <c r="H1712">
-        <v>0.008483467094967534</v>
-      </c>
-      <c r="I1712">
-        <v>0.04722738351862743</v>
-      </c>
-      <c r="J1712">
-        <v>1.277261648137216</v>
-      </c>
-      <c r="K1712">
-        <v>2.98</v>
-      </c>
-      <c r="L1712">
-        <v>4.75</v>
-      </c>
-      <c r="M1712">
-        <v>2.97</v>
-      </c>
-      <c r="N1712">
-        <v>4.69</v>
-      </c>
-      <c r="O1712">
-        <v>1</v>
-      </c>
-      <c r="P1712" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5229" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5226" uniqueCount="581">
   <si>
     <t>trade_time</t>
   </si>
@@ -2114,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1739"/>
+  <dimension ref="A1:P1738"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -85469,43 +85469,43 @@
         <v>0</v>
       </c>
       <c r="B1668" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1668">
-        <v>1.381575977020794</v>
+        <v>1.371917246540982</v>
       </c>
       <c r="D1668" t="s">
-        <v>250</v>
+        <v>442</v>
       </c>
       <c r="E1668">
-        <v>1.468962598106643</v>
+        <v>1.258621328586455</v>
       </c>
       <c r="F1668">
         <v>-1</v>
       </c>
       <c r="G1668">
-        <v>0.008038424022979206</v>
+        <v>0.007868082753459019</v>
       </c>
       <c r="H1668">
-        <v>0.008011037401893358</v>
+        <v>0.007961378671413544</v>
       </c>
       <c r="I1668">
-        <v>-0.08738662108584849</v>
+        <v>0.1132959179545265</v>
       </c>
       <c r="J1668">
         <v>1.147732421716968</v>
       </c>
       <c r="K1668">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="L1668">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="M1668">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="N1668">
-        <v>4.74</v>
+        <v>4.61</v>
       </c>
       <c r="O1668">
         <v>1</v>
@@ -85519,43 +85519,43 @@
         <v>1</v>
       </c>
       <c r="B1669" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1669">
-        <v>1.371917246540982</v>
+        <v>1.234984141111739</v>
       </c>
       <c r="D1669" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E1669">
-        <v>1.258621328586455</v>
+        <v>1.31498414111174</v>
       </c>
       <c r="F1669">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1669">
-        <v>0.007868082753459019</v>
+        <v>0.00830501585888826</v>
       </c>
       <c r="H1669">
-        <v>0.007961378671413544</v>
+        <v>0.00838501585888826</v>
       </c>
       <c r="I1669">
-        <v>0.1132959179545265</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1669">
         <v>1.147732421716968</v>
       </c>
       <c r="K1669">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1669">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1669">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1669">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1669">
         <v>1</v>
@@ -85569,43 +85569,43 @@
         <v>2</v>
       </c>
       <c r="B1670" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1670">
-        <v>1.234984141111739</v>
+        <v>1.238621328586455</v>
       </c>
       <c r="D1670" t="s">
-        <v>445</v>
+        <v>263</v>
       </c>
       <c r="E1670">
-        <v>1.31498414111174</v>
+        <v>1.329757383283437</v>
       </c>
       <c r="F1670">
         <v>1</v>
       </c>
       <c r="G1670">
-        <v>0.00830501585888826</v>
+        <v>0.007941378671413545</v>
       </c>
       <c r="H1670">
-        <v>0.00838501585888826</v>
+        <v>0.008170242616716564</v>
       </c>
       <c r="I1670">
-        <v>0.08000000000000007</v>
+        <v>0.09113605469698216</v>
       </c>
       <c r="J1670">
         <v>1.147732421716968</v>
       </c>
       <c r="K1670">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="L1670">
-        <v>4.77</v>
+        <v>4.59</v>
       </c>
       <c r="M1670">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="N1670">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="O1670">
         <v>1</v>
@@ -85619,43 +85619,43 @@
         <v>3</v>
       </c>
       <c r="B1671" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C1671">
-        <v>1.238621328586455</v>
+        <v>1.229757383283437</v>
       </c>
       <c r="D1671" t="s">
-        <v>263</v>
+        <v>444</v>
       </c>
       <c r="E1671">
-        <v>1.329757383283437</v>
+        <v>1.375778926288534</v>
       </c>
       <c r="F1671">
         <v>1</v>
       </c>
       <c r="G1671">
-        <v>0.007941378671413545</v>
+        <v>0.008070242616716563</v>
       </c>
       <c r="H1671">
-        <v>0.008170242616716564</v>
+        <v>0.008744221073711466</v>
       </c>
       <c r="I1671">
-        <v>0.09113605469698216</v>
+        <v>0.1460215430050966</v>
       </c>
       <c r="J1671">
         <v>1.147732421716968</v>
       </c>
       <c r="K1671">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="L1671">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="M1671">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="N1671">
-        <v>4.75</v>
+        <v>5.06</v>
       </c>
       <c r="O1671">
         <v>1</v>
@@ -85669,10 +85669,10 @@
         <v>4</v>
       </c>
       <c r="B1672" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1672">
-        <v>1.229757383283437</v>
+        <v>1.238733574722874</v>
       </c>
       <c r="D1672" t="s">
         <v>444</v>
@@ -85684,22 +85684,22 @@
         <v>1</v>
       </c>
       <c r="G1672">
-        <v>0.008070242616716563</v>
+        <v>0.008561266425277127</v>
       </c>
       <c r="H1672">
         <v>0.008744221073711466</v>
       </c>
       <c r="I1672">
-        <v>0.1460215430050966</v>
+        <v>0.1370453515656598</v>
       </c>
       <c r="J1672">
         <v>1.147732421716968</v>
       </c>
       <c r="K1672">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1672">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1672">
         <v>3.21</v>
@@ -85716,96 +85716,96 @@
     </row>
     <row r="1673" spans="1:16">
       <c r="A1673" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1673" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C1673">
-        <v>1.238733574722874</v>
+        <v>1.298944189815882</v>
       </c>
       <c r="D1673" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E1673">
-        <v>1.375778926288534</v>
+        <v>1.183327573944303</v>
       </c>
       <c r="F1673">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1673">
-        <v>0.008561266425277127</v>
+        <v>0.007941055810184118</v>
       </c>
       <c r="H1673">
-        <v>0.008744221073711466</v>
+        <v>0.008036672426055699</v>
       </c>
       <c r="I1673">
-        <v>0.1370453515656598</v>
+        <v>0.1156166158715792</v>
       </c>
       <c r="J1673">
-        <v>1.147732421716968</v>
+        <v>1.173517954128664</v>
       </c>
       <c r="K1673">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="L1673">
-        <v>4.9</v>
+        <v>4.62</v>
       </c>
       <c r="M1673">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
       <c r="N1673">
-        <v>5.06</v>
+        <v>4.61</v>
       </c>
       <c r="O1673">
         <v>1</v>
       </c>
       <c r="P1673" t="s">
-        <v>435</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1674" spans="1:16">
       <c r="A1674" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1674" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1674">
-        <v>1.298944189815882</v>
+        <v>1.155564701283716</v>
       </c>
       <c r="D1674" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E1674">
-        <v>1.183327573944303</v>
+        <v>1.235564701283716</v>
       </c>
       <c r="F1674">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1674">
-        <v>0.007941055810184118</v>
+        <v>0.008384435298716283</v>
       </c>
       <c r="H1674">
-        <v>0.008036672426055699</v>
+        <v>0.008464435298716284</v>
       </c>
       <c r="I1674">
-        <v>0.1156166158715792</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1674">
         <v>1.173517954128664</v>
       </c>
       <c r="K1674">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1674">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1674">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1674">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1674">
         <v>1</v>
@@ -85816,46 +85816,46 @@
     </row>
     <row r="1675" spans="1:16">
       <c r="A1675" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1675" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1675">
-        <v>1.155564701283716</v>
+        <v>1.163327573944303</v>
       </c>
       <c r="D1675" t="s">
-        <v>445</v>
+        <v>263</v>
       </c>
       <c r="E1675">
-        <v>1.235564701283716</v>
+        <v>1.252916496696582</v>
       </c>
       <c r="F1675">
         <v>1</v>
       </c>
       <c r="G1675">
-        <v>0.008384435298716283</v>
+        <v>0.008016672426055697</v>
       </c>
       <c r="H1675">
-        <v>0.008464435298716284</v>
+        <v>0.008247083503303419</v>
       </c>
       <c r="I1675">
-        <v>0.08000000000000007</v>
+        <v>0.08958892275227992</v>
       </c>
       <c r="J1675">
         <v>1.173517954128664</v>
       </c>
       <c r="K1675">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="L1675">
-        <v>4.77</v>
+        <v>4.59</v>
       </c>
       <c r="M1675">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="N1675">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="O1675">
         <v>1</v>
@@ -85866,46 +85866,46 @@
     </row>
     <row r="1676" spans="1:16">
       <c r="A1676" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1676" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C1676">
-        <v>1.163327573944303</v>
+        <v>1.152916496696583</v>
       </c>
       <c r="D1676" t="s">
-        <v>263</v>
+        <v>444</v>
       </c>
       <c r="E1676">
-        <v>1.252916496696582</v>
+        <v>1.29300736724699</v>
       </c>
       <c r="F1676">
         <v>1</v>
       </c>
       <c r="G1676">
-        <v>0.008016672426055697</v>
+        <v>0.008147083503303417</v>
       </c>
       <c r="H1676">
-        <v>0.008247083503303419</v>
+        <v>0.00882699263275301</v>
       </c>
       <c r="I1676">
-        <v>0.08958892275227992</v>
+        <v>0.1400908705504067</v>
       </c>
       <c r="J1676">
         <v>1.173517954128664</v>
       </c>
       <c r="K1676">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="L1676">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="M1676">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="N1676">
-        <v>4.75</v>
+        <v>5.06</v>
       </c>
       <c r="O1676">
         <v>1</v>
@@ -85916,13 +85916,13 @@
     </row>
     <row r="1677" spans="1:16">
       <c r="A1677" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1677" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1677">
-        <v>1.152916496696583</v>
+        <v>1.156477726329564</v>
       </c>
       <c r="D1677" t="s">
         <v>444</v>
@@ -85934,22 +85934,22 @@
         <v>1</v>
       </c>
       <c r="G1677">
-        <v>0.008147083503303417</v>
+        <v>0.008643522273670436</v>
       </c>
       <c r="H1677">
         <v>0.00882699263275301</v>
       </c>
       <c r="I1677">
-        <v>0.1400908705504067</v>
+        <v>0.1365296409174257</v>
       </c>
       <c r="J1677">
         <v>1.173517954128664</v>
       </c>
       <c r="K1677">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1677">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1677">
         <v>3.21</v>
@@ -85966,96 +85966,96 @@
     </row>
     <row r="1678" spans="1:16">
       <c r="A1678" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1678" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C1678">
-        <v>1.156477726329564</v>
+        <v>1.199709616662221</v>
       </c>
       <c r="D1678" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E1678">
-        <v>1.29300736724699</v>
+        <v>1.080937130973034</v>
       </c>
       <c r="F1678">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1678">
-        <v>0.008643522273670436</v>
+        <v>0.00804029038333778</v>
       </c>
       <c r="H1678">
-        <v>0.00882699263275301</v>
+        <v>0.008139062869026967</v>
       </c>
       <c r="I1678">
-        <v>0.1365296409174257</v>
+        <v>0.118772485689187</v>
       </c>
       <c r="J1678">
-        <v>1.173517954128664</v>
+        <v>1.208583174324304</v>
       </c>
       <c r="K1678">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="L1678">
-        <v>4.9</v>
+        <v>4.62</v>
       </c>
       <c r="M1678">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
       <c r="N1678">
-        <v>5.06</v>
+        <v>4.61</v>
       </c>
       <c r="O1678">
         <v>1</v>
       </c>
       <c r="P1678" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="1679" spans="1:16">
       <c r="A1679" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1679" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C1679">
-        <v>1.199709616662221</v>
+        <v>1.047563823081144</v>
       </c>
       <c r="D1679" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E1679">
-        <v>1.080937130973034</v>
+        <v>1.127563823081144</v>
       </c>
       <c r="F1679">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1679">
-        <v>0.00804029038333778</v>
+        <v>0.008492436176918855</v>
       </c>
       <c r="H1679">
-        <v>0.008139062869026967</v>
+        <v>0.008572436176918854</v>
       </c>
       <c r="I1679">
-        <v>0.118772485689187</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1679">
         <v>1.208583174324304</v>
       </c>
       <c r="K1679">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="L1679">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="M1679">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="N1679">
-        <v>4.61</v>
+        <v>4.85</v>
       </c>
       <c r="O1679">
         <v>1</v>
@@ -86066,46 +86066,46 @@
     </row>
     <row r="1680" spans="1:16">
       <c r="A1680" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1680" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C1680">
-        <v>1.047563823081144</v>
+        <v>1.060937130973033</v>
       </c>
       <c r="D1680" t="s">
-        <v>445</v>
+        <v>263</v>
       </c>
       <c r="E1680">
-        <v>1.127563823081144</v>
+        <v>1.148422140513575</v>
       </c>
       <c r="F1680">
         <v>1</v>
       </c>
       <c r="G1680">
-        <v>0.008492436176918855</v>
+        <v>0.008119062869026967</v>
       </c>
       <c r="H1680">
-        <v>0.008572436176918854</v>
+        <v>0.008351577859486425</v>
       </c>
       <c r="I1680">
-        <v>0.08000000000000007</v>
+        <v>0.08748500954054172</v>
       </c>
       <c r="J1680">
         <v>1.208583174324304</v>
       </c>
       <c r="K1680">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="L1680">
-        <v>4.77</v>
+        <v>4.59</v>
       </c>
       <c r="M1680">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="N1680">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="O1680">
         <v>1</v>
@@ -86116,46 +86116,46 @@
     </row>
     <row r="1681" spans="1:16">
       <c r="A1681" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1681" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C1681">
-        <v>1.060937130973033</v>
+        <v>1.048422140513575</v>
       </c>
       <c r="D1681" t="s">
-        <v>263</v>
+        <v>444</v>
       </c>
       <c r="E1681">
-        <v>1.148422140513575</v>
+        <v>1.180448010418985</v>
       </c>
       <c r="F1681">
         <v>1</v>
       </c>
       <c r="G1681">
-        <v>0.008119062869026967</v>
+        <v>0.008251577859486424</v>
       </c>
       <c r="H1681">
-        <v>0.008351577859486425</v>
+        <v>0.008939551989581015</v>
       </c>
       <c r="I1681">
-        <v>0.08748500954054172</v>
+        <v>0.1320258699054095</v>
       </c>
       <c r="J1681">
         <v>1.208583174324304</v>
       </c>
       <c r="K1681">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="L1681">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="M1681">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="N1681">
-        <v>4.75</v>
+        <v>5.06</v>
       </c>
       <c r="O1681">
         <v>1</v>
@@ -86166,13 +86166,13 @@
     </row>
     <row r="1682" spans="1:16">
       <c r="A1682" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1682" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1682">
-        <v>1.048422140513575</v>
+        <v>1.044619673905472</v>
       </c>
       <c r="D1682" t="s">
         <v>444</v>
@@ -86184,22 +86184,22 @@
         <v>1</v>
       </c>
       <c r="G1682">
-        <v>0.008251577859486424</v>
+        <v>0.008755380326094528</v>
       </c>
       <c r="H1682">
         <v>0.008939551989581015</v>
       </c>
       <c r="I1682">
-        <v>0.1320258699054095</v>
+        <v>0.1358283365135131</v>
       </c>
       <c r="J1682">
         <v>1.208583174324304</v>
       </c>
       <c r="K1682">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1682">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1682">
         <v>3.21</v>
@@ -86216,96 +86216,96 @@
     </row>
     <row r="1683" spans="1:16">
       <c r="A1683" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1683" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C1683">
-        <v>1.044619673905472</v>
+        <v>0.9916025460884326</v>
       </c>
       <c r="D1683" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E1683">
-        <v>1.180448010418985</v>
+        <v>1.071602546088433</v>
       </c>
       <c r="F1683">
         <v>1</v>
       </c>
       <c r="G1683">
-        <v>0.008755380326094528</v>
+        <v>0.008548397453911566</v>
       </c>
       <c r="H1683">
-        <v>0.008939551989581015</v>
+        <v>0.008628397453911568</v>
       </c>
       <c r="I1683">
-        <v>0.1358283365135131</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1683">
-        <v>1.208583174324304</v>
+        <v>1.226752420101158</v>
       </c>
       <c r="K1683">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="L1683">
-        <v>4.9</v>
+        <v>4.77</v>
       </c>
       <c r="M1683">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="N1683">
-        <v>5.06</v>
+        <v>4.85</v>
       </c>
       <c r="O1683">
         <v>1</v>
       </c>
       <c r="P1683" t="s">
-        <v>250</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1684" spans="1:16">
       <c r="A1684" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1684" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1684">
-        <v>0.9916025460884326</v>
+        <v>0.9942777880985489</v>
       </c>
       <c r="D1684" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E1684">
-        <v>1.071602546088433</v>
+        <v>1.122124731475282</v>
       </c>
       <c r="F1684">
         <v>1</v>
       </c>
       <c r="G1684">
-        <v>0.008548397453911566</v>
+        <v>0.008305722211901453</v>
       </c>
       <c r="H1684">
-        <v>0.008628397453911568</v>
+        <v>0.008997875268524717</v>
       </c>
       <c r="I1684">
-        <v>0.08000000000000007</v>
+        <v>0.1278469433767331</v>
       </c>
       <c r="J1684">
         <v>1.226752420101158</v>
       </c>
       <c r="K1684">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="L1684">
-        <v>4.77</v>
+        <v>4.65</v>
       </c>
       <c r="M1684">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1684">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1684">
         <v>1</v>
@@ -86316,13 +86316,13 @@
     </row>
     <row r="1685" spans="1:16">
       <c r="A1685" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1685" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1685">
-        <v>0.9942777880985489</v>
+        <v>0.9866597798773058</v>
       </c>
       <c r="D1685" t="s">
         <v>444</v>
@@ -86334,22 +86334,22 @@
         <v>1</v>
       </c>
       <c r="G1685">
-        <v>0.008305722211901453</v>
+        <v>0.008813340220122695</v>
       </c>
       <c r="H1685">
         <v>0.008997875268524717</v>
       </c>
       <c r="I1685">
-        <v>0.1278469433767331</v>
+        <v>0.1354649515979762</v>
       </c>
       <c r="J1685">
         <v>1.226752420101158</v>
       </c>
       <c r="K1685">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1685">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1685">
         <v>3.21</v>
@@ -86366,96 +86366,96 @@
     </row>
     <row r="1686" spans="1:16">
       <c r="A1686" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1686" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C1686">
-        <v>0.9866597798773058</v>
+        <v>0.9133372588035056</v>
       </c>
       <c r="D1686" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E1686">
-        <v>1.122124731475282</v>
+        <v>0.9933372588035057</v>
       </c>
       <c r="F1686">
         <v>1</v>
       </c>
       <c r="G1686">
-        <v>0.008813340220122695</v>
+        <v>0.008626662741196495</v>
       </c>
       <c r="H1686">
-        <v>0.008997875268524717</v>
+        <v>0.008706662741196493</v>
       </c>
       <c r="I1686">
-        <v>0.1354649515979762</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1686">
-        <v>1.226752420101158</v>
+        <v>1.252163227661199</v>
       </c>
       <c r="K1686">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="L1686">
-        <v>4.9</v>
+        <v>4.77</v>
       </c>
       <c r="M1686">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="N1686">
-        <v>5.06</v>
+        <v>4.85</v>
       </c>
       <c r="O1686">
         <v>1</v>
       </c>
       <c r="P1686" t="s">
-        <v>439</v>
+        <v>256</v>
       </c>
     </row>
     <row r="1687" spans="1:16">
       <c r="A1687" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1687" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C1687">
-        <v>0.9133372588035056</v>
+        <v>0.9160319492930138</v>
       </c>
       <c r="D1687" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E1687">
-        <v>0.9933372588035057</v>
+        <v>0.9835103170164023</v>
       </c>
       <c r="F1687">
         <v>1</v>
       </c>
       <c r="G1687">
-        <v>0.008626662741196495</v>
+        <v>0.008403968050706987</v>
       </c>
       <c r="H1687">
-        <v>0.008706662741196493</v>
+        <v>0.008496489682983598</v>
       </c>
       <c r="I1687">
-        <v>0.08000000000000007</v>
+        <v>0.06747836772338855</v>
       </c>
       <c r="J1687">
         <v>1.252163227661199</v>
       </c>
       <c r="K1687">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="L1687">
-        <v>4.77</v>
+        <v>4.66</v>
       </c>
       <c r="M1687">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N1687">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
       <c r="O1687">
         <v>1</v>
@@ -86466,46 +86466,46 @@
     </row>
     <row r="1688" spans="1:16">
       <c r="A1688" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1688" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1688">
-        <v>0.9160319492930138</v>
+        <v>1.018553581569626</v>
       </c>
       <c r="D1688" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E1688">
-        <v>0.9835103170164023</v>
+        <v>0.971075213846238</v>
       </c>
       <c r="F1688">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1688">
-        <v>0.008403968050706987</v>
+        <v>0.008481446418430374</v>
       </c>
       <c r="H1688">
-        <v>0.008496489682983598</v>
+        <v>0.008408924786153764</v>
       </c>
       <c r="I1688">
-        <v>0.06747836772338855</v>
+        <v>0.04747836772338809</v>
       </c>
       <c r="J1688">
         <v>1.252163227661199</v>
       </c>
       <c r="K1688">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1688">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1688">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N1688">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="O1688">
         <v>1</v>
@@ -86516,31 +86516,31 @@
     </row>
     <row r="1689" spans="1:16">
       <c r="A1689" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1689" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C1689">
-        <v>1.018553581569626</v>
+        <v>0.9185535815696264</v>
       </c>
       <c r="D1689" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E1689">
-        <v>0.971075213846238</v>
+        <v>1.04055603920755</v>
       </c>
       <c r="F1689">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1689">
-        <v>0.008481446418430374</v>
+        <v>0.008381446418430376</v>
       </c>
       <c r="H1689">
-        <v>0.008408924786153764</v>
+        <v>0.00907944396079245</v>
       </c>
       <c r="I1689">
-        <v>0.04747836772338809</v>
+        <v>0.1220024576379233</v>
       </c>
       <c r="J1689">
         <v>1.252163227661199</v>
@@ -86549,13 +86549,13 @@
         <v>2.98</v>
       </c>
       <c r="L1689">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="M1689">
-        <v>2.97</v>
+        <v>3.21</v>
       </c>
       <c r="N1689">
-        <v>4.69</v>
+        <v>5.06</v>
       </c>
       <c r="O1689">
         <v>1</v>
@@ -86566,13 +86566,13 @@
     </row>
     <row r="1690" spans="1:16">
       <c r="A1690" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1690" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1690">
-        <v>0.9185535815696264</v>
+        <v>0.9055993037607744</v>
       </c>
       <c r="D1690" t="s">
         <v>444</v>
@@ -86584,22 +86584,22 @@
         <v>1</v>
       </c>
       <c r="G1690">
-        <v>0.008381446418430376</v>
+        <v>0.008894400696239228</v>
       </c>
       <c r="H1690">
         <v>0.00907944396079245</v>
       </c>
       <c r="I1690">
-        <v>0.1220024576379233</v>
+        <v>0.1349567354467753</v>
       </c>
       <c r="J1690">
         <v>1.252163227661199</v>
       </c>
       <c r="K1690">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1690">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1690">
         <v>3.21</v>
@@ -86616,96 +86616,96 @@
     </row>
     <row r="1691" spans="1:16">
       <c r="A1691" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1691" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C1691">
-        <v>0.9055993037607744</v>
+        <v>0.8640876530634416</v>
       </c>
       <c r="D1691" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E1691">
-        <v>1.04055603920755</v>
+        <v>0.9440876530634417</v>
       </c>
       <c r="F1691">
         <v>1</v>
       </c>
       <c r="G1691">
-        <v>0.008894400696239228</v>
+        <v>0.008675912346936559</v>
       </c>
       <c r="H1691">
-        <v>0.00907944396079245</v>
+        <v>0.008755912346936559</v>
       </c>
       <c r="I1691">
-        <v>0.1349567354467753</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1691">
-        <v>1.252163227661199</v>
+        <v>1.268153359394986</v>
       </c>
       <c r="K1691">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="L1691">
-        <v>4.9</v>
+        <v>4.77</v>
       </c>
       <c r="M1691">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="N1691">
-        <v>5.06</v>
+        <v>4.85</v>
       </c>
       <c r="O1691">
         <v>1</v>
       </c>
       <c r="P1691" t="s">
-        <v>256</v>
+        <v>569</v>
       </c>
     </row>
     <row r="1692" spans="1:16">
       <c r="A1692" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1692" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C1692">
-        <v>0.8640876530634416</v>
+        <v>0.8682214554089906</v>
       </c>
       <c r="D1692" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E1692">
-        <v>0.9440876530634417</v>
+        <v>0.9355399218150415</v>
       </c>
       <c r="F1692">
         <v>1</v>
       </c>
       <c r="G1692">
-        <v>0.008675912346936559</v>
+        <v>0.00845177854459101</v>
       </c>
       <c r="H1692">
-        <v>0.008755912346936559</v>
+        <v>0.008544460078184959</v>
       </c>
       <c r="I1692">
-        <v>0.08000000000000007</v>
+        <v>0.06731846640605088</v>
       </c>
       <c r="J1692">
         <v>1.268153359394986</v>
       </c>
       <c r="K1692">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="L1692">
-        <v>4.77</v>
+        <v>4.66</v>
       </c>
       <c r="M1692">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N1692">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
       <c r="O1692">
         <v>1</v>
@@ -86716,46 +86716,46 @@
     </row>
     <row r="1693" spans="1:16">
       <c r="A1693" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1693" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1693">
-        <v>0.8682214554089906</v>
+        <v>0.970902989002941</v>
       </c>
       <c r="D1693" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E1693">
-        <v>0.9355399218150415</v>
+        <v>0.9201768546271412</v>
       </c>
       <c r="F1693">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1693">
-        <v>0.00845177854459101</v>
+        <v>0.00852909701099706</v>
       </c>
       <c r="H1693">
-        <v>0.008544460078184959</v>
+        <v>0.00857982314537286</v>
       </c>
       <c r="I1693">
-        <v>0.06731846640605088</v>
+        <v>0.05072613437579987</v>
       </c>
       <c r="J1693">
         <v>1.268153359394986</v>
       </c>
       <c r="K1693">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1693">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1693">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="N1693">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="O1693">
         <v>1</v>
@@ -86766,31 +86766,31 @@
     </row>
     <row r="1694" spans="1:16">
       <c r="A1694" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1694" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C1694">
-        <v>0.970902989002941</v>
+        <v>0.8709029890029414</v>
       </c>
       <c r="D1694" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E1694">
-        <v>0.9201768546271412</v>
+        <v>0.9892277163420937</v>
       </c>
       <c r="F1694">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1694">
-        <v>0.00852909701099706</v>
+        <v>0.008429097010997059</v>
       </c>
       <c r="H1694">
-        <v>0.00857982314537286</v>
+        <v>0.009130772283657905</v>
       </c>
       <c r="I1694">
-        <v>0.05072613437579987</v>
+        <v>0.1183247273391523</v>
       </c>
       <c r="J1694">
         <v>1.268153359394986</v>
@@ -86799,13 +86799,13 @@
         <v>2.98</v>
       </c>
       <c r="L1694">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="M1694">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N1694">
-        <v>4.75</v>
+        <v>5.06</v>
       </c>
       <c r="O1694">
         <v>1</v>
@@ -86816,13 +86816,13 @@
     </row>
     <row r="1695" spans="1:16">
       <c r="A1695" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1695" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1695">
-        <v>0.8709029890029414</v>
+        <v>0.8545907835299937</v>
       </c>
       <c r="D1695" t="s">
         <v>444</v>
@@ -86834,22 +86834,22 @@
         <v>1</v>
       </c>
       <c r="G1695">
-        <v>0.008429097010997059</v>
+        <v>0.008945409216470008</v>
       </c>
       <c r="H1695">
         <v>0.009130772283657905</v>
       </c>
       <c r="I1695">
-        <v>0.1183247273391523</v>
+        <v>0.1346369328121</v>
       </c>
       <c r="J1695">
         <v>1.268153359394986</v>
       </c>
       <c r="K1695">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1695">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1695">
         <v>3.21</v>
@@ -86866,96 +86866,96 @@
     </row>
     <row r="1696" spans="1:16">
       <c r="A1696" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1696" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C1696">
-        <v>0.8545907835299937</v>
+        <v>0.8361486892860226</v>
       </c>
       <c r="D1696" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E1696">
-        <v>0.9892277163420937</v>
+        <v>0.9161486892860227</v>
       </c>
       <c r="F1696">
         <v>1</v>
       </c>
       <c r="G1696">
-        <v>0.008945409216470008</v>
+        <v>0.008703851310713976</v>
       </c>
       <c r="H1696">
-        <v>0.009130772283657905</v>
+        <v>0.008783851310713978</v>
       </c>
       <c r="I1696">
-        <v>0.1346369328121</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1696">
-        <v>1.268153359394986</v>
+        <v>1.277224451530512</v>
       </c>
       <c r="K1696">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="L1696">
-        <v>4.9</v>
+        <v>4.77</v>
       </c>
       <c r="M1696">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="N1696">
-        <v>5.06</v>
+        <v>4.85</v>
       </c>
       <c r="O1696">
         <v>1</v>
       </c>
       <c r="P1696" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="1697" spans="1:16">
       <c r="A1697" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1697" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C1697">
-        <v>0.8361486892860226</v>
+        <v>0.841098889923769</v>
       </c>
       <c r="D1697" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E1697">
-        <v>0.9161486892860227</v>
+        <v>0.9083266454084642</v>
       </c>
       <c r="F1697">
         <v>1</v>
       </c>
       <c r="G1697">
-        <v>0.008703851310713976</v>
+        <v>0.008478901110076232</v>
       </c>
       <c r="H1697">
-        <v>0.008783851310713978</v>
+        <v>0.008571673354591535</v>
       </c>
       <c r="I1697">
-        <v>0.08000000000000007</v>
+        <v>0.06722775548469517</v>
       </c>
       <c r="J1697">
         <v>1.277224451530512</v>
       </c>
       <c r="K1697">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="L1697">
-        <v>4.77</v>
+        <v>4.66</v>
       </c>
       <c r="M1697">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N1697">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
       <c r="O1697">
         <v>1</v>
@@ -86966,46 +86966,46 @@
     </row>
     <row r="1698" spans="1:16">
       <c r="A1698" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1698" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1698">
-        <v>0.841098889923769</v>
+        <v>0.9438711344390742</v>
       </c>
       <c r="D1698" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E1698">
-        <v>0.9083266454084642</v>
+        <v>0.8927821563778537</v>
       </c>
       <c r="F1698">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1698">
-        <v>0.008478901110076232</v>
+        <v>0.008556128865560925</v>
       </c>
       <c r="H1698">
-        <v>0.008571673354591535</v>
+        <v>0.008607217843622146</v>
       </c>
       <c r="I1698">
-        <v>0.06722775548469517</v>
+        <v>0.05108897806122048</v>
       </c>
       <c r="J1698">
         <v>1.277224451530512</v>
       </c>
       <c r="K1698">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1698">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1698">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="N1698">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="O1698">
         <v>1</v>
@@ -87016,31 +87016,31 @@
     </row>
     <row r="1699" spans="1:16">
       <c r="A1699" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1699" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C1699">
-        <v>0.9438711344390742</v>
+        <v>0.8438711344390746</v>
       </c>
       <c r="D1699" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E1699">
-        <v>0.8927821563778537</v>
+        <v>0.9601095105870563</v>
       </c>
       <c r="F1699">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1699">
-        <v>0.008556128865560925</v>
+        <v>0.008456128865560925</v>
       </c>
       <c r="H1699">
-        <v>0.008607217843622146</v>
+        <v>0.009159890489412943</v>
       </c>
       <c r="I1699">
-        <v>0.05108897806122048</v>
+        <v>0.1162383761479817</v>
       </c>
       <c r="J1699">
         <v>1.277224451530512</v>
@@ -87049,13 +87049,13 @@
         <v>2.98</v>
       </c>
       <c r="L1699">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="M1699">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N1699">
-        <v>4.75</v>
+        <v>5.06</v>
       </c>
       <c r="O1699">
         <v>1</v>
@@ -87066,13 +87066,13 @@
     </row>
     <row r="1700" spans="1:16">
       <c r="A1700" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1700" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1700">
-        <v>0.8438711344390746</v>
+        <v>0.8256539996176668</v>
       </c>
       <c r="D1700" t="s">
         <v>444</v>
@@ -87084,22 +87084,22 @@
         <v>1</v>
       </c>
       <c r="G1700">
-        <v>0.008456128865560925</v>
+        <v>0.008974346000382332</v>
       </c>
       <c r="H1700">
         <v>0.009159890489412943</v>
       </c>
       <c r="I1700">
-        <v>0.1162383761479817</v>
+        <v>0.1344555109693895</v>
       </c>
       <c r="J1700">
         <v>1.277224451530512</v>
       </c>
       <c r="K1700">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1700">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1700">
         <v>3.21</v>
@@ -87116,96 +87116,96 @@
     </row>
     <row r="1701" spans="1:16">
       <c r="A1701" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1701" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1701">
-        <v>0.8256539996176668</v>
+        <v>0.8509968968061137</v>
       </c>
       <c r="D1701" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E1701">
-        <v>0.9601095105870563</v>
+        <v>0.9182577559927565</v>
       </c>
       <c r="F1701">
         <v>1</v>
       </c>
       <c r="G1701">
-        <v>0.008974346000382332</v>
+        <v>0.008469003103193887</v>
       </c>
       <c r="H1701">
-        <v>0.009159890489412943</v>
+        <v>0.008561742244007244</v>
       </c>
       <c r="I1701">
-        <v>0.1344555109693895</v>
+        <v>0.06726085918664282</v>
       </c>
       <c r="J1701">
-        <v>1.277224451530512</v>
+        <v>1.273914081335748</v>
       </c>
       <c r="K1701">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="L1701">
-        <v>4.9</v>
+        <v>4.66</v>
       </c>
       <c r="M1701">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1701">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1701">
         <v>1</v>
       </c>
       <c r="P1701" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1702" spans="1:16">
       <c r="A1702" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1702" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1702">
-        <v>0.8509968968061137</v>
+        <v>0.9537360376194712</v>
       </c>
       <c r="D1702" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1702">
-        <v>0.9182577559927565</v>
+        <v>0.8537360376194716</v>
       </c>
       <c r="F1702">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1702">
-        <v>0.008469003103193887</v>
+        <v>0.00854626396238053</v>
       </c>
       <c r="H1702">
-        <v>0.008561742244007244</v>
+        <v>0.00844626396238053</v>
       </c>
       <c r="I1702">
-        <v>0.06726085918664282</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1702">
         <v>1.273914081335748</v>
       </c>
       <c r="K1702">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1702">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1702">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1702">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1702">
         <v>1</v>
@@ -87216,46 +87216,46 @@
     </row>
     <row r="1703" spans="1:16">
       <c r="A1703" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1703" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1703">
-        <v>0.9537360376194712</v>
+        <v>0.8362140805389648</v>
       </c>
       <c r="D1703" t="s">
-        <v>258</v>
+        <v>444</v>
       </c>
       <c r="E1703">
-        <v>0.8537360376194716</v>
+        <v>0.9707357989122487</v>
       </c>
       <c r="F1703">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1703">
-        <v>0.00854626396238053</v>
+        <v>0.008963785919461035</v>
       </c>
       <c r="H1703">
-        <v>0.00844626396238053</v>
+        <v>0.00914926420108775</v>
       </c>
       <c r="I1703">
-        <v>0.09999999999999964</v>
+        <v>0.1345217183732839</v>
       </c>
       <c r="J1703">
         <v>1.273914081335748</v>
       </c>
       <c r="K1703">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1703">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="M1703">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="N1703">
-        <v>4.65</v>
+        <v>5.06</v>
       </c>
       <c r="O1703">
         <v>1</v>
@@ -87266,96 +87266,96 @@
     </row>
     <row r="1704" spans="1:16">
       <c r="A1704" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1704" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1704">
-        <v>0.8362140805389648</v>
+        <v>0.8399183689206069</v>
       </c>
       <c r="D1704" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E1704">
-        <v>0.9707357989122487</v>
+        <v>0.9071421761745224</v>
       </c>
       <c r="F1704">
         <v>1</v>
       </c>
       <c r="G1704">
-        <v>0.008963785919461035</v>
+        <v>0.008480081631079394</v>
       </c>
       <c r="H1704">
-        <v>0.00914926420108775</v>
+        <v>0.008572857823825478</v>
       </c>
       <c r="I1704">
-        <v>0.1345217183732839</v>
+        <v>0.06722380725391552</v>
       </c>
       <c r="J1704">
-        <v>1.273914081335748</v>
+        <v>1.277619274608493</v>
       </c>
       <c r="K1704">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="L1704">
-        <v>4.9</v>
+        <v>4.66</v>
       </c>
       <c r="M1704">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1704">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1704">
         <v>1</v>
       </c>
       <c r="P1704" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="1705" spans="1:16">
       <c r="A1705" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1705" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1705">
-        <v>0.8399183689206069</v>
+        <v>0.9426945616666917</v>
       </c>
       <c r="D1705" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1705">
-        <v>0.9071421761745224</v>
+        <v>0.8426945616666921</v>
       </c>
       <c r="F1705">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1705">
-        <v>0.008480081631079394</v>
+        <v>0.008557305438333308</v>
       </c>
       <c r="H1705">
-        <v>0.008572857823825478</v>
+        <v>0.008457305438333309</v>
       </c>
       <c r="I1705">
-        <v>0.06722380725391552</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1705">
         <v>1.277619274608493</v>
       </c>
       <c r="K1705">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1705">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1705">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1705">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1705">
         <v>1</v>
@@ -87366,96 +87366,96 @@
     </row>
     <row r="1706" spans="1:16">
       <c r="A1706" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1706" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1706">
-        <v>0.9426945616666917</v>
+        <v>0.8064988749071667</v>
       </c>
       <c r="D1706" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1706">
-        <v>0.8426945616666921</v>
+        <v>0.8736109112780941</v>
       </c>
       <c r="F1706">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1706">
-        <v>0.008557305438333308</v>
+        <v>0.008513501125092833</v>
       </c>
       <c r="H1706">
-        <v>0.008457305438333309</v>
+        <v>0.008606389088721907</v>
       </c>
       <c r="I1706">
-        <v>0.09999999999999964</v>
+        <v>0.06711203637092744</v>
       </c>
       <c r="J1706">
-        <v>1.277619274608493</v>
+        <v>1.288796362907302</v>
       </c>
       <c r="K1706">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1706">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1706">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1706">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1706">
         <v>1</v>
       </c>
       <c r="P1706" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1707" spans="1:16">
       <c r="A1707" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1707" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1707">
-        <v>0.8064988749071667</v>
+        <v>0.90938683853624</v>
       </c>
       <c r="D1707" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1707">
-        <v>0.8736109112780941</v>
+        <v>0.8093868385362404</v>
       </c>
       <c r="F1707">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1707">
-        <v>0.008513501125092833</v>
+        <v>0.008590613161463761</v>
       </c>
       <c r="H1707">
-        <v>0.008606389088721907</v>
+        <v>0.00849061316146376</v>
       </c>
       <c r="I1707">
-        <v>0.06711203637092744</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1707">
         <v>1.288796362907302</v>
       </c>
       <c r="K1707">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1707">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1707">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1707">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1707">
         <v>1</v>
@@ -87466,96 +87466,96 @@
     </row>
     <row r="1708" spans="1:16">
       <c r="A1708" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1708" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1708">
-        <v>0.90938683853624</v>
+        <v>0.7862584850929837</v>
       </c>
       <c r="D1708" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1708">
-        <v>0.8093868385362404</v>
+        <v>0.8533028278524921</v>
       </c>
       <c r="F1708">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1708">
-        <v>0.008590613161463761</v>
+        <v>0.008533741514907017</v>
       </c>
       <c r="H1708">
-        <v>0.00849061316146376</v>
+        <v>0.008626697172147509</v>
       </c>
       <c r="I1708">
-        <v>0.09999999999999964</v>
+        <v>0.06704434275950844</v>
       </c>
       <c r="J1708">
-        <v>1.288796362907302</v>
+        <v>1.295565724049169</v>
       </c>
       <c r="K1708">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1708">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1708">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1708">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1708">
         <v>1</v>
       </c>
       <c r="P1708" t="s">
-        <v>573</v>
+        <v>259</v>
       </c>
     </row>
     <row r="1709" spans="1:16">
       <c r="A1709" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1709" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1709">
-        <v>0.7862584850929837</v>
+        <v>0.8892141423334752</v>
       </c>
       <c r="D1709" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1709">
-        <v>0.8533028278524921</v>
+        <v>0.7892141423334755</v>
       </c>
       <c r="F1709">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1709">
-        <v>0.008533741514907017</v>
+        <v>0.008610785857666524</v>
       </c>
       <c r="H1709">
-        <v>0.008626697172147509</v>
+        <v>0.008510785857666524</v>
       </c>
       <c r="I1709">
-        <v>0.06704434275950844</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1709">
         <v>1.295565724049169</v>
       </c>
       <c r="K1709">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1709">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1709">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1709">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1709">
         <v>1</v>
@@ -87566,96 +87566,96 @@
     </row>
     <row r="1710" spans="1:16">
       <c r="A1710" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1710" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1710">
-        <v>0.8892141423334752</v>
+        <v>0.7524917367489325</v>
       </c>
       <c r="D1710" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1710">
-        <v>0.7892141423334755</v>
+        <v>0.819423147239732</v>
       </c>
       <c r="F1710">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1710">
-        <v>0.008610785857666524</v>
+        <v>0.008567508263251068</v>
       </c>
       <c r="H1710">
-        <v>0.008510785857666524</v>
+        <v>0.008660576852760268</v>
       </c>
       <c r="I1710">
-        <v>0.09999999999999964</v>
+        <v>0.06693141049079943</v>
       </c>
       <c r="J1710">
-        <v>1.295565724049169</v>
+        <v>1.306858950920089</v>
       </c>
       <c r="K1710">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1710">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1710">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1710">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1710">
         <v>1</v>
       </c>
       <c r="P1710" t="s">
-        <v>259</v>
+        <v>574</v>
       </c>
     </row>
     <row r="1711" spans="1:16">
       <c r="A1711" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1711" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1711">
-        <v>0.7524917367489325</v>
+        <v>0.8555603262581335</v>
       </c>
       <c r="D1711" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1711">
-        <v>0.819423147239732</v>
+        <v>0.7555603262581339</v>
       </c>
       <c r="F1711">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1711">
-        <v>0.008567508263251068</v>
+        <v>0.008644439673741866</v>
       </c>
       <c r="H1711">
-        <v>0.008660576852760268</v>
+        <v>0.008544439673741867</v>
       </c>
       <c r="I1711">
-        <v>0.06693141049079943</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1711">
         <v>1.306858950920089</v>
       </c>
       <c r="K1711">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1711">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1711">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1711">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1711">
         <v>1</v>
@@ -87666,96 +87666,96 @@
     </row>
     <row r="1712" spans="1:16">
       <c r="A1712" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1712" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1712">
-        <v>0.8555603262581335</v>
+        <v>0.747940275032922</v>
       </c>
       <c r="D1712" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1712">
-        <v>0.7555603262581339</v>
+        <v>0.8148564632437347</v>
       </c>
       <c r="F1712">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1712">
-        <v>0.008644439673741866</v>
+        <v>0.008572059724967078</v>
       </c>
       <c r="H1712">
-        <v>0.008544439673741867</v>
+        <v>0.008665143536756265</v>
       </c>
       <c r="I1712">
-        <v>0.09999999999999964</v>
+        <v>0.06691618821081269</v>
       </c>
       <c r="J1712">
-        <v>1.306858950920089</v>
+        <v>1.308381178918755</v>
       </c>
       <c r="K1712">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1712">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1712">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1712">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1712">
         <v>1</v>
       </c>
       <c r="P1712" t="s">
-        <v>574</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1713" spans="1:16">
       <c r="A1713" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1713" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1713">
-        <v>0.747940275032922</v>
+        <v>0.8510240868221097</v>
       </c>
       <c r="D1713" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1713">
-        <v>0.8148564632437347</v>
+        <v>0.7510240868221101</v>
       </c>
       <c r="F1713">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1713">
-        <v>0.008572059724967078</v>
+        <v>0.008648975913177891</v>
       </c>
       <c r="H1713">
-        <v>0.008665143536756265</v>
+        <v>0.008548975913177891</v>
       </c>
       <c r="I1713">
-        <v>0.06691618821081269</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1713">
         <v>1.308381178918755</v>
       </c>
       <c r="K1713">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1713">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1713">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1713">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1713">
         <v>1</v>
@@ -87766,96 +87766,96 @@
     </row>
     <row r="1714" spans="1:16">
       <c r="A1714" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1714" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1714">
-        <v>0.8510240868221097</v>
+        <v>0.7508817338992388</v>
       </c>
       <c r="D1714" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1714">
-        <v>0.7510240868221101</v>
+        <v>0.817807759765123</v>
       </c>
       <c r="F1714">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1714">
-        <v>0.008648975913177891</v>
+        <v>0.008569118266100762</v>
       </c>
       <c r="H1714">
-        <v>0.008548975913177891</v>
+        <v>0.008662192240234876</v>
       </c>
       <c r="I1714">
-        <v>0.09999999999999964</v>
+        <v>0.06692602586588414</v>
       </c>
       <c r="J1714">
-        <v>1.308381178918755</v>
+        <v>1.307397413411626</v>
       </c>
       <c r="K1714">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1714">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1714">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1714">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1714">
         <v>1</v>
       </c>
       <c r="P1714" t="s">
-        <v>445</v>
+        <v>575</v>
       </c>
     </row>
     <row r="1715" spans="1:16">
       <c r="A1715" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1715" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1715">
-        <v>0.7508817338992388</v>
+        <v>0.8539557080333555</v>
       </c>
       <c r="D1715" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1715">
-        <v>0.817807759765123</v>
+        <v>0.7539557080333559</v>
       </c>
       <c r="F1715">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1715">
-        <v>0.008569118266100762</v>
+        <v>0.008646044291966644</v>
       </c>
       <c r="H1715">
-        <v>0.008662192240234876</v>
+        <v>0.008546044291966644</v>
       </c>
       <c r="I1715">
-        <v>0.06692602586588414</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1715">
         <v>1.307397413411626</v>
       </c>
       <c r="K1715">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1715">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1715">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1715">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1715">
         <v>1</v>
@@ -87866,96 +87866,96 @@
     </row>
     <row r="1716" spans="1:16">
       <c r="A1716" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1716" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1716">
-        <v>0.8539557080333555</v>
+        <v>0.7342938724207762</v>
       </c>
       <c r="D1716" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1716">
-        <v>0.7539557080333559</v>
+        <v>0.8011644204890738</v>
       </c>
       <c r="F1716">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1716">
-        <v>0.008646044291966644</v>
+        <v>0.008585706127579223</v>
       </c>
       <c r="H1716">
-        <v>0.008546044291966644</v>
+        <v>0.008678835579510928</v>
       </c>
       <c r="I1716">
-        <v>0.09999999999999964</v>
+        <v>0.06687054806829762</v>
       </c>
       <c r="J1716">
-        <v>1.307397413411626</v>
+        <v>1.312945193170309</v>
       </c>
       <c r="K1716">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1716">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1716">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1716">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1716">
         <v>1</v>
       </c>
       <c r="P1716" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="1717" spans="1:16">
       <c r="A1717" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1717" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1717">
-        <v>0.7342938724207762</v>
+        <v>0.8374233243524793</v>
       </c>
       <c r="D1717" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1717">
-        <v>0.8011644204890738</v>
+        <v>0.7374233243524797</v>
       </c>
       <c r="F1717">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1717">
-        <v>0.008585706127579223</v>
+        <v>0.008662576675647522</v>
       </c>
       <c r="H1717">
-        <v>0.008678835579510928</v>
+        <v>0.008562576675647521</v>
       </c>
       <c r="I1717">
-        <v>0.06687054806829762</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1717">
         <v>1.312945193170309</v>
       </c>
       <c r="K1717">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1717">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1717">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1717">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1717">
         <v>1</v>
@@ -87966,96 +87966,96 @@
     </row>
     <row r="1718" spans="1:16">
       <c r="A1718" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1718" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1718">
-        <v>0.8374233243524793</v>
+        <v>0.7280081951252568</v>
       </c>
       <c r="D1718" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1718">
-        <v>0.7374233243524797</v>
+        <v>0.7948577208614624</v>
       </c>
       <c r="F1718">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1718">
-        <v>0.008662576675647522</v>
+        <v>0.008591991804874743</v>
       </c>
       <c r="H1718">
-        <v>0.008562576675647521</v>
+        <v>0.008685142279138539</v>
       </c>
       <c r="I1718">
-        <v>0.09999999999999964</v>
+        <v>0.06684952573620562</v>
       </c>
       <c r="J1718">
-        <v>1.312945193170309</v>
+        <v>1.315047426379513</v>
       </c>
       <c r="K1718">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1718">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1718">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1718">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1718">
         <v>1</v>
       </c>
       <c r="P1718" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="1719" spans="1:16">
       <c r="A1719" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1719" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1719">
-        <v>0.7280081951252568</v>
+        <v>0.8311586693890525</v>
       </c>
       <c r="D1719" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1719">
-        <v>0.7948577208614624</v>
+        <v>0.7311586693890528</v>
       </c>
       <c r="F1719">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1719">
-        <v>0.008591991804874743</v>
+        <v>0.008668841330610947</v>
       </c>
       <c r="H1719">
-        <v>0.008685142279138539</v>
+        <v>0.008568841330610947</v>
       </c>
       <c r="I1719">
-        <v>0.06684952573620562</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1719">
         <v>1.315047426379513</v>
       </c>
       <c r="K1719">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1719">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1719">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1719">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1719">
         <v>1</v>
@@ -88066,96 +88066,96 @@
     </row>
     <row r="1720" spans="1:16">
       <c r="A1720" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1720" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1720">
-        <v>0.8311586693890525</v>
+        <v>0.7202147488435684</v>
       </c>
       <c r="D1720" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1720">
-        <v>0.7311586693890528</v>
+        <v>0.7870382095420423</v>
       </c>
       <c r="F1720">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1720">
-        <v>0.008668841330610947</v>
+        <v>0.008599785251156431</v>
       </c>
       <c r="H1720">
-        <v>0.008568841330610947</v>
+        <v>0.008692961790457957</v>
       </c>
       <c r="I1720">
-        <v>0.09999999999999964</v>
+        <v>0.06682346069847389</v>
       </c>
       <c r="J1720">
-        <v>1.315047426379513</v>
+        <v>1.317653930152653</v>
       </c>
       <c r="K1720">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1720">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1720">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1720">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1720">
         <v>1</v>
       </c>
       <c r="P1720" t="s">
-        <v>577</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1721" spans="1:16">
       <c r="A1721" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1721" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1721">
-        <v>0.7202147488435684</v>
+        <v>0.8233912881450953</v>
       </c>
       <c r="D1721" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1721">
-        <v>0.7870382095420423</v>
+        <v>0.7233912881450957</v>
       </c>
       <c r="F1721">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1721">
-        <v>0.008599785251156431</v>
+        <v>0.008676608711854904</v>
       </c>
       <c r="H1721">
-        <v>0.008692961790457957</v>
+        <v>0.008576608711854906</v>
       </c>
       <c r="I1721">
-        <v>0.06682346069847389</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1721">
         <v>1.317653930152653</v>
       </c>
       <c r="K1721">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1721">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1721">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1721">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1721">
         <v>1</v>
@@ -88166,96 +88166,96 @@
     </row>
     <row r="1722" spans="1:16">
       <c r="A1722" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1722" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1722">
-        <v>0.8233912881450953</v>
+        <v>0.7246351928069408</v>
       </c>
       <c r="D1722" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1722">
-        <v>0.7233912881450957</v>
+        <v>0.7914734375989374</v>
       </c>
       <c r="F1722">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1722">
-        <v>0.008676608711854904</v>
+        <v>0.00859536480719306</v>
       </c>
       <c r="H1722">
-        <v>0.008576608711854906</v>
+        <v>0.008688526562401062</v>
       </c>
       <c r="I1722">
-        <v>0.09999999999999964</v>
+        <v>0.06683824479199663</v>
       </c>
       <c r="J1722">
-        <v>1.317653930152653</v>
+        <v>1.316175520800354</v>
       </c>
       <c r="K1722">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1722">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1722">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1722">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1722">
         <v>1</v>
       </c>
       <c r="P1722" t="s">
-        <v>257</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1723" spans="1:16">
       <c r="A1723" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1723" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1723">
-        <v>0.7246351928069408</v>
+        <v>0.8277969480149441</v>
       </c>
       <c r="D1723" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1723">
-        <v>0.7914734375989374</v>
+        <v>0.7277969480149444</v>
       </c>
       <c r="F1723">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1723">
-        <v>0.00859536480719306</v>
+        <v>0.008672203051985057</v>
       </c>
       <c r="H1723">
-        <v>0.008688526562401062</v>
+        <v>0.008572203051985056</v>
       </c>
       <c r="I1723">
-        <v>0.06683824479199663</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1723">
         <v>1.316175520800354</v>
       </c>
       <c r="K1723">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1723">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1723">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1723">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1723">
         <v>1</v>
@@ -88266,96 +88266,96 @@
     </row>
     <row r="1724" spans="1:16">
       <c r="A1724" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1724" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1724">
-        <v>0.8277969480149441</v>
+        <v>0.7398440110333406</v>
       </c>
       <c r="D1724" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1724">
-        <v>0.7277969480149444</v>
+        <v>0.8067331214381346</v>
       </c>
       <c r="F1724">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1724">
-        <v>0.008672203051985057</v>
+        <v>0.008580155988966659</v>
       </c>
       <c r="H1724">
-        <v>0.008572203051985056</v>
+        <v>0.008673266878561865</v>
       </c>
       <c r="I1724">
-        <v>0.09999999999999964</v>
+        <v>0.06688911040479395</v>
       </c>
       <c r="J1724">
-        <v>1.316175520800354</v>
+        <v>1.311088959520622</v>
       </c>
       <c r="K1724">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1724">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1724">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1724">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1724">
         <v>1</v>
       </c>
       <c r="P1724" t="s">
-        <v>446</v>
+        <v>578</v>
       </c>
     </row>
     <row r="1725" spans="1:16">
       <c r="A1725" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1725" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1725">
-        <v>0.7398440110333406</v>
+        <v>0.8429549006285466</v>
       </c>
       <c r="D1725" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1725">
-        <v>0.8067331214381346</v>
+        <v>0.742954900628547</v>
       </c>
       <c r="F1725">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1725">
-        <v>0.008580155988966659</v>
+        <v>0.008657045099371454</v>
       </c>
       <c r="H1725">
-        <v>0.008673266878561865</v>
+        <v>0.008557045099371455</v>
       </c>
       <c r="I1725">
-        <v>0.06688911040479395</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1725">
         <v>1.311088959520622</v>
       </c>
       <c r="K1725">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1725">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1725">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1725">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1725">
         <v>1</v>
@@ -88366,96 +88366,96 @@
     </row>
     <row r="1726" spans="1:16">
       <c r="A1726" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1726" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1726">
-        <v>0.8429549006285466</v>
+        <v>0.760654448446985</v>
       </c>
       <c r="D1726" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1726">
-        <v>0.742954900628547</v>
+        <v>0.8276131589769085</v>
       </c>
       <c r="F1726">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1726">
-        <v>0.008657045099371454</v>
+        <v>0.008559345551553016</v>
       </c>
       <c r="H1726">
-        <v>0.008557045099371455</v>
+        <v>0.008652386841023091</v>
       </c>
       <c r="I1726">
-        <v>0.09999999999999964</v>
+        <v>0.06695871052992342</v>
       </c>
       <c r="J1726">
-        <v>1.311088959520622</v>
+        <v>1.304128947007697</v>
       </c>
       <c r="K1726">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1726">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1726">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1726">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1726">
         <v>1</v>
       </c>
       <c r="P1726" t="s">
-        <v>578</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1727" spans="1:16">
       <c r="A1727" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1727" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1727">
-        <v>0.760654448446985</v>
+        <v>0.863695737917062</v>
       </c>
       <c r="D1727" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1727">
-        <v>0.8276131589769085</v>
+        <v>0.7636957379170624</v>
       </c>
       <c r="F1727">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1727">
-        <v>0.008559345551553016</v>
+        <v>0.008636304262082938</v>
       </c>
       <c r="H1727">
-        <v>0.008652386841023091</v>
+        <v>0.008536304262082938</v>
       </c>
       <c r="I1727">
-        <v>0.06695871052992342</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1727">
         <v>1.304128947007697</v>
       </c>
       <c r="K1727">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1727">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1727">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1727">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1727">
         <v>1</v>
@@ -88466,96 +88466,96 @@
     </row>
     <row r="1728" spans="1:16">
       <c r="A1728" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1728" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1728">
-        <v>0.863695737917062</v>
+        <v>0.7913874491098194</v>
       </c>
       <c r="D1728" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1728">
-        <v>0.7636957379170624</v>
+        <v>0.858448945595137</v>
       </c>
       <c r="F1728">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1728">
-        <v>0.008636304262082938</v>
+        <v>0.00852861255089018</v>
       </c>
       <c r="H1728">
-        <v>0.008536304262082938</v>
+        <v>0.008621551054404862</v>
       </c>
       <c r="I1728">
-        <v>0.09999999999999964</v>
+        <v>0.06706149648531756</v>
       </c>
       <c r="J1728">
-        <v>1.304128947007697</v>
+        <v>1.293850351468288</v>
       </c>
       <c r="K1728">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1728">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1728">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1728">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1728">
         <v>1</v>
       </c>
       <c r="P1728" t="s">
-        <v>443</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1729" spans="1:16">
       <c r="A1729" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1729" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1729">
-        <v>0.7913874491098194</v>
+        <v>0.8943259526245027</v>
       </c>
       <c r="D1729" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1729">
-        <v>0.858448945595137</v>
+        <v>0.794325952624503</v>
       </c>
       <c r="F1729">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1729">
-        <v>0.00852861255089018</v>
+        <v>0.008605674047375498</v>
       </c>
       <c r="H1729">
-        <v>0.008621551054404862</v>
+        <v>0.008505674047375499</v>
       </c>
       <c r="I1729">
-        <v>0.06706149648531756</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1729">
         <v>1.293850351468288</v>
       </c>
       <c r="K1729">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1729">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1729">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1729">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1729">
         <v>1</v>
@@ -88566,96 +88566,96 @@
     </row>
     <row r="1730" spans="1:16">
       <c r="A1730" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1730" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C1730">
-        <v>0.8943259526245027</v>
+        <v>0.8238855201820487</v>
       </c>
       <c r="D1730" t="s">
-        <v>258</v>
+        <v>447</v>
       </c>
       <c r="E1730">
-        <v>0.794325952624503</v>
+        <v>0.8910557058682764</v>
       </c>
       <c r="F1730">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1730">
-        <v>0.008605674047375498</v>
+        <v>0.008496114479817952</v>
       </c>
       <c r="H1730">
-        <v>0.008505674047375499</v>
+        <v>0.008588944294131725</v>
       </c>
       <c r="I1730">
-        <v>0.09999999999999964</v>
+        <v>0.06717018568622768</v>
       </c>
       <c r="J1730">
-        <v>1.293850351468288</v>
+        <v>1.282981431377241</v>
       </c>
       <c r="K1730">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1730">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="M1730">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N1730">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="O1730">
         <v>1</v>
       </c>
       <c r="P1730" t="s">
-        <v>579</v>
+        <v>260</v>
       </c>
     </row>
     <row r="1731" spans="1:16">
       <c r="A1731" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1731" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C1731">
-        <v>0.8238855201820487</v>
+        <v>0.9267153344958214</v>
       </c>
       <c r="D1731" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E1731">
-        <v>0.8910557058682764</v>
+        <v>0.8267153344958218</v>
       </c>
       <c r="F1731">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1731">
-        <v>0.008496114479817952</v>
+        <v>0.00857328466550418</v>
       </c>
       <c r="H1731">
-        <v>0.008588944294131725</v>
+        <v>0.008473284665504179</v>
       </c>
       <c r="I1731">
-        <v>0.06717018568622768</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="J1731">
         <v>1.282981431377241</v>
       </c>
       <c r="K1731">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="L1731">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="M1731">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N1731">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="O1731">
         <v>1</v>
@@ -88666,34 +88666,34 @@
     </row>
     <row r="1732" spans="1:16">
       <c r="A1732" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1732" t="s">
         <v>263</v>
       </c>
       <c r="C1732">
-        <v>0.9267153344958214</v>
+        <v>0.9437602885510952</v>
       </c>
       <c r="D1732" t="s">
         <v>258</v>
       </c>
       <c r="E1732">
-        <v>0.8267153344958218</v>
+        <v>0.8437602885510955</v>
       </c>
       <c r="F1732">
         <v>-1</v>
       </c>
       <c r="G1732">
-        <v>0.00857328466550418</v>
+        <v>0.008556239711448905</v>
       </c>
       <c r="H1732">
-        <v>0.008473284665504179</v>
+        <v>0.008456239711448906</v>
       </c>
       <c r="I1732">
         <v>0.09999999999999964</v>
       </c>
       <c r="J1732">
-        <v>1.282981431377241</v>
+        <v>1.277261648137216</v>
       </c>
       <c r="K1732">
         <v>2.98</v>
@@ -88711,7 +88711,7 @@
         <v>1</v>
       </c>
       <c r="P1732" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1733" spans="1:16">
@@ -88722,28 +88722,28 @@
         <v>263</v>
       </c>
       <c r="C1733">
-        <v>0.9437602885510952</v>
+        <v>0.9604710066405513</v>
       </c>
       <c r="D1733" t="s">
-        <v>258</v>
+        <v>449</v>
       </c>
       <c r="E1733">
-        <v>0.8437602885510955</v>
+        <v>0.9096048456558603</v>
       </c>
       <c r="F1733">
         <v>-1</v>
       </c>
       <c r="G1733">
-        <v>0.008556239711448905</v>
+        <v>0.00853952899335945</v>
       </c>
       <c r="H1733">
-        <v>0.008456239711448906</v>
+        <v>0.008590395154344141</v>
       </c>
       <c r="I1733">
-        <v>0.09999999999999964</v>
+        <v>0.05086616098469099</v>
       </c>
       <c r="J1733">
-        <v>1.277261648137216</v>
+        <v>1.271654024617265</v>
       </c>
       <c r="K1733">
         <v>2.98</v>
@@ -88752,45 +88752,45 @@
         <v>4.75</v>
       </c>
       <c r="M1733">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="N1733">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="O1733">
         <v>1</v>
       </c>
       <c r="P1733" t="s">
-        <v>262</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1734" spans="1:16">
       <c r="A1734" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1734" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C1734">
-        <v>0.9604710066405513</v>
+        <v>0.8604710066405516</v>
       </c>
       <c r="D1734" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E1734">
-        <v>0.9096048456558603</v>
+        <v>0.97799058097858</v>
       </c>
       <c r="F1734">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1734">
-        <v>0.00853952899335945</v>
+        <v>0.008439528993359448</v>
       </c>
       <c r="H1734">
-        <v>0.008590395154344141</v>
+        <v>0.00914200941902142</v>
       </c>
       <c r="I1734">
-        <v>0.05086616098469099</v>
+        <v>0.1175195743380284</v>
       </c>
       <c r="J1734">
         <v>1.271654024617265</v>
@@ -88799,13 +88799,13 @@
         <v>2.98</v>
       </c>
       <c r="L1734">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="M1734">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N1734">
-        <v>4.75</v>
+        <v>5.06</v>
       </c>
       <c r="O1734">
         <v>1</v>
@@ -88816,13 +88816,13 @@
     </row>
     <row r="1735" spans="1:16">
       <c r="A1735" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1735" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1735">
-        <v>0.8604710066405516</v>
+        <v>0.8434236614709256</v>
       </c>
       <c r="D1735" t="s">
         <v>444</v>
@@ -88834,22 +88834,22 @@
         <v>1</v>
       </c>
       <c r="G1735">
-        <v>0.008439528993359448</v>
+        <v>0.008956576338529075</v>
       </c>
       <c r="H1735">
         <v>0.00914200941902142</v>
       </c>
       <c r="I1735">
-        <v>0.1175195743380284</v>
+        <v>0.1345669195076544</v>
       </c>
       <c r="J1735">
         <v>1.271654024617265</v>
       </c>
       <c r="K1735">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1735">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1735">
         <v>3.21</v>
@@ -88866,40 +88866,40 @@
     </row>
     <row r="1736" spans="1:16">
       <c r="A1736" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1736" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1736">
-        <v>0.8434236614709256</v>
+        <v>0.8778494143553166</v>
       </c>
       <c r="D1736" t="s">
         <v>444</v>
       </c>
       <c r="E1736">
-        <v>0.97799058097858</v>
+        <v>0.99671027519482</v>
       </c>
       <c r="F1736">
         <v>1</v>
       </c>
       <c r="G1736">
-        <v>0.008956576338529075</v>
+        <v>0.008422150585644684</v>
       </c>
       <c r="H1736">
-        <v>0.00914200941902142</v>
+        <v>0.009123289724805179</v>
       </c>
       <c r="I1736">
-        <v>0.1345669195076544</v>
+        <v>0.1188608608395034</v>
       </c>
       <c r="J1736">
-        <v>1.271654024617265</v>
+        <v>1.265822344176068</v>
       </c>
       <c r="K1736">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1736">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1736">
         <v>3.21</v>
@@ -88911,18 +88911,18 @@
         <v>1</v>
       </c>
       <c r="P1736" t="s">
-        <v>447</v>
+        <v>263</v>
       </c>
     </row>
     <row r="1737" spans="1:16">
       <c r="A1737" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1737" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1737">
-        <v>0.8778494143553166</v>
+        <v>0.8620267220783422</v>
       </c>
       <c r="D1737" t="s">
         <v>444</v>
@@ -88934,22 +88934,22 @@
         <v>1</v>
       </c>
       <c r="G1737">
-        <v>0.008422150585644684</v>
+        <v>0.008937973277921658</v>
       </c>
       <c r="H1737">
         <v>0.009123289724805179</v>
       </c>
       <c r="I1737">
-        <v>0.1188608608395034</v>
+        <v>0.1346835531164778</v>
       </c>
       <c r="J1737">
         <v>1.265822344176068</v>
       </c>
       <c r="K1737">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1737">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1737">
         <v>3.21</v>
@@ -88966,34 +88966,34 @@
     </row>
     <row r="1738" spans="1:16">
       <c r="A1738" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1738" t="s">
         <v>261</v>
       </c>
       <c r="C1738">
-        <v>0.8620267220783422</v>
+        <v>0.8836581328456559</v>
       </c>
       <c r="D1738" t="s">
         <v>444</v>
       </c>
       <c r="E1738">
-        <v>0.99671027519482</v>
+        <v>1.018477306092337</v>
       </c>
       <c r="F1738">
         <v>1</v>
       </c>
       <c r="G1738">
-        <v>0.008937973277921658</v>
+        <v>0.008916341867154344</v>
       </c>
       <c r="H1738">
-        <v>0.009123289724805179</v>
+        <v>0.009101522693907661</v>
       </c>
       <c r="I1738">
-        <v>0.1346835531164778</v>
+        <v>0.1348191732466812</v>
       </c>
       <c r="J1738">
-        <v>1.265822344176068</v>
+        <v>1.259041337665939</v>
       </c>
       <c r="K1738">
         <v>3.19</v>
@@ -89011,56 +89011,6 @@
         <v>1</v>
       </c>
       <c r="P1738" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="1739" spans="1:16">
-      <c r="A1739" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1739" t="s">
-        <v>261</v>
-      </c>
-      <c r="C1739">
-        <v>0.8836581328456559</v>
-      </c>
-      <c r="D1739" t="s">
-        <v>444</v>
-      </c>
-      <c r="E1739">
-        <v>1.018477306092337</v>
-      </c>
-      <c r="F1739">
-        <v>1</v>
-      </c>
-      <c r="G1739">
-        <v>0.008916341867154344</v>
-      </c>
-      <c r="H1739">
-        <v>0.009101522693907661</v>
-      </c>
-      <c r="I1739">
-        <v>0.1348191732466812</v>
-      </c>
-      <c r="J1739">
-        <v>1.259041337665939</v>
-      </c>
-      <c r="K1739">
-        <v>3.19</v>
-      </c>
-      <c r="L1739">
-        <v>4.9</v>
-      </c>
-      <c r="M1739">
-        <v>3.21</v>
-      </c>
-      <c r="N1739">
-        <v>5.06</v>
-      </c>
-      <c r="O1739">
-        <v>1</v>
-      </c>
-      <c r="P1739" t="s">
         <v>580</v>
       </c>
     </row>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5271" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5265" uniqueCount="585">
   <si>
     <t>trade_time</t>
   </si>
@@ -781,6 +781,9 @@
     <t>2021-08-11</t>
   </si>
   <si>
+    <t>2021-08-18</t>
+  </si>
+  <si>
     <t>2021-09-09</t>
   </si>
   <si>
@@ -791,9 +794,6 @@
   </si>
   <si>
     <t>2021-10-15</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
   </si>
   <si>
     <t>2021-09-01</t>
@@ -808,7 +808,7 @@
     <t>2021-09-17</t>
   </si>
   <si>
-    <t>2021-10-12</t>
+    <t>2021-10-18</t>
   </si>
   <si>
     <t>2016-10-20</t>
@@ -1357,7 +1357,7 @@
     <t>2021-10-11</t>
   </si>
   <si>
-    <t>2021-10-18</t>
+    <t>2021-10-19</t>
   </si>
   <si>
     <t>2021-09-03</t>
@@ -1767,6 +1767,9 @@
   <si>
     <t>2021-09-30</t>
   </si>
+  <si>
+    <t>2021-10-12</t>
+  </si>
 </sst>
 </file>
 
@@ -2123,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1753"/>
+  <dimension ref="A1:P1751"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -80734,7 +80737,7 @@
         <v>1.76226175520578</v>
       </c>
       <c r="D1573" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E1573">
         <v>2.006323623273507</v>
@@ -82284,7 +82287,7 @@
         <v>1.411337710358634</v>
       </c>
       <c r="D1604" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E1604">
         <v>1.647985690154943</v>
@@ -84428,10 +84431,10 @@
         <v>0</v>
       </c>
       <c r="B1647" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C1647">
-        <v>1.752593254719144</v>
+        <v>1.670182610065094</v>
       </c>
       <c r="D1647" t="s">
         <v>443</v>
@@ -84443,22 +84446,22 @@
         <v>-1</v>
       </c>
       <c r="G1647">
-        <v>0.007727406745280856</v>
+        <v>0.007749817389934906</v>
       </c>
       <c r="H1647">
         <v>0.007670781647796526</v>
       </c>
       <c r="I1647">
-        <v>0.2033749025156699</v>
+        <v>0.1209642578616195</v>
       </c>
       <c r="J1647">
         <v>1.048212893081002</v>
       </c>
       <c r="K1647">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="L1647">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="M1647">
         <v>2.92</v>
@@ -84478,7 +84481,7 @@
         <v>1</v>
       </c>
       <c r="B1648" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1648">
         <v>1.685236613209983</v>
@@ -84528,7 +84531,7 @@
         <v>2</v>
       </c>
       <c r="B1649" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1649">
         <v>1.529218352203474</v>
@@ -84578,7 +84581,7 @@
         <v>3</v>
       </c>
       <c r="B1650" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1650">
         <v>1.526325578618614</v>
@@ -84628,7 +84631,7 @@
         <v>4</v>
       </c>
       <c r="B1651" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C1651">
         <v>1.716683000002413</v>
@@ -84637,7 +84640,7 @@
         <v>447</v>
       </c>
       <c r="E1651">
-        <v>1.798611515725653</v>
+        <v>1.587165128933223</v>
       </c>
       <c r="F1651">
         <v>-1</v>
@@ -84646,10 +84649,10 @@
         <v>0.008383316999997587</v>
       </c>
       <c r="H1651">
-        <v>0.008381388484274346</v>
+        <v>0.008232834871066777</v>
       </c>
       <c r="I1651">
-        <v>-0.08192851572324011</v>
+        <v>0.1295178710691895</v>
       </c>
       <c r="J1651">
         <v>1.048212893081002</v>
@@ -84661,10 +84664,10 @@
         <v>5.05</v>
       </c>
       <c r="M1651">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="N1651">
-        <v>5.09</v>
+        <v>4.91</v>
       </c>
       <c r="O1651">
         <v>1</v>
@@ -84678,7 +84681,7 @@
         <v>0</v>
       </c>
       <c r="B1652" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C1652">
         <v>1.608934335394003</v>
@@ -84728,7 +84731,7 @@
         <v>1</v>
       </c>
       <c r="B1653" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1653">
         <v>1.6174411091775</v>
@@ -84778,7 +84781,7 @@
         <v>2</v>
       </c>
       <c r="B1654" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1654">
         <v>1.467547675638099</v>
@@ -84828,7 +84831,7 @@
         <v>3</v>
       </c>
       <c r="B1655" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1655">
         <v>1.46338769637039</v>
@@ -84878,7 +84881,7 @@
         <v>4</v>
       </c>
       <c r="B1656" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C1656">
         <v>1.649521098811355</v>
@@ -84887,7 +84890,7 @@
         <v>447</v>
       </c>
       <c r="E1656">
-        <v>1.732294418323161</v>
+        <v>1.520214428689307</v>
       </c>
       <c r="F1656">
         <v>-1</v>
@@ -84896,10 +84899,10 @@
         <v>0.008450478901188645</v>
       </c>
       <c r="H1656">
-        <v>0.00844770558167684</v>
+        <v>0.008299785571310694</v>
       </c>
       <c r="I1656">
-        <v>-0.08277331951180678</v>
+        <v>0.1293066701220478</v>
       </c>
       <c r="J1656">
         <v>1.069332987795171</v>
@@ -84911,10 +84914,10 @@
         <v>5.05</v>
       </c>
       <c r="M1656">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="N1656">
-        <v>5.09</v>
+        <v>4.91</v>
       </c>
       <c r="O1656">
         <v>1</v>
@@ -84928,7 +84931,7 @@
         <v>0</v>
       </c>
       <c r="B1657" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C1657">
         <v>1.546278323136421</v>
@@ -85028,7 +85031,7 @@
         <v>2</v>
       </c>
       <c r="B1659" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C1659">
         <v>1.548087385264796</v>
@@ -85078,7 +85081,7 @@
         <v>3</v>
       </c>
       <c r="B1660" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1660">
         <v>1.404459552951154</v>
@@ -85128,7 +85131,7 @@
         <v>4</v>
       </c>
       <c r="B1661" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1661">
         <v>1.399003242395357</v>
@@ -85178,7 +85181,7 @@
         <v>5</v>
       </c>
       <c r="B1662" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C1662">
         <v>1.580815540542695</v>
@@ -85187,7 +85190,7 @@
         <v>447</v>
       </c>
       <c r="E1662">
-        <v>1.664453080913228</v>
+        <v>1.451724925635329</v>
       </c>
       <c r="F1662">
         <v>-1</v>
@@ -85196,10 +85199,10 @@
         <v>0.008519184459457303</v>
       </c>
       <c r="H1662">
-        <v>0.008515546919086773</v>
+        <v>0.008368275074364672</v>
       </c>
       <c r="I1662">
-        <v>-0.08363754037053228</v>
+        <v>0.1290906149073665</v>
       </c>
       <c r="J1662">
         <v>1.090938509263303</v>
@@ -85211,10 +85214,10 @@
         <v>5.05</v>
       </c>
       <c r="M1662">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="N1662">
-        <v>5.09</v>
+        <v>4.91</v>
       </c>
       <c r="O1662">
         <v>1</v>
@@ -85228,7 +85231,7 @@
         <v>0</v>
       </c>
       <c r="B1663" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C1663">
         <v>1.476561626064879</v>
@@ -85328,7 +85331,7 @@
         <v>2</v>
       </c>
       <c r="B1665" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C1665">
         <v>1.334262051072223</v>
@@ -85378,7 +85381,7 @@
         <v>3</v>
       </c>
       <c r="B1666" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1666">
         <v>1.327363326094256</v>
@@ -85478,7 +85481,7 @@
         <v>5</v>
       </c>
       <c r="B1668" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C1668">
         <v>1.504367576167695</v>
@@ -85487,7 +85490,7 @@
         <v>447</v>
       </c>
       <c r="E1668">
-        <v>1.588966726153007</v>
+        <v>1.375517363664023</v>
       </c>
       <c r="F1668">
         <v>-1</v>
@@ -85496,10 +85499,10 @@
         <v>0.008595632423832305</v>
       </c>
       <c r="H1668">
-        <v>0.008591033273846993</v>
+        <v>0.008444482636335977</v>
       </c>
       <c r="I1668">
-        <v>-0.08459914998531204</v>
+        <v>0.1288502125036715</v>
       </c>
       <c r="J1668">
         <v>1.1149787496328</v>
@@ -85511,10 +85514,10 @@
         <v>5.05</v>
       </c>
       <c r="M1668">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="N1668">
-        <v>5.09</v>
+        <v>4.91</v>
       </c>
       <c r="O1668">
         <v>1</v>
@@ -85528,7 +85531,7 @@
         <v>0</v>
       </c>
       <c r="B1669" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C1669">
         <v>1.381575977020794</v>
@@ -85578,43 +85581,43 @@
         <v>1</v>
       </c>
       <c r="B1670" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C1670">
-        <v>1.234984141111739</v>
+        <v>1.371917246540982</v>
       </c>
       <c r="D1670" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E1670">
-        <v>1.31498414111174</v>
+        <v>1.258621328586455</v>
       </c>
       <c r="F1670">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1670">
-        <v>0.00830501585888826</v>
+        <v>0.007868082753459019</v>
       </c>
       <c r="H1670">
-        <v>0.00838501585888826</v>
+        <v>0.007961378671413544</v>
       </c>
       <c r="I1670">
-        <v>0.08000000000000007</v>
+        <v>0.1132959179545265</v>
       </c>
       <c r="J1670">
         <v>1.147732421716968</v>
       </c>
       <c r="K1670">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1670">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1670">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1670">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1670">
         <v>1</v>
@@ -85628,43 +85631,43 @@
         <v>2</v>
       </c>
       <c r="B1671" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C1671">
-        <v>1.238621328586455</v>
+        <v>1.234984141111739</v>
       </c>
       <c r="D1671" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E1671">
-        <v>1.329757383283437</v>
+        <v>1.31498414111174</v>
       </c>
       <c r="F1671">
         <v>1</v>
       </c>
       <c r="G1671">
-        <v>0.007941378671413545</v>
+        <v>0.00830501585888826</v>
       </c>
       <c r="H1671">
-        <v>0.008170242616716564</v>
+        <v>0.00838501585888826</v>
       </c>
       <c r="I1671">
-        <v>0.09113605469698216</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1671">
         <v>1.147732421716968</v>
       </c>
       <c r="K1671">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="L1671">
-        <v>4.59</v>
+        <v>4.77</v>
       </c>
       <c r="M1671">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="N1671">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="O1671">
         <v>1</v>
@@ -85681,40 +85684,40 @@
         <v>257</v>
       </c>
       <c r="C1672">
-        <v>1.229757383283437</v>
+        <v>1.238621328586455</v>
       </c>
       <c r="D1672" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E1672">
-        <v>1.375778926288534</v>
+        <v>1.329757383283437</v>
       </c>
       <c r="F1672">
         <v>1</v>
       </c>
       <c r="G1672">
-        <v>0.008070242616716563</v>
+        <v>0.007941378671413545</v>
       </c>
       <c r="H1672">
-        <v>0.008744221073711466</v>
+        <v>0.008170242616716564</v>
       </c>
       <c r="I1672">
-        <v>0.1460215430050966</v>
+        <v>0.09113605469698216</v>
       </c>
       <c r="J1672">
         <v>1.147732421716968</v>
       </c>
       <c r="K1672">
+        <v>2.92</v>
+      </c>
+      <c r="L1672">
+        <v>4.59</v>
+      </c>
+      <c r="M1672">
         <v>2.98</v>
       </c>
-      <c r="L1672">
-        <v>4.65</v>
-      </c>
-      <c r="M1672">
-        <v>3.21</v>
-      </c>
       <c r="N1672">
-        <v>5.06</v>
+        <v>4.75</v>
       </c>
       <c r="O1672">
         <v>1</v>
@@ -85728,10 +85731,10 @@
         <v>4</v>
       </c>
       <c r="B1673" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1673">
-        <v>1.238733574722874</v>
+        <v>1.229757383283437</v>
       </c>
       <c r="D1673" t="s">
         <v>446</v>
@@ -85743,22 +85746,22 @@
         <v>1</v>
       </c>
       <c r="G1673">
-        <v>0.008561266425277127</v>
+        <v>0.008070242616716563</v>
       </c>
       <c r="H1673">
         <v>0.008744221073711466</v>
       </c>
       <c r="I1673">
-        <v>0.1370453515656598</v>
+        <v>0.1460215430050966</v>
       </c>
       <c r="J1673">
         <v>1.147732421716968</v>
       </c>
       <c r="K1673">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1673">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1673">
         <v>3.21</v>
@@ -85778,43 +85781,43 @@
         <v>5</v>
       </c>
       <c r="B1674" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1674">
-        <v>1.400210898940043</v>
+        <v>1.238733574722874</v>
       </c>
       <c r="D1674" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E1674">
-        <v>1.486120195808722</v>
+        <v>1.375778926288534</v>
       </c>
       <c r="F1674">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1674">
-        <v>0.008699789101059957</v>
+        <v>0.008561266425277127</v>
       </c>
       <c r="H1674">
-        <v>0.008693879804191278</v>
+        <v>0.008744221073711466</v>
       </c>
       <c r="I1674">
-        <v>-0.08590929686867899</v>
+        <v>0.1370453515656598</v>
       </c>
       <c r="J1674">
         <v>1.147732421716968</v>
       </c>
       <c r="K1674">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="L1674">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="M1674">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="N1674">
-        <v>5.09</v>
+        <v>5.06</v>
       </c>
       <c r="O1674">
         <v>1</v>
@@ -85825,213 +85828,213 @@
     </row>
     <row r="1675" spans="1:16">
       <c r="A1675" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1675" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C1675">
-        <v>1.298944189815882</v>
+        <v>1.400210898940043</v>
       </c>
       <c r="D1675" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E1675">
-        <v>1.183327573944303</v>
+        <v>1.271688223157213</v>
       </c>
       <c r="F1675">
         <v>-1</v>
       </c>
       <c r="G1675">
-        <v>0.007941055810184118</v>
+        <v>0.008699789101059957</v>
       </c>
       <c r="H1675">
-        <v>0.008036672426055699</v>
+        <v>0.008548311776842787</v>
       </c>
       <c r="I1675">
-        <v>0.1156166158715792</v>
+        <v>0.1285226757828295</v>
       </c>
       <c r="J1675">
-        <v>1.173517954128664</v>
+        <v>1.147732421716968</v>
       </c>
       <c r="K1675">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="L1675">
-        <v>4.62</v>
+        <v>5.05</v>
       </c>
       <c r="M1675">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="N1675">
-        <v>4.61</v>
+        <v>4.91</v>
       </c>
       <c r="O1675">
         <v>1</v>
       </c>
       <c r="P1675" t="s">
-        <v>259</v>
+        <v>436</v>
       </c>
     </row>
     <row r="1676" spans="1:16">
       <c r="A1676" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1676" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C1676">
-        <v>1.155564701283716</v>
+        <v>1.298944189815882</v>
       </c>
       <c r="D1676" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E1676">
-        <v>1.235564701283716</v>
+        <v>1.183327573944303</v>
       </c>
       <c r="F1676">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1676">
-        <v>0.008384435298716283</v>
+        <v>0.007941055810184118</v>
       </c>
       <c r="H1676">
-        <v>0.008464435298716284</v>
+        <v>0.008036672426055699</v>
       </c>
       <c r="I1676">
-        <v>0.08000000000000007</v>
+        <v>0.1156166158715792</v>
       </c>
       <c r="J1676">
         <v>1.173517954128664</v>
       </c>
       <c r="K1676">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1676">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1676">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1676">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1676">
         <v>1</v>
       </c>
       <c r="P1676" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1677" spans="1:16">
       <c r="A1677" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1677" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C1677">
-        <v>1.163327573944303</v>
+        <v>1.155564701283716</v>
       </c>
       <c r="D1677" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E1677">
-        <v>1.252916496696582</v>
+        <v>1.235564701283716</v>
       </c>
       <c r="F1677">
         <v>1</v>
       </c>
       <c r="G1677">
-        <v>0.008016672426055697</v>
+        <v>0.008384435298716283</v>
       </c>
       <c r="H1677">
-        <v>0.008247083503303419</v>
+        <v>0.008464435298716284</v>
       </c>
       <c r="I1677">
-        <v>0.08958892275227992</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1677">
         <v>1.173517954128664</v>
       </c>
       <c r="K1677">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="L1677">
-        <v>4.59</v>
+        <v>4.77</v>
       </c>
       <c r="M1677">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="N1677">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="O1677">
         <v>1</v>
       </c>
       <c r="P1677" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1678" spans="1:16">
       <c r="A1678" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1678" t="s">
         <v>257</v>
       </c>
       <c r="C1678">
-        <v>1.152916496696583</v>
+        <v>1.163327573944303</v>
       </c>
       <c r="D1678" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E1678">
-        <v>1.29300736724699</v>
+        <v>1.252916496696582</v>
       </c>
       <c r="F1678">
         <v>1</v>
       </c>
       <c r="G1678">
-        <v>0.008147083503303417</v>
+        <v>0.008016672426055697</v>
       </c>
       <c r="H1678">
-        <v>0.00882699263275301</v>
+        <v>0.008247083503303419</v>
       </c>
       <c r="I1678">
-        <v>0.1400908705504067</v>
+        <v>0.08958892275227992</v>
       </c>
       <c r="J1678">
         <v>1.173517954128664</v>
       </c>
       <c r="K1678">
+        <v>2.92</v>
+      </c>
+      <c r="L1678">
+        <v>4.59</v>
+      </c>
+      <c r="M1678">
         <v>2.98</v>
       </c>
-      <c r="L1678">
-        <v>4.65</v>
-      </c>
-      <c r="M1678">
-        <v>3.21</v>
-      </c>
       <c r="N1678">
-        <v>5.06</v>
+        <v>4.75</v>
       </c>
       <c r="O1678">
         <v>1</v>
       </c>
       <c r="P1678" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1679" spans="1:16">
       <c r="A1679" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1679" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1679">
-        <v>1.156477726329564</v>
+        <v>1.152916496696583</v>
       </c>
       <c r="D1679" t="s">
         <v>446</v>
@@ -86043,22 +86046,22 @@
         <v>1</v>
       </c>
       <c r="G1679">
-        <v>0.008643522273670436</v>
+        <v>0.008147083503303417</v>
       </c>
       <c r="H1679">
         <v>0.00882699263275301</v>
       </c>
       <c r="I1679">
-        <v>0.1365296409174257</v>
+        <v>0.1400908705504067</v>
       </c>
       <c r="J1679">
         <v>1.173517954128664</v>
       </c>
       <c r="K1679">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1679">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1679">
         <v>3.21</v>
@@ -86070,101 +86073,101 @@
         <v>1</v>
       </c>
       <c r="P1679" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1680" spans="1:16">
       <c r="A1680" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1680" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1680">
-        <v>1.199709616662221</v>
+        <v>1.156477726329564</v>
       </c>
       <c r="D1680" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E1680">
-        <v>1.080937130973034</v>
+        <v>1.29300736724699</v>
       </c>
       <c r="F1680">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1680">
-        <v>0.00804029038333778</v>
+        <v>0.008643522273670436</v>
       </c>
       <c r="H1680">
-        <v>0.008139062869026967</v>
+        <v>0.00882699263275301</v>
       </c>
       <c r="I1680">
-        <v>0.118772485689187</v>
+        <v>0.1365296409174257</v>
       </c>
       <c r="J1680">
-        <v>1.208583174324304</v>
+        <v>1.173517954128664</v>
       </c>
       <c r="K1680">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="L1680">
-        <v>4.62</v>
+        <v>4.9</v>
       </c>
       <c r="M1680">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="N1680">
-        <v>4.61</v>
+        <v>5.06</v>
       </c>
       <c r="O1680">
         <v>1</v>
       </c>
       <c r="P1680" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1681" spans="1:16">
       <c r="A1681" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1681" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C1681">
-        <v>1.047563823081144</v>
+        <v>1.199709616662221</v>
       </c>
       <c r="D1681" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E1681">
-        <v>1.127563823081144</v>
+        <v>1.080937130973034</v>
       </c>
       <c r="F1681">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1681">
-        <v>0.008492436176918855</v>
+        <v>0.00804029038333778</v>
       </c>
       <c r="H1681">
-        <v>0.008572436176918854</v>
+        <v>0.008139062869026967</v>
       </c>
       <c r="I1681">
-        <v>0.08000000000000007</v>
+        <v>0.118772485689187</v>
       </c>
       <c r="J1681">
         <v>1.208583174324304</v>
       </c>
       <c r="K1681">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1681">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1681">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1681">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1681">
         <v>1</v>
@@ -86175,46 +86178,46 @@
     </row>
     <row r="1682" spans="1:16">
       <c r="A1682" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1682" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C1682">
-        <v>1.060937130973033</v>
+        <v>1.047563823081144</v>
       </c>
       <c r="D1682" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E1682">
-        <v>1.148422140513575</v>
+        <v>1.127563823081144</v>
       </c>
       <c r="F1682">
         <v>1</v>
       </c>
       <c r="G1682">
-        <v>0.008119062869026967</v>
+        <v>0.008492436176918855</v>
       </c>
       <c r="H1682">
-        <v>0.008351577859486425</v>
+        <v>0.008572436176918854</v>
       </c>
       <c r="I1682">
-        <v>0.08748500954054172</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1682">
         <v>1.208583174324304</v>
       </c>
       <c r="K1682">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="L1682">
-        <v>4.59</v>
+        <v>4.77</v>
       </c>
       <c r="M1682">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="N1682">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="O1682">
         <v>1</v>
@@ -86225,46 +86228,46 @@
     </row>
     <row r="1683" spans="1:16">
       <c r="A1683" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1683" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1683">
-        <v>1.048422140513575</v>
+        <v>1.046336308770332</v>
       </c>
       <c r="D1683" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E1683">
-        <v>1.180448010418985</v>
+        <v>1.148422140513575</v>
       </c>
       <c r="F1683">
         <v>1</v>
       </c>
       <c r="G1683">
-        <v>0.008251577859486424</v>
+        <v>0.008273663691229668</v>
       </c>
       <c r="H1683">
-        <v>0.008939551989581015</v>
+        <v>0.008351577859486425</v>
       </c>
       <c r="I1683">
-        <v>0.1320258699054095</v>
+        <v>0.1020858317432429</v>
       </c>
       <c r="J1683">
         <v>1.208583174324304</v>
       </c>
       <c r="K1683">
+        <v>2.99</v>
+      </c>
+      <c r="L1683">
+        <v>4.66</v>
+      </c>
+      <c r="M1683">
         <v>2.98</v>
       </c>
-      <c r="L1683">
-        <v>4.65</v>
-      </c>
-      <c r="M1683">
-        <v>3.21</v>
-      </c>
       <c r="N1683">
-        <v>5.06</v>
+        <v>4.75</v>
       </c>
       <c r="O1683">
         <v>1</v>
@@ -86275,13 +86278,13 @@
     </row>
     <row r="1684" spans="1:16">
       <c r="A1684" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1684" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1684">
-        <v>1.044619673905472</v>
+        <v>1.048422140513575</v>
       </c>
       <c r="D1684" t="s">
         <v>446</v>
@@ -86293,22 +86296,22 @@
         <v>1</v>
       </c>
       <c r="G1684">
-        <v>0.008755380326094528</v>
+        <v>0.008251577859486424</v>
       </c>
       <c r="H1684">
         <v>0.008939551989581015</v>
       </c>
       <c r="I1684">
-        <v>0.1358283365135131</v>
+        <v>0.1320258699054095</v>
       </c>
       <c r="J1684">
         <v>1.208583174324304</v>
       </c>
       <c r="K1684">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1684">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1684">
         <v>3.21</v>
@@ -86325,96 +86328,96 @@
     </row>
     <row r="1685" spans="1:16">
       <c r="A1685" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1685" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1685">
-        <v>1.148290651113722</v>
+        <v>1.044619673905472</v>
       </c>
       <c r="D1685" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E1685">
-        <v>1.027882933304618</v>
+        <v>1.180448010418985</v>
       </c>
       <c r="F1685">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1685">
-        <v>0.008091709348886278</v>
+        <v>0.008755380326094528</v>
       </c>
       <c r="H1685">
-        <v>0.008192117066695381</v>
+        <v>0.008939551989581015</v>
       </c>
       <c r="I1685">
-        <v>0.1204077178091039</v>
+        <v>0.1358283365135131</v>
       </c>
       <c r="J1685">
-        <v>1.226752420101158</v>
+        <v>1.208583174324304</v>
       </c>
       <c r="K1685">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="L1685">
-        <v>4.62</v>
+        <v>4.9</v>
       </c>
       <c r="M1685">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="N1685">
-        <v>4.61</v>
+        <v>5.06</v>
       </c>
       <c r="O1685">
         <v>1</v>
       </c>
       <c r="P1685" t="s">
-        <v>440</v>
+        <v>250</v>
       </c>
     </row>
     <row r="1686" spans="1:16">
       <c r="A1686" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1686" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C1686">
-        <v>0.9916025460884326</v>
+        <v>1.148290651113722</v>
       </c>
       <c r="D1686" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E1686">
-        <v>1.071602546088433</v>
+        <v>1.027882933304618</v>
       </c>
       <c r="F1686">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1686">
-        <v>0.008548397453911566</v>
+        <v>0.008091709348886278</v>
       </c>
       <c r="H1686">
-        <v>0.008628397453911568</v>
+        <v>0.008192117066695381</v>
       </c>
       <c r="I1686">
-        <v>0.08000000000000007</v>
+        <v>0.1204077178091039</v>
       </c>
       <c r="J1686">
         <v>1.226752420101158</v>
       </c>
       <c r="K1686">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1686">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1686">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1686">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1686">
         <v>1</v>
@@ -86425,46 +86428,46 @@
     </row>
     <row r="1687" spans="1:16">
       <c r="A1687" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1687" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C1687">
-        <v>1.007882933304618</v>
+        <v>0.9916025460884326</v>
       </c>
       <c r="D1687" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E1687">
-        <v>1.094277788098549</v>
+        <v>1.071602546088433</v>
       </c>
       <c r="F1687">
         <v>1</v>
       </c>
       <c r="G1687">
-        <v>0.008172117066695381</v>
+        <v>0.008548397453911566</v>
       </c>
       <c r="H1687">
-        <v>0.008405722211901452</v>
+        <v>0.008628397453911568</v>
       </c>
       <c r="I1687">
-        <v>0.08639485479393061</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1687">
         <v>1.226752420101158</v>
       </c>
       <c r="K1687">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="L1687">
-        <v>4.59</v>
+        <v>4.77</v>
       </c>
       <c r="M1687">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="N1687">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="O1687">
         <v>1</v>
@@ -86475,46 +86478,46 @@
     </row>
     <row r="1688" spans="1:16">
       <c r="A1688" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1688" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1688">
-        <v>0.9942777880985489</v>
+        <v>0.9920102638975372</v>
       </c>
       <c r="D1688" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E1688">
-        <v>1.122124731475282</v>
+        <v>1.094277788098549</v>
       </c>
       <c r="F1688">
         <v>1</v>
       </c>
       <c r="G1688">
-        <v>0.008305722211901453</v>
+        <v>0.008327989736102463</v>
       </c>
       <c r="H1688">
-        <v>0.008997875268524717</v>
+        <v>0.008405722211901452</v>
       </c>
       <c r="I1688">
-        <v>0.1278469433767331</v>
+        <v>0.1022675242010114</v>
       </c>
       <c r="J1688">
         <v>1.226752420101158</v>
       </c>
       <c r="K1688">
+        <v>2.99</v>
+      </c>
+      <c r="L1688">
+        <v>4.66</v>
+      </c>
+      <c r="M1688">
         <v>2.98</v>
       </c>
-      <c r="L1688">
-        <v>4.65</v>
-      </c>
-      <c r="M1688">
-        <v>3.21</v>
-      </c>
       <c r="N1688">
-        <v>5.06</v>
+        <v>4.75</v>
       </c>
       <c r="O1688">
         <v>1</v>
@@ -86525,13 +86528,13 @@
     </row>
     <row r="1689" spans="1:16">
       <c r="A1689" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1689" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1689">
-        <v>0.9866597798773058</v>
+        <v>0.9942777880985489</v>
       </c>
       <c r="D1689" t="s">
         <v>446</v>
@@ -86543,22 +86546,22 @@
         <v>1</v>
       </c>
       <c r="G1689">
-        <v>0.008813340220122695</v>
+        <v>0.008305722211901453</v>
       </c>
       <c r="H1689">
         <v>0.008997875268524717</v>
       </c>
       <c r="I1689">
-        <v>0.1354649515979762</v>
+        <v>0.1278469433767331</v>
       </c>
       <c r="J1689">
         <v>1.226752420101158</v>
       </c>
       <c r="K1689">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1689">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1689">
         <v>3.21</v>
@@ -86575,96 +86578,96 @@
     </row>
     <row r="1690" spans="1:16">
       <c r="A1690" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1690" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1690">
-        <v>0.9133372588035056</v>
+        <v>0.9866597798773058</v>
       </c>
       <c r="D1690" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1690">
-        <v>0.9933372588035057</v>
+        <v>1.122124731475282</v>
       </c>
       <c r="F1690">
         <v>1</v>
       </c>
       <c r="G1690">
-        <v>0.008626662741196495</v>
+        <v>0.008813340220122695</v>
       </c>
       <c r="H1690">
-        <v>0.008706662741196493</v>
+        <v>0.008997875268524717</v>
       </c>
       <c r="I1690">
-        <v>0.08000000000000007</v>
+        <v>0.1354649515979762</v>
       </c>
       <c r="J1690">
-        <v>1.252163227661199</v>
+        <v>1.226752420101158</v>
       </c>
       <c r="K1690">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1690">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1690">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1690">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1690">
         <v>1</v>
       </c>
       <c r="P1690" t="s">
-        <v>262</v>
+        <v>440</v>
       </c>
     </row>
     <row r="1691" spans="1:16">
       <c r="A1691" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1691" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1691">
-        <v>0.9160319492930138</v>
+        <v>0.9133372588035056</v>
       </c>
       <c r="D1691" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1691">
-        <v>0.9835103170164023</v>
+        <v>0.9933372588035057</v>
       </c>
       <c r="F1691">
         <v>1</v>
       </c>
       <c r="G1691">
-        <v>0.008403968050706987</v>
+        <v>0.008626662741196495</v>
       </c>
       <c r="H1691">
-        <v>0.008496489682983598</v>
+        <v>0.008706662741196493</v>
       </c>
       <c r="I1691">
-        <v>0.06747836772338855</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1691">
         <v>1.252163227661199</v>
       </c>
       <c r="K1691">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1691">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1691">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1691">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1691">
         <v>1</v>
@@ -86675,46 +86678,46 @@
     </row>
     <row r="1692" spans="1:16">
       <c r="A1692" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1692" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1692">
-        <v>0.9185535815696264</v>
+        <v>0.9160319492930138</v>
       </c>
       <c r="D1692" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1692">
-        <v>1.04055603920755</v>
+        <v>0.9835103170164023</v>
       </c>
       <c r="F1692">
         <v>1</v>
       </c>
       <c r="G1692">
-        <v>0.008381446418430376</v>
+        <v>0.008403968050706987</v>
       </c>
       <c r="H1692">
-        <v>0.00907944396079245</v>
+        <v>0.008496489682983598</v>
       </c>
       <c r="I1692">
-        <v>0.1220024576379233</v>
+        <v>0.06747836772338855</v>
       </c>
       <c r="J1692">
         <v>1.252163227661199</v>
       </c>
       <c r="K1692">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1692">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1692">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1692">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1692">
         <v>1</v>
@@ -86725,13 +86728,13 @@
     </row>
     <row r="1693" spans="1:16">
       <c r="A1693" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1693" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1693">
-        <v>0.9055993037607744</v>
+        <v>0.9185535815696264</v>
       </c>
       <c r="D1693" t="s">
         <v>446</v>
@@ -86743,22 +86746,22 @@
         <v>1</v>
       </c>
       <c r="G1693">
-        <v>0.008894400696239228</v>
+        <v>0.008381446418430376</v>
       </c>
       <c r="H1693">
         <v>0.00907944396079245</v>
       </c>
       <c r="I1693">
-        <v>0.1349567354467753</v>
+        <v>0.1220024576379233</v>
       </c>
       <c r="J1693">
         <v>1.252163227661199</v>
       </c>
       <c r="K1693">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1693">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1693">
         <v>3.21</v>
@@ -86775,96 +86778,96 @@
     </row>
     <row r="1694" spans="1:16">
       <c r="A1694" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1694" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1694">
-        <v>0.8640876530634416</v>
+        <v>0.9055993037607744</v>
       </c>
       <c r="D1694" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1694">
-        <v>0.9440876530634417</v>
+        <v>1.04055603920755</v>
       </c>
       <c r="F1694">
         <v>1</v>
       </c>
       <c r="G1694">
-        <v>0.008675912346936559</v>
+        <v>0.008894400696239228</v>
       </c>
       <c r="H1694">
-        <v>0.008755912346936559</v>
+        <v>0.00907944396079245</v>
       </c>
       <c r="I1694">
-        <v>0.08000000000000007</v>
+        <v>0.1349567354467753</v>
       </c>
       <c r="J1694">
-        <v>1.268153359394986</v>
+        <v>1.252163227661199</v>
       </c>
       <c r="K1694">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1694">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1694">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1694">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1694">
         <v>1</v>
       </c>
       <c r="P1694" t="s">
-        <v>570</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1695" spans="1:16">
       <c r="A1695" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1695" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1695">
-        <v>0.8682214554089906</v>
+        <v>0.8640876530634416</v>
       </c>
       <c r="D1695" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1695">
-        <v>0.9355399218150415</v>
+        <v>0.9440876530634417</v>
       </c>
       <c r="F1695">
         <v>1</v>
       </c>
       <c r="G1695">
-        <v>0.00845177854459101</v>
+        <v>0.008675912346936559</v>
       </c>
       <c r="H1695">
-        <v>0.008544460078184959</v>
+        <v>0.008755912346936559</v>
       </c>
       <c r="I1695">
-        <v>0.06731846640605088</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1695">
         <v>1.268153359394986</v>
       </c>
       <c r="K1695">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1695">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1695">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1695">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1695">
         <v>1</v>
@@ -86875,46 +86878,46 @@
     </row>
     <row r="1696" spans="1:16">
       <c r="A1696" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1696" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1696">
-        <v>0.8709029890029414</v>
+        <v>0.8682214554089906</v>
       </c>
       <c r="D1696" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1696">
-        <v>0.9892277163420937</v>
+        <v>0.9355399218150415</v>
       </c>
       <c r="F1696">
         <v>1</v>
       </c>
       <c r="G1696">
-        <v>0.008429097010997059</v>
+        <v>0.00845177854459101</v>
       </c>
       <c r="H1696">
-        <v>0.009130772283657905</v>
+        <v>0.008544460078184959</v>
       </c>
       <c r="I1696">
-        <v>0.1183247273391523</v>
+        <v>0.06731846640605088</v>
       </c>
       <c r="J1696">
         <v>1.268153359394986</v>
       </c>
       <c r="K1696">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1696">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1696">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1696">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1696">
         <v>1</v>
@@ -86925,13 +86928,13 @@
     </row>
     <row r="1697" spans="1:16">
       <c r="A1697" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1697" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1697">
-        <v>0.8545907835299937</v>
+        <v>0.8709029890029414</v>
       </c>
       <c r="D1697" t="s">
         <v>446</v>
@@ -86943,22 +86946,22 @@
         <v>1</v>
       </c>
       <c r="G1697">
-        <v>0.008945409216470008</v>
+        <v>0.008429097010997059</v>
       </c>
       <c r="H1697">
         <v>0.009130772283657905</v>
       </c>
       <c r="I1697">
-        <v>0.1346369328121</v>
+        <v>0.1183247273391523</v>
       </c>
       <c r="J1697">
         <v>1.268153359394986</v>
       </c>
       <c r="K1697">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1697">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1697">
         <v>3.21</v>
@@ -86975,96 +86978,96 @@
     </row>
     <row r="1698" spans="1:16">
       <c r="A1698" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1698" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1698">
-        <v>0.8361486892860226</v>
+        <v>0.8545907835299937</v>
       </c>
       <c r="D1698" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1698">
-        <v>0.9161486892860227</v>
+        <v>0.9892277163420937</v>
       </c>
       <c r="F1698">
         <v>1</v>
       </c>
       <c r="G1698">
-        <v>0.008703851310713976</v>
+        <v>0.008945409216470008</v>
       </c>
       <c r="H1698">
-        <v>0.008783851310713978</v>
+        <v>0.009130772283657905</v>
       </c>
       <c r="I1698">
-        <v>0.08000000000000007</v>
+        <v>0.1346369328121</v>
       </c>
       <c r="J1698">
-        <v>1.277224451530512</v>
+        <v>1.268153359394986</v>
       </c>
       <c r="K1698">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1698">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1698">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1698">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1698">
         <v>1</v>
       </c>
       <c r="P1698" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="1699" spans="1:16">
       <c r="A1699" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1699" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1699">
-        <v>0.841098889923769</v>
+        <v>0.8361486892860226</v>
       </c>
       <c r="D1699" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1699">
-        <v>0.9083266454084642</v>
+        <v>0.9161486892860227</v>
       </c>
       <c r="F1699">
         <v>1</v>
       </c>
       <c r="G1699">
-        <v>0.008478901110076232</v>
+        <v>0.008703851310713976</v>
       </c>
       <c r="H1699">
-        <v>0.008571673354591535</v>
+        <v>0.008783851310713978</v>
       </c>
       <c r="I1699">
-        <v>0.06722775548469517</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1699">
         <v>1.277224451530512</v>
       </c>
       <c r="K1699">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1699">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1699">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1699">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1699">
         <v>1</v>
@@ -87075,46 +87078,46 @@
     </row>
     <row r="1700" spans="1:16">
       <c r="A1700" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1700" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1700">
-        <v>0.8438711344390746</v>
+        <v>0.841098889923769</v>
       </c>
       <c r="D1700" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1700">
-        <v>0.9601095105870563</v>
+        <v>0.9083266454084642</v>
       </c>
       <c r="F1700">
         <v>1</v>
       </c>
       <c r="G1700">
-        <v>0.008456128865560925</v>
+        <v>0.008478901110076232</v>
       </c>
       <c r="H1700">
-        <v>0.009159890489412943</v>
+        <v>0.008571673354591535</v>
       </c>
       <c r="I1700">
-        <v>0.1162383761479817</v>
+        <v>0.06722775548469517</v>
       </c>
       <c r="J1700">
         <v>1.277224451530512</v>
       </c>
       <c r="K1700">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1700">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1700">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1700">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1700">
         <v>1</v>
@@ -87125,13 +87128,13 @@
     </row>
     <row r="1701" spans="1:16">
       <c r="A1701" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1701" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1701">
-        <v>0.8256539996176668</v>
+        <v>0.8438711344390746</v>
       </c>
       <c r="D1701" t="s">
         <v>446</v>
@@ -87143,22 +87146,22 @@
         <v>1</v>
       </c>
       <c r="G1701">
-        <v>0.008974346000382332</v>
+        <v>0.008456128865560925</v>
       </c>
       <c r="H1701">
         <v>0.009159890489412943</v>
       </c>
       <c r="I1701">
-        <v>0.1344555109693895</v>
+        <v>0.1162383761479817</v>
       </c>
       <c r="J1701">
         <v>1.277224451530512</v>
       </c>
       <c r="K1701">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1701">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1701">
         <v>3.21</v>
@@ -87175,96 +87178,96 @@
     </row>
     <row r="1702" spans="1:16">
       <c r="A1702" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1702" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1702">
-        <v>0.8463446294858961</v>
+        <v>0.8256539996176668</v>
       </c>
       <c r="D1702" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1702">
-        <v>0.9263446294858961</v>
+        <v>0.9601095105870563</v>
       </c>
       <c r="F1702">
         <v>1</v>
       </c>
       <c r="G1702">
-        <v>0.008693655370514104</v>
+        <v>0.008974346000382332</v>
       </c>
       <c r="H1702">
-        <v>0.008773655370514102</v>
+        <v>0.009159890489412943</v>
       </c>
       <c r="I1702">
-        <v>0.08000000000000007</v>
+        <v>0.1344555109693895</v>
       </c>
       <c r="J1702">
-        <v>1.273914081335748</v>
+        <v>1.277224451530512</v>
       </c>
       <c r="K1702">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1702">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1702">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1702">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1702">
         <v>1</v>
       </c>
       <c r="P1702" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1703" spans="1:16">
       <c r="A1703" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1703" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1703">
-        <v>0.8509968968061137</v>
+        <v>0.8463446294858961</v>
       </c>
       <c r="D1703" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1703">
-        <v>0.9182577559927565</v>
+        <v>0.9263446294858961</v>
       </c>
       <c r="F1703">
         <v>1</v>
       </c>
       <c r="G1703">
-        <v>0.008469003103193887</v>
+        <v>0.008693655370514104</v>
       </c>
       <c r="H1703">
-        <v>0.008561742244007244</v>
+        <v>0.008773655370514102</v>
       </c>
       <c r="I1703">
-        <v>0.06726085918664282</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1703">
         <v>1.273914081335748</v>
       </c>
       <c r="K1703">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1703">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1703">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1703">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1703">
         <v>1</v>
@@ -87275,46 +87278,46 @@
     </row>
     <row r="1704" spans="1:16">
       <c r="A1704" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1704" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1704">
-        <v>0.8537360376194716</v>
+        <v>0.8509968968061137</v>
       </c>
       <c r="D1704" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1704">
-        <v>0.9707357989122487</v>
+        <v>0.9182577559927565</v>
       </c>
       <c r="F1704">
         <v>1</v>
       </c>
       <c r="G1704">
-        <v>0.00844626396238053</v>
+        <v>0.008469003103193887</v>
       </c>
       <c r="H1704">
-        <v>0.00914926420108775</v>
+        <v>0.008561742244007244</v>
       </c>
       <c r="I1704">
-        <v>0.1169997612927771</v>
+        <v>0.06726085918664282</v>
       </c>
       <c r="J1704">
         <v>1.273914081335748</v>
       </c>
       <c r="K1704">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1704">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1704">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1704">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1704">
         <v>1</v>
@@ -87325,13 +87328,13 @@
     </row>
     <row r="1705" spans="1:16">
       <c r="A1705" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1705" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1705">
-        <v>0.8362140805389648</v>
+        <v>0.8537360376194716</v>
       </c>
       <c r="D1705" t="s">
         <v>446</v>
@@ -87343,22 +87346,22 @@
         <v>1</v>
       </c>
       <c r="G1705">
-        <v>0.008963785919461035</v>
+        <v>0.00844626396238053</v>
       </c>
       <c r="H1705">
         <v>0.00914926420108775</v>
       </c>
       <c r="I1705">
-        <v>0.1345217183732839</v>
+        <v>0.1169997612927771</v>
       </c>
       <c r="J1705">
         <v>1.273914081335748</v>
       </c>
       <c r="K1705">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1705">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1705">
         <v>3.21</v>
@@ -87375,96 +87378,96 @@
     </row>
     <row r="1706" spans="1:16">
       <c r="A1706" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1706" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1706">
-        <v>0.8349326342058419</v>
+        <v>0.8362140805389648</v>
       </c>
       <c r="D1706" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1706">
-        <v>0.9149326342058419</v>
+        <v>0.9707357989122487</v>
       </c>
       <c r="F1706">
         <v>1</v>
       </c>
       <c r="G1706">
-        <v>0.008705067365794157</v>
+        <v>0.008963785919461035</v>
       </c>
       <c r="H1706">
-        <v>0.008785067365794158</v>
+        <v>0.00914926420108775</v>
       </c>
       <c r="I1706">
-        <v>0.08000000000000007</v>
+        <v>0.1345217183732839</v>
       </c>
       <c r="J1706">
-        <v>1.277619274608493</v>
+        <v>1.273914081335748</v>
       </c>
       <c r="K1706">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1706">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1706">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1706">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1706">
         <v>1</v>
       </c>
       <c r="P1706" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="1707" spans="1:16">
       <c r="A1707" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1707" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1707">
-        <v>0.8399183689206069</v>
+        <v>0.8349326342058419</v>
       </c>
       <c r="D1707" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1707">
-        <v>0.9071421761745224</v>
+        <v>0.9149326342058419</v>
       </c>
       <c r="F1707">
         <v>1</v>
       </c>
       <c r="G1707">
-        <v>0.008480081631079394</v>
+        <v>0.008705067365794157</v>
       </c>
       <c r="H1707">
-        <v>0.008572857823825478</v>
+        <v>0.008785067365794158</v>
       </c>
       <c r="I1707">
-        <v>0.06722380725391552</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1707">
         <v>1.277619274608493</v>
       </c>
       <c r="K1707">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1707">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1707">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1707">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1707">
         <v>1</v>
@@ -87475,46 +87478,46 @@
     </row>
     <row r="1708" spans="1:16">
       <c r="A1708" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1708" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1708">
-        <v>0.8426945616666921</v>
+        <v>0.8399183689206069</v>
       </c>
       <c r="D1708" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1708">
-        <v>0.9588421285067383</v>
+        <v>0.9071421761745224</v>
       </c>
       <c r="F1708">
         <v>1</v>
       </c>
       <c r="G1708">
-        <v>0.008457305438333309</v>
+        <v>0.008480081631079394</v>
       </c>
       <c r="H1708">
-        <v>0.009161157871493261</v>
+        <v>0.008572857823825478</v>
       </c>
       <c r="I1708">
-        <v>0.1161475668400462</v>
+        <v>0.06722380725391552</v>
       </c>
       <c r="J1708">
         <v>1.277619274608493</v>
       </c>
       <c r="K1708">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1708">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1708">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1708">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1708">
         <v>1</v>
@@ -87525,13 +87528,13 @@
     </row>
     <row r="1709" spans="1:16">
       <c r="A1709" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1709" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1709">
-        <v>0.8243945139989091</v>
+        <v>0.8426945616666921</v>
       </c>
       <c r="D1709" t="s">
         <v>446</v>
@@ -87543,22 +87546,22 @@
         <v>1</v>
       </c>
       <c r="G1709">
-        <v>0.008975605486001091</v>
+        <v>0.008457305438333309</v>
       </c>
       <c r="H1709">
         <v>0.009161157871493261</v>
       </c>
       <c r="I1709">
-        <v>0.1344476145078293</v>
+        <v>0.1161475668400462</v>
       </c>
       <c r="J1709">
         <v>1.277619274608493</v>
       </c>
       <c r="K1709">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1709">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1709">
         <v>3.21</v>
@@ -87575,96 +87578,96 @@
     </row>
     <row r="1710" spans="1:16">
       <c r="A1710" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1710" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1710">
-        <v>0.8005072022455093</v>
+        <v>0.8243945139989091</v>
       </c>
       <c r="D1710" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1710">
-        <v>0.8805072022455094</v>
+        <v>0.9588421285067383</v>
       </c>
       <c r="F1710">
         <v>1</v>
       </c>
       <c r="G1710">
-        <v>0.008739492797754491</v>
+        <v>0.008975605486001091</v>
       </c>
       <c r="H1710">
-        <v>0.008819492797754491</v>
+        <v>0.009161157871493261</v>
       </c>
       <c r="I1710">
-        <v>0.08000000000000007</v>
+        <v>0.1344476145078293</v>
       </c>
       <c r="J1710">
-        <v>1.288796362907302</v>
+        <v>1.277619274608493</v>
       </c>
       <c r="K1710">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1710">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1710">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1710">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1710">
         <v>1</v>
       </c>
       <c r="P1710" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1711" spans="1:16">
       <c r="A1711" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1711" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1711">
-        <v>0.8064988749071667</v>
+        <v>0.8005072022455093</v>
       </c>
       <c r="D1711" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1711">
-        <v>0.8736109112780941</v>
+        <v>0.8805072022455094</v>
       </c>
       <c r="F1711">
         <v>1</v>
       </c>
       <c r="G1711">
-        <v>0.008513501125092833</v>
+        <v>0.008739492797754491</v>
       </c>
       <c r="H1711">
-        <v>0.008606389088721907</v>
+        <v>0.008819492797754491</v>
       </c>
       <c r="I1711">
-        <v>0.06711203637092744</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1711">
         <v>1.288796362907302</v>
       </c>
       <c r="K1711">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1711">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1711">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1711">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1711">
         <v>1</v>
@@ -87675,46 +87678,46 @@
     </row>
     <row r="1712" spans="1:16">
       <c r="A1712" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1712" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1712">
-        <v>0.8093868385362404</v>
+        <v>0.8064988749071667</v>
       </c>
       <c r="D1712" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1712">
-        <v>0.9229636750675603</v>
+        <v>0.8736109112780941</v>
       </c>
       <c r="F1712">
         <v>1</v>
       </c>
       <c r="G1712">
-        <v>0.00849061316146376</v>
+        <v>0.008513501125092833</v>
       </c>
       <c r="H1712">
-        <v>0.009197036324932439</v>
+        <v>0.008606389088721907</v>
       </c>
       <c r="I1712">
-        <v>0.1135768365313199</v>
+        <v>0.06711203637092744</v>
       </c>
       <c r="J1712">
         <v>1.288796362907302</v>
       </c>
       <c r="K1712">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1712">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1712">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1712">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1712">
         <v>1</v>
@@ -87725,13 +87728,13 @@
     </row>
     <row r="1713" spans="1:16">
       <c r="A1713" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1713" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1713">
-        <v>0.7887396023257072</v>
+        <v>0.8093868385362404</v>
       </c>
       <c r="D1713" t="s">
         <v>446</v>
@@ -87743,22 +87746,22 @@
         <v>1</v>
       </c>
       <c r="G1713">
-        <v>0.009011260397674293</v>
+        <v>0.00849061316146376</v>
       </c>
       <c r="H1713">
         <v>0.009197036324932439</v>
       </c>
       <c r="I1713">
-        <v>0.1342240727418531</v>
+        <v>0.1135768365313199</v>
       </c>
       <c r="J1713">
         <v>1.288796362907302</v>
       </c>
       <c r="K1713">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1713">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1713">
         <v>3.21</v>
@@ -87775,96 +87778,96 @@
     </row>
     <row r="1714" spans="1:16">
       <c r="A1714" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1714" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1714">
-        <v>0.7862584850929837</v>
+        <v>0.7887396023257072</v>
       </c>
       <c r="D1714" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1714">
-        <v>0.8533028278524921</v>
+        <v>0.9229636750675603</v>
       </c>
       <c r="F1714">
         <v>1</v>
       </c>
       <c r="G1714">
-        <v>0.008533741514907017</v>
+        <v>0.009011260397674293</v>
       </c>
       <c r="H1714">
-        <v>0.008626697172147509</v>
+        <v>0.009197036324932439</v>
       </c>
       <c r="I1714">
-        <v>0.06704434275950844</v>
+        <v>0.1342240727418531</v>
       </c>
       <c r="J1714">
-        <v>1.295565724049169</v>
+        <v>1.288796362907302</v>
       </c>
       <c r="K1714">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1714">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1714">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1714">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1714">
         <v>1</v>
       </c>
       <c r="P1714" t="s">
-        <v>260</v>
+        <v>574</v>
       </c>
     </row>
     <row r="1715" spans="1:16">
       <c r="A1715" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1715" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1715">
-        <v>0.7892141423334755</v>
+        <v>0.7862584850929837</v>
       </c>
       <c r="D1715" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1715">
-        <v>0.9012340258021663</v>
+        <v>0.8533028278524921</v>
       </c>
       <c r="F1715">
         <v>1</v>
       </c>
       <c r="G1715">
-        <v>0.008510785857666524</v>
+        <v>0.008533741514907017</v>
       </c>
       <c r="H1715">
-        <v>0.009218765974197834</v>
+        <v>0.008626697172147509</v>
       </c>
       <c r="I1715">
-        <v>0.1120198834686907</v>
+        <v>0.06704434275950844</v>
       </c>
       <c r="J1715">
         <v>1.295565724049169</v>
       </c>
       <c r="K1715">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1715">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1715">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1715">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1715">
         <v>1</v>
@@ -87875,13 +87878,13 @@
     </row>
     <row r="1716" spans="1:16">
       <c r="A1716" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1716" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1716">
-        <v>0.7671453402831503</v>
+        <v>0.7892141423334755</v>
       </c>
       <c r="D1716" t="s">
         <v>446</v>
@@ -87893,22 +87896,22 @@
         <v>1</v>
       </c>
       <c r="G1716">
-        <v>0.00903285465971685</v>
+        <v>0.008510785857666524</v>
       </c>
       <c r="H1716">
         <v>0.009218765974197834</v>
       </c>
       <c r="I1716">
-        <v>0.134088685519016</v>
+        <v>0.1120198834686907</v>
       </c>
       <c r="J1716">
         <v>1.295565724049169</v>
       </c>
       <c r="K1716">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1716">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1716">
         <v>3.21</v>
@@ -87925,96 +87928,96 @@
     </row>
     <row r="1717" spans="1:16">
       <c r="A1717" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1717" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1717">
-        <v>0.7524917367489325</v>
+        <v>0.7671453402831503</v>
       </c>
       <c r="D1717" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1717">
-        <v>0.819423147239732</v>
+        <v>0.9012340258021663</v>
       </c>
       <c r="F1717">
         <v>1</v>
       </c>
       <c r="G1717">
-        <v>0.008567508263251068</v>
+        <v>0.00903285465971685</v>
       </c>
       <c r="H1717">
-        <v>0.008660576852760268</v>
+        <v>0.009218765974197834</v>
       </c>
       <c r="I1717">
-        <v>0.06693141049079943</v>
+        <v>0.134088685519016</v>
       </c>
       <c r="J1717">
-        <v>1.306858950920089</v>
+        <v>1.295565724049169</v>
       </c>
       <c r="K1717">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1717">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1717">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1717">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1717">
         <v>1</v>
       </c>
       <c r="P1717" t="s">
-        <v>575</v>
+        <v>260</v>
       </c>
     </row>
     <row r="1718" spans="1:16">
       <c r="A1718" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1718" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1718">
-        <v>0.7555603262581339</v>
+        <v>0.7524917367489325</v>
       </c>
       <c r="D1718" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1718">
-        <v>0.8649827675465129</v>
+        <v>0.819423147239732</v>
       </c>
       <c r="F1718">
         <v>1</v>
       </c>
       <c r="G1718">
-        <v>0.008544439673741867</v>
+        <v>0.008567508263251068</v>
       </c>
       <c r="H1718">
-        <v>0.009255017232453486</v>
+        <v>0.008660576852760268</v>
       </c>
       <c r="I1718">
-        <v>0.1094224412883791</v>
+        <v>0.06693141049079943</v>
       </c>
       <c r="J1718">
         <v>1.306858950920089</v>
       </c>
       <c r="K1718">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1718">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1718">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1718">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1718">
         <v>1</v>
@@ -88025,13 +88028,13 @@
     </row>
     <row r="1719" spans="1:16">
       <c r="A1719" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1719" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1719">
-        <v>0.731119946564915</v>
+        <v>0.7555603262581339</v>
       </c>
       <c r="D1719" t="s">
         <v>446</v>
@@ -88043,22 +88046,22 @@
         <v>1</v>
       </c>
       <c r="G1719">
-        <v>0.009068880053435086</v>
+        <v>0.008544439673741867</v>
       </c>
       <c r="H1719">
         <v>0.009255017232453486</v>
       </c>
       <c r="I1719">
-        <v>0.133862820981598</v>
+        <v>0.1094224412883791</v>
       </c>
       <c r="J1719">
         <v>1.306858950920089</v>
       </c>
       <c r="K1719">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1719">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1719">
         <v>3.21</v>
@@ -88075,96 +88078,96 @@
     </row>
     <row r="1720" spans="1:16">
       <c r="A1720" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1720" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1720">
-        <v>0.747940275032922</v>
+        <v>0.731119946564915</v>
       </c>
       <c r="D1720" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1720">
-        <v>0.8148564632437347</v>
+        <v>0.8649827675465129</v>
       </c>
       <c r="F1720">
         <v>1</v>
       </c>
       <c r="G1720">
-        <v>0.008572059724967078</v>
+        <v>0.009068880053435086</v>
       </c>
       <c r="H1720">
-        <v>0.008665143536756265</v>
+        <v>0.009255017232453486</v>
       </c>
       <c r="I1720">
-        <v>0.06691618821081269</v>
+        <v>0.133862820981598</v>
       </c>
       <c r="J1720">
-        <v>1.308381178918755</v>
+        <v>1.306858950920089</v>
       </c>
       <c r="K1720">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1720">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1720">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1720">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1720">
         <v>1</v>
       </c>
       <c r="P1720" t="s">
-        <v>448</v>
+        <v>575</v>
       </c>
     </row>
     <row r="1721" spans="1:16">
       <c r="A1721" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1721" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1721">
-        <v>0.7510240868221101</v>
+        <v>0.747940275032922</v>
       </c>
       <c r="D1721" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1721">
-        <v>0.860096415670796</v>
+        <v>0.8148564632437347</v>
       </c>
       <c r="F1721">
         <v>1</v>
       </c>
       <c r="G1721">
-        <v>0.008548975913177891</v>
+        <v>0.008572059724967078</v>
       </c>
       <c r="H1721">
-        <v>0.009259903584329203</v>
+        <v>0.008665143536756265</v>
       </c>
       <c r="I1721">
-        <v>0.1090723288486859</v>
+        <v>0.06691618821081269</v>
       </c>
       <c r="J1721">
         <v>1.308381178918755</v>
       </c>
       <c r="K1721">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1721">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1721">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1721">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1721">
         <v>1</v>
@@ -88175,13 +88178,13 @@
     </row>
     <row r="1722" spans="1:16">
       <c r="A1722" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1722" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1722">
-        <v>0.7262640392491715</v>
+        <v>0.7510240868221101</v>
       </c>
       <c r="D1722" t="s">
         <v>446</v>
@@ -88193,22 +88196,22 @@
         <v>1</v>
       </c>
       <c r="G1722">
-        <v>0.009073735960750829</v>
+        <v>0.008548975913177891</v>
       </c>
       <c r="H1722">
         <v>0.009259903584329203</v>
       </c>
       <c r="I1722">
-        <v>0.1338323764216245</v>
+        <v>0.1090723288486859</v>
       </c>
       <c r="J1722">
         <v>1.308381178918755</v>
       </c>
       <c r="K1722">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1722">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1722">
         <v>3.21</v>
@@ -88225,96 +88228,96 @@
     </row>
     <row r="1723" spans="1:16">
       <c r="A1723" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1723" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1723">
-        <v>0.7508817338992388</v>
+        <v>0.7262640392491715</v>
       </c>
       <c r="D1723" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1723">
-        <v>0.817807759765123</v>
+        <v>0.860096415670796</v>
       </c>
       <c r="F1723">
         <v>1</v>
       </c>
       <c r="G1723">
-        <v>0.008569118266100762</v>
+        <v>0.009073735960750829</v>
       </c>
       <c r="H1723">
-        <v>0.008662192240234876</v>
+        <v>0.009259903584329203</v>
       </c>
       <c r="I1723">
-        <v>0.06692602586588414</v>
+        <v>0.1338323764216245</v>
       </c>
       <c r="J1723">
-        <v>1.307397413411626</v>
+        <v>1.308381178918755</v>
       </c>
       <c r="K1723">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1723">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1723">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1723">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1723">
         <v>1</v>
       </c>
       <c r="P1723" t="s">
-        <v>576</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1724" spans="1:16">
       <c r="A1724" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1724" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1724">
-        <v>0.7539557080333559</v>
+        <v>0.7508817338992388</v>
       </c>
       <c r="D1724" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1724">
-        <v>0.8632543029486808</v>
+        <v>0.817807759765123</v>
       </c>
       <c r="F1724">
         <v>1</v>
       </c>
       <c r="G1724">
-        <v>0.008546044291966644</v>
+        <v>0.008569118266100762</v>
       </c>
       <c r="H1724">
-        <v>0.009256745697051318</v>
+        <v>0.008662192240234876</v>
       </c>
       <c r="I1724">
-        <v>0.1092985949153249</v>
+        <v>0.06692602586588414</v>
       </c>
       <c r="J1724">
         <v>1.307397413411626</v>
       </c>
       <c r="K1724">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1724">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1724">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1724">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1724">
         <v>1</v>
@@ -88325,7 +88328,7 @@
     </row>
     <row r="1725" spans="1:16">
       <c r="A1725" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1725" t="s">
         <v>261</v>
@@ -88478,43 +88481,43 @@
         <v>0</v>
       </c>
       <c r="B1728" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1728">
-        <v>0.7280081951252568</v>
+        <v>0.7049987098493551</v>
       </c>
       <c r="D1728" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1728">
-        <v>0.7948577208614624</v>
+        <v>0.8386977613217637</v>
       </c>
       <c r="F1728">
         <v>1</v>
       </c>
       <c r="G1728">
-        <v>0.008591991804874743</v>
+        <v>0.009095001290150645</v>
       </c>
       <c r="H1728">
-        <v>0.008685142279138539</v>
+        <v>0.009281302238678237</v>
       </c>
       <c r="I1728">
-        <v>0.06684952573620562</v>
+        <v>0.1336990514724086</v>
       </c>
       <c r="J1728">
         <v>1.315047426379513</v>
       </c>
       <c r="K1728">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1728">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1728">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1728">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1728">
         <v>1</v>
@@ -88525,34 +88528,34 @@
     </row>
     <row r="1729" spans="1:16">
       <c r="A1729" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1729" t="s">
         <v>261</v>
       </c>
       <c r="C1729">
-        <v>0.7049987098493551</v>
+        <v>0.6966839628130383</v>
       </c>
       <c r="D1729" t="s">
         <v>446</v>
       </c>
       <c r="E1729">
-        <v>0.8386977613217637</v>
+        <v>0.8303308842099844</v>
       </c>
       <c r="F1729">
         <v>1</v>
       </c>
       <c r="G1729">
-        <v>0.009095001290150645</v>
+        <v>0.009103316037186962</v>
       </c>
       <c r="H1729">
-        <v>0.009281302238678237</v>
+        <v>0.009289669115790015</v>
       </c>
       <c r="I1729">
-        <v>0.1336990514724086</v>
+        <v>0.133646921396946</v>
       </c>
       <c r="J1729">
-        <v>1.315047426379513</v>
+        <v>1.317653930152653</v>
       </c>
       <c r="K1729">
         <v>3.19</v>
@@ -88570,7 +88573,7 @@
         <v>1</v>
       </c>
       <c r="P1729" t="s">
-        <v>578</v>
+        <v>256</v>
       </c>
     </row>
     <row r="1730" spans="1:16">
@@ -88578,81 +88581,81 @@
         <v>0</v>
       </c>
       <c r="B1730" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1730">
-        <v>0.7202147488435684</v>
+        <v>0.7014000886468699</v>
       </c>
       <c r="D1730" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1730">
-        <v>0.7870382095420423</v>
+        <v>0.8350765782308622</v>
       </c>
       <c r="F1730">
         <v>1</v>
       </c>
       <c r="G1730">
-        <v>0.008599785251156431</v>
+        <v>0.009098599911353131</v>
       </c>
       <c r="H1730">
-        <v>0.008692961790457957</v>
+        <v>0.009284923421769136</v>
       </c>
       <c r="I1730">
-        <v>0.06682346069847389</v>
+        <v>0.1336764895839924</v>
       </c>
       <c r="J1730">
-        <v>1.317653930152653</v>
+        <v>1.316175520800354</v>
       </c>
       <c r="K1730">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1730">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1730">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1730">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1730">
         <v>1</v>
       </c>
       <c r="P1730" t="s">
-        <v>255</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1731" spans="1:16">
       <c r="A1731" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1731" t="s">
         <v>261</v>
       </c>
       <c r="C1731">
-        <v>0.6966839628130383</v>
+        <v>0.7176262191292162</v>
       </c>
       <c r="D1731" t="s">
         <v>446</v>
       </c>
       <c r="E1731">
-        <v>0.8303308842099844</v>
+        <v>0.8514044399388032</v>
       </c>
       <c r="F1731">
         <v>1</v>
       </c>
       <c r="G1731">
-        <v>0.009103316037186962</v>
+        <v>0.009082373780870786</v>
       </c>
       <c r="H1731">
-        <v>0.009289669115790015</v>
+        <v>0.009268595560061196</v>
       </c>
       <c r="I1731">
-        <v>0.133646921396946</v>
+        <v>0.133778220809587</v>
       </c>
       <c r="J1731">
-        <v>1.317653930152653</v>
+        <v>1.311088959520622</v>
       </c>
       <c r="K1731">
         <v>3.19</v>
@@ -88670,7 +88673,7 @@
         <v>1</v>
       </c>
       <c r="P1731" t="s">
-        <v>255</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1732" spans="1:16">
@@ -88681,28 +88684,28 @@
         <v>261</v>
       </c>
       <c r="C1732">
-        <v>0.7014000886468699</v>
+        <v>0.7398286590454459</v>
       </c>
       <c r="D1732" t="s">
         <v>446</v>
       </c>
       <c r="E1732">
-        <v>0.8350765782308622</v>
+        <v>0.873746080105291</v>
       </c>
       <c r="F1732">
         <v>1</v>
       </c>
       <c r="G1732">
-        <v>0.009098599911353131</v>
+        <v>0.009060171340954553</v>
       </c>
       <c r="H1732">
-        <v>0.009284923421769136</v>
+        <v>0.00924625391989471</v>
       </c>
       <c r="I1732">
-        <v>0.1336764895839924</v>
+        <v>0.1339174210598451</v>
       </c>
       <c r="J1732">
-        <v>1.316175520800354</v>
+        <v>1.304128947007697</v>
       </c>
       <c r="K1732">
         <v>3.19</v>
@@ -88720,7 +88723,7 @@
         <v>1</v>
       </c>
       <c r="P1732" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1733" spans="1:16">
@@ -88731,28 +88734,28 @@
         <v>263</v>
       </c>
       <c r="C1733">
-        <v>0.7398440110333406</v>
+        <v>0.7913874491098194</v>
       </c>
       <c r="D1733" t="s">
         <v>450</v>
       </c>
       <c r="E1733">
-        <v>0.8067331214381346</v>
+        <v>0.858448945595137</v>
       </c>
       <c r="F1733">
         <v>1</v>
       </c>
       <c r="G1733">
-        <v>0.008580155988966659</v>
+        <v>0.00852861255089018</v>
       </c>
       <c r="H1733">
-        <v>0.008673266878561865</v>
+        <v>0.008621551054404862</v>
       </c>
       <c r="I1733">
-        <v>0.06688911040479395</v>
+        <v>0.06706149648531756</v>
       </c>
       <c r="J1733">
-        <v>1.311088959520622</v>
+        <v>1.293850351468288</v>
       </c>
       <c r="K1733">
         <v>2.99</v>
@@ -88770,7 +88773,7 @@
         <v>1</v>
       </c>
       <c r="P1733" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1734" spans="1:16">
@@ -88781,28 +88784,28 @@
         <v>261</v>
       </c>
       <c r="C1734">
-        <v>0.7176262191292162</v>
+        <v>0.7726173788161628</v>
       </c>
       <c r="D1734" t="s">
         <v>446</v>
       </c>
       <c r="E1734">
-        <v>0.8514044399388032</v>
+        <v>0.9067403717867961</v>
       </c>
       <c r="F1734">
         <v>1</v>
       </c>
       <c r="G1734">
-        <v>0.009082373780870786</v>
+        <v>0.009027382621183837</v>
       </c>
       <c r="H1734">
-        <v>0.009268595560061196</v>
+        <v>0.009213259628213203</v>
       </c>
       <c r="I1734">
-        <v>0.133778220809587</v>
+        <v>0.1341229929706333</v>
       </c>
       <c r="J1734">
-        <v>1.311088959520622</v>
+        <v>1.293850351468288</v>
       </c>
       <c r="K1734">
         <v>3.19</v>
@@ -88820,7 +88823,7 @@
         <v>1</v>
       </c>
       <c r="P1734" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1735" spans="1:16">
@@ -88831,28 +88834,28 @@
         <v>261</v>
       </c>
       <c r="C1735">
-        <v>0.7398286590454459</v>
+        <v>0.8072892339066007</v>
       </c>
       <c r="D1735" t="s">
         <v>446</v>
       </c>
       <c r="E1735">
-        <v>0.873746080105291</v>
+        <v>0.9416296052790551</v>
       </c>
       <c r="F1735">
         <v>1</v>
       </c>
       <c r="G1735">
-        <v>0.009060171340954553</v>
+        <v>0.0089927107660934</v>
       </c>
       <c r="H1735">
-        <v>0.00924625391989471</v>
+        <v>0.009178370394720943</v>
       </c>
       <c r="I1735">
-        <v>0.1339174210598451</v>
+        <v>0.1343403713724545</v>
       </c>
       <c r="J1735">
-        <v>1.304128947007697</v>
+        <v>1.282981431377241</v>
       </c>
       <c r="K1735">
         <v>3.19</v>
@@ -88870,7 +88873,7 @@
         <v>1</v>
       </c>
       <c r="P1735" t="s">
-        <v>444</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1736" spans="1:16">
@@ -88878,81 +88881,81 @@
         <v>0</v>
       </c>
       <c r="B1736" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1736">
+        <v>0.8255353424422802</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>446</v>
+      </c>
+      <c r="E1736">
+        <v>0.9599901094795351</v>
+      </c>
+      <c r="F1736">
+        <v>1</v>
+      </c>
+      <c r="G1736">
+        <v>0.008974464657557722</v>
+      </c>
+      <c r="H1736">
+        <v>0.009160009890520463</v>
+      </c>
+      <c r="I1736">
+        <v>0.1344547670372549</v>
+      </c>
+      <c r="J1736">
+        <v>1.277261648137216</v>
+      </c>
+      <c r="K1736">
+        <v>3.19</v>
+      </c>
+      <c r="L1736">
+        <v>4.9</v>
+      </c>
+      <c r="M1736">
+        <v>3.21</v>
+      </c>
+      <c r="N1736">
+        <v>5.06</v>
+      </c>
+      <c r="O1736">
+        <v>1</v>
+      </c>
+      <c r="P1736" t="s">
         <v>263</v>
-      </c>
-      <c r="C1736">
-        <v>0.7913874491098194</v>
-      </c>
-      <c r="D1736" t="s">
-        <v>445</v>
-      </c>
-      <c r="E1736">
-        <v>0.8943259526245027</v>
-      </c>
-      <c r="F1736">
-        <v>1</v>
-      </c>
-      <c r="G1736">
-        <v>0.00852861255089018</v>
-      </c>
-      <c r="H1736">
-        <v>0.008605674047375498</v>
-      </c>
-      <c r="I1736">
-        <v>0.1029385035146833</v>
-      </c>
-      <c r="J1736">
-        <v>1.293850351468288</v>
-      </c>
-      <c r="K1736">
-        <v>2.99</v>
-      </c>
-      <c r="L1736">
-        <v>4.66</v>
-      </c>
-      <c r="M1736">
-        <v>2.98</v>
-      </c>
-      <c r="N1736">
-        <v>4.75</v>
-      </c>
-      <c r="O1736">
-        <v>1</v>
-      </c>
-      <c r="P1736" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="1737" spans="1:16">
       <c r="A1737" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1737" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1737">
-        <v>0.794325952624503</v>
+        <v>0.8604710066405516</v>
       </c>
       <c r="D1737" t="s">
         <v>446</v>
       </c>
       <c r="E1737">
-        <v>0.9067403717867961</v>
+        <v>0.97799058097858</v>
       </c>
       <c r="F1737">
         <v>1</v>
       </c>
       <c r="G1737">
-        <v>0.008505674047375499</v>
+        <v>0.008439528993359448</v>
       </c>
       <c r="H1737">
-        <v>0.009213259628213203</v>
+        <v>0.00914200941902142</v>
       </c>
       <c r="I1737">
-        <v>0.1124144191622931</v>
+        <v>0.1175195743380284</v>
       </c>
       <c r="J1737">
-        <v>1.293850351468288</v>
+        <v>1.271654024617265</v>
       </c>
       <c r="K1737">
         <v>2.98</v>
@@ -88970,39 +88973,39 @@
         <v>1</v>
       </c>
       <c r="P1737" t="s">
-        <v>580</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1738" spans="1:16">
       <c r="A1738" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1738" t="s">
         <v>261</v>
       </c>
       <c r="C1738">
-        <v>0.7726173788161628</v>
+        <v>0.8434236614709256</v>
       </c>
       <c r="D1738" t="s">
         <v>446</v>
       </c>
       <c r="E1738">
-        <v>0.9067403717867961</v>
+        <v>0.97799058097858</v>
       </c>
       <c r="F1738">
         <v>1</v>
       </c>
       <c r="G1738">
-        <v>0.009027382621183837</v>
+        <v>0.008956576338529075</v>
       </c>
       <c r="H1738">
-        <v>0.009213259628213203</v>
+        <v>0.00914200941902142</v>
       </c>
       <c r="I1738">
-        <v>0.1341229929706333</v>
+        <v>0.1345669195076544</v>
       </c>
       <c r="J1738">
-        <v>1.293850351468288</v>
+        <v>1.271654024617265</v>
       </c>
       <c r="K1738">
         <v>3.19</v>
@@ -89020,7 +89023,7 @@
         <v>1</v>
       </c>
       <c r="P1738" t="s">
-        <v>580</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1739" spans="1:16">
@@ -89028,49 +89031,49 @@
         <v>0</v>
       </c>
       <c r="B1739" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C1739">
-        <v>0.8238855201820487</v>
+        <v>0.8778494143553166</v>
       </c>
       <c r="D1739" t="s">
+        <v>446</v>
+      </c>
+      <c r="E1739">
+        <v>0.99671027519482</v>
+      </c>
+      <c r="F1739">
+        <v>1</v>
+      </c>
+      <c r="G1739">
+        <v>0.008422150585644684</v>
+      </c>
+      <c r="H1739">
+        <v>0.009123289724805179</v>
+      </c>
+      <c r="I1739">
+        <v>0.1188608608395034</v>
+      </c>
+      <c r="J1739">
+        <v>1.265822344176068</v>
+      </c>
+      <c r="K1739">
+        <v>2.98</v>
+      </c>
+      <c r="L1739">
+        <v>4.65</v>
+      </c>
+      <c r="M1739">
+        <v>3.21</v>
+      </c>
+      <c r="N1739">
+        <v>5.06</v>
+      </c>
+      <c r="O1739">
+        <v>1</v>
+      </c>
+      <c r="P1739" t="s">
         <v>445</v>
-      </c>
-      <c r="E1739">
-        <v>0.9267153344958214</v>
-      </c>
-      <c r="F1739">
-        <v>1</v>
-      </c>
-      <c r="G1739">
-        <v>0.008496114479817952</v>
-      </c>
-      <c r="H1739">
-        <v>0.00857328466550418</v>
-      </c>
-      <c r="I1739">
-        <v>0.1028298143137727</v>
-      </c>
-      <c r="J1739">
-        <v>1.282981431377241</v>
-      </c>
-      <c r="K1739">
-        <v>2.99</v>
-      </c>
-      <c r="L1739">
-        <v>4.66</v>
-      </c>
-      <c r="M1739">
-        <v>2.98</v>
-      </c>
-      <c r="N1739">
-        <v>4.75</v>
-      </c>
-      <c r="O1739">
-        <v>1</v>
-      </c>
-      <c r="P1739" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="1740" spans="1:16">
@@ -89081,28 +89084,28 @@
         <v>261</v>
       </c>
       <c r="C1740">
-        <v>0.8072892339066007</v>
+        <v>0.8620267220783422</v>
       </c>
       <c r="D1740" t="s">
         <v>446</v>
       </c>
       <c r="E1740">
-        <v>0.9416296052790551</v>
+        <v>0.99671027519482</v>
       </c>
       <c r="F1740">
         <v>1</v>
       </c>
       <c r="G1740">
-        <v>0.0089927107660934</v>
+        <v>0.008937973277921658</v>
       </c>
       <c r="H1740">
-        <v>0.009178370394720943</v>
+        <v>0.009123289724805179</v>
       </c>
       <c r="I1740">
-        <v>0.1343403713724545</v>
+        <v>0.1346835531164778</v>
       </c>
       <c r="J1740">
-        <v>1.282981431377241</v>
+        <v>1.265822344176068</v>
       </c>
       <c r="K1740">
         <v>3.19</v>
@@ -89120,7 +89123,7 @@
         <v>1</v>
       </c>
       <c r="P1740" t="s">
-        <v>256</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1741" spans="1:16">
@@ -89128,37 +89131,37 @@
         <v>0</v>
       </c>
       <c r="B1741" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C1741">
-        <v>0.8437602885510955</v>
+        <v>0.8787266818708703</v>
       </c>
       <c r="D1741" t="s">
         <v>446</v>
       </c>
       <c r="E1741">
-        <v>0.9599901094795351</v>
+        <v>1.013514936929621</v>
       </c>
       <c r="F1741">
         <v>1</v>
       </c>
       <c r="G1741">
-        <v>0.008456239711448906</v>
+        <v>0.008921273318129131</v>
       </c>
       <c r="H1741">
-        <v>0.009160009890520463</v>
+        <v>0.009106485063070378</v>
       </c>
       <c r="I1741">
-        <v>0.1162298209284396</v>
+        <v>0.1347882550587505</v>
       </c>
       <c r="J1741">
-        <v>1.277261648137216</v>
+        <v>1.260587247062423</v>
       </c>
       <c r="K1741">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1741">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1741">
         <v>3.21</v>
@@ -89170,39 +89173,39 @@
         <v>1</v>
       </c>
       <c r="P1741" t="s">
-        <v>263</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1742" spans="1:16">
       <c r="A1742" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1742" t="s">
         <v>261</v>
       </c>
       <c r="C1742">
-        <v>0.8255353424422802</v>
+        <v>0.8827952100288972</v>
       </c>
       <c r="D1742" t="s">
         <v>446</v>
       </c>
       <c r="E1742">
-        <v>0.9599901094795351</v>
+        <v>1.017608973101177</v>
       </c>
       <c r="F1742">
         <v>1</v>
       </c>
       <c r="G1742">
-        <v>0.008974464657557722</v>
+        <v>0.008917204789971104</v>
       </c>
       <c r="H1742">
-        <v>0.009160009890520463</v>
+        <v>0.009102391026898821</v>
       </c>
       <c r="I1742">
-        <v>0.1344547670372549</v>
+        <v>0.1348137630722803</v>
       </c>
       <c r="J1742">
-        <v>1.277261648137216</v>
+        <v>1.259311846385926</v>
       </c>
       <c r="K1742">
         <v>3.19</v>
@@ -89220,89 +89223,89 @@
         <v>1</v>
       </c>
       <c r="P1742" t="s">
-        <v>263</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1743" spans="1:16">
       <c r="A1743" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1743" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C1743">
-        <v>0.8604710066405516</v>
+        <v>1.135760802348193</v>
       </c>
       <c r="D1743" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1743">
-        <v>0.97799058097858</v>
+        <v>0.9179814469566154</v>
       </c>
       <c r="F1743">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1743">
-        <v>0.008439528993359448</v>
+        <v>0.009044239197651807</v>
       </c>
       <c r="H1743">
-        <v>0.00914200941902142</v>
+        <v>0.008902018553043385</v>
       </c>
       <c r="I1743">
-        <v>0.1175195743380284</v>
+        <v>0.2177793553915772</v>
       </c>
       <c r="J1743">
-        <v>1.271654024617265</v>
+        <v>1.259311846385926</v>
       </c>
       <c r="K1743">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="L1743">
-        <v>4.65</v>
+        <v>5.09</v>
       </c>
       <c r="M1743">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N1743">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="O1743">
         <v>1</v>
       </c>
       <c r="P1743" t="s">
-        <v>450</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1744" spans="1:16">
       <c r="A1744" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1744" t="s">
         <v>261</v>
       </c>
       <c r="C1744">
-        <v>0.8434236614709256</v>
+        <v>0.8817169145093411</v>
       </c>
       <c r="D1744" t="s">
         <v>446</v>
       </c>
       <c r="E1744">
-        <v>0.97799058097858</v>
+        <v>1.016523917108145</v>
       </c>
       <c r="F1744">
         <v>1</v>
       </c>
       <c r="G1744">
-        <v>0.008956576338529075</v>
+        <v>0.00891828308549066</v>
       </c>
       <c r="H1744">
-        <v>0.00914200941902142</v>
+        <v>0.009103476082891854</v>
       </c>
       <c r="I1744">
-        <v>0.1345669195076544</v>
+        <v>0.1348070025988042</v>
       </c>
       <c r="J1744">
-        <v>1.271654024617265</v>
+        <v>1.259649870059768</v>
       </c>
       <c r="K1744">
         <v>3.19</v>
@@ -89320,89 +89323,89 @@
         <v>1</v>
       </c>
       <c r="P1744" t="s">
-        <v>450</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1745" spans="1:16">
       <c r="A1745" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1745" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C1745">
-        <v>0.8778494143553166</v>
+        <v>1.134699408012329</v>
       </c>
       <c r="D1745" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1745">
-        <v>0.99671027519482</v>
+        <v>0.9169099119105364</v>
       </c>
       <c r="F1745">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1745">
-        <v>0.008422150585644684</v>
+        <v>0.009045300591987672</v>
       </c>
       <c r="H1745">
-        <v>0.009123289724805179</v>
+        <v>0.008903090088089463</v>
       </c>
       <c r="I1745">
-        <v>0.1188608608395034</v>
+        <v>0.2177894961017923</v>
       </c>
       <c r="J1745">
-        <v>1.265822344176068</v>
+        <v>1.259649870059768</v>
       </c>
       <c r="K1745">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="L1745">
-        <v>4.65</v>
+        <v>5.09</v>
       </c>
       <c r="M1745">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N1745">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="O1745">
         <v>1</v>
       </c>
       <c r="P1745" t="s">
-        <v>445</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1746" spans="1:16">
       <c r="A1746" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1746" t="s">
         <v>261</v>
       </c>
       <c r="C1746">
-        <v>0.8620267220783422</v>
+        <v>0.8836581328456559</v>
       </c>
       <c r="D1746" t="s">
         <v>446</v>
       </c>
       <c r="E1746">
-        <v>0.99671027519482</v>
+        <v>1.018477306092337</v>
       </c>
       <c r="F1746">
         <v>1</v>
       </c>
       <c r="G1746">
-        <v>0.008937973277921658</v>
+        <v>0.008916341867154344</v>
       </c>
       <c r="H1746">
-        <v>0.009123289724805179</v>
+        <v>0.009101522693907661</v>
       </c>
       <c r="I1746">
-        <v>0.1346835531164778</v>
+        <v>0.1348191732466812</v>
       </c>
       <c r="J1746">
-        <v>1.265822344176068</v>
+        <v>1.259041337665939</v>
       </c>
       <c r="K1746">
         <v>3.19</v>
@@ -89420,107 +89423,107 @@
         <v>1</v>
       </c>
       <c r="P1746" t="s">
-        <v>445</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1747" spans="1:16">
       <c r="A1747" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1747" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C1747">
-        <v>0.893450003753979</v>
+        <v>1.136610199728953</v>
       </c>
       <c r="D1747" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1747">
-        <v>1.013514936929621</v>
+        <v>0.918838959598975</v>
       </c>
       <c r="F1747">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1747">
-        <v>0.008406549996246021</v>
+        <v>0.009043389800271048</v>
       </c>
       <c r="H1747">
-        <v>0.009106485063070378</v>
+        <v>0.008901161040401026</v>
       </c>
       <c r="I1747">
-        <v>0.1200649331756418</v>
+        <v>0.2177712401299776</v>
       </c>
       <c r="J1747">
-        <v>1.260587247062423</v>
+        <v>1.259041337665939</v>
       </c>
       <c r="K1747">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="L1747">
-        <v>4.65</v>
+        <v>5.09</v>
       </c>
       <c r="M1747">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N1747">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="O1747">
         <v>1</v>
       </c>
       <c r="P1747" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1748" spans="1:16">
       <c r="A1748" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1748" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1748">
+        <v>1.131086318915693</v>
+      </c>
+      <c r="D1748" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1748">
+        <v>0.9132623028543789</v>
+      </c>
+      <c r="F1748">
+        <v>-1</v>
+      </c>
+      <c r="G1748">
+        <v>0.009048913681084306</v>
+      </c>
+      <c r="H1748">
+        <v>0.00890673769714562</v>
+      </c>
+      <c r="I1748">
+        <v>0.2178240160613143</v>
+      </c>
+      <c r="J1748">
+        <v>1.260800535377168</v>
+      </c>
+      <c r="K1748">
+        <v>3.14</v>
+      </c>
+      <c r="L1748">
+        <v>5.09</v>
+      </c>
+      <c r="M1748">
+        <v>3.17</v>
+      </c>
+      <c r="N1748">
+        <v>4.91</v>
+      </c>
+      <c r="O1748">
+        <v>1</v>
+      </c>
+      <c r="P1748" t="s">
         <v>261</v>
-      </c>
-      <c r="C1748">
-        <v>0.8787266818708703</v>
-      </c>
-      <c r="D1748" t="s">
-        <v>446</v>
-      </c>
-      <c r="E1748">
-        <v>1.013514936929621</v>
-      </c>
-      <c r="F1748">
-        <v>1</v>
-      </c>
-      <c r="G1748">
-        <v>0.008921273318129131</v>
-      </c>
-      <c r="H1748">
-        <v>0.009106485063070378</v>
-      </c>
-      <c r="I1748">
-        <v>0.1347882550587505</v>
-      </c>
-      <c r="J1748">
-        <v>1.260587247062423</v>
-      </c>
-      <c r="K1748">
-        <v>3.19</v>
-      </c>
-      <c r="L1748">
-        <v>4.9</v>
-      </c>
-      <c r="M1748">
-        <v>3.21</v>
-      </c>
-      <c r="N1748">
-        <v>5.06</v>
-      </c>
-      <c r="O1748">
-        <v>1</v>
-      </c>
-      <c r="P1748" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="1749" spans="1:16">
@@ -89528,99 +89531,99 @@
         <v>0</v>
       </c>
       <c r="B1749" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C1749">
-        <v>0.8972506977699415</v>
+        <v>1.127143579938229</v>
       </c>
       <c r="D1749" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1749">
+        <v>0.909281894396238</v>
+      </c>
+      <c r="F1749">
+        <v>-1</v>
+      </c>
+      <c r="G1749">
+        <v>0.00905285642006177</v>
+      </c>
+      <c r="H1749">
+        <v>0.008910718105603763</v>
+      </c>
+      <c r="I1749">
+        <v>0.2178616855419908</v>
+      </c>
+      <c r="J1749">
+        <v>1.262056184733048</v>
+      </c>
+      <c r="K1749">
+        <v>3.14</v>
+      </c>
+      <c r="L1749">
+        <v>5.09</v>
+      </c>
+      <c r="M1749">
+        <v>3.17</v>
+      </c>
+      <c r="N1749">
+        <v>4.91</v>
+      </c>
+      <c r="O1749">
+        <v>1</v>
+      </c>
+      <c r="P1749" t="s">
         <v>446</v>
-      </c>
-      <c r="E1749">
-        <v>1.017608973101177</v>
-      </c>
-      <c r="F1749">
-        <v>1</v>
-      </c>
-      <c r="G1749">
-        <v>0.00840274930223006</v>
-      </c>
-      <c r="H1749">
-        <v>0.009102391026898821</v>
-      </c>
-      <c r="I1749">
-        <v>0.120358275331236</v>
-      </c>
-      <c r="J1749">
-        <v>1.259311846385926</v>
-      </c>
-      <c r="K1749">
-        <v>2.98</v>
-      </c>
-      <c r="L1749">
-        <v>4.65</v>
-      </c>
-      <c r="M1749">
-        <v>3.21</v>
-      </c>
-      <c r="N1749">
-        <v>5.06</v>
-      </c>
-      <c r="O1749">
-        <v>1</v>
-      </c>
-      <c r="P1749" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="1750" spans="1:16">
       <c r="A1750" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1750" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C1750">
-        <v>0.8827952100288972</v>
+        <v>1.123418970437326</v>
       </c>
       <c r="D1750" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1750">
-        <v>1.017608973101177</v>
+        <v>0.9055216994542441</v>
       </c>
       <c r="F1750">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1750">
-        <v>0.008917204789971104</v>
+        <v>0.009056581029562675</v>
       </c>
       <c r="H1750">
-        <v>0.009102391026898821</v>
+        <v>0.008914478300545757</v>
       </c>
       <c r="I1750">
-        <v>0.1348137630722803</v>
+        <v>0.217897270983082</v>
       </c>
       <c r="J1750">
-        <v>1.259311846385926</v>
+        <v>1.263242366102762</v>
       </c>
       <c r="K1750">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="L1750">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="M1750">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N1750">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="O1750">
         <v>1</v>
       </c>
       <c r="P1750" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1751" spans="1:16">
@@ -89628,149 +89631,49 @@
         <v>0</v>
       </c>
       <c r="B1751" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C1751">
-        <v>0.8817169145093411</v>
+        <v>1.103124629069044</v>
       </c>
       <c r="D1751" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1751">
-        <v>1.016523917108145</v>
+        <v>0.8850334631047359</v>
       </c>
       <c r="F1751">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1751">
-        <v>0.00891828308549066</v>
+        <v>0.009076875370930956</v>
       </c>
       <c r="H1751">
-        <v>0.009103476082891854</v>
+        <v>0.008934966536895263</v>
       </c>
       <c r="I1751">
-        <v>0.1348070025988042</v>
+        <v>0.2180911659643079</v>
       </c>
       <c r="J1751">
-        <v>1.259649870059768</v>
+        <v>1.269705532143617</v>
       </c>
       <c r="K1751">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="L1751">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="M1751">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N1751">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="O1751">
         <v>1</v>
       </c>
       <c r="P1751" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="1752" spans="1:16">
-      <c r="A1752" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1752" t="s">
-        <v>261</v>
-      </c>
-      <c r="C1752">
-        <v>0.8836581328456559</v>
-      </c>
-      <c r="D1752" t="s">
-        <v>446</v>
-      </c>
-      <c r="E1752">
-        <v>1.018477306092337</v>
-      </c>
-      <c r="F1752">
-        <v>1</v>
-      </c>
-      <c r="G1752">
-        <v>0.008916341867154344</v>
-      </c>
-      <c r="H1752">
-        <v>0.009101522693907661</v>
-      </c>
-      <c r="I1752">
-        <v>0.1348191732466812</v>
-      </c>
-      <c r="J1752">
-        <v>1.259041337665939</v>
-      </c>
-      <c r="K1752">
-        <v>3.19</v>
-      </c>
-      <c r="L1752">
-        <v>4.9</v>
-      </c>
-      <c r="M1752">
-        <v>3.21</v>
-      </c>
-      <c r="N1752">
-        <v>5.06</v>
-      </c>
-      <c r="O1752">
-        <v>1</v>
-      </c>
-      <c r="P1752" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="1753" spans="1:16">
-      <c r="A1753" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1753" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1753">
-        <v>0.9435585233122543</v>
-      </c>
-      <c r="D1753" t="s">
-        <v>258</v>
-      </c>
-      <c r="E1753">
-        <v>1.036661332548907</v>
-      </c>
-      <c r="F1753">
-        <v>1</v>
-      </c>
-      <c r="G1753">
-        <v>0.009096441476687743</v>
-      </c>
-      <c r="H1753">
-        <v>0.009063338667451092</v>
-      </c>
-      <c r="I1753">
-        <v>0.09310280923665282</v>
-      </c>
-      <c r="J1753">
-        <v>1.262056184733048</v>
-      </c>
-      <c r="K1753">
-        <v>3.23</v>
-      </c>
-      <c r="L1753">
-        <v>5.02</v>
-      </c>
-      <c r="M1753">
-        <v>3.18</v>
-      </c>
-      <c r="N1753">
-        <v>5.05</v>
-      </c>
-      <c r="O1753">
-        <v>1</v>
-      </c>
-      <c r="P1753" t="s">
-        <v>446</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5265" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5253" uniqueCount="585">
   <si>
     <t>trade_time</t>
   </si>
@@ -2126,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1751"/>
+  <dimension ref="A1:P1747"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -85187,10 +85187,10 @@
         <v>1.580815540542695</v>
       </c>
       <c r="D1662" t="s">
-        <v>447</v>
+        <v>264</v>
       </c>
       <c r="E1662">
-        <v>1.451724925635329</v>
+        <v>1.664453080913228</v>
       </c>
       <c r="F1662">
         <v>-1</v>
@@ -85199,10 +85199,10 @@
         <v>0.008519184459457303</v>
       </c>
       <c r="H1662">
-        <v>0.008368275074364672</v>
+        <v>0.008515546919086773</v>
       </c>
       <c r="I1662">
-        <v>0.1290906149073665</v>
+        <v>-0.08363754037053228</v>
       </c>
       <c r="J1662">
         <v>1.090938509263303</v>
@@ -85214,10 +85214,10 @@
         <v>5.05</v>
       </c>
       <c r="M1662">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="N1662">
-        <v>4.91</v>
+        <v>5.09</v>
       </c>
       <c r="O1662">
         <v>1</v>
@@ -86128,96 +86128,96 @@
     </row>
     <row r="1681" spans="1:16">
       <c r="A1681" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1681" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C1681">
-        <v>1.199709616662221</v>
+        <v>1.318212905870849</v>
       </c>
       <c r="D1681" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E1681">
-        <v>1.080937130973034</v>
+        <v>1.189948085412137</v>
       </c>
       <c r="F1681">
         <v>-1</v>
       </c>
       <c r="G1681">
-        <v>0.00804029038333778</v>
+        <v>0.00878178709412915</v>
       </c>
       <c r="H1681">
-        <v>0.008139062869026967</v>
+        <v>0.008630051914587863</v>
       </c>
       <c r="I1681">
-        <v>0.118772485689187</v>
+        <v>0.1282648204587127</v>
       </c>
       <c r="J1681">
-        <v>1.208583174324304</v>
+        <v>1.173517954128664</v>
       </c>
       <c r="K1681">
-        <v>2.83</v>
+        <v>3.18</v>
       </c>
       <c r="L1681">
-        <v>4.62</v>
+        <v>5.05</v>
       </c>
       <c r="M1681">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="N1681">
-        <v>4.61</v>
+        <v>4.91</v>
       </c>
       <c r="O1681">
         <v>1</v>
       </c>
       <c r="P1681" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1682" spans="1:16">
       <c r="A1682" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1682" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C1682">
-        <v>1.047563823081144</v>
+        <v>1.199709616662221</v>
       </c>
       <c r="D1682" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E1682">
-        <v>1.127563823081144</v>
+        <v>1.080937130973034</v>
       </c>
       <c r="F1682">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1682">
-        <v>0.008492436176918855</v>
+        <v>0.00804029038333778</v>
       </c>
       <c r="H1682">
-        <v>0.008572436176918854</v>
+        <v>0.008139062869026967</v>
       </c>
       <c r="I1682">
-        <v>0.08000000000000007</v>
+        <v>0.118772485689187</v>
       </c>
       <c r="J1682">
         <v>1.208583174324304</v>
       </c>
       <c r="K1682">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1682">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1682">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1682">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1682">
         <v>1</v>
@@ -86228,46 +86228,46 @@
     </row>
     <row r="1683" spans="1:16">
       <c r="A1683" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1683" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1683">
-        <v>1.046336308770332</v>
+        <v>1.047563823081144</v>
       </c>
       <c r="D1683" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E1683">
-        <v>1.148422140513575</v>
+        <v>1.127563823081144</v>
       </c>
       <c r="F1683">
         <v>1</v>
       </c>
       <c r="G1683">
-        <v>0.008273663691229668</v>
+        <v>0.008492436176918855</v>
       </c>
       <c r="H1683">
-        <v>0.008351577859486425</v>
+        <v>0.008572436176918854</v>
       </c>
       <c r="I1683">
-        <v>0.1020858317432429</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1683">
         <v>1.208583174324304</v>
       </c>
       <c r="K1683">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1683">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1683">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="N1683">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="O1683">
         <v>1</v>
@@ -86278,46 +86278,46 @@
     </row>
     <row r="1684" spans="1:16">
       <c r="A1684" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1684" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1684">
-        <v>1.048422140513575</v>
+        <v>1.046336308770332</v>
       </c>
       <c r="D1684" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E1684">
-        <v>1.180448010418985</v>
+        <v>1.148422140513575</v>
       </c>
       <c r="F1684">
         <v>1</v>
       </c>
       <c r="G1684">
-        <v>0.008251577859486424</v>
+        <v>0.008273663691229668</v>
       </c>
       <c r="H1684">
-        <v>0.008939551989581015</v>
+        <v>0.008351577859486425</v>
       </c>
       <c r="I1684">
-        <v>0.1320258699054095</v>
+        <v>0.1020858317432429</v>
       </c>
       <c r="J1684">
         <v>1.208583174324304</v>
       </c>
       <c r="K1684">
+        <v>2.99</v>
+      </c>
+      <c r="L1684">
+        <v>4.66</v>
+      </c>
+      <c r="M1684">
         <v>2.98</v>
       </c>
-      <c r="L1684">
-        <v>4.65</v>
-      </c>
-      <c r="M1684">
-        <v>3.21</v>
-      </c>
       <c r="N1684">
-        <v>5.06</v>
+        <v>4.75</v>
       </c>
       <c r="O1684">
         <v>1</v>
@@ -86328,13 +86328,13 @@
     </row>
     <row r="1685" spans="1:16">
       <c r="A1685" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1685" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1685">
-        <v>1.044619673905472</v>
+        <v>1.048422140513575</v>
       </c>
       <c r="D1685" t="s">
         <v>446</v>
@@ -86346,22 +86346,22 @@
         <v>1</v>
       </c>
       <c r="G1685">
-        <v>0.008755380326094528</v>
+        <v>0.008251577859486424</v>
       </c>
       <c r="H1685">
         <v>0.008939551989581015</v>
       </c>
       <c r="I1685">
-        <v>0.1358283365135131</v>
+        <v>0.1320258699054095</v>
       </c>
       <c r="J1685">
         <v>1.208583174324304</v>
       </c>
       <c r="K1685">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1685">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1685">
         <v>3.21</v>
@@ -86378,96 +86378,96 @@
     </row>
     <row r="1686" spans="1:16">
       <c r="A1686" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1686" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1686">
-        <v>1.148290651113722</v>
+        <v>1.044619673905472</v>
       </c>
       <c r="D1686" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E1686">
-        <v>1.027882933304618</v>
+        <v>1.180448010418985</v>
       </c>
       <c r="F1686">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1686">
-        <v>0.008091709348886278</v>
+        <v>0.008755380326094528</v>
       </c>
       <c r="H1686">
-        <v>0.008192117066695381</v>
+        <v>0.008939551989581015</v>
       </c>
       <c r="I1686">
-        <v>0.1204077178091039</v>
+        <v>0.1358283365135131</v>
       </c>
       <c r="J1686">
-        <v>1.226752420101158</v>
+        <v>1.208583174324304</v>
       </c>
       <c r="K1686">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="L1686">
-        <v>4.62</v>
+        <v>4.9</v>
       </c>
       <c r="M1686">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="N1686">
-        <v>4.61</v>
+        <v>5.06</v>
       </c>
       <c r="O1686">
         <v>1</v>
       </c>
       <c r="P1686" t="s">
-        <v>440</v>
+        <v>250</v>
       </c>
     </row>
     <row r="1687" spans="1:16">
       <c r="A1687" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1687" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C1687">
-        <v>0.9916025460884326</v>
+        <v>1.148290651113722</v>
       </c>
       <c r="D1687" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E1687">
-        <v>1.071602546088433</v>
+        <v>1.027882933304618</v>
       </c>
       <c r="F1687">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1687">
-        <v>0.008548397453911566</v>
+        <v>0.008091709348886278</v>
       </c>
       <c r="H1687">
-        <v>0.008628397453911568</v>
+        <v>0.008192117066695381</v>
       </c>
       <c r="I1687">
-        <v>0.08000000000000007</v>
+        <v>0.1204077178091039</v>
       </c>
       <c r="J1687">
         <v>1.226752420101158</v>
       </c>
       <c r="K1687">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="L1687">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="M1687">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="N1687">
-        <v>4.85</v>
+        <v>4.61</v>
       </c>
       <c r="O1687">
         <v>1</v>
@@ -86478,46 +86478,46 @@
     </row>
     <row r="1688" spans="1:16">
       <c r="A1688" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1688" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1688">
-        <v>0.9920102638975372</v>
+        <v>0.9916025460884326</v>
       </c>
       <c r="D1688" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E1688">
-        <v>1.094277788098549</v>
+        <v>1.071602546088433</v>
       </c>
       <c r="F1688">
         <v>1</v>
       </c>
       <c r="G1688">
-        <v>0.008327989736102463</v>
+        <v>0.008548397453911566</v>
       </c>
       <c r="H1688">
-        <v>0.008405722211901452</v>
+        <v>0.008628397453911568</v>
       </c>
       <c r="I1688">
-        <v>0.1022675242010114</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1688">
         <v>1.226752420101158</v>
       </c>
       <c r="K1688">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1688">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1688">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="N1688">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="O1688">
         <v>1</v>
@@ -86528,46 +86528,46 @@
     </row>
     <row r="1689" spans="1:16">
       <c r="A1689" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1689" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1689">
-        <v>0.9942777880985489</v>
+        <v>0.9920102638975372</v>
       </c>
       <c r="D1689" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1689">
-        <v>1.122124731475282</v>
+        <v>1.059742739696526</v>
       </c>
       <c r="F1689">
         <v>1</v>
       </c>
       <c r="G1689">
-        <v>0.008305722211901453</v>
+        <v>0.008327989736102463</v>
       </c>
       <c r="H1689">
-        <v>0.008997875268524717</v>
+        <v>0.008420257260303474</v>
       </c>
       <c r="I1689">
-        <v>0.1278469433767331</v>
+        <v>0.06773247579898856</v>
       </c>
       <c r="J1689">
         <v>1.226752420101158</v>
       </c>
       <c r="K1689">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1689">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1689">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1689">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1689">
         <v>1</v>
@@ -86578,13 +86578,13 @@
     </row>
     <row r="1690" spans="1:16">
       <c r="A1690" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1690" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1690">
-        <v>0.9866597798773058</v>
+        <v>0.9942777880985489</v>
       </c>
       <c r="D1690" t="s">
         <v>446</v>
@@ -86596,22 +86596,22 @@
         <v>1</v>
       </c>
       <c r="G1690">
-        <v>0.008813340220122695</v>
+        <v>0.008305722211901453</v>
       </c>
       <c r="H1690">
         <v>0.008997875268524717</v>
       </c>
       <c r="I1690">
-        <v>0.1354649515979762</v>
+        <v>0.1278469433767331</v>
       </c>
       <c r="J1690">
         <v>1.226752420101158</v>
       </c>
       <c r="K1690">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1690">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1690">
         <v>3.21</v>
@@ -86628,96 +86628,96 @@
     </row>
     <row r="1691" spans="1:16">
       <c r="A1691" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1691" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1691">
-        <v>0.9133372588035056</v>
+        <v>0.9866597798773058</v>
       </c>
       <c r="D1691" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1691">
-        <v>0.9933372588035057</v>
+        <v>1.122124731475282</v>
       </c>
       <c r="F1691">
         <v>1</v>
       </c>
       <c r="G1691">
-        <v>0.008626662741196495</v>
+        <v>0.008813340220122695</v>
       </c>
       <c r="H1691">
-        <v>0.008706662741196493</v>
+        <v>0.008997875268524717</v>
       </c>
       <c r="I1691">
-        <v>0.08000000000000007</v>
+        <v>0.1354649515979762</v>
       </c>
       <c r="J1691">
-        <v>1.252163227661199</v>
+        <v>1.226752420101158</v>
       </c>
       <c r="K1691">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1691">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1691">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1691">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1691">
         <v>1</v>
       </c>
       <c r="P1691" t="s">
-        <v>262</v>
+        <v>440</v>
       </c>
     </row>
     <row r="1692" spans="1:16">
       <c r="A1692" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1692" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1692">
-        <v>0.9160319492930138</v>
+        <v>0.9133372588035056</v>
       </c>
       <c r="D1692" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1692">
-        <v>0.9835103170164023</v>
+        <v>0.9933372588035057</v>
       </c>
       <c r="F1692">
         <v>1</v>
       </c>
       <c r="G1692">
-        <v>0.008403968050706987</v>
+        <v>0.008626662741196495</v>
       </c>
       <c r="H1692">
-        <v>0.008496489682983598</v>
+        <v>0.008706662741196493</v>
       </c>
       <c r="I1692">
-        <v>0.06747836772338855</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1692">
         <v>1.252163227661199</v>
       </c>
       <c r="K1692">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1692">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1692">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1692">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1692">
         <v>1</v>
@@ -86728,46 +86728,46 @@
     </row>
     <row r="1693" spans="1:16">
       <c r="A1693" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1693" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1693">
-        <v>0.9185535815696264</v>
+        <v>0.9160319492930138</v>
       </c>
       <c r="D1693" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1693">
-        <v>1.04055603920755</v>
+        <v>0.9835103170164023</v>
       </c>
       <c r="F1693">
         <v>1</v>
       </c>
       <c r="G1693">
-        <v>0.008381446418430376</v>
+        <v>0.008403968050706987</v>
       </c>
       <c r="H1693">
-        <v>0.00907944396079245</v>
+        <v>0.008496489682983598</v>
       </c>
       <c r="I1693">
-        <v>0.1220024576379233</v>
+        <v>0.06747836772338855</v>
       </c>
       <c r="J1693">
         <v>1.252163227661199</v>
       </c>
       <c r="K1693">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1693">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1693">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1693">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1693">
         <v>1</v>
@@ -86778,13 +86778,13 @@
     </row>
     <row r="1694" spans="1:16">
       <c r="A1694" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1694" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1694">
-        <v>0.9055993037607744</v>
+        <v>0.9185535815696264</v>
       </c>
       <c r="D1694" t="s">
         <v>446</v>
@@ -86796,22 +86796,22 @@
         <v>1</v>
       </c>
       <c r="G1694">
-        <v>0.008894400696239228</v>
+        <v>0.008381446418430376</v>
       </c>
       <c r="H1694">
         <v>0.00907944396079245</v>
       </c>
       <c r="I1694">
-        <v>0.1349567354467753</v>
+        <v>0.1220024576379233</v>
       </c>
       <c r="J1694">
         <v>1.252163227661199</v>
       </c>
       <c r="K1694">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1694">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1694">
         <v>3.21</v>
@@ -86828,96 +86828,96 @@
     </row>
     <row r="1695" spans="1:16">
       <c r="A1695" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1695" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1695">
-        <v>0.8640876530634416</v>
+        <v>0.9055993037607744</v>
       </c>
       <c r="D1695" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1695">
-        <v>0.9440876530634417</v>
+        <v>1.04055603920755</v>
       </c>
       <c r="F1695">
         <v>1</v>
       </c>
       <c r="G1695">
-        <v>0.008675912346936559</v>
+        <v>0.008894400696239228</v>
       </c>
       <c r="H1695">
-        <v>0.008755912346936559</v>
+        <v>0.00907944396079245</v>
       </c>
       <c r="I1695">
-        <v>0.08000000000000007</v>
+        <v>0.1349567354467753</v>
       </c>
       <c r="J1695">
-        <v>1.268153359394986</v>
+        <v>1.252163227661199</v>
       </c>
       <c r="K1695">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1695">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1695">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1695">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1695">
         <v>1</v>
       </c>
       <c r="P1695" t="s">
-        <v>570</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1696" spans="1:16">
       <c r="A1696" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1696" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1696">
-        <v>0.8682214554089906</v>
+        <v>0.8640876530634416</v>
       </c>
       <c r="D1696" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1696">
-        <v>0.9355399218150415</v>
+        <v>0.9440876530634417</v>
       </c>
       <c r="F1696">
         <v>1</v>
       </c>
       <c r="G1696">
-        <v>0.00845177854459101</v>
+        <v>0.008675912346936559</v>
       </c>
       <c r="H1696">
-        <v>0.008544460078184959</v>
+        <v>0.008755912346936559</v>
       </c>
       <c r="I1696">
-        <v>0.06731846640605088</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1696">
         <v>1.268153359394986</v>
       </c>
       <c r="K1696">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1696">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1696">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1696">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1696">
         <v>1</v>
@@ -86928,46 +86928,46 @@
     </row>
     <row r="1697" spans="1:16">
       <c r="A1697" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1697" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1697">
-        <v>0.8709029890029414</v>
+        <v>0.8682214554089906</v>
       </c>
       <c r="D1697" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1697">
-        <v>0.9892277163420937</v>
+        <v>0.9355399218150415</v>
       </c>
       <c r="F1697">
         <v>1</v>
       </c>
       <c r="G1697">
-        <v>0.008429097010997059</v>
+        <v>0.00845177854459101</v>
       </c>
       <c r="H1697">
-        <v>0.009130772283657905</v>
+        <v>0.008544460078184959</v>
       </c>
       <c r="I1697">
-        <v>0.1183247273391523</v>
+        <v>0.06731846640605088</v>
       </c>
       <c r="J1697">
         <v>1.268153359394986</v>
       </c>
       <c r="K1697">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1697">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1697">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1697">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1697">
         <v>1</v>
@@ -86978,13 +86978,13 @@
     </row>
     <row r="1698" spans="1:16">
       <c r="A1698" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1698" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1698">
-        <v>0.8545907835299937</v>
+        <v>0.8709029890029414</v>
       </c>
       <c r="D1698" t="s">
         <v>446</v>
@@ -86996,22 +86996,22 @@
         <v>1</v>
       </c>
       <c r="G1698">
-        <v>0.008945409216470008</v>
+        <v>0.008429097010997059</v>
       </c>
       <c r="H1698">
         <v>0.009130772283657905</v>
       </c>
       <c r="I1698">
-        <v>0.1346369328121</v>
+        <v>0.1183247273391523</v>
       </c>
       <c r="J1698">
         <v>1.268153359394986</v>
       </c>
       <c r="K1698">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1698">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1698">
         <v>3.21</v>
@@ -87028,96 +87028,96 @@
     </row>
     <row r="1699" spans="1:16">
       <c r="A1699" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1699" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1699">
-        <v>0.8361486892860226</v>
+        <v>0.8545907835299937</v>
       </c>
       <c r="D1699" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1699">
-        <v>0.9161486892860227</v>
+        <v>0.9892277163420937</v>
       </c>
       <c r="F1699">
         <v>1</v>
       </c>
       <c r="G1699">
-        <v>0.008703851310713976</v>
+        <v>0.008945409216470008</v>
       </c>
       <c r="H1699">
-        <v>0.008783851310713978</v>
+        <v>0.009130772283657905</v>
       </c>
       <c r="I1699">
-        <v>0.08000000000000007</v>
+        <v>0.1346369328121</v>
       </c>
       <c r="J1699">
-        <v>1.277224451530512</v>
+        <v>1.268153359394986</v>
       </c>
       <c r="K1699">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1699">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1699">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1699">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1699">
         <v>1</v>
       </c>
       <c r="P1699" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="1700" spans="1:16">
       <c r="A1700" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1700" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1700">
-        <v>0.841098889923769</v>
+        <v>0.8361486892860226</v>
       </c>
       <c r="D1700" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1700">
-        <v>0.9083266454084642</v>
+        <v>0.9161486892860227</v>
       </c>
       <c r="F1700">
         <v>1</v>
       </c>
       <c r="G1700">
-        <v>0.008478901110076232</v>
+        <v>0.008703851310713976</v>
       </c>
       <c r="H1700">
-        <v>0.008571673354591535</v>
+        <v>0.008783851310713978</v>
       </c>
       <c r="I1700">
-        <v>0.06722775548469517</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1700">
         <v>1.277224451530512</v>
       </c>
       <c r="K1700">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1700">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1700">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1700">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1700">
         <v>1</v>
@@ -87128,46 +87128,46 @@
     </row>
     <row r="1701" spans="1:16">
       <c r="A1701" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1701" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1701">
-        <v>0.8438711344390746</v>
+        <v>0.841098889923769</v>
       </c>
       <c r="D1701" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1701">
-        <v>0.9601095105870563</v>
+        <v>0.9083266454084642</v>
       </c>
       <c r="F1701">
         <v>1</v>
       </c>
       <c r="G1701">
-        <v>0.008456128865560925</v>
+        <v>0.008478901110076232</v>
       </c>
       <c r="H1701">
-        <v>0.009159890489412943</v>
+        <v>0.008571673354591535</v>
       </c>
       <c r="I1701">
-        <v>0.1162383761479817</v>
+        <v>0.06722775548469517</v>
       </c>
       <c r="J1701">
         <v>1.277224451530512</v>
       </c>
       <c r="K1701">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1701">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1701">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1701">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1701">
         <v>1</v>
@@ -87178,13 +87178,13 @@
     </row>
     <row r="1702" spans="1:16">
       <c r="A1702" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1702" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1702">
-        <v>0.8256539996176668</v>
+        <v>0.8438711344390746</v>
       </c>
       <c r="D1702" t="s">
         <v>446</v>
@@ -87196,22 +87196,22 @@
         <v>1</v>
       </c>
       <c r="G1702">
-        <v>0.008974346000382332</v>
+        <v>0.008456128865560925</v>
       </c>
       <c r="H1702">
         <v>0.009159890489412943</v>
       </c>
       <c r="I1702">
-        <v>0.1344555109693895</v>
+        <v>0.1162383761479817</v>
       </c>
       <c r="J1702">
         <v>1.277224451530512</v>
       </c>
       <c r="K1702">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1702">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1702">
         <v>3.21</v>
@@ -87228,96 +87228,96 @@
     </row>
     <row r="1703" spans="1:16">
       <c r="A1703" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1703" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1703">
-        <v>0.8463446294858961</v>
+        <v>0.8256539996176668</v>
       </c>
       <c r="D1703" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1703">
-        <v>0.9263446294858961</v>
+        <v>0.9601095105870563</v>
       </c>
       <c r="F1703">
         <v>1</v>
       </c>
       <c r="G1703">
-        <v>0.008693655370514104</v>
+        <v>0.008974346000382332</v>
       </c>
       <c r="H1703">
-        <v>0.008773655370514102</v>
+        <v>0.009159890489412943</v>
       </c>
       <c r="I1703">
-        <v>0.08000000000000007</v>
+        <v>0.1344555109693895</v>
       </c>
       <c r="J1703">
-        <v>1.273914081335748</v>
+        <v>1.277224451530512</v>
       </c>
       <c r="K1703">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1703">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1703">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1703">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1703">
         <v>1</v>
       </c>
       <c r="P1703" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1704" spans="1:16">
       <c r="A1704" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1704" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1704">
-        <v>0.8509968968061137</v>
+        <v>0.8463446294858961</v>
       </c>
       <c r="D1704" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1704">
-        <v>0.9182577559927565</v>
+        <v>0.9263446294858961</v>
       </c>
       <c r="F1704">
         <v>1</v>
       </c>
       <c r="G1704">
-        <v>0.008469003103193887</v>
+        <v>0.008693655370514104</v>
       </c>
       <c r="H1704">
-        <v>0.008561742244007244</v>
+        <v>0.008773655370514102</v>
       </c>
       <c r="I1704">
-        <v>0.06726085918664282</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1704">
         <v>1.273914081335748</v>
       </c>
       <c r="K1704">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1704">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1704">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1704">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1704">
         <v>1</v>
@@ -87328,46 +87328,46 @@
     </row>
     <row r="1705" spans="1:16">
       <c r="A1705" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1705" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1705">
-        <v>0.8537360376194716</v>
+        <v>0.8509968968061137</v>
       </c>
       <c r="D1705" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1705">
-        <v>0.9707357989122487</v>
+        <v>0.9182577559927565</v>
       </c>
       <c r="F1705">
         <v>1</v>
       </c>
       <c r="G1705">
-        <v>0.00844626396238053</v>
+        <v>0.008469003103193887</v>
       </c>
       <c r="H1705">
-        <v>0.00914926420108775</v>
+        <v>0.008561742244007244</v>
       </c>
       <c r="I1705">
-        <v>0.1169997612927771</v>
+        <v>0.06726085918664282</v>
       </c>
       <c r="J1705">
         <v>1.273914081335748</v>
       </c>
       <c r="K1705">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1705">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1705">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1705">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1705">
         <v>1</v>
@@ -87378,13 +87378,13 @@
     </row>
     <row r="1706" spans="1:16">
       <c r="A1706" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1706" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1706">
-        <v>0.8362140805389648</v>
+        <v>0.8537360376194716</v>
       </c>
       <c r="D1706" t="s">
         <v>446</v>
@@ -87396,22 +87396,22 @@
         <v>1</v>
       </c>
       <c r="G1706">
-        <v>0.008963785919461035</v>
+        <v>0.00844626396238053</v>
       </c>
       <c r="H1706">
         <v>0.00914926420108775</v>
       </c>
       <c r="I1706">
-        <v>0.1345217183732839</v>
+        <v>0.1169997612927771</v>
       </c>
       <c r="J1706">
         <v>1.273914081335748</v>
       </c>
       <c r="K1706">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1706">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1706">
         <v>3.21</v>
@@ -87428,96 +87428,96 @@
     </row>
     <row r="1707" spans="1:16">
       <c r="A1707" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1707" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1707">
-        <v>0.8349326342058419</v>
+        <v>0.8362140805389648</v>
       </c>
       <c r="D1707" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1707">
-        <v>0.9149326342058419</v>
+        <v>0.9707357989122487</v>
       </c>
       <c r="F1707">
         <v>1</v>
       </c>
       <c r="G1707">
-        <v>0.008705067365794157</v>
+        <v>0.008963785919461035</v>
       </c>
       <c r="H1707">
-        <v>0.008785067365794158</v>
+        <v>0.00914926420108775</v>
       </c>
       <c r="I1707">
-        <v>0.08000000000000007</v>
+        <v>0.1345217183732839</v>
       </c>
       <c r="J1707">
-        <v>1.277619274608493</v>
+        <v>1.273914081335748</v>
       </c>
       <c r="K1707">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1707">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1707">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1707">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1707">
         <v>1</v>
       </c>
       <c r="P1707" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="1708" spans="1:16">
       <c r="A1708" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1708" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1708">
-        <v>0.8399183689206069</v>
+        <v>0.8349326342058419</v>
       </c>
       <c r="D1708" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1708">
-        <v>0.9071421761745224</v>
+        <v>0.9149326342058419</v>
       </c>
       <c r="F1708">
         <v>1</v>
       </c>
       <c r="G1708">
-        <v>0.008480081631079394</v>
+        <v>0.008705067365794157</v>
       </c>
       <c r="H1708">
-        <v>0.008572857823825478</v>
+        <v>0.008785067365794158</v>
       </c>
       <c r="I1708">
-        <v>0.06722380725391552</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1708">
         <v>1.277619274608493</v>
       </c>
       <c r="K1708">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1708">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1708">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1708">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1708">
         <v>1</v>
@@ -87528,46 +87528,46 @@
     </row>
     <row r="1709" spans="1:16">
       <c r="A1709" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1709" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1709">
-        <v>0.8426945616666921</v>
+        <v>0.8399183689206069</v>
       </c>
       <c r="D1709" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1709">
-        <v>0.9588421285067383</v>
+        <v>0.9071421761745224</v>
       </c>
       <c r="F1709">
         <v>1</v>
       </c>
       <c r="G1709">
-        <v>0.008457305438333309</v>
+        <v>0.008480081631079394</v>
       </c>
       <c r="H1709">
-        <v>0.009161157871493261</v>
+        <v>0.008572857823825478</v>
       </c>
       <c r="I1709">
-        <v>0.1161475668400462</v>
+        <v>0.06722380725391552</v>
       </c>
       <c r="J1709">
         <v>1.277619274608493</v>
       </c>
       <c r="K1709">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1709">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1709">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1709">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1709">
         <v>1</v>
@@ -87578,13 +87578,13 @@
     </row>
     <row r="1710" spans="1:16">
       <c r="A1710" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1710" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1710">
-        <v>0.8243945139989091</v>
+        <v>0.8426945616666921</v>
       </c>
       <c r="D1710" t="s">
         <v>446</v>
@@ -87596,22 +87596,22 @@
         <v>1</v>
       </c>
       <c r="G1710">
-        <v>0.008975605486001091</v>
+        <v>0.008457305438333309</v>
       </c>
       <c r="H1710">
         <v>0.009161157871493261</v>
       </c>
       <c r="I1710">
-        <v>0.1344476145078293</v>
+        <v>0.1161475668400462</v>
       </c>
       <c r="J1710">
         <v>1.277619274608493</v>
       </c>
       <c r="K1710">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1710">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1710">
         <v>3.21</v>
@@ -87628,96 +87628,96 @@
     </row>
     <row r="1711" spans="1:16">
       <c r="A1711" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1711" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1711">
-        <v>0.8005072022455093</v>
+        <v>0.8243945139989091</v>
       </c>
       <c r="D1711" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1711">
-        <v>0.8805072022455094</v>
+        <v>0.9588421285067383</v>
       </c>
       <c r="F1711">
         <v>1</v>
       </c>
       <c r="G1711">
-        <v>0.008739492797754491</v>
+        <v>0.008975605486001091</v>
       </c>
       <c r="H1711">
-        <v>0.008819492797754491</v>
+        <v>0.009161157871493261</v>
       </c>
       <c r="I1711">
-        <v>0.08000000000000007</v>
+        <v>0.1344476145078293</v>
       </c>
       <c r="J1711">
-        <v>1.288796362907302</v>
+        <v>1.277619274608493</v>
       </c>
       <c r="K1711">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="L1711">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M1711">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="N1711">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="O1711">
         <v>1</v>
       </c>
       <c r="P1711" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="1712" spans="1:16">
       <c r="A1712" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1712" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C1712">
-        <v>0.8064988749071667</v>
+        <v>0.8005072022455093</v>
       </c>
       <c r="D1712" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E1712">
-        <v>0.8736109112780941</v>
+        <v>0.8805072022455094</v>
       </c>
       <c r="F1712">
         <v>1</v>
       </c>
       <c r="G1712">
-        <v>0.008513501125092833</v>
+        <v>0.008739492797754491</v>
       </c>
       <c r="H1712">
-        <v>0.008606389088721907</v>
+        <v>0.008819492797754491</v>
       </c>
       <c r="I1712">
-        <v>0.06711203637092744</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1712">
         <v>1.288796362907302</v>
       </c>
       <c r="K1712">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="L1712">
-        <v>4.66</v>
+        <v>4.77</v>
       </c>
       <c r="M1712">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N1712">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="O1712">
         <v>1</v>
@@ -87728,46 +87728,46 @@
     </row>
     <row r="1713" spans="1:16">
       <c r="A1713" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1713" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1713">
-        <v>0.8093868385362404</v>
+        <v>0.8064988749071667</v>
       </c>
       <c r="D1713" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1713">
-        <v>0.9229636750675603</v>
+        <v>0.8736109112780941</v>
       </c>
       <c r="F1713">
         <v>1</v>
       </c>
       <c r="G1713">
-        <v>0.00849061316146376</v>
+        <v>0.008513501125092833</v>
       </c>
       <c r="H1713">
-        <v>0.009197036324932439</v>
+        <v>0.008606389088721907</v>
       </c>
       <c r="I1713">
-        <v>0.1135768365313199</v>
+        <v>0.06711203637092744</v>
       </c>
       <c r="J1713">
         <v>1.288796362907302</v>
       </c>
       <c r="K1713">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1713">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1713">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1713">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1713">
         <v>1</v>
@@ -87778,13 +87778,13 @@
     </row>
     <row r="1714" spans="1:16">
       <c r="A1714" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1714" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1714">
-        <v>0.7887396023257072</v>
+        <v>0.8093868385362404</v>
       </c>
       <c r="D1714" t="s">
         <v>446</v>
@@ -87796,22 +87796,22 @@
         <v>1</v>
       </c>
       <c r="G1714">
-        <v>0.009011260397674293</v>
+        <v>0.00849061316146376</v>
       </c>
       <c r="H1714">
         <v>0.009197036324932439</v>
       </c>
       <c r="I1714">
-        <v>0.1342240727418531</v>
+        <v>0.1135768365313199</v>
       </c>
       <c r="J1714">
         <v>1.288796362907302</v>
       </c>
       <c r="K1714">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1714">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1714">
         <v>3.21</v>
@@ -87828,96 +87828,96 @@
     </row>
     <row r="1715" spans="1:16">
       <c r="A1715" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1715" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1715">
-        <v>0.7862584850929837</v>
+        <v>0.7887396023257072</v>
       </c>
       <c r="D1715" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1715">
-        <v>0.8533028278524921</v>
+        <v>0.9229636750675603</v>
       </c>
       <c r="F1715">
         <v>1</v>
       </c>
       <c r="G1715">
-        <v>0.008533741514907017</v>
+        <v>0.009011260397674293</v>
       </c>
       <c r="H1715">
-        <v>0.008626697172147509</v>
+        <v>0.009197036324932439</v>
       </c>
       <c r="I1715">
-        <v>0.06704434275950844</v>
+        <v>0.1342240727418531</v>
       </c>
       <c r="J1715">
-        <v>1.295565724049169</v>
+        <v>1.288796362907302</v>
       </c>
       <c r="K1715">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1715">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1715">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1715">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1715">
         <v>1</v>
       </c>
       <c r="P1715" t="s">
-        <v>260</v>
+        <v>574</v>
       </c>
     </row>
     <row r="1716" spans="1:16">
       <c r="A1716" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1716" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1716">
-        <v>0.7892141423334755</v>
+        <v>0.7862584850929837</v>
       </c>
       <c r="D1716" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1716">
-        <v>0.9012340258021663</v>
+        <v>0.8533028278524921</v>
       </c>
       <c r="F1716">
         <v>1</v>
       </c>
       <c r="G1716">
-        <v>0.008510785857666524</v>
+        <v>0.008533741514907017</v>
       </c>
       <c r="H1716">
-        <v>0.009218765974197834</v>
+        <v>0.008626697172147509</v>
       </c>
       <c r="I1716">
-        <v>0.1120198834686907</v>
+        <v>0.06704434275950844</v>
       </c>
       <c r="J1716">
         <v>1.295565724049169</v>
       </c>
       <c r="K1716">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1716">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1716">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1716">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1716">
         <v>1</v>
@@ -87928,7 +87928,7 @@
     </row>
     <row r="1717" spans="1:16">
       <c r="A1717" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1717" t="s">
         <v>261</v>
@@ -88181,10 +88181,10 @@
         <v>1</v>
       </c>
       <c r="B1722" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1722">
-        <v>0.7510240868221101</v>
+        <v>0.7262640392491715</v>
       </c>
       <c r="D1722" t="s">
         <v>446</v>
@@ -88196,22 +88196,22 @@
         <v>1</v>
       </c>
       <c r="G1722">
-        <v>0.008548975913177891</v>
+        <v>0.009073735960750829</v>
       </c>
       <c r="H1722">
         <v>0.009259903584329203</v>
       </c>
       <c r="I1722">
-        <v>0.1090723288486859</v>
+        <v>0.1338323764216245</v>
       </c>
       <c r="J1722">
         <v>1.308381178918755</v>
       </c>
       <c r="K1722">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1722">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1722">
         <v>3.21</v>
@@ -88228,96 +88228,96 @@
     </row>
     <row r="1723" spans="1:16">
       <c r="A1723" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1723" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C1723">
-        <v>0.7262640392491715</v>
+        <v>0.7508817338992388</v>
       </c>
       <c r="D1723" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1723">
-        <v>0.860096415670796</v>
+        <v>0.817807759765123</v>
       </c>
       <c r="F1723">
         <v>1</v>
       </c>
       <c r="G1723">
-        <v>0.009073735960750829</v>
+        <v>0.008569118266100762</v>
       </c>
       <c r="H1723">
-        <v>0.009259903584329203</v>
+        <v>0.008662192240234876</v>
       </c>
       <c r="I1723">
-        <v>0.1338323764216245</v>
+        <v>0.06692602586588414</v>
       </c>
       <c r="J1723">
-        <v>1.308381178918755</v>
+        <v>1.307397413411626</v>
       </c>
       <c r="K1723">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="L1723">
-        <v>4.9</v>
+        <v>4.66</v>
       </c>
       <c r="M1723">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1723">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1723">
         <v>1</v>
       </c>
       <c r="P1723" t="s">
-        <v>448</v>
+        <v>576</v>
       </c>
     </row>
     <row r="1724" spans="1:16">
       <c r="A1724" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1724" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1724">
-        <v>0.7508817338992388</v>
+        <v>0.7294022512169143</v>
       </c>
       <c r="D1724" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1724">
-        <v>0.817807759765123</v>
+        <v>0.8632543029486808</v>
       </c>
       <c r="F1724">
         <v>1</v>
       </c>
       <c r="G1724">
-        <v>0.008569118266100762</v>
+        <v>0.009070597748783087</v>
       </c>
       <c r="H1724">
-        <v>0.008662192240234876</v>
+        <v>0.009256745697051318</v>
       </c>
       <c r="I1724">
-        <v>0.06692602586588414</v>
+        <v>0.1338520517317665</v>
       </c>
       <c r="J1724">
         <v>1.307397413411626</v>
       </c>
       <c r="K1724">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1724">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1724">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1724">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1724">
         <v>1</v>
@@ -88328,34 +88328,34 @@
     </row>
     <row r="1725" spans="1:16">
       <c r="A1725" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1725" t="s">
         <v>261</v>
       </c>
       <c r="C1725">
-        <v>0.7294022512169143</v>
+        <v>0.7117048337867153</v>
       </c>
       <c r="D1725" t="s">
         <v>446</v>
       </c>
       <c r="E1725">
-        <v>0.8632543029486808</v>
+        <v>0.8454459299233079</v>
       </c>
       <c r="F1725">
         <v>1</v>
       </c>
       <c r="G1725">
-        <v>0.009070597748783087</v>
+        <v>0.009088295166213286</v>
       </c>
       <c r="H1725">
-        <v>0.009256745697051318</v>
+        <v>0.009274554070076692</v>
       </c>
       <c r="I1725">
-        <v>0.1338520517317665</v>
+        <v>0.1337410961365926</v>
       </c>
       <c r="J1725">
-        <v>1.307397413411626</v>
+        <v>1.312945193170309</v>
       </c>
       <c r="K1725">
         <v>3.19</v>
@@ -88373,7 +88373,7 @@
         <v>1</v>
       </c>
       <c r="P1725" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="1726" spans="1:16">
@@ -88381,81 +88381,81 @@
         <v>0</v>
       </c>
       <c r="B1726" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1726">
-        <v>0.7342938724207762</v>
+        <v>0.7049987098493551</v>
       </c>
       <c r="D1726" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1726">
-        <v>0.8011644204890738</v>
+        <v>0.8386977613217637</v>
       </c>
       <c r="F1726">
         <v>1</v>
       </c>
       <c r="G1726">
-        <v>0.008585706127579223</v>
+        <v>0.009095001290150645</v>
       </c>
       <c r="H1726">
-        <v>0.008678835579510928</v>
+        <v>0.009281302238678237</v>
       </c>
       <c r="I1726">
-        <v>0.06687054806829762</v>
+        <v>0.1336990514724086</v>
       </c>
       <c r="J1726">
-        <v>1.312945193170309</v>
+        <v>1.315047426379513</v>
       </c>
       <c r="K1726">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1726">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1726">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1726">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1726">
         <v>1</v>
       </c>
       <c r="P1726" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="1727" spans="1:16">
       <c r="A1727" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1727" t="s">
         <v>261</v>
       </c>
       <c r="C1727">
-        <v>0.7117048337867153</v>
+        <v>0.6966839628130383</v>
       </c>
       <c r="D1727" t="s">
         <v>446</v>
       </c>
       <c r="E1727">
-        <v>0.8454459299233079</v>
+        <v>0.8303308842099844</v>
       </c>
       <c r="F1727">
         <v>1</v>
       </c>
       <c r="G1727">
-        <v>0.009088295166213286</v>
+        <v>0.009103316037186962</v>
       </c>
       <c r="H1727">
-        <v>0.009274554070076692</v>
+        <v>0.009289669115790015</v>
       </c>
       <c r="I1727">
-        <v>0.1337410961365926</v>
+        <v>0.133646921396946</v>
       </c>
       <c r="J1727">
-        <v>1.312945193170309</v>
+        <v>1.317653930152653</v>
       </c>
       <c r="K1727">
         <v>3.19</v>
@@ -88473,7 +88473,7 @@
         <v>1</v>
       </c>
       <c r="P1727" t="s">
-        <v>577</v>
+        <v>256</v>
       </c>
     </row>
     <row r="1728" spans="1:16">
@@ -88484,28 +88484,28 @@
         <v>261</v>
       </c>
       <c r="C1728">
-        <v>0.7049987098493551</v>
+        <v>0.7014000886468699</v>
       </c>
       <c r="D1728" t="s">
         <v>446</v>
       </c>
       <c r="E1728">
-        <v>0.8386977613217637</v>
+        <v>0.8350765782308622</v>
       </c>
       <c r="F1728">
         <v>1</v>
       </c>
       <c r="G1728">
-        <v>0.009095001290150645</v>
+        <v>0.009098599911353131</v>
       </c>
       <c r="H1728">
-        <v>0.009281302238678237</v>
+        <v>0.009284923421769136</v>
       </c>
       <c r="I1728">
-        <v>0.1336990514724086</v>
+        <v>0.1336764895839924</v>
       </c>
       <c r="J1728">
-        <v>1.315047426379513</v>
+        <v>1.316175520800354</v>
       </c>
       <c r="K1728">
         <v>3.19</v>
@@ -88523,7 +88523,7 @@
         <v>1</v>
       </c>
       <c r="P1728" t="s">
-        <v>578</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1729" spans="1:16">
@@ -88534,28 +88534,28 @@
         <v>261</v>
       </c>
       <c r="C1729">
-        <v>0.6966839628130383</v>
+        <v>0.7176262191292162</v>
       </c>
       <c r="D1729" t="s">
         <v>446</v>
       </c>
       <c r="E1729">
-        <v>0.8303308842099844</v>
+        <v>0.8514044399388032</v>
       </c>
       <c r="F1729">
         <v>1</v>
       </c>
       <c r="G1729">
-        <v>0.009103316037186962</v>
+        <v>0.009082373780870786</v>
       </c>
       <c r="H1729">
-        <v>0.009289669115790015</v>
+        <v>0.009268595560061196</v>
       </c>
       <c r="I1729">
-        <v>0.133646921396946</v>
+        <v>0.133778220809587</v>
       </c>
       <c r="J1729">
-        <v>1.317653930152653</v>
+        <v>1.311088959520622</v>
       </c>
       <c r="K1729">
         <v>3.19</v>
@@ -88573,7 +88573,7 @@
         <v>1</v>
       </c>
       <c r="P1729" t="s">
-        <v>256</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1730" spans="1:16">
@@ -88584,28 +88584,28 @@
         <v>261</v>
       </c>
       <c r="C1730">
-        <v>0.7014000886468699</v>
+        <v>0.7398286590454459</v>
       </c>
       <c r="D1730" t="s">
         <v>446</v>
       </c>
       <c r="E1730">
-        <v>0.8350765782308622</v>
+        <v>0.873746080105291</v>
       </c>
       <c r="F1730">
         <v>1</v>
       </c>
       <c r="G1730">
-        <v>0.009098599911353131</v>
+        <v>0.009060171340954553</v>
       </c>
       <c r="H1730">
-        <v>0.009284923421769136</v>
+        <v>0.00924625391989471</v>
       </c>
       <c r="I1730">
-        <v>0.1336764895839924</v>
+        <v>0.1339174210598451</v>
       </c>
       <c r="J1730">
-        <v>1.316175520800354</v>
+        <v>1.304128947007697</v>
       </c>
       <c r="K1730">
         <v>3.19</v>
@@ -88623,7 +88623,7 @@
         <v>1</v>
       </c>
       <c r="P1730" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1731" spans="1:16">
@@ -88634,28 +88634,28 @@
         <v>261</v>
       </c>
       <c r="C1731">
-        <v>0.7176262191292162</v>
+        <v>0.7726173788161628</v>
       </c>
       <c r="D1731" t="s">
         <v>446</v>
       </c>
       <c r="E1731">
-        <v>0.8514044399388032</v>
+        <v>0.9067403717867961</v>
       </c>
       <c r="F1731">
         <v>1</v>
       </c>
       <c r="G1731">
-        <v>0.009082373780870786</v>
+        <v>0.009027382621183837</v>
       </c>
       <c r="H1731">
-        <v>0.009268595560061196</v>
+        <v>0.009213259628213203</v>
       </c>
       <c r="I1731">
-        <v>0.133778220809587</v>
+        <v>0.1341229929706333</v>
       </c>
       <c r="J1731">
-        <v>1.311088959520622</v>
+        <v>1.293850351468288</v>
       </c>
       <c r="K1731">
         <v>3.19</v>
@@ -88673,7 +88673,7 @@
         <v>1</v>
       </c>
       <c r="P1731" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1732" spans="1:16">
@@ -88684,28 +88684,28 @@
         <v>261</v>
       </c>
       <c r="C1732">
-        <v>0.7398286590454459</v>
+        <v>0.8072892339066007</v>
       </c>
       <c r="D1732" t="s">
         <v>446</v>
       </c>
       <c r="E1732">
-        <v>0.873746080105291</v>
+        <v>0.9416296052790551</v>
       </c>
       <c r="F1732">
         <v>1</v>
       </c>
       <c r="G1732">
-        <v>0.009060171340954553</v>
+        <v>0.0089927107660934</v>
       </c>
       <c r="H1732">
-        <v>0.00924625391989471</v>
+        <v>0.009178370394720943</v>
       </c>
       <c r="I1732">
-        <v>0.1339174210598451</v>
+        <v>0.1343403713724545</v>
       </c>
       <c r="J1732">
-        <v>1.304128947007697</v>
+        <v>1.282981431377241</v>
       </c>
       <c r="K1732">
         <v>3.19</v>
@@ -88723,7 +88723,7 @@
         <v>1</v>
       </c>
       <c r="P1732" t="s">
-        <v>444</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1733" spans="1:16">
@@ -88731,87 +88731,87 @@
         <v>0</v>
       </c>
       <c r="B1733" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1733">
+        <v>0.8255353424422802</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>446</v>
+      </c>
+      <c r="E1733">
+        <v>0.9599901094795351</v>
+      </c>
+      <c r="F1733">
+        <v>1</v>
+      </c>
+      <c r="G1733">
+        <v>0.008974464657557722</v>
+      </c>
+      <c r="H1733">
+        <v>0.009160009890520463</v>
+      </c>
+      <c r="I1733">
+        <v>0.1344547670372549</v>
+      </c>
+      <c r="J1733">
+        <v>1.277261648137216</v>
+      </c>
+      <c r="K1733">
+        <v>3.19</v>
+      </c>
+      <c r="L1733">
+        <v>4.9</v>
+      </c>
+      <c r="M1733">
+        <v>3.21</v>
+      </c>
+      <c r="N1733">
+        <v>5.06</v>
+      </c>
+      <c r="O1733">
+        <v>1</v>
+      </c>
+      <c r="P1733" t="s">
         <v>263</v>
-      </c>
-      <c r="C1733">
-        <v>0.7913874491098194</v>
-      </c>
-      <c r="D1733" t="s">
-        <v>450</v>
-      </c>
-      <c r="E1733">
-        <v>0.858448945595137</v>
-      </c>
-      <c r="F1733">
-        <v>1</v>
-      </c>
-      <c r="G1733">
-        <v>0.00852861255089018</v>
-      </c>
-      <c r="H1733">
-        <v>0.008621551054404862</v>
-      </c>
-      <c r="I1733">
-        <v>0.06706149648531756</v>
-      </c>
-      <c r="J1733">
-        <v>1.293850351468288</v>
-      </c>
-      <c r="K1733">
-        <v>2.99</v>
-      </c>
-      <c r="L1733">
-        <v>4.66</v>
-      </c>
-      <c r="M1733">
-        <v>3</v>
-      </c>
-      <c r="N1733">
-        <v>4.74</v>
-      </c>
-      <c r="O1733">
-        <v>1</v>
-      </c>
-      <c r="P1733" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="1734" spans="1:16">
       <c r="A1734" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1734" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1734">
-        <v>0.7726173788161628</v>
+        <v>0.8604710066405516</v>
       </c>
       <c r="D1734" t="s">
         <v>446</v>
       </c>
       <c r="E1734">
-        <v>0.9067403717867961</v>
+        <v>0.97799058097858</v>
       </c>
       <c r="F1734">
         <v>1</v>
       </c>
       <c r="G1734">
-        <v>0.009027382621183837</v>
+        <v>0.008439528993359448</v>
       </c>
       <c r="H1734">
-        <v>0.009213259628213203</v>
+        <v>0.00914200941902142</v>
       </c>
       <c r="I1734">
-        <v>0.1341229929706333</v>
+        <v>0.1175195743380284</v>
       </c>
       <c r="J1734">
-        <v>1.293850351468288</v>
+        <v>1.271654024617265</v>
       </c>
       <c r="K1734">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1734">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1734">
         <v>3.21</v>
@@ -88823,39 +88823,39 @@
         <v>1</v>
       </c>
       <c r="P1734" t="s">
-        <v>580</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1735" spans="1:16">
       <c r="A1735" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1735" t="s">
         <v>261</v>
       </c>
       <c r="C1735">
-        <v>0.8072892339066007</v>
+        <v>0.8434236614709256</v>
       </c>
       <c r="D1735" t="s">
         <v>446</v>
       </c>
       <c r="E1735">
-        <v>0.9416296052790551</v>
+        <v>0.97799058097858</v>
       </c>
       <c r="F1735">
         <v>1</v>
       </c>
       <c r="G1735">
-        <v>0.0089927107660934</v>
+        <v>0.008956576338529075</v>
       </c>
       <c r="H1735">
-        <v>0.009178370394720943</v>
+        <v>0.00914200941902142</v>
       </c>
       <c r="I1735">
-        <v>0.1343403713724545</v>
+        <v>0.1345669195076544</v>
       </c>
       <c r="J1735">
-        <v>1.282981431377241</v>
+        <v>1.271654024617265</v>
       </c>
       <c r="K1735">
         <v>3.19</v>
@@ -88873,7 +88873,7 @@
         <v>1</v>
       </c>
       <c r="P1735" t="s">
-        <v>257</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1736" spans="1:16">
@@ -88881,37 +88881,37 @@
         <v>0</v>
       </c>
       <c r="B1736" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1736">
-        <v>0.8255353424422802</v>
+        <v>0.8778494143553166</v>
       </c>
       <c r="D1736" t="s">
         <v>446</v>
       </c>
       <c r="E1736">
-        <v>0.9599901094795351</v>
+        <v>0.99671027519482</v>
       </c>
       <c r="F1736">
         <v>1</v>
       </c>
       <c r="G1736">
-        <v>0.008974464657557722</v>
+        <v>0.008422150585644684</v>
       </c>
       <c r="H1736">
-        <v>0.009160009890520463</v>
+        <v>0.009123289724805179</v>
       </c>
       <c r="I1736">
-        <v>0.1344547670372549</v>
+        <v>0.1188608608395034</v>
       </c>
       <c r="J1736">
-        <v>1.277261648137216</v>
+        <v>1.265822344176068</v>
       </c>
       <c r="K1736">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="L1736">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="M1736">
         <v>3.21</v>
@@ -88923,45 +88923,45 @@
         <v>1</v>
       </c>
       <c r="P1736" t="s">
-        <v>263</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1737" spans="1:16">
       <c r="A1737" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1737" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1737">
-        <v>0.8604710066405516</v>
+        <v>0.8620267220783422</v>
       </c>
       <c r="D1737" t="s">
         <v>446</v>
       </c>
       <c r="E1737">
-        <v>0.97799058097858</v>
+        <v>0.99671027519482</v>
       </c>
       <c r="F1737">
         <v>1</v>
       </c>
       <c r="G1737">
-        <v>0.008439528993359448</v>
+        <v>0.008937973277921658</v>
       </c>
       <c r="H1737">
-        <v>0.00914200941902142</v>
+        <v>0.009123289724805179</v>
       </c>
       <c r="I1737">
-        <v>0.1175195743380284</v>
+        <v>0.1346835531164778</v>
       </c>
       <c r="J1737">
-        <v>1.271654024617265</v>
+        <v>1.265822344176068</v>
       </c>
       <c r="K1737">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1737">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1737">
         <v>3.21</v>
@@ -88973,39 +88973,39 @@
         <v>1</v>
       </c>
       <c r="P1737" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1738" spans="1:16">
       <c r="A1738" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1738" t="s">
         <v>261</v>
       </c>
       <c r="C1738">
-        <v>0.8434236614709256</v>
+        <v>0.8787266818708703</v>
       </c>
       <c r="D1738" t="s">
         <v>446</v>
       </c>
       <c r="E1738">
-        <v>0.97799058097858</v>
+        <v>1.013514936929621</v>
       </c>
       <c r="F1738">
         <v>1</v>
       </c>
       <c r="G1738">
-        <v>0.008956576338529075</v>
+        <v>0.008921273318129131</v>
       </c>
       <c r="H1738">
-        <v>0.00914200941902142</v>
+        <v>0.009106485063070378</v>
       </c>
       <c r="I1738">
-        <v>0.1345669195076544</v>
+        <v>0.1347882550587505</v>
       </c>
       <c r="J1738">
-        <v>1.271654024617265</v>
+        <v>1.260587247062423</v>
       </c>
       <c r="K1738">
         <v>3.19</v>
@@ -89023,7 +89023,7 @@
         <v>1</v>
       </c>
       <c r="P1738" t="s">
-        <v>450</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1739" spans="1:16">
@@ -89031,37 +89031,37 @@
         <v>0</v>
       </c>
       <c r="B1739" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1739">
-        <v>0.8778494143553166</v>
+        <v>0.8827952100288972</v>
       </c>
       <c r="D1739" t="s">
         <v>446</v>
       </c>
       <c r="E1739">
-        <v>0.99671027519482</v>
+        <v>1.017608973101177</v>
       </c>
       <c r="F1739">
         <v>1</v>
       </c>
       <c r="G1739">
-        <v>0.008422150585644684</v>
+        <v>0.008917204789971104</v>
       </c>
       <c r="H1739">
-        <v>0.009123289724805179</v>
+        <v>0.009102391026898821</v>
       </c>
       <c r="I1739">
-        <v>0.1188608608395034</v>
+        <v>0.1348137630722803</v>
       </c>
       <c r="J1739">
-        <v>1.265822344176068</v>
+        <v>1.259311846385926</v>
       </c>
       <c r="K1739">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1739">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1739">
         <v>3.21</v>
@@ -89073,39 +89073,39 @@
         <v>1</v>
       </c>
       <c r="P1739" t="s">
-        <v>445</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1740" spans="1:16">
       <c r="A1740" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1740" t="s">
         <v>261</v>
       </c>
       <c r="C1740">
-        <v>0.8620267220783422</v>
+        <v>0.8817169145093411</v>
       </c>
       <c r="D1740" t="s">
         <v>446</v>
       </c>
       <c r="E1740">
-        <v>0.99671027519482</v>
+        <v>1.016523917108145</v>
       </c>
       <c r="F1740">
         <v>1</v>
       </c>
       <c r="G1740">
-        <v>0.008937973277921658</v>
+        <v>0.00891828308549066</v>
       </c>
       <c r="H1740">
-        <v>0.009123289724805179</v>
+        <v>0.009103476082891854</v>
       </c>
       <c r="I1740">
-        <v>0.1346835531164778</v>
+        <v>0.1348070025988042</v>
       </c>
       <c r="J1740">
-        <v>1.265822344176068</v>
+        <v>1.259649870059768</v>
       </c>
       <c r="K1740">
         <v>3.19</v>
@@ -89123,57 +89123,57 @@
         <v>1</v>
       </c>
       <c r="P1740" t="s">
-        <v>445</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1741" spans="1:16">
       <c r="A1741" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1741" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C1741">
-        <v>0.8787266818708703</v>
+        <v>1.134699408012329</v>
       </c>
       <c r="D1741" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1741">
-        <v>1.013514936929621</v>
+        <v>0.9169099119105364</v>
       </c>
       <c r="F1741">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1741">
-        <v>0.008921273318129131</v>
+        <v>0.009045300591987672</v>
       </c>
       <c r="H1741">
-        <v>0.009106485063070378</v>
+        <v>0.008903090088089463</v>
       </c>
       <c r="I1741">
-        <v>0.1347882550587505</v>
+        <v>0.2177894961017923</v>
       </c>
       <c r="J1741">
-        <v>1.260587247062423</v>
+        <v>1.259649870059768</v>
       </c>
       <c r="K1741">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="L1741">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="M1741">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N1741">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="O1741">
         <v>1</v>
       </c>
       <c r="P1741" t="s">
-        <v>581</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1742" spans="1:16">
@@ -89184,28 +89184,28 @@
         <v>261</v>
       </c>
       <c r="C1742">
-        <v>0.8827952100288972</v>
+        <v>0.8836581328456559</v>
       </c>
       <c r="D1742" t="s">
         <v>446</v>
       </c>
       <c r="E1742">
-        <v>1.017608973101177</v>
+        <v>1.018477306092337</v>
       </c>
       <c r="F1742">
         <v>1</v>
       </c>
       <c r="G1742">
-        <v>0.008917204789971104</v>
+        <v>0.008916341867154344</v>
       </c>
       <c r="H1742">
-        <v>0.009102391026898821</v>
+        <v>0.009101522693907661</v>
       </c>
       <c r="I1742">
-        <v>0.1348137630722803</v>
+        <v>0.1348191732466812</v>
       </c>
       <c r="J1742">
-        <v>1.259311846385926</v>
+        <v>1.259041337665939</v>
       </c>
       <c r="K1742">
         <v>3.19</v>
@@ -89223,7 +89223,7 @@
         <v>1</v>
       </c>
       <c r="P1742" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1743" spans="1:16">
@@ -89234,28 +89234,28 @@
         <v>264</v>
       </c>
       <c r="C1743">
-        <v>1.135760802348193</v>
+        <v>1.136610199728953</v>
       </c>
       <c r="D1743" t="s">
         <v>447</v>
       </c>
       <c r="E1743">
-        <v>0.9179814469566154</v>
+        <v>0.918838959598975</v>
       </c>
       <c r="F1743">
         <v>-1</v>
       </c>
       <c r="G1743">
-        <v>0.009044239197651807</v>
+        <v>0.009043389800271048</v>
       </c>
       <c r="H1743">
-        <v>0.008902018553043385</v>
+        <v>0.008901161040401026</v>
       </c>
       <c r="I1743">
-        <v>0.2177793553915772</v>
+        <v>0.2177712401299776</v>
       </c>
       <c r="J1743">
-        <v>1.259311846385926</v>
+        <v>1.259041337665939</v>
       </c>
       <c r="K1743">
         <v>3.14</v>
@@ -89273,7 +89273,7 @@
         <v>1</v>
       </c>
       <c r="P1743" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1744" spans="1:16">
@@ -89281,81 +89281,81 @@
         <v>0</v>
       </c>
       <c r="B1744" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1744">
+        <v>1.131086318915693</v>
+      </c>
+      <c r="D1744" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1744">
+        <v>0.9132623028543789</v>
+      </c>
+      <c r="F1744">
+        <v>-1</v>
+      </c>
+      <c r="G1744">
+        <v>0.009048913681084306</v>
+      </c>
+      <c r="H1744">
+        <v>0.00890673769714562</v>
+      </c>
+      <c r="I1744">
+        <v>0.2178240160613143</v>
+      </c>
+      <c r="J1744">
+        <v>1.260800535377168</v>
+      </c>
+      <c r="K1744">
+        <v>3.14</v>
+      </c>
+      <c r="L1744">
+        <v>5.09</v>
+      </c>
+      <c r="M1744">
+        <v>3.17</v>
+      </c>
+      <c r="N1744">
+        <v>4.91</v>
+      </c>
+      <c r="O1744">
+        <v>1</v>
+      </c>
+      <c r="P1744" t="s">
         <v>261</v>
-      </c>
-      <c r="C1744">
-        <v>0.8817169145093411</v>
-      </c>
-      <c r="D1744" t="s">
-        <v>446</v>
-      </c>
-      <c r="E1744">
-        <v>1.016523917108145</v>
-      </c>
-      <c r="F1744">
-        <v>1</v>
-      </c>
-      <c r="G1744">
-        <v>0.00891828308549066</v>
-      </c>
-      <c r="H1744">
-        <v>0.009103476082891854</v>
-      </c>
-      <c r="I1744">
-        <v>0.1348070025988042</v>
-      </c>
-      <c r="J1744">
-        <v>1.259649870059768</v>
-      </c>
-      <c r="K1744">
-        <v>3.19</v>
-      </c>
-      <c r="L1744">
-        <v>4.9</v>
-      </c>
-      <c r="M1744">
-        <v>3.21</v>
-      </c>
-      <c r="N1744">
-        <v>5.06</v>
-      </c>
-      <c r="O1744">
-        <v>1</v>
-      </c>
-      <c r="P1744" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="1745" spans="1:16">
       <c r="A1745" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1745" t="s">
         <v>264</v>
       </c>
       <c r="C1745">
-        <v>1.134699408012329</v>
+        <v>1.127143579938229</v>
       </c>
       <c r="D1745" t="s">
         <v>447</v>
       </c>
       <c r="E1745">
-        <v>0.9169099119105364</v>
+        <v>0.909281894396238</v>
       </c>
       <c r="F1745">
         <v>-1</v>
       </c>
       <c r="G1745">
-        <v>0.009045300591987672</v>
+        <v>0.00905285642006177</v>
       </c>
       <c r="H1745">
-        <v>0.008903090088089463</v>
+        <v>0.008910718105603763</v>
       </c>
       <c r="I1745">
-        <v>0.2177894961017923</v>
+        <v>0.2178616855419908</v>
       </c>
       <c r="J1745">
-        <v>1.259649870059768</v>
+        <v>1.262056184733048</v>
       </c>
       <c r="K1745">
         <v>3.14</v>
@@ -89373,7 +89373,7 @@
         <v>1</v>
       </c>
       <c r="P1745" t="s">
-        <v>258</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1746" spans="1:16">
@@ -89381,81 +89381,81 @@
         <v>0</v>
       </c>
       <c r="B1746" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C1746">
-        <v>0.8836581328456559</v>
+        <v>1.123418970437326</v>
       </c>
       <c r="D1746" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1746">
-        <v>1.018477306092337</v>
+        <v>0.9055216994542441</v>
       </c>
       <c r="F1746">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1746">
-        <v>0.008916341867154344</v>
+        <v>0.009056581029562675</v>
       </c>
       <c r="H1746">
-        <v>0.009101522693907661</v>
+        <v>0.008914478300545757</v>
       </c>
       <c r="I1746">
-        <v>0.1348191732466812</v>
+        <v>0.217897270983082</v>
       </c>
       <c r="J1746">
-        <v>1.259041337665939</v>
+        <v>1.263242366102762</v>
       </c>
       <c r="K1746">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="L1746">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="M1746">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N1746">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="O1746">
         <v>1</v>
       </c>
       <c r="P1746" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1747" spans="1:16">
       <c r="A1747" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1747" t="s">
         <v>264</v>
       </c>
       <c r="C1747">
-        <v>1.136610199728953</v>
+        <v>1.103124629069044</v>
       </c>
       <c r="D1747" t="s">
         <v>447</v>
       </c>
       <c r="E1747">
-        <v>0.918838959598975</v>
+        <v>0.8850334631047359</v>
       </c>
       <c r="F1747">
         <v>-1</v>
       </c>
       <c r="G1747">
-        <v>0.009043389800271048</v>
+        <v>0.009076875370930956</v>
       </c>
       <c r="H1747">
-        <v>0.008901161040401026</v>
+        <v>0.008934966536895263</v>
       </c>
       <c r="I1747">
-        <v>0.2177712401299776</v>
+        <v>0.2180911659643079</v>
       </c>
       <c r="J1747">
-        <v>1.259041337665939</v>
+        <v>1.269705532143617</v>
       </c>
       <c r="K1747">
         <v>3.14</v>
@@ -89473,206 +89473,6 @@
         <v>1</v>
       </c>
       <c r="P1747" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="1748" spans="1:16">
-      <c r="A1748" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1748" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1748">
-        <v>1.131086318915693</v>
-      </c>
-      <c r="D1748" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1748">
-        <v>0.9132623028543789</v>
-      </c>
-      <c r="F1748">
-        <v>-1</v>
-      </c>
-      <c r="G1748">
-        <v>0.009048913681084306</v>
-      </c>
-      <c r="H1748">
-        <v>0.00890673769714562</v>
-      </c>
-      <c r="I1748">
-        <v>0.2178240160613143</v>
-      </c>
-      <c r="J1748">
-        <v>1.260800535377168</v>
-      </c>
-      <c r="K1748">
-        <v>3.14</v>
-      </c>
-      <c r="L1748">
-        <v>5.09</v>
-      </c>
-      <c r="M1748">
-        <v>3.17</v>
-      </c>
-      <c r="N1748">
-        <v>4.91</v>
-      </c>
-      <c r="O1748">
-        <v>1</v>
-      </c>
-      <c r="P1748" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1749" spans="1:16">
-      <c r="A1749" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1749" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1749">
-        <v>1.127143579938229</v>
-      </c>
-      <c r="D1749" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1749">
-        <v>0.909281894396238</v>
-      </c>
-      <c r="F1749">
-        <v>-1</v>
-      </c>
-      <c r="G1749">
-        <v>0.00905285642006177</v>
-      </c>
-      <c r="H1749">
-        <v>0.008910718105603763</v>
-      </c>
-      <c r="I1749">
-        <v>0.2178616855419908</v>
-      </c>
-      <c r="J1749">
-        <v>1.262056184733048</v>
-      </c>
-      <c r="K1749">
-        <v>3.14</v>
-      </c>
-      <c r="L1749">
-        <v>5.09</v>
-      </c>
-      <c r="M1749">
-        <v>3.17</v>
-      </c>
-      <c r="N1749">
-        <v>4.91</v>
-      </c>
-      <c r="O1749">
-        <v>1</v>
-      </c>
-      <c r="P1749" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="1750" spans="1:16">
-      <c r="A1750" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1750" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1750">
-        <v>1.123418970437326</v>
-      </c>
-      <c r="D1750" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1750">
-        <v>0.9055216994542441</v>
-      </c>
-      <c r="F1750">
-        <v>-1</v>
-      </c>
-      <c r="G1750">
-        <v>0.009056581029562675</v>
-      </c>
-      <c r="H1750">
-        <v>0.008914478300545757</v>
-      </c>
-      <c r="I1750">
-        <v>0.217897270983082</v>
-      </c>
-      <c r="J1750">
-        <v>1.263242366102762</v>
-      </c>
-      <c r="K1750">
-        <v>3.14</v>
-      </c>
-      <c r="L1750">
-        <v>5.09</v>
-      </c>
-      <c r="M1750">
-        <v>3.17</v>
-      </c>
-      <c r="N1750">
-        <v>4.91</v>
-      </c>
-      <c r="O1750">
-        <v>1</v>
-      </c>
-      <c r="P1750" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="1751" spans="1:16">
-      <c r="A1751" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1751" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1751">
-        <v>1.103124629069044</v>
-      </c>
-      <c r="D1751" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1751">
-        <v>0.8850334631047359</v>
-      </c>
-      <c r="F1751">
-        <v>-1</v>
-      </c>
-      <c r="G1751">
-        <v>0.009076875370930956</v>
-      </c>
-      <c r="H1751">
-        <v>0.008934966536895263</v>
-      </c>
-      <c r="I1751">
-        <v>0.2180911659643079</v>
-      </c>
-      <c r="J1751">
-        <v>1.269705532143617</v>
-      </c>
-      <c r="K1751">
-        <v>3.14</v>
-      </c>
-      <c r="L1751">
-        <v>5.09</v>
-      </c>
-      <c r="M1751">
-        <v>3.17</v>
-      </c>
-      <c r="N1751">
-        <v>4.91</v>
-      </c>
-      <c r="O1751">
-        <v>1</v>
-      </c>
-      <c r="P1751" t="s">
         <v>259</v>
       </c>
     </row>

--- a/s60_signal/position-00670-600115.xlsx
+++ b/s60_signal/position-00670-600115.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5253" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5235" uniqueCount="585">
   <si>
     <t>trade_time</t>
   </si>
@@ -2126,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1747"/>
+  <dimension ref="A1:P1741"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -85487,10 +85487,10 @@
         <v>1.504367576167695</v>
       </c>
       <c r="D1668" t="s">
-        <v>447</v>
+        <v>264</v>
       </c>
       <c r="E1668">
-        <v>1.375517363664023</v>
+        <v>1.588966726153007</v>
       </c>
       <c r="F1668">
         <v>-1</v>
@@ -85499,10 +85499,10 @@
         <v>0.008595632423832305</v>
       </c>
       <c r="H1668">
-        <v>0.008444482636335977</v>
+        <v>0.008591033273846993</v>
       </c>
       <c r="I1668">
-        <v>0.1288502125036715</v>
+        <v>-0.08459914998531204</v>
       </c>
       <c r="J1668">
         <v>1.1149787496328</v>
@@ -85514,10 +85514,10 @@
         <v>5.05</v>
       </c>
       <c r="M1668">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="N1668">
-        <v>4.91</v>
+        <v>5.09</v>
       </c>
       <c r="O1668">
         <v>1</v>
@@ -87781,10 +87781,10 @@
         <v>2</v>
       </c>
       <c r="B1714" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1714">
-        <v>0.8093868385362404</v>
+        <v>0.7887396023257072</v>
       </c>
       <c r="D1714" t="s">
         <v>446</v>
@@ -87796,22 +87796,22 @@
         <v>1</v>
       </c>
       <c r="G1714">
-        <v>0.00849061316146376</v>
+        <v>0.009011260397674293</v>
       </c>
       <c r="H1714">
         <v>0.009197036324932439</v>
       </c>
       <c r="I1714">
-        <v>0.1135768365313199</v>
+        <v>0.1342240727418531</v>
       </c>
       <c r="J1714">
         <v>1.288796362907302</v>
       </c>
       <c r="K1714">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1714">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1714">
         <v>3.21</v>
@@ -87828,96 +87828,96 @@
     </row>
     <row r="1715" spans="1:16">
       <c r="A1715" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1715">
+        <v>0.7862584850929837</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1715">
+        <v>0.8533028278524921</v>
+      </c>
+      <c r="F1715">
+        <v>1</v>
+      </c>
+      <c r="G1715">
+        <v>0.008533741514907017</v>
+      </c>
+      <c r="H1715">
+        <v>0.008626697172147509</v>
+      </c>
+      <c r="I1715">
+        <v>0.06704434275950844</v>
+      </c>
+      <c r="J1715">
+        <v>1.295565724049169</v>
+      </c>
+      <c r="K1715">
+        <v>2.99</v>
+      </c>
+      <c r="L1715">
+        <v>4.66</v>
+      </c>
+      <c r="M1715">
         <v>3</v>
       </c>
-      <c r="B1715" t="s">
-        <v>261</v>
-      </c>
-      <c r="C1715">
-        <v>0.7887396023257072</v>
-      </c>
-      <c r="D1715" t="s">
-        <v>446</v>
-      </c>
-      <c r="E1715">
-        <v>0.9229636750675603</v>
-      </c>
-      <c r="F1715">
-        <v>1</v>
-      </c>
-      <c r="G1715">
-        <v>0.009011260397674293</v>
-      </c>
-      <c r="H1715">
-        <v>0.009197036324932439</v>
-      </c>
-      <c r="I1715">
-        <v>0.1342240727418531</v>
-      </c>
-      <c r="J1715">
-        <v>1.288796362907302</v>
-      </c>
-      <c r="K1715">
-        <v>3.19</v>
-      </c>
-      <c r="L1715">
-        <v>4.9</v>
-      </c>
-      <c r="M1715">
-        <v>3.21</v>
-      </c>
       <c r="N1715">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1715">
         <v>1</v>
       </c>
       <c r="P1715" t="s">
-        <v>574</v>
+        <v>260</v>
       </c>
     </row>
     <row r="1716" spans="1:16">
       <c r="A1716" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1716" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1716">
-        <v>0.7862584850929837</v>
+        <v>0.7671453402831503</v>
       </c>
       <c r="D1716" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1716">
-        <v>0.8533028278524921</v>
+        <v>0.9012340258021663</v>
       </c>
       <c r="F1716">
         <v>1</v>
       </c>
       <c r="G1716">
-        <v>0.008533741514907017</v>
+        <v>0.00903285465971685</v>
       </c>
       <c r="H1716">
-        <v>0.008626697172147509</v>
+        <v>0.009218765974197834</v>
       </c>
       <c r="I1716">
-        <v>0.06704434275950844</v>
+        <v>0.134088685519016</v>
       </c>
       <c r="J1716">
         <v>1.295565724049169</v>
       </c>
       <c r="K1716">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1716">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1716">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1716">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1716">
         <v>1</v>
@@ -87928,96 +87928,96 @@
     </row>
     <row r="1717" spans="1:16">
       <c r="A1717" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1717" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C1717">
-        <v>0.7671453402831503</v>
+        <v>0.7524917367489325</v>
       </c>
       <c r="D1717" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1717">
-        <v>0.9012340258021663</v>
+        <v>0.819423147239732</v>
       </c>
       <c r="F1717">
         <v>1</v>
       </c>
       <c r="G1717">
-        <v>0.00903285465971685</v>
+        <v>0.008567508263251068</v>
       </c>
       <c r="H1717">
-        <v>0.009218765974197834</v>
+        <v>0.008660576852760268</v>
       </c>
       <c r="I1717">
-        <v>0.134088685519016</v>
+        <v>0.06693141049079943</v>
       </c>
       <c r="J1717">
-        <v>1.295565724049169</v>
+        <v>1.306858950920089</v>
       </c>
       <c r="K1717">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="L1717">
-        <v>4.9</v>
+        <v>4.66</v>
       </c>
       <c r="M1717">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1717">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1717">
         <v>1</v>
       </c>
       <c r="P1717" t="s">
-        <v>260</v>
+        <v>575</v>
       </c>
     </row>
     <row r="1718" spans="1:16">
       <c r="A1718" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1718" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1718">
-        <v>0.7524917367489325</v>
+        <v>0.731119946564915</v>
       </c>
       <c r="D1718" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1718">
-        <v>0.819423147239732</v>
+        <v>0.8649827675465129</v>
       </c>
       <c r="F1718">
         <v>1</v>
       </c>
       <c r="G1718">
-        <v>0.008567508263251068</v>
+        <v>0.009068880053435086</v>
       </c>
       <c r="H1718">
-        <v>0.008660576852760268</v>
+        <v>0.009255017232453486</v>
       </c>
       <c r="I1718">
-        <v>0.06693141049079943</v>
+        <v>0.133862820981598</v>
       </c>
       <c r="J1718">
         <v>1.306858950920089</v>
       </c>
       <c r="K1718">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1718">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1718">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1718">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1718">
         <v>1</v>
@@ -88028,84 +88028,84 @@
     </row>
     <row r="1719" spans="1:16">
       <c r="A1719" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1719" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1719">
-        <v>0.7555603262581339</v>
+        <v>0.747940275032922</v>
       </c>
       <c r="D1719" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E1719">
-        <v>0.8649827675465129</v>
+        <v>0.8148564632437347</v>
       </c>
       <c r="F1719">
         <v>1</v>
       </c>
       <c r="G1719">
-        <v>0.008544439673741867</v>
+        <v>0.008572059724967078</v>
       </c>
       <c r="H1719">
-        <v>0.009255017232453486</v>
+        <v>0.008665143536756265</v>
       </c>
       <c r="I1719">
-        <v>0.1094224412883791</v>
+        <v>0.06691618821081269</v>
       </c>
       <c r="J1719">
-        <v>1.306858950920089</v>
+        <v>1.308381178918755</v>
       </c>
       <c r="K1719">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="L1719">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M1719">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N1719">
-        <v>5.06</v>
+        <v>4.74</v>
       </c>
       <c r="O1719">
         <v>1</v>
       </c>
       <c r="P1719" t="s">
-        <v>575</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1720" spans="1:16">
       <c r="A1720" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1720" t="s">
         <v>261</v>
       </c>
       <c r="C1720">
-        <v>0.731119946564915</v>
+        <v>0.7262640392491715</v>
       </c>
       <c r="D1720" t="s">
         <v>446</v>
       </c>
       <c r="E1720">
-        <v>0.8649827675465129</v>
+        <v>0.860096415670796</v>
       </c>
       <c r="F1720">
         <v>1</v>
       </c>
       <c r="G1720">
-        <v>0.009068880053435086</v>
+        <v>0.009073735960750829</v>
       </c>
       <c r="H1720">
-        <v>0.009255017232453486</v>
+        <v>0.009259903584329203</v>
       </c>
       <c r="I1720">
-        <v>0.133862820981598</v>
+        <v>0.1338323764216245</v>
       </c>
       <c r="J1720">
-        <v>1.306858950920089</v>
+        <v>1.308381178918755</v>
       </c>
       <c r="K1720">
         <v>3.19</v>
@@ -88123,7 +88123,7 @@
         <v>1</v>
       </c>
       <c r="P1720" t="s">
-        <v>575</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1721" spans="1:16">
@@ -88131,81 +88131,81 @@
         <v>0</v>
       </c>
       <c r="B1721" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1721">
-        <v>0.747940275032922</v>
+        <v>0.7294022512169143</v>
       </c>
       <c r="D1721" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1721">
-        <v>0.8148564632437347</v>
+        <v>0.8632543029486808</v>
       </c>
       <c r="F1721">
         <v>1</v>
       </c>
       <c r="G1721">
-        <v>0.008572059724967078</v>
+        <v>0.009070597748783087</v>
       </c>
       <c r="H1721">
-        <v>0.008665143536756265</v>
+        <v>0.009256745697051318</v>
       </c>
       <c r="I1721">
-        <v>0.06691618821081269</v>
+        <v>0.1338520517317665</v>
       </c>
       <c r="J1721">
-        <v>1.308381178918755</v>
+        <v>1.307397413411626</v>
       </c>
       <c r="K1721">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1721">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1721">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1721">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1721">
         <v>1</v>
       </c>
       <c r="P1721" t="s">
-        <v>448</v>
+        <v>576</v>
       </c>
     </row>
     <row r="1722" spans="1:16">
       <c r="A1722" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1722" t="s">
         <v>261</v>
       </c>
       <c r="C1722">
-        <v>0.7262640392491715</v>
+        <v>0.7117048337867153</v>
       </c>
       <c r="D1722" t="s">
         <v>446</v>
       </c>
       <c r="E1722">
-        <v>0.860096415670796</v>
+        <v>0.8454459299233079</v>
       </c>
       <c r="F1722">
         <v>1</v>
       </c>
       <c r="G1722">
-        <v>0.009073735960750829</v>
+        <v>0.009088295166213286</v>
       </c>
       <c r="H1722">
-        <v>0.009259903584329203</v>
+        <v>0.009274554070076692</v>
       </c>
       <c r="I1722">
-        <v>0.1338323764216245</v>
+        <v>0.1337410961365926</v>
       </c>
       <c r="J1722">
-        <v>1.308381178918755</v>
+        <v>1.312945193170309</v>
       </c>
       <c r="K1722">
         <v>3.19</v>
@@ -88223,7 +88223,7 @@
         <v>1</v>
       </c>
       <c r="P1722" t="s">
-        <v>448</v>
+        <v>577</v>
       </c>
     </row>
     <row r="1723" spans="1:16">
@@ -88231,81 +88231,81 @@
         <v>0</v>
       </c>
       <c r="B1723" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1723">
-        <v>0.7508817338992388</v>
+        <v>0.7049987098493551</v>
       </c>
       <c r="D1723" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E1723">
-        <v>0.817807759765123</v>
+        <v>0.8386977613217637</v>
       </c>
       <c r="F1723">
         <v>1</v>
       </c>
       <c r="G1723">
-        <v>0.008569118266100762</v>
+        <v>0.009095001290150645</v>
       </c>
       <c r="H1723">
-        <v>0.008662192240234876</v>
+        <v>0.009281302238678237</v>
       </c>
       <c r="I1723">
-        <v>0.06692602586588414</v>
+        <v>0.1336990514724086</v>
       </c>
       <c r="J1723">
-        <v>1.307397413411626</v>
+        <v>1.315047426379513</v>
       </c>
       <c r="K1723">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="L1723">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M1723">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N1723">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="O1723">
         <v>1</v>
       </c>
       <c r="P1723" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="1724" spans="1:16">
       <c r="A1724" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1724" t="s">
         <v>261</v>
       </c>
       <c r="C1724">
-        <v>0.7294022512169143</v>
+        <v>0.6966839628130383</v>
       </c>
       <c r="D1724" t="s">
         <v>446</v>
       </c>
       <c r="E1724">
-        <v>0.8632543029486808</v>
+        <v>0.8303308842099844</v>
       </c>
       <c r="F1724">
         <v>1</v>
       </c>
       <c r="G1724">
-        <v>0.009070597748783087</v>
+        <v>0.009103316037186962</v>
       </c>
       <c r="H1724">
-        <v>0.009256745697051318</v>
+        <v>0.009289669115790015</v>
       </c>
       <c r="I1724">
-        <v>0.1338520517317665</v>
+        <v>0.133646921396946</v>
       </c>
       <c r="J1724">
-        <v>1.307397413411626</v>
+        <v>1.317653930152653</v>
       </c>
       <c r="K1724">
         <v>3.19</v>
@@ -88323,7 +88323,7 @@
         <v>1</v>
       </c>
       <c r="P1724" t="s">
-        <v>576</v>
+        <v>256</v>
       </c>
     </row>
     <row r="1725" spans="1:16">
@@ -88334,28 +88334,28 @@
         <v>261</v>
       </c>
       <c r="C1725">
-        <v>0.7117048337867153</v>
+        <v>0.7014000886468699</v>
       </c>
       <c r="D1725" t="s">
         <v>446</v>
       </c>
       <c r="E1725">
-        <v>0.8454459299233079</v>
+        <v>0.8350765782308622</v>
       </c>
       <c r="F1725">
         <v>1</v>
       </c>
       <c r="G1725">
-        <v>0.009088295166213286</v>
+        <v>0.009098599911353131</v>
       </c>
       <c r="H1725">
-        <v>0.009274554070076692</v>
+        <v>0.009284923421769136</v>
       </c>
       <c r="I1725">
-        <v>0.1337410961365926</v>
+        <v>0.1336764895839924</v>
       </c>
       <c r="J1725">
-        <v>1.312945193170309</v>
+        <v>1.316175520800354</v>
       </c>
       <c r="K1725">
         <v>3.19</v>
@@ -88373,7 +88373,7 @@
         <v>1</v>
       </c>
       <c r="P1725" t="s">
-        <v>577</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1726" spans="1:16">
@@ -88384,28 +88384,28 @@
         <v>261</v>
       </c>
       <c r="C1726">
-        <v>0.7049987098493551</v>
+        <v>0.7176262191292162</v>
       </c>
       <c r="D1726" t="s">
         <v>446</v>
       </c>
       <c r="E1726">
-        <v>0.8386977613217637</v>
+        <v>0.8514044399388032</v>
       </c>
       <c r="F1726">
         <v>1</v>
       </c>
       <c r="G1726">
-        <v>0.009095001290150645</v>
+        <v>0.009082373780870786</v>
       </c>
       <c r="H1726">
-        <v>0.009281302238678237</v>
+        <v>0.009268595560061196</v>
       </c>
       <c r="I1726">
-        <v>0.1336990514724086</v>
+        <v>0.133778220809587</v>
       </c>
       <c r="J1726">
-        <v>1.315047426379513</v>
+        <v>1.311088959520622</v>
       </c>
       <c r="K1726">
         <v>3.19</v>
@@ -88423,7 +88423,7 @@
         <v>1</v>
       </c>
       <c r="P1726" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="1727" spans="1:16">
@@ -88434,28 +88434,28 @@
         <v>261</v>
       </c>
       <c r="C1727">
-        <v>0.6966839628130383</v>
+        <v>0.7398286590454459</v>
       </c>
       <c r="D1727" t="s">
         <v>446</v>
       </c>
       <c r="E1727">
-        <v>0.8303308842099844</v>
+        <v>0.873746080105291</v>
       </c>
       <c r="F1727">
         <v>1</v>
       </c>
       <c r="G1727">
-        <v>0.009103316037186962</v>
+        <v>0.009060171340954553</v>
       </c>
       <c r="H1727">
-        <v>0.009289669115790015</v>
+        <v>0.00924625391989471</v>
       </c>
       <c r="I1727">
-        <v>0.133646921396946</v>
+        <v>0.1339174210598451</v>
       </c>
       <c r="J1727">
-        <v>1.317653930152653</v>
+        <v>1.304128947007697</v>
       </c>
       <c r="K1727">
         <v>3.19</v>
@@ -88473,7 +88473,7 @@
         <v>1</v>
       </c>
       <c r="P1727" t="s">
-        <v>256</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1728" spans="1:16">
@@ -88484,28 +88484,28 @@
         <v>261</v>
       </c>
       <c r="C1728">
-        <v>0.7014000886468699</v>
+        <v>0.7726173788161628</v>
       </c>
       <c r="D1728" t="s">
         <v>446</v>
       </c>
       <c r="E1728">
-        <v>0.8350765782308622</v>
+        <v>0.9067403717867961</v>
       </c>
       <c r="F1728">
         <v>1</v>
       </c>
       <c r="G1728">
-        <v>0.009098599911353131</v>
+        <v>0.009027382621183837</v>
       </c>
       <c r="H1728">
-        <v>0.009284923421769136</v>
+        <v>0.009213259628213203</v>
       </c>
       <c r="I1728">
-        <v>0.1336764895839924</v>
+        <v>0.1341229929706333</v>
       </c>
       <c r="J1728">
-        <v>1.316175520800354</v>
+        <v>1.293850351468288</v>
       </c>
       <c r="K1728">
         <v>3.19</v>
@@ -88523,7 +88523,7 @@
         <v>1</v>
       </c>
       <c r="P1728" t="s">
-        <v>449</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1729" spans="1:16">
@@ -88534,28 +88534,28 @@
         <v>261</v>
       </c>
       <c r="C1729">
-        <v>0.7176262191292162</v>
+        <v>0.8072892339066007</v>
       </c>
       <c r="D1729" t="s">
         <v>446</v>
       </c>
       <c r="E1729">
-        <v>0.8514044399388032</v>
+        <v>0.9416296052790551</v>
       </c>
       <c r="F1729">
         <v>1</v>
       </c>
       <c r="G1729">
-        <v>0.009082373780870786</v>
+        <v>0.0089927107660934</v>
       </c>
       <c r="H1729">
-        <v>0.009268595560061196</v>
+        <v>0.009178370394720943</v>
       </c>
       <c r="I1729">
-        <v>0.133778220809587</v>
+        <v>0.1343403713724545</v>
       </c>
       <c r="J1729">
-        <v>1.311088959520622</v>
+        <v>1.282981431377241</v>
       </c>
       <c r="K1729">
         <v>3.19</v>
@@ -88573,7 +88573,7 @@
         <v>1</v>
       </c>
       <c r="P1729" t="s">
-        <v>579</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1730" spans="1:16">
@@ -88584,28 +88584,28 @@
         <v>261</v>
       </c>
       <c r="C1730">
-        <v>0.7398286590454459</v>
+        <v>0.8255353424422802</v>
       </c>
       <c r="D1730" t="s">
         <v>446</v>
       </c>
       <c r="E1730">
-        <v>0.873746080105291</v>
+        <v>0.9599901094795351</v>
       </c>
       <c r="F1730">
         <v>1</v>
       </c>
       <c r="G1730">
-        <v>0.009060171340954553</v>
+        <v>0.008974464657557722</v>
       </c>
       <c r="H1730">
-        <v>0.00924625391989471</v>
+        <v>0.009160009890520463</v>
       </c>
       <c r="I1730">
-        <v>0.1339174210598451</v>
+        <v>0.1344547670372549</v>
       </c>
       <c r="J1730">
-        <v>1.304128947007697</v>
+        <v>1.277261648137216</v>
       </c>
       <c r="K1730">
         <v>3.19</v>
@@ -88623,7 +88623,7 @@
         <v>1</v>
       </c>
       <c r="P1730" t="s">
-        <v>444</v>
+        <v>263</v>
       </c>
     </row>
     <row r="1731" spans="1:16">
@@ -88634,28 +88634,28 @@
         <v>261</v>
       </c>
       <c r="C1731">
-        <v>0.7726173788161628</v>
+        <v>0.8434236614709256</v>
       </c>
       <c r="D1731" t="s">
         <v>446</v>
       </c>
       <c r="E1731">
-        <v>0.9067403717867961</v>
+        <v>0.97799058097858</v>
       </c>
       <c r="F1731">
         <v>1</v>
       </c>
       <c r="G1731">
-        <v>0.009027382621183837</v>
+        <v>0.008956576338529075</v>
       </c>
       <c r="H1731">
-        <v>0.009213259628213203</v>
+        <v>0.00914200941902142</v>
       </c>
       <c r="I1731">
-        <v>0.1341229929706333</v>
+        <v>0.1345669195076544</v>
       </c>
       <c r="J1731">
-        <v>1.293850351468288</v>
+        <v>1.271654024617265</v>
       </c>
       <c r="K1731">
         <v>3.19</v>
@@ -88673,7 +88673,7 @@
         <v>1</v>
       </c>
       <c r="P1731" t="s">
-        <v>580</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1732" spans="1:16">
@@ -88684,28 +88684,28 @@
         <v>261</v>
       </c>
       <c r="C1732">
-        <v>0.8072892339066007</v>
+        <v>0.8620267220783422</v>
       </c>
       <c r="D1732" t="s">
         <v>446</v>
       </c>
       <c r="E1732">
-        <v>0.9416296052790551</v>
+        <v>0.99671027519482</v>
       </c>
       <c r="F1732">
         <v>1</v>
       </c>
       <c r="G1732">
-        <v>0.0089927107660934</v>
+        <v>0.008937973277921658</v>
       </c>
       <c r="H1732">
-        <v>0.009178370394720943</v>
+        <v>0.009123289724805179</v>
       </c>
       <c r="I1732">
-        <v>0.1343403713724545</v>
+        <v>0.1346835531164778</v>
       </c>
       <c r="J1732">
-        <v>1.282981431377241</v>
+        <v>1.265822344176068</v>
       </c>
       <c r="K1732">
         <v>3.19</v>
@@ -88723,7 +88723,7 @@
         <v>1</v>
       </c>
       <c r="P1732" t="s">
-        <v>257</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1733" spans="1:16">
@@ -88734,28 +88734,28 @@
         <v>261</v>
       </c>
       <c r="C1733">
-        <v>0.8255353424422802</v>
+        <v>0.8787266818708703</v>
       </c>
       <c r="D1733" t="s">
         <v>446</v>
       </c>
       <c r="E1733">
-        <v>0.9599901094795351</v>
+        <v>1.013514936929621</v>
       </c>
       <c r="F1733">
         <v>1</v>
       </c>
       <c r="G1733">
-        <v>0.008974464657557722</v>
+        <v>0.008921273318129131</v>
       </c>
       <c r="H1733">
-        <v>0.009160009890520463</v>
+        <v>0.009106485063070378</v>
       </c>
       <c r="I1733">
-        <v>0.1344547670372549</v>
+        <v>0.1347882550587505</v>
       </c>
       <c r="J1733">
-        <v>1.277261648137216</v>
+        <v>1.260587247062423</v>
       </c>
       <c r="K1733">
         <v>3.19</v>
@@ -88773,7 +88773,7 @@
         <v>1</v>
       </c>
       <c r="P1733" t="s">
-        <v>263</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1734" spans="1:16">
@@ -88781,37 +88781,37 @@
         <v>0</v>
       </c>
       <c r="B1734" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1734">
-        <v>0.8604710066405516</v>
+        <v>0.8827952100288972</v>
       </c>
       <c r="D1734" t="s">
         <v>446</v>
       </c>
       <c r="E1734">
-        <v>0.97799058097858</v>
+        <v>1.017608973101177</v>
       </c>
       <c r="F1734">
         <v>1</v>
       </c>
       <c r="G1734">
-        <v>0.008439528993359448</v>
+        <v>0.008917204789971104</v>
       </c>
       <c r="H1734">
-        <v>0.00914200941902142</v>
+        <v>0.009102391026898821</v>
       </c>
       <c r="I1734">
-        <v>0.1175195743380284</v>
+        <v>0.1348137630722803</v>
       </c>
       <c r="J1734">
-        <v>1.271654024617265</v>
+        <v>1.259311846385926</v>
       </c>
       <c r="K1734">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1734">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1734">
         <v>3.21</v>
@@ -88823,39 +88823,39 @@
         <v>1</v>
       </c>
       <c r="P1734" t="s">
-        <v>450</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1735" spans="1:16">
       <c r="A1735" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1735" t="s">
         <v>261</v>
       </c>
       <c r="C1735">
-        <v>0.8434236614709256</v>
+        <v>0.8817169145093411</v>
       </c>
       <c r="D1735" t="s">
         <v>446</v>
       </c>
       <c r="E1735">
-        <v>0.97799058097858</v>
+        <v>1.016523917108145</v>
       </c>
       <c r="F1735">
         <v>1</v>
       </c>
       <c r="G1735">
-        <v>0.008956576338529075</v>
+        <v>0.00891828308549066</v>
       </c>
       <c r="H1735">
-        <v>0.00914200941902142</v>
+        <v>0.009103476082891854</v>
       </c>
       <c r="I1735">
-        <v>0.1345669195076544</v>
+        <v>0.1348070025988042</v>
       </c>
       <c r="J1735">
-        <v>1.271654024617265</v>
+        <v>1.259649870059768</v>
       </c>
       <c r="K1735">
         <v>3.19</v>
@@ -88873,7 +88873,7 @@
         <v>1</v>
       </c>
       <c r="P1735" t="s">
-        <v>450</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1736" spans="1:16">
@@ -88881,37 +88881,37 @@
         <v>0</v>
       </c>
       <c r="B1736" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1736">
-        <v>0.8778494143553166</v>
+        <v>0.8836581328456559</v>
       </c>
       <c r="D1736" t="s">
         <v>446</v>
       </c>
       <c r="E1736">
-        <v>0.99671027519482</v>
+        <v>1.018477306092337</v>
       </c>
       <c r="F1736">
         <v>1</v>
       </c>
       <c r="G1736">
-        <v>0.008422150585644684</v>
+        <v>0.008916341867154344</v>
       </c>
       <c r="H1736">
-        <v>0.009123289724805179</v>
+        <v>0.009101522693907661</v>
       </c>
       <c r="I1736">
-        <v>0.1188608608395034</v>
+        <v>0.1348191732466812</v>
       </c>
       <c r="J1736">
-        <v>1.265822344176068</v>
+        <v>1.259041337665939</v>
       </c>
       <c r="K1736">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="L1736">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="M1736">
         <v>3.21</v>
@@ -88923,7 +88923,7 @@
         <v>1</v>
       </c>
       <c r="P1736" t="s">
-        <v>445</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1737" spans="1:16">
@@ -88931,49 +88931,49 @@
         <v>1</v>
       </c>
       <c r="B1737" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C1737">
-        <v>0.8620267220783422</v>
+        <v>1.136610199728953</v>
       </c>
       <c r="D1737" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1737">
-        <v>0.99671027519482</v>
+        <v>0.918838959598975</v>
       </c>
       <c r="F1737">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1737">
-        <v>0.008937973277921658</v>
+        <v>0.009043389800271048</v>
       </c>
       <c r="H1737">
-        <v>0.009123289724805179</v>
+        <v>0.008901161040401026</v>
       </c>
       <c r="I1737">
-        <v>0.1346835531164778</v>
+        <v>0.2177712401299776</v>
       </c>
       <c r="J1737">
-        <v>1.265822344176068</v>
+        <v>1.259041337665939</v>
       </c>
       <c r="K1737">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="L1737">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="M1737">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N1737">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="O1737">
         <v>1</v>
       </c>
       <c r="P1737" t="s">
-        <v>445</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1738" spans="1:16">
@@ -88981,49 +88981,49 @@
         <v>0</v>
       </c>
       <c r="B1738" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1738">
+        <v>1.131086318915693</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1738">
+        <v>0.9132623028543789</v>
+      </c>
+      <c r="F1738">
+        <v>-1</v>
+      </c>
+      <c r="G1738">
+        <v>0.009048913681084306</v>
+      </c>
+      <c r="H1738">
+        <v>0.00890673769714562</v>
+      </c>
+      <c r="I1738">
+        <v>0.2178240160613143</v>
+      </c>
+      <c r="J1738">
+        <v>1.260800535377168</v>
+      </c>
+      <c r="K1738">
+        <v>3.14</v>
+      </c>
+      <c r="L1738">
+        <v>5.09</v>
+      </c>
+      <c r="M1738">
+        <v>3.17</v>
+      </c>
+      <c r="N1738">
+        <v>4.91</v>
+      </c>
+      <c r="O1738">
+        <v>1</v>
+      </c>
+      <c r="P1738" t="s">
         <v>261</v>
-      </c>
-      <c r="C1738">
-        <v>0.8787266818708703</v>
-      </c>
-      <c r="D1738" t="s">
-        <v>446</v>
-      </c>
-      <c r="E1738">
-        <v>1.013514936929621</v>
-      </c>
-      <c r="F1738">
-        <v>1</v>
-      </c>
-      <c r="G1738">
-        <v>0.008921273318129131</v>
-      </c>
-      <c r="H1738">
-        <v>0.009106485063070378</v>
-      </c>
-      <c r="I1738">
-        <v>0.1347882550587505</v>
-      </c>
-      <c r="J1738">
-        <v>1.260587247062423</v>
-      </c>
-      <c r="K1738">
-        <v>3.19</v>
-      </c>
-      <c r="L1738">
-        <v>4.9</v>
-      </c>
-      <c r="M1738">
-        <v>3.21</v>
-      </c>
-      <c r="N1738">
-        <v>5.06</v>
-      </c>
-      <c r="O1738">
-        <v>1</v>
-      </c>
-      <c r="P1738" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="1739" spans="1:16">
@@ -89031,49 +89031,49 @@
         <v>0</v>
       </c>
       <c r="B1739" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C1739">
-        <v>0.8827952100288972</v>
+        <v>1.127143579938229</v>
       </c>
       <c r="D1739" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1739">
+        <v>0.909281894396238</v>
+      </c>
+      <c r="F1739">
+        <v>-1</v>
+      </c>
+      <c r="G1739">
+        <v>0.00905285642006177</v>
+      </c>
+      <c r="H1739">
+        <v>0.008910718105603763</v>
+      </c>
+      <c r="I1739">
+        <v>0.2178616855419908</v>
+      </c>
+      <c r="J1739">
+        <v>1.262056184733048</v>
+      </c>
+      <c r="K1739">
+        <v>3.14</v>
+      </c>
+      <c r="L1739">
+        <v>5.09</v>
+      </c>
+      <c r="M1739">
+        <v>3.17</v>
+      </c>
+      <c r="N1739">
+        <v>4.91</v>
+      </c>
+      <c r="O1739">
+        <v>1</v>
+      </c>
+      <c r="P1739" t="s">
         <v>446</v>
-      </c>
-      <c r="E1739">
-        <v>1.017608973101177</v>
-      </c>
-      <c r="F1739">
-        <v>1</v>
-      </c>
-      <c r="G1739">
-        <v>0.008917204789971104</v>
-      </c>
-      <c r="H1739">
-        <v>0.009102391026898821</v>
-      </c>
-      <c r="I1739">
-        <v>0.1348137630722803</v>
-      </c>
-      <c r="J1739">
-        <v>1.259311846385926</v>
-      </c>
-      <c r="K1739">
-        <v>3.19</v>
-      </c>
-      <c r="L1739">
-        <v>4.9</v>
-      </c>
-      <c r="M1739">
-        <v>3.21</v>
-      </c>
-      <c r="N1739">
-        <v>5.06</v>
-      </c>
-      <c r="O1739">
-        <v>1</v>
-      </c>
-      <c r="P1739" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="1740" spans="1:16">
@@ -89081,81 +89081,81 @@
         <v>0</v>
       </c>
       <c r="B1740" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C1740">
-        <v>0.8817169145093411</v>
+        <v>1.123418970437326</v>
       </c>
       <c r="D1740" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1740">
-        <v>1.016523917108145</v>
+        <v>0.9055216994542441</v>
       </c>
       <c r="F1740">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1740">
-        <v>0.00891828308549066</v>
+        <v>0.009056581029562675</v>
       </c>
       <c r="H1740">
-        <v>0.009103476082891854</v>
+        <v>0.008914478300545757</v>
       </c>
       <c r="I1740">
-        <v>0.1348070025988042</v>
+        <v>0.217897270983082</v>
       </c>
       <c r="J1740">
-        <v>1.259649870059768</v>
+        <v>1.263242366102762</v>
       </c>
       <c r="K1740">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="L1740">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="M1740">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="N1740">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="O1740">
         <v>1</v>
       </c>
       <c r="P1740" t="s">
-        <v>258</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1741" spans="1:16">
       <c r="A1741" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1741" t="s">
         <v>264</v>
       </c>
       <c r="C1741">
-        <v>1.134699408012329</v>
+        <v>1.103124629069044</v>
       </c>
       <c r="D1741" t="s">
         <v>447</v>
       </c>
       <c r="E1741">
-        <v>0.9169099119105364</v>
+        <v>0.8850334631047359</v>
       </c>
       <c r="F1741">
         <v>-1</v>
       </c>
       <c r="G1741">
-        <v>0.009045300591987672</v>
+        <v>0.009076875370930956</v>
       </c>
       <c r="H1741">
-        <v>0.008903090088089463</v>
+        <v>0.008934966536895263</v>
       </c>
       <c r="I1741">
-        <v>0.2177894961017923</v>
+        <v>0.2180911659643079</v>
       </c>
       <c r="J1741">
-        <v>1.259649870059768</v>
+        <v>1.269705532143617</v>
       </c>
       <c r="K1741">
         <v>3.14</v>
@@ -89173,306 +89173,6 @@
         <v>1</v>
       </c>
       <c r="P1741" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="1742" spans="1:16">
-      <c r="A1742" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1742" t="s">
-        <v>261</v>
-      </c>
-      <c r="C1742">
-        <v>0.8836581328456559</v>
-      </c>
-      <c r="D1742" t="s">
-        <v>446</v>
-      </c>
-      <c r="E1742">
-        <v>1.018477306092337</v>
-      </c>
-      <c r="F1742">
-        <v>1</v>
-      </c>
-      <c r="G1742">
-        <v>0.008916341867154344</v>
-      </c>
-      <c r="H1742">
-        <v>0.009101522693907661</v>
-      </c>
-      <c r="I1742">
-        <v>0.1348191732466812</v>
-      </c>
-      <c r="J1742">
-        <v>1.259041337665939</v>
-      </c>
-      <c r="K1742">
-        <v>3.19</v>
-      </c>
-      <c r="L1742">
-        <v>4.9</v>
-      </c>
-      <c r="M1742">
-        <v>3.21</v>
-      </c>
-      <c r="N1742">
-        <v>5.06</v>
-      </c>
-      <c r="O1742">
-        <v>1</v>
-      </c>
-      <c r="P1742" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="1743" spans="1:16">
-      <c r="A1743" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1743" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1743">
-        <v>1.136610199728953</v>
-      </c>
-      <c r="D1743" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1743">
-        <v>0.918838959598975</v>
-      </c>
-      <c r="F1743">
-        <v>-1</v>
-      </c>
-      <c r="G1743">
-        <v>0.009043389800271048</v>
-      </c>
-      <c r="H1743">
-        <v>0.008901161040401026</v>
-      </c>
-      <c r="I1743">
-        <v>0.2177712401299776</v>
-      </c>
-      <c r="J1743">
-        <v>1.259041337665939</v>
-      </c>
-      <c r="K1743">
-        <v>3.14</v>
-      </c>
-      <c r="L1743">
-        <v>5.09</v>
-      </c>
-      <c r="M1743">
-        <v>3.17</v>
-      </c>
-      <c r="N1743">
-        <v>4.91</v>
-      </c>
-      <c r="O1743">
-        <v>1</v>
-      </c>
-      <c r="P1743" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="1744" spans="1:16">
-      <c r="A1744" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1744" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1744">
-        <v>1.131086318915693</v>
-      </c>
-      <c r="D1744" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1744">
-        <v>0.9132623028543789</v>
-      </c>
-      <c r="F1744">
-        <v>-1</v>
-      </c>
-      <c r="G1744">
-        <v>0.009048913681084306</v>
-      </c>
-      <c r="H1744">
-        <v>0.00890673769714562</v>
-      </c>
-      <c r="I1744">
-        <v>0.2178240160613143</v>
-      </c>
-      <c r="J1744">
-        <v>1.260800535377168</v>
-      </c>
-      <c r="K1744">
-        <v>3.14</v>
-      </c>
-      <c r="L1744">
-        <v>5.09</v>
-      </c>
-      <c r="M1744">
-        <v>3.17</v>
-      </c>
-      <c r="N1744">
-        <v>4.91</v>
-      </c>
-      <c r="O1744">
-        <v>1</v>
-      </c>
-      <c r="P1744" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="1745" spans="1:16">
-      <c r="A1745" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1745" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1745">
-        <v>1.127143579938229</v>
-      </c>
-      <c r="D1745" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1745">
-        <v>0.909281894396238</v>
-      </c>
-      <c r="F1745">
-        <v>-1</v>
-      </c>
-      <c r="G1745">
-        <v>0.00905285642006177</v>
-      </c>
-      <c r="H1745">
-        <v>0.008910718105603763</v>
-      </c>
-      <c r="I1745">
-        <v>0.2178616855419908</v>
-      </c>
-      <c r="J1745">
-        <v>1.262056184733048</v>
-      </c>
-      <c r="K1745">
-        <v>3.14</v>
-      </c>
-      <c r="L1745">
-        <v>5.09</v>
-      </c>
-      <c r="M1745">
-        <v>3.17</v>
-      </c>
-      <c r="N1745">
-        <v>4.91</v>
-      </c>
-      <c r="O1745">
-        <v>1</v>
-      </c>
-      <c r="P1745" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="1746" spans="1:16">
-      <c r="A1746" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1746" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1746">
-        <v>1.123418970437326</v>
-      </c>
-      <c r="D1746" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1746">
-        <v>0.9055216994542441</v>
-      </c>
-      <c r="F1746">
-        <v>-1</v>
-      </c>
-      <c r="G1746">
-        <v>0.009056581029562675</v>
-      </c>
-      <c r="H1746">
-        <v>0.008914478300545757</v>
-      </c>
-      <c r="I1746">
-        <v>0.217897270983082</v>
-      </c>
-      <c r="J1746">
-        <v>1.263242366102762</v>
-      </c>
-      <c r="K1746">
-        <v>3.14</v>
-      </c>
-      <c r="L1746">
-        <v>5.09</v>
-      </c>
-      <c r="M1746">
-        <v>3.17</v>
-      </c>
-      <c r="N1746">
-        <v>4.91</v>
-      </c>
-      <c r="O1746">
-        <v>1</v>
-      </c>
-      <c r="P1746" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="1747" spans="1:16">
-      <c r="A1747" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1747" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1747">
-        <v>1.103124629069044</v>
-      </c>
-      <c r="D1747" t="s">
-        <v>447</v>
-      </c>
-      <c r="E1747">
-        <v>0.8850334631047359</v>
-      </c>
-      <c r="F1747">
-        <v>-1</v>
-      </c>
-      <c r="G1747">
-        <v>0.009076875370930956</v>
-      </c>
-      <c r="H1747">
-        <v>0.008934966536895263</v>
-      </c>
-      <c r="I1747">
-        <v>0.2180911659643079</v>
-      </c>
-      <c r="J1747">
-        <v>1.269705532143617</v>
-      </c>
-      <c r="K1747">
-        <v>3.14</v>
-      </c>
-      <c r="L1747">
-        <v>5.09</v>
-      </c>
-      <c r="M1747">
-        <v>3.17</v>
-      </c>
-      <c r="N1747">
-        <v>4.91</v>
-      </c>
-      <c r="O1747">
-        <v>1</v>
-      </c>
-      <c r="P1747" t="s">
         <v>259</v>
       </c>
     </row>
